--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9138A7D-7B73-49DB-B019-B5DDC296B200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6467CE16-A1A4-4056-AFAF-3F235DF20CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{09E8D2D0-BB12-495B-A39A-B0FC9433E411}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="257">
   <si>
     <t>13-332</t>
   </si>
@@ -747,6 +747,66 @@
   </si>
   <si>
     <t>park Źródliska I (Palmiarnia)</t>
+  </si>
+  <si>
+    <t>30-698</t>
+  </si>
+  <si>
+    <t>Tuchowska</t>
+  </si>
+  <si>
+    <t>1-DK</t>
+  </si>
+  <si>
+    <t>Kraków</t>
+  </si>
+  <si>
+    <t>małopolskie</t>
+  </si>
+  <si>
+    <t>45-DK(n) 50-DK(p)</t>
+  </si>
+  <si>
+    <t>30-619</t>
+  </si>
+  <si>
+    <t>Turniejowa</t>
+  </si>
+  <si>
+    <t>57-DK</t>
+  </si>
+  <si>
+    <t>Nakładający się zakres</t>
+  </si>
+  <si>
+    <t>57-59(n) 61-DK(n) 24-DK(p)</t>
+  </si>
+  <si>
+    <t>30-418</t>
+  </si>
+  <si>
+    <t>Zakopiańska</t>
+  </si>
+  <si>
+    <t>33-147(n), 46-58b(p), 62-70a(p)</t>
+  </si>
+  <si>
+    <t>33-147(n),46-58b(p),62(p),64-70a(p)</t>
+  </si>
+  <si>
+    <t>30-435</t>
+  </si>
+  <si>
+    <t>60-62b(p), 72-264(p), 149-DK(n), 265-277</t>
+  </si>
+  <si>
+    <t>60,62a-62b(p),72-264(p),149-DK(n),265-277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kraków </t>
+  </si>
+  <si>
+    <t>Ulica w postaci odwrotnej</t>
   </si>
 </sst>
 </file>
@@ -1119,13 +1179,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EC6EBE-762D-4FEE-AB4D-0625E60C23B9}">
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.42578125" customWidth="1"/>
     <col min="3" max="3" width="42.42578125" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.85546875" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
@@ -2712,7 +2772,7 @@
         <v>142</v>
       </c>
       <c r="H88" t="s">
-        <v>103</v>
+        <v>256</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -2869,7 +2929,7 @@
         <v>52</v>
       </c>
       <c r="H96" t="s">
-        <v>106</v>
+        <v>256</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -3346,7 +3406,7 @@
         <v>59</v>
       </c>
       <c r="H126" t="s">
-        <v>108</v>
+        <v>256</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -3473,7 +3533,7 @@
         <v>52</v>
       </c>
       <c r="H134" t="s">
-        <v>109</v>
+        <v>256</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -3740,7 +3800,7 @@
         <v>52</v>
       </c>
       <c r="H152" t="s">
-        <v>110</v>
+        <v>256</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -4063,7 +4123,7 @@
         <v>52</v>
       </c>
       <c r="H174" t="s">
-        <v>111</v>
+        <v>256</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -4109,7 +4169,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>234</v>
       </c>
@@ -4127,6 +4187,202 @@
       </c>
       <c r="G177" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>237</v>
+      </c>
+      <c r="B178" t="s">
+        <v>240</v>
+      </c>
+      <c r="C178" t="s">
+        <v>238</v>
+      </c>
+      <c r="D178" t="s">
+        <v>239</v>
+      </c>
+      <c r="E178" t="s">
+        <v>240</v>
+      </c>
+      <c r="F178" t="s">
+        <v>240</v>
+      </c>
+      <c r="G178" t="s">
+        <v>241</v>
+      </c>
+      <c r="H178" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>237</v>
+      </c>
+      <c r="B179" t="s">
+        <v>240</v>
+      </c>
+      <c r="C179" t="s">
+        <v>238</v>
+      </c>
+      <c r="D179" t="s">
+        <v>242</v>
+      </c>
+      <c r="E179" t="s">
+        <v>240</v>
+      </c>
+      <c r="F179" t="s">
+        <v>240</v>
+      </c>
+      <c r="G179" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>243</v>
+      </c>
+      <c r="B180" t="s">
+        <v>240</v>
+      </c>
+      <c r="C180" t="s">
+        <v>244</v>
+      </c>
+      <c r="D180" t="s">
+        <v>245</v>
+      </c>
+      <c r="E180" t="s">
+        <v>240</v>
+      </c>
+      <c r="F180" t="s">
+        <v>240</v>
+      </c>
+      <c r="G180" t="s">
+        <v>241</v>
+      </c>
+      <c r="H180" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>243</v>
+      </c>
+      <c r="B181" t="s">
+        <v>240</v>
+      </c>
+      <c r="C181" t="s">
+        <v>244</v>
+      </c>
+      <c r="D181" t="s">
+        <v>247</v>
+      </c>
+      <c r="E181" t="s">
+        <v>240</v>
+      </c>
+      <c r="F181" t="s">
+        <v>240</v>
+      </c>
+      <c r="G181" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>248</v>
+      </c>
+      <c r="B182" t="s">
+        <v>240</v>
+      </c>
+      <c r="C182" t="s">
+        <v>249</v>
+      </c>
+      <c r="D182" t="s">
+        <v>250</v>
+      </c>
+      <c r="E182" t="s">
+        <v>240</v>
+      </c>
+      <c r="F182" t="s">
+        <v>240</v>
+      </c>
+      <c r="G182" t="s">
+        <v>241</v>
+      </c>
+      <c r="H182" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>248</v>
+      </c>
+      <c r="B183" t="s">
+        <v>240</v>
+      </c>
+      <c r="C183" t="s">
+        <v>249</v>
+      </c>
+      <c r="D183" t="s">
+        <v>251</v>
+      </c>
+      <c r="E183" t="s">
+        <v>240</v>
+      </c>
+      <c r="F183" t="s">
+        <v>240</v>
+      </c>
+      <c r="G183" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>252</v>
+      </c>
+      <c r="B184" t="s">
+        <v>240</v>
+      </c>
+      <c r="C184" t="s">
+        <v>249</v>
+      </c>
+      <c r="D184" t="s">
+        <v>253</v>
+      </c>
+      <c r="E184" t="s">
+        <v>240</v>
+      </c>
+      <c r="F184" t="s">
+        <v>240</v>
+      </c>
+      <c r="G184" t="s">
+        <v>241</v>
+      </c>
+      <c r="H184" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>252</v>
+      </c>
+      <c r="B185" t="s">
+        <v>255</v>
+      </c>
+      <c r="C185" t="s">
+        <v>249</v>
+      </c>
+      <c r="D185" t="s">
+        <v>254</v>
+      </c>
+      <c r="E185" t="s">
+        <v>240</v>
+      </c>
+      <c r="F185" t="s">
+        <v>240</v>
+      </c>
+      <c r="G185" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6467CE16-A1A4-4056-AFAF-3F235DF20CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEE648E-05BC-41FE-A853-3E668CCF76F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{09E8D2D0-BB12-495B-A39A-B0FC9433E411}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="330">
   <si>
     <t>13-332</t>
   </si>
@@ -807,6 +807,225 @@
   </si>
   <si>
     <t>Ulica w postaci odwrotnej</t>
+  </si>
+  <si>
+    <t>75-669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koszalin </t>
+  </si>
+  <si>
+    <t>Piniowa</t>
+  </si>
+  <si>
+    <t>20-719</t>
+  </si>
+  <si>
+    <t>Owcza</t>
+  </si>
+  <si>
+    <t>91-531</t>
+  </si>
+  <si>
+    <t>Dolomitowa</t>
+  </si>
+  <si>
+    <t>91-156</t>
+  </si>
+  <si>
+    <t>Słodowa</t>
+  </si>
+  <si>
+    <t>Wąska</t>
+  </si>
+  <si>
+    <t>91-305</t>
+  </si>
+  <si>
+    <t>Deszczowa</t>
+  </si>
+  <si>
+    <t>93-410</t>
+  </si>
+  <si>
+    <t>93-424</t>
+  </si>
+  <si>
+    <t>Foniczna</t>
+  </si>
+  <si>
+    <t>93-431</t>
+  </si>
+  <si>
+    <t>Rzeczowa</t>
+  </si>
+  <si>
+    <t>Jana III Sobieskiego</t>
+  </si>
+  <si>
+    <t>Rycerski</t>
+  </si>
+  <si>
+    <t>92-237</t>
+  </si>
+  <si>
+    <t>Tunelowa</t>
+  </si>
+  <si>
+    <t>Nie istnieje</t>
+  </si>
+  <si>
+    <t>64-917</t>
+  </si>
+  <si>
+    <t>Skórka</t>
+  </si>
+  <si>
+    <t>Młynarska</t>
+  </si>
+  <si>
+    <t>54-917</t>
+  </si>
+  <si>
+    <t>Wybudowanie</t>
+  </si>
+  <si>
+    <t>Skórka Wybudowanie</t>
+  </si>
+  <si>
+    <t>03-173</t>
+  </si>
+  <si>
+    <t>Jeżyka</t>
+  </si>
+  <si>
+    <t>Jerzyka</t>
+  </si>
+  <si>
+    <t>03-155</t>
+  </si>
+  <si>
+    <t>Sudecka</t>
+  </si>
+  <si>
+    <t>01-727</t>
+  </si>
+  <si>
+    <t>Libawska</t>
+  </si>
+  <si>
+    <t>Rymowa</t>
+  </si>
+  <si>
+    <t>01-909</t>
+  </si>
+  <si>
+    <t>00-713</t>
+  </si>
+  <si>
+    <t>Pułku AK "Kampinos"</t>
+  </si>
+  <si>
+    <t>02-928</t>
+  </si>
+  <si>
+    <t>Sopocka</t>
+  </si>
+  <si>
+    <t>02-983</t>
+  </si>
+  <si>
+    <t>Szymanówka</t>
+  </si>
+  <si>
+    <t>03-907</t>
+  </si>
+  <si>
+    <t>Gallijska</t>
+  </si>
+  <si>
+    <t>Galijska</t>
+  </si>
+  <si>
+    <t>03-579</t>
+  </si>
+  <si>
+    <t>Rypińska</t>
+  </si>
+  <si>
+    <t>02-882</t>
+  </si>
+  <si>
+    <t>Agaty</t>
+  </si>
+  <si>
+    <t>02-871</t>
+  </si>
+  <si>
+    <t>Żmijewska</t>
+  </si>
+  <si>
+    <t>Berberysowa</t>
+  </si>
+  <si>
+    <t>04-667</t>
+  </si>
+  <si>
+    <t>04-982</t>
+  </si>
+  <si>
+    <t>Biecka</t>
+  </si>
+  <si>
+    <t>04-741</t>
+  </si>
+  <si>
+    <t>Kowarska</t>
+  </si>
+  <si>
+    <t>Połąska</t>
+  </si>
+  <si>
+    <t>01-741</t>
+  </si>
+  <si>
+    <t>Poprawka</t>
+  </si>
+  <si>
+    <t>Ortografia</t>
+  </si>
+  <si>
+    <t>Nie istnieje od 40 lat</t>
+  </si>
+  <si>
+    <t>Nie istnieje w Teryt, jest na google</t>
+  </si>
+  <si>
+    <t>Nie istnieje, jest w Jeziorkach Południowych</t>
+  </si>
+  <si>
+    <t>Zgrupowania AK "Kampinos"</t>
+  </si>
+  <si>
+    <t>Błąd w nazwie</t>
+  </si>
+  <si>
+    <t>Młyńska</t>
+  </si>
+  <si>
+    <t>Franciszka Smudy</t>
+  </si>
+  <si>
+    <t>Zmiana nazwy</t>
+  </si>
+  <si>
+    <t>Plac</t>
+  </si>
+  <si>
+    <t>Krajenka</t>
+  </si>
+  <si>
+    <t>złotowski</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EC6EBE-762D-4FEE-AB4D-0625E60C23B9}">
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H243"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -4385,6 +4604,914 @@
         <v>241</v>
       </c>
     </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>257</v>
+      </c>
+      <c r="B186" t="s">
+        <v>258</v>
+      </c>
+      <c r="C186" t="s">
+        <v>259</v>
+      </c>
+      <c r="H186" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>260</v>
+      </c>
+      <c r="B188" t="s">
+        <v>184</v>
+      </c>
+      <c r="C188" t="s">
+        <v>261</v>
+      </c>
+      <c r="E188" t="s">
+        <v>184</v>
+      </c>
+      <c r="F188" t="s">
+        <v>184</v>
+      </c>
+      <c r="G188" t="s">
+        <v>68</v>
+      </c>
+      <c r="H188" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>262</v>
+      </c>
+      <c r="B190" t="s">
+        <v>122</v>
+      </c>
+      <c r="C190" t="s">
+        <v>263</v>
+      </c>
+      <c r="E190" t="s">
+        <v>122</v>
+      </c>
+      <c r="F190" t="s">
+        <v>122</v>
+      </c>
+      <c r="G190" t="s">
+        <v>52</v>
+      </c>
+      <c r="H190" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>264</v>
+      </c>
+      <c r="B192" t="s">
+        <v>122</v>
+      </c>
+      <c r="C192" t="s">
+        <v>265</v>
+      </c>
+      <c r="E192" t="s">
+        <v>122</v>
+      </c>
+      <c r="F192" t="s">
+        <v>122</v>
+      </c>
+      <c r="G192" t="s">
+        <v>52</v>
+      </c>
+      <c r="H192" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>267</v>
+      </c>
+      <c r="B194" t="s">
+        <v>122</v>
+      </c>
+      <c r="C194" t="s">
+        <v>266</v>
+      </c>
+      <c r="E194" t="s">
+        <v>122</v>
+      </c>
+      <c r="F194" t="s">
+        <v>122</v>
+      </c>
+      <c r="G194" t="s">
+        <v>52</v>
+      </c>
+      <c r="H194" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>269</v>
+      </c>
+      <c r="B196" t="s">
+        <v>122</v>
+      </c>
+      <c r="C196" t="s">
+        <v>268</v>
+      </c>
+      <c r="E196" t="s">
+        <v>122</v>
+      </c>
+      <c r="F196" t="s">
+        <v>122</v>
+      </c>
+      <c r="G196" t="s">
+        <v>52</v>
+      </c>
+      <c r="H196" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>270</v>
+      </c>
+      <c r="B198" t="s">
+        <v>122</v>
+      </c>
+      <c r="C198" t="s">
+        <v>271</v>
+      </c>
+      <c r="E198" t="s">
+        <v>122</v>
+      </c>
+      <c r="F198" t="s">
+        <v>122</v>
+      </c>
+      <c r="G198" t="s">
+        <v>52</v>
+      </c>
+      <c r="H198" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>272</v>
+      </c>
+      <c r="B200" t="s">
+        <v>122</v>
+      </c>
+      <c r="C200" t="s">
+        <v>273</v>
+      </c>
+      <c r="E200" t="s">
+        <v>122</v>
+      </c>
+      <c r="F200" t="s">
+        <v>122</v>
+      </c>
+      <c r="G200" t="s">
+        <v>52</v>
+      </c>
+      <c r="H200" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>272</v>
+      </c>
+      <c r="B202" t="s">
+        <v>122</v>
+      </c>
+      <c r="C202" t="s">
+        <v>274</v>
+      </c>
+      <c r="E202" t="s">
+        <v>122</v>
+      </c>
+      <c r="F202" t="s">
+        <v>122</v>
+      </c>
+      <c r="G202" t="s">
+        <v>52</v>
+      </c>
+      <c r="H202" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>211</v>
+      </c>
+      <c r="B204" t="s">
+        <v>122</v>
+      </c>
+      <c r="C204" t="s">
+        <v>275</v>
+      </c>
+      <c r="E204" t="s">
+        <v>122</v>
+      </c>
+      <c r="F204" t="s">
+        <v>122</v>
+      </c>
+      <c r="G204" t="s">
+        <v>52</v>
+      </c>
+      <c r="H204" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>211</v>
+      </c>
+      <c r="B205" t="s">
+        <v>122</v>
+      </c>
+      <c r="C205" t="s">
+        <v>110</v>
+      </c>
+      <c r="E205" t="s">
+        <v>122</v>
+      </c>
+      <c r="F205" t="s">
+        <v>122</v>
+      </c>
+      <c r="G205" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>214</v>
+      </c>
+      <c r="B206" t="s">
+        <v>122</v>
+      </c>
+      <c r="C206" t="s">
+        <v>215</v>
+      </c>
+      <c r="E206" t="s">
+        <v>122</v>
+      </c>
+      <c r="F206" t="s">
+        <v>122</v>
+      </c>
+      <c r="G206" t="s">
+        <v>52</v>
+      </c>
+      <c r="H206" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>276</v>
+      </c>
+      <c r="B208" t="s">
+        <v>122</v>
+      </c>
+      <c r="C208" t="s">
+        <v>277</v>
+      </c>
+      <c r="E208" t="s">
+        <v>122</v>
+      </c>
+      <c r="F208" t="s">
+        <v>122</v>
+      </c>
+      <c r="G208" t="s">
+        <v>52</v>
+      </c>
+      <c r="H208" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>276</v>
+      </c>
+      <c r="B209" t="s">
+        <v>122</v>
+      </c>
+      <c r="C209" t="s">
+        <v>325</v>
+      </c>
+      <c r="E209" t="s">
+        <v>122</v>
+      </c>
+      <c r="F209" t="s">
+        <v>122</v>
+      </c>
+      <c r="G209" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>279</v>
+      </c>
+      <c r="B210" t="s">
+        <v>280</v>
+      </c>
+      <c r="C210" t="s">
+        <v>281</v>
+      </c>
+      <c r="E210" t="s">
+        <v>328</v>
+      </c>
+      <c r="F210" t="s">
+        <v>329</v>
+      </c>
+      <c r="G210" t="s">
+        <v>135</v>
+      </c>
+      <c r="H210" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>279</v>
+      </c>
+      <c r="B211" t="s">
+        <v>280</v>
+      </c>
+      <c r="C211" t="s">
+        <v>324</v>
+      </c>
+      <c r="E211" t="s">
+        <v>328</v>
+      </c>
+      <c r="F211" t="s">
+        <v>329</v>
+      </c>
+      <c r="G211" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>282</v>
+      </c>
+      <c r="B212" t="s">
+        <v>280</v>
+      </c>
+      <c r="C212" t="s">
+        <v>283</v>
+      </c>
+      <c r="E212" t="s">
+        <v>328</v>
+      </c>
+      <c r="F212" t="s">
+        <v>329</v>
+      </c>
+      <c r="G212" t="s">
+        <v>135</v>
+      </c>
+      <c r="H212" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>282</v>
+      </c>
+      <c r="B213" t="s">
+        <v>280</v>
+      </c>
+      <c r="C213" t="s">
+        <v>284</v>
+      </c>
+      <c r="E213" t="s">
+        <v>328</v>
+      </c>
+      <c r="F213" t="s">
+        <v>329</v>
+      </c>
+      <c r="G213" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>285</v>
+      </c>
+      <c r="B214" t="s">
+        <v>113</v>
+      </c>
+      <c r="C214" t="s">
+        <v>286</v>
+      </c>
+      <c r="E214" t="s">
+        <v>113</v>
+      </c>
+      <c r="F214" t="s">
+        <v>113</v>
+      </c>
+      <c r="G214" t="s">
+        <v>59</v>
+      </c>
+      <c r="H214" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>285</v>
+      </c>
+      <c r="B215" t="s">
+        <v>113</v>
+      </c>
+      <c r="C215" t="s">
+        <v>287</v>
+      </c>
+      <c r="E215" t="s">
+        <v>113</v>
+      </c>
+      <c r="F215" t="s">
+        <v>113</v>
+      </c>
+      <c r="G215" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>288</v>
+      </c>
+      <c r="B216" t="s">
+        <v>113</v>
+      </c>
+      <c r="C216" t="s">
+        <v>289</v>
+      </c>
+      <c r="E216" t="s">
+        <v>113</v>
+      </c>
+      <c r="F216" t="s">
+        <v>113</v>
+      </c>
+      <c r="G216" t="s">
+        <v>59</v>
+      </c>
+      <c r="H216" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>290</v>
+      </c>
+      <c r="B218" t="s">
+        <v>113</v>
+      </c>
+      <c r="C218" t="s">
+        <v>291</v>
+      </c>
+      <c r="E218" t="s">
+        <v>113</v>
+      </c>
+      <c r="F218" t="s">
+        <v>113</v>
+      </c>
+      <c r="G218" t="s">
+        <v>59</v>
+      </c>
+      <c r="H218" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>293</v>
+      </c>
+      <c r="B220" t="s">
+        <v>113</v>
+      </c>
+      <c r="C220" t="s">
+        <v>292</v>
+      </c>
+      <c r="E220" t="s">
+        <v>113</v>
+      </c>
+      <c r="F220" t="s">
+        <v>113</v>
+      </c>
+      <c r="G220" t="s">
+        <v>59</v>
+      </c>
+      <c r="H220" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>294</v>
+      </c>
+      <c r="B222" t="s">
+        <v>113</v>
+      </c>
+      <c r="C222" t="s">
+        <v>295</v>
+      </c>
+      <c r="E222" t="s">
+        <v>113</v>
+      </c>
+      <c r="F222" t="s">
+        <v>113</v>
+      </c>
+      <c r="G222" t="s">
+        <v>59</v>
+      </c>
+      <c r="H222" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>294</v>
+      </c>
+      <c r="B223" t="s">
+        <v>113</v>
+      </c>
+      <c r="C223" t="s">
+        <v>322</v>
+      </c>
+      <c r="E223" t="s">
+        <v>113</v>
+      </c>
+      <c r="F223" t="s">
+        <v>113</v>
+      </c>
+      <c r="G223" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>296</v>
+      </c>
+      <c r="B224" t="s">
+        <v>113</v>
+      </c>
+      <c r="C224" t="s">
+        <v>297</v>
+      </c>
+      <c r="E224" t="s">
+        <v>113</v>
+      </c>
+      <c r="F224" t="s">
+        <v>113</v>
+      </c>
+      <c r="G224" t="s">
+        <v>59</v>
+      </c>
+      <c r="H224" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>298</v>
+      </c>
+      <c r="B226" t="s">
+        <v>113</v>
+      </c>
+      <c r="C226" t="s">
+        <v>299</v>
+      </c>
+      <c r="E226" t="s">
+        <v>113</v>
+      </c>
+      <c r="F226" t="s">
+        <v>113</v>
+      </c>
+      <c r="G226" t="s">
+        <v>59</v>
+      </c>
+      <c r="H226" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>300</v>
+      </c>
+      <c r="B228" t="s">
+        <v>113</v>
+      </c>
+      <c r="C228" t="s">
+        <v>301</v>
+      </c>
+      <c r="E228" t="s">
+        <v>113</v>
+      </c>
+      <c r="F228" t="s">
+        <v>113</v>
+      </c>
+      <c r="G228" t="s">
+        <v>59</v>
+      </c>
+      <c r="H228" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>300</v>
+      </c>
+      <c r="B229" t="s">
+        <v>113</v>
+      </c>
+      <c r="C229" t="s">
+        <v>302</v>
+      </c>
+      <c r="E229" t="s">
+        <v>113</v>
+      </c>
+      <c r="F229" t="s">
+        <v>113</v>
+      </c>
+      <c r="G229" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>303</v>
+      </c>
+      <c r="B230" t="s">
+        <v>113</v>
+      </c>
+      <c r="C230" t="s">
+        <v>304</v>
+      </c>
+      <c r="E230" t="s">
+        <v>113</v>
+      </c>
+      <c r="F230" t="s">
+        <v>113</v>
+      </c>
+      <c r="G230" t="s">
+        <v>59</v>
+      </c>
+      <c r="H230" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>305</v>
+      </c>
+      <c r="B232" t="s">
+        <v>113</v>
+      </c>
+      <c r="C232" t="s">
+        <v>306</v>
+      </c>
+      <c r="E232" t="s">
+        <v>113</v>
+      </c>
+      <c r="F232" t="s">
+        <v>113</v>
+      </c>
+      <c r="G232" t="s">
+        <v>59</v>
+      </c>
+      <c r="H232" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>307</v>
+      </c>
+      <c r="B234" t="s">
+        <v>113</v>
+      </c>
+      <c r="C234" t="s">
+        <v>308</v>
+      </c>
+      <c r="E234" t="s">
+        <v>113</v>
+      </c>
+      <c r="F234" t="s">
+        <v>113</v>
+      </c>
+      <c r="G234" t="s">
+        <v>59</v>
+      </c>
+      <c r="H234" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>310</v>
+      </c>
+      <c r="B236" t="s">
+        <v>113</v>
+      </c>
+      <c r="C236" t="s">
+        <v>309</v>
+      </c>
+      <c r="E236" t="s">
+        <v>113</v>
+      </c>
+      <c r="F236" t="s">
+        <v>113</v>
+      </c>
+      <c r="G236" t="s">
+        <v>59</v>
+      </c>
+      <c r="H236" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>311</v>
+      </c>
+      <c r="B238" t="s">
+        <v>113</v>
+      </c>
+      <c r="C238" t="s">
+        <v>312</v>
+      </c>
+      <c r="E238" t="s">
+        <v>113</v>
+      </c>
+      <c r="F238" t="s">
+        <v>113</v>
+      </c>
+      <c r="G238" t="s">
+        <v>59</v>
+      </c>
+      <c r="H238" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>313</v>
+      </c>
+      <c r="B240" t="s">
+        <v>113</v>
+      </c>
+      <c r="C240" t="s">
+        <v>314</v>
+      </c>
+      <c r="E240" t="s">
+        <v>113</v>
+      </c>
+      <c r="F240" t="s">
+        <v>113</v>
+      </c>
+      <c r="G240" t="s">
+        <v>59</v>
+      </c>
+      <c r="H240" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>316</v>
+      </c>
+      <c r="B242" t="s">
+        <v>113</v>
+      </c>
+      <c r="C242" t="s">
+        <v>315</v>
+      </c>
+      <c r="E242" t="s">
+        <v>113</v>
+      </c>
+      <c r="F242" t="s">
+        <v>113</v>
+      </c>
+      <c r="G242" t="s">
+        <v>59</v>
+      </c>
+      <c r="H242" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G51">
     <sortCondition ref="B2:B51"/>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEE648E-05BC-41FE-A853-3E668CCF76F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5834072-7EF1-4B2C-85B1-9E913A75903B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{09E8D2D0-BB12-495B-A39A-B0FC9433E411}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{09E8D2D0-BB12-495B-A39A-B0FC9433E411}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="378">
   <si>
     <t>13-332</t>
   </si>
@@ -1026,6 +1026,150 @@
   </si>
   <si>
     <t>złotowski</t>
+  </si>
+  <si>
+    <t>05-410</t>
+  </si>
+  <si>
+    <t>Józefów</t>
+  </si>
+  <si>
+    <t>otwocki</t>
+  </si>
+  <si>
+    <t>Niepodległości Pl.</t>
+  </si>
+  <si>
+    <t>inwersja</t>
+  </si>
+  <si>
+    <t>Pl. Niepodległości</t>
+  </si>
+  <si>
+    <t>Zamkowy Pl.</t>
+  </si>
+  <si>
+    <t>Pl. Zamkowy</t>
+  </si>
+  <si>
+    <t>23-204</t>
+  </si>
+  <si>
+    <t>Kraśnik</t>
+  </si>
+  <si>
+    <t>kraśnicki</t>
+  </si>
+  <si>
+    <t>Górnika Pl.</t>
+  </si>
+  <si>
+    <t>Pl. Górnika</t>
+  </si>
+  <si>
+    <t>91-718</t>
+  </si>
+  <si>
+    <t>70-545</t>
+  </si>
+  <si>
+    <t>Szczecin</t>
+  </si>
+  <si>
+    <t>Piastowski Bulw.</t>
+  </si>
+  <si>
+    <t>Bulw. Piastowski</t>
+  </si>
+  <si>
+    <t>66-002</t>
+  </si>
+  <si>
+    <t>Zielona Góra</t>
+  </si>
+  <si>
+    <t>Stary Kisielin-Pionierów Lub.</t>
+  </si>
+  <si>
+    <t>skrót</t>
+  </si>
+  <si>
+    <t>lubuskie</t>
+  </si>
+  <si>
+    <t>Stary Kisielin-Pionierów Lubuskich</t>
+  </si>
+  <si>
+    <t>04-410</t>
+  </si>
+  <si>
+    <t>Parkowa Al.</t>
+  </si>
+  <si>
+    <t>01-588</t>
+  </si>
+  <si>
+    <t>02-510</t>
+  </si>
+  <si>
+    <t>Na Skarpie Al.</t>
+  </si>
+  <si>
+    <t>Harcerska Al.</t>
+  </si>
+  <si>
+    <t>Kominiarska Al.</t>
+  </si>
+  <si>
+    <t>Niepodległości Al.</t>
+  </si>
+  <si>
+    <t>Al. Na Skarpie</t>
+  </si>
+  <si>
+    <t>Al. Parkowa</t>
+  </si>
+  <si>
+    <t>Al. Kominiarska</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al. Młodości </t>
+  </si>
+  <si>
+    <t>Al. Niepodległości</t>
+  </si>
+  <si>
+    <t>Al. Róż</t>
+  </si>
+  <si>
+    <t>Młodości Al.</t>
+  </si>
+  <si>
+    <t>Al. Harcerska</t>
+  </si>
+  <si>
+    <t>Róż Al.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kraśnik </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Józefów </t>
+  </si>
+  <si>
+    <t>62-500</t>
+  </si>
+  <si>
+    <t>Wolności Pl.</t>
+  </si>
+  <si>
+    <t>Pl. Wolności</t>
+  </si>
+  <si>
+    <t>ul. Chryzantem</t>
+  </si>
+  <si>
+    <t>Chryzantem Al.</t>
   </si>
 </sst>
 </file>
@@ -1398,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EC6EBE-762D-4FEE-AB4D-0625E60C23B9}">
-  <dimension ref="A1:H243"/>
+  <dimension ref="A1:H271"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -5512,6 +5656,605 @@
         <v>98</v>
       </c>
     </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>330</v>
+      </c>
+      <c r="B244" t="s">
+        <v>372</v>
+      </c>
+      <c r="C244" t="s">
+        <v>370</v>
+      </c>
+      <c r="E244" t="s">
+        <v>331</v>
+      </c>
+      <c r="F244" t="s">
+        <v>332</v>
+      </c>
+      <c r="G244" t="s">
+        <v>59</v>
+      </c>
+      <c r="H244" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>330</v>
+      </c>
+      <c r="B245" t="s">
+        <v>331</v>
+      </c>
+      <c r="C245" t="s">
+        <v>367</v>
+      </c>
+      <c r="E245" t="s">
+        <v>331</v>
+      </c>
+      <c r="F245" t="s">
+        <v>332</v>
+      </c>
+      <c r="G245" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>228</v>
+      </c>
+      <c r="B246" t="s">
+        <v>229</v>
+      </c>
+      <c r="C246" t="s">
+        <v>333</v>
+      </c>
+      <c r="E246" t="s">
+        <v>229</v>
+      </c>
+      <c r="F246" t="s">
+        <v>229</v>
+      </c>
+      <c r="G246" t="s">
+        <v>135</v>
+      </c>
+      <c r="H246" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>228</v>
+      </c>
+      <c r="B247" t="s">
+        <v>229</v>
+      </c>
+      <c r="C247" t="s">
+        <v>335</v>
+      </c>
+      <c r="E247" t="s">
+        <v>229</v>
+      </c>
+      <c r="F247" t="s">
+        <v>229</v>
+      </c>
+      <c r="G247" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>373</v>
+      </c>
+      <c r="B248" t="s">
+        <v>229</v>
+      </c>
+      <c r="C248" t="s">
+        <v>374</v>
+      </c>
+      <c r="E248" t="s">
+        <v>229</v>
+      </c>
+      <c r="F248" t="s">
+        <v>229</v>
+      </c>
+      <c r="G248" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>373</v>
+      </c>
+      <c r="B249" t="s">
+        <v>229</v>
+      </c>
+      <c r="C249" t="s">
+        <v>375</v>
+      </c>
+      <c r="E249" t="s">
+        <v>229</v>
+      </c>
+      <c r="F249" t="s">
+        <v>229</v>
+      </c>
+      <c r="G249" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>373</v>
+      </c>
+      <c r="B250" t="s">
+        <v>229</v>
+      </c>
+      <c r="C250" t="s">
+        <v>336</v>
+      </c>
+      <c r="E250" t="s">
+        <v>229</v>
+      </c>
+      <c r="F250" t="s">
+        <v>229</v>
+      </c>
+      <c r="G250" t="s">
+        <v>135</v>
+      </c>
+      <c r="H250" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>373</v>
+      </c>
+      <c r="B251" t="s">
+        <v>229</v>
+      </c>
+      <c r="C251" t="s">
+        <v>337</v>
+      </c>
+      <c r="E251" t="s">
+        <v>229</v>
+      </c>
+      <c r="F251" t="s">
+        <v>229</v>
+      </c>
+      <c r="G251" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>228</v>
+      </c>
+      <c r="B252" t="s">
+        <v>229</v>
+      </c>
+      <c r="C252" t="s">
+        <v>341</v>
+      </c>
+      <c r="E252" t="s">
+        <v>229</v>
+      </c>
+      <c r="F252" t="s">
+        <v>229</v>
+      </c>
+      <c r="G252" t="s">
+        <v>135</v>
+      </c>
+      <c r="H252" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>228</v>
+      </c>
+      <c r="B253" t="s">
+        <v>229</v>
+      </c>
+      <c r="C253" t="s">
+        <v>342</v>
+      </c>
+      <c r="E253" t="s">
+        <v>229</v>
+      </c>
+      <c r="F253" t="s">
+        <v>229</v>
+      </c>
+      <c r="G253" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>338</v>
+      </c>
+      <c r="B254" t="s">
+        <v>371</v>
+      </c>
+      <c r="C254" t="s">
+        <v>368</v>
+      </c>
+      <c r="E254" t="s">
+        <v>339</v>
+      </c>
+      <c r="F254" t="s">
+        <v>340</v>
+      </c>
+      <c r="G254" t="s">
+        <v>68</v>
+      </c>
+      <c r="H254" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>338</v>
+      </c>
+      <c r="B255" t="s">
+        <v>371</v>
+      </c>
+      <c r="C255" t="s">
+        <v>365</v>
+      </c>
+      <c r="E255" t="s">
+        <v>339</v>
+      </c>
+      <c r="F255" t="s">
+        <v>340</v>
+      </c>
+      <c r="G255" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>338</v>
+      </c>
+      <c r="B256" t="s">
+        <v>371</v>
+      </c>
+      <c r="C256" t="s">
+        <v>361</v>
+      </c>
+      <c r="E256" t="s">
+        <v>339</v>
+      </c>
+      <c r="F256" t="s">
+        <v>340</v>
+      </c>
+      <c r="G256" t="s">
+        <v>68</v>
+      </c>
+      <c r="H256" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>338</v>
+      </c>
+      <c r="B257" t="s">
+        <v>371</v>
+      </c>
+      <c r="C257" t="s">
+        <v>366</v>
+      </c>
+      <c r="E257" t="s">
+        <v>339</v>
+      </c>
+      <c r="F257" t="s">
+        <v>340</v>
+      </c>
+      <c r="G257" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>343</v>
+      </c>
+      <c r="B258" t="s">
+        <v>122</v>
+      </c>
+      <c r="C258" t="s">
+        <v>377</v>
+      </c>
+      <c r="E258" t="s">
+        <v>122</v>
+      </c>
+      <c r="F258" t="s">
+        <v>122</v>
+      </c>
+      <c r="G258" t="s">
+        <v>52</v>
+      </c>
+      <c r="H258" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>343</v>
+      </c>
+      <c r="B259" t="s">
+        <v>122</v>
+      </c>
+      <c r="C259" t="s">
+        <v>376</v>
+      </c>
+      <c r="E259" t="s">
+        <v>122</v>
+      </c>
+      <c r="F259" t="s">
+        <v>122</v>
+      </c>
+      <c r="G259" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>344</v>
+      </c>
+      <c r="B260" t="s">
+        <v>345</v>
+      </c>
+      <c r="C260" t="s">
+        <v>346</v>
+      </c>
+      <c r="E260" t="s">
+        <v>345</v>
+      </c>
+      <c r="F260" t="s">
+        <v>345</v>
+      </c>
+      <c r="G260" t="s">
+        <v>142</v>
+      </c>
+      <c r="H260" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>344</v>
+      </c>
+      <c r="B261" t="s">
+        <v>345</v>
+      </c>
+      <c r="C261" t="s">
+        <v>347</v>
+      </c>
+      <c r="E261" t="s">
+        <v>345</v>
+      </c>
+      <c r="F261" t="s">
+        <v>345</v>
+      </c>
+      <c r="G261" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>348</v>
+      </c>
+      <c r="B262" t="s">
+        <v>349</v>
+      </c>
+      <c r="C262" t="s">
+        <v>350</v>
+      </c>
+      <c r="E262" t="s">
+        <v>349</v>
+      </c>
+      <c r="F262" t="s">
+        <v>349</v>
+      </c>
+      <c r="G262" t="s">
+        <v>352</v>
+      </c>
+      <c r="H262" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>348</v>
+      </c>
+      <c r="B263" t="s">
+        <v>349</v>
+      </c>
+      <c r="C263" t="s">
+        <v>353</v>
+      </c>
+      <c r="E263" t="s">
+        <v>349</v>
+      </c>
+      <c r="F263" t="s">
+        <v>349</v>
+      </c>
+      <c r="G263" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>354</v>
+      </c>
+      <c r="B264" t="s">
+        <v>123</v>
+      </c>
+      <c r="C264" t="s">
+        <v>360</v>
+      </c>
+      <c r="E264" t="s">
+        <v>113</v>
+      </c>
+      <c r="F264" t="s">
+        <v>113</v>
+      </c>
+      <c r="G264" t="s">
+        <v>59</v>
+      </c>
+      <c r="H264" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>354</v>
+      </c>
+      <c r="B265" t="s">
+        <v>123</v>
+      </c>
+      <c r="C265" t="s">
+        <v>364</v>
+      </c>
+      <c r="E265" t="s">
+        <v>113</v>
+      </c>
+      <c r="F265" t="s">
+        <v>113</v>
+      </c>
+      <c r="G265" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>138</v>
+      </c>
+      <c r="B266" t="s">
+        <v>140</v>
+      </c>
+      <c r="C266" t="s">
+        <v>355</v>
+      </c>
+      <c r="E266" t="s">
+        <v>140</v>
+      </c>
+      <c r="F266" t="s">
+        <v>141</v>
+      </c>
+      <c r="G266" t="s">
+        <v>142</v>
+      </c>
+      <c r="H266" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>138</v>
+      </c>
+      <c r="B267" t="s">
+        <v>140</v>
+      </c>
+      <c r="C267" t="s">
+        <v>363</v>
+      </c>
+      <c r="E267" t="s">
+        <v>140</v>
+      </c>
+      <c r="F267" t="s">
+        <v>141</v>
+      </c>
+      <c r="G267" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>356</v>
+      </c>
+      <c r="B268" t="s">
+        <v>113</v>
+      </c>
+      <c r="C268" t="s">
+        <v>359</v>
+      </c>
+      <c r="E268" t="s">
+        <v>113</v>
+      </c>
+      <c r="F268" t="s">
+        <v>113</v>
+      </c>
+      <c r="G268" t="s">
+        <v>59</v>
+      </c>
+      <c r="H268" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>356</v>
+      </c>
+      <c r="B269" t="s">
+        <v>113</v>
+      </c>
+      <c r="C269" t="s">
+        <v>369</v>
+      </c>
+      <c r="E269" t="s">
+        <v>113</v>
+      </c>
+      <c r="F269" t="s">
+        <v>113</v>
+      </c>
+      <c r="G269" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>357</v>
+      </c>
+      <c r="B270" t="s">
+        <v>113</v>
+      </c>
+      <c r="C270" t="s">
+        <v>358</v>
+      </c>
+      <c r="E270" t="s">
+        <v>113</v>
+      </c>
+      <c r="F270" t="s">
+        <v>113</v>
+      </c>
+      <c r="G270" t="s">
+        <v>59</v>
+      </c>
+      <c r="H270" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>357</v>
+      </c>
+      <c r="B271" t="s">
+        <v>113</v>
+      </c>
+      <c r="C271" t="s">
+        <v>362</v>
+      </c>
+      <c r="E271" t="s">
+        <v>113</v>
+      </c>
+      <c r="F271" t="s">
+        <v>113</v>
+      </c>
+      <c r="G271" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G51">
     <sortCondition ref="B2:B51"/>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF5D3CB-66C4-4B39-B27F-9E5DCF82653E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB132F56-C59C-46DF-A0EA-DBB39C453F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="354">
   <si>
     <t>Kod</t>
   </si>
@@ -422,9 +422,6 @@
     <t>Żbikowa</t>
   </si>
   <si>
-    <t>podkarpackie</t>
-  </si>
-  <si>
     <t>Szczecin</t>
   </si>
   <si>
@@ -957,24 +954,6 @@
   </si>
   <si>
     <t>Stanisława Trembeckiego</t>
-  </si>
-  <si>
-    <t>37-500</t>
-  </si>
-  <si>
-    <t>Wietlin</t>
-  </si>
-  <si>
-    <t>Laszki</t>
-  </si>
-  <si>
-    <t>jarosławski</t>
-  </si>
-  <si>
-    <t>Brak miasta: Wietlin w gminie Laszki</t>
-  </si>
-  <si>
-    <t>37-512</t>
   </si>
   <si>
     <t>41-800</t>
@@ -1994,7 +1973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H303"/>
+  <dimension ref="A1:H299"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -2056,7 +2035,7 @@
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2067,7 +2046,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -2108,12 +2087,12 @@
         <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -2145,7 +2124,7 @@
         <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2156,7 +2135,7 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -2197,7 +2176,7 @@
         <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2208,7 +2187,7 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -2249,7 +2228,7 @@
         <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2260,7 +2239,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -2301,7 +2280,7 @@
         <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -2312,7 +2291,7 @@
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -2358,7 +2337,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -2390,7 +2369,7 @@
         <v>19</v>
       </c>
       <c r="H16" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -2401,7 +2380,7 @@
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -2447,7 +2426,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -2487,7 +2466,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -2522,7 +2501,7 @@
         <v>48</v>
       </c>
       <c r="H22" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -2533,7 +2512,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -2574,7 +2553,7 @@
         <v>48</v>
       </c>
       <c r="H24" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -2585,7 +2564,7 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -2626,7 +2605,7 @@
         <v>48</v>
       </c>
       <c r="H26" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -2637,7 +2616,7 @@
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -2678,7 +2657,7 @@
         <v>48</v>
       </c>
       <c r="H28" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -2689,7 +2668,7 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -2730,7 +2709,7 @@
         <v>48</v>
       </c>
       <c r="H30" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -2741,7 +2720,7 @@
         <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -2787,7 +2766,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -2824,7 +2803,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -2861,7 +2840,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -2893,7 +2872,7 @@
         <v>63</v>
       </c>
       <c r="H38" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -2904,7 +2883,7 @@
         <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
@@ -2945,7 +2924,7 @@
         <v>63</v>
       </c>
       <c r="H40" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -2956,7 +2935,7 @@
         <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -3002,7 +2981,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -3037,7 +3016,7 @@
         <v>63</v>
       </c>
       <c r="H44" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -3048,7 +3027,7 @@
         <v>66</v>
       </c>
       <c r="C45" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
@@ -3094,7 +3073,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
@@ -3131,7 +3110,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -3160,7 +3139,7 @@
         <v>76</v>
       </c>
       <c r="H50" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -3171,7 +3150,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -3217,7 +3196,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -3254,7 +3233,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -3291,7 +3270,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -3328,7 +3307,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -3365,7 +3344,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -3402,7 +3381,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -3439,7 +3418,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
@@ -3476,7 +3455,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
@@ -3513,7 +3492,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
@@ -3550,7 +3529,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -3587,7 +3566,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -3624,7 +3603,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
@@ -3661,7 +3640,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D77" t="s">
         <v>11</v>
@@ -3698,7 +3677,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="H79" t="s">
         <v>11</v>
@@ -3732,7 +3711,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="H81" t="s">
         <v>11</v>
@@ -3761,7 +3740,7 @@
         <v>76</v>
       </c>
       <c r="H82" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -3772,7 +3751,7 @@
         <v>74</v>
       </c>
       <c r="C83" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D83" t="s">
         <v>11</v>
@@ -3818,7 +3797,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
@@ -3855,7 +3834,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="H87" t="s">
         <v>11</v>
@@ -3889,7 +3868,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D89" t="s">
         <v>11</v>
@@ -3926,7 +3905,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D91" t="s">
         <v>11</v>
@@ -3963,7 +3942,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
@@ -4000,7 +3979,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D95" t="s">
         <v>11</v>
@@ -4037,7 +4016,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D97" t="s">
         <v>11</v>
@@ -4074,7 +4053,7 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="H99" t="s">
         <v>11</v>
@@ -4108,7 +4087,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D101" t="s">
         <v>11</v>
@@ -4140,7 +4119,7 @@
         <v>76</v>
       </c>
       <c r="H102" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -4151,7 +4130,7 @@
         <v>74</v>
       </c>
       <c r="C103" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D103" t="s">
         <v>11</v>
@@ -4197,7 +4176,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
@@ -4208,48 +4187,48 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>130</v>
+      </c>
+      <c r="B106" t="s">
+        <v>129</v>
+      </c>
+      <c r="C106" t="s">
         <v>131</v>
       </c>
-      <c r="B106" t="s">
-        <v>130</v>
-      </c>
-      <c r="C106" t="s">
-        <v>132</v>
-      </c>
       <c r="D106" t="s">
         <v>11</v>
       </c>
       <c r="E106" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F106" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G106" t="s">
         <v>29</v>
       </c>
       <c r="H106" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B107" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C107" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="D107" t="s">
         <v>11</v>
       </c>
       <c r="E107" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F107" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G107" t="s">
         <v>29</v>
@@ -4260,22 +4239,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B108" t="s">
+        <v>133</v>
+      </c>
+      <c r="C108" t="s">
         <v>134</v>
       </c>
-      <c r="C108" t="s">
-        <v>135</v>
-      </c>
       <c r="D108" t="s">
         <v>11</v>
       </c>
       <c r="E108" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F108" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G108" t="s">
         <v>19</v>
@@ -4286,7 +4265,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D109" t="s">
         <v>11</v>
@@ -4297,22 +4276,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>135</v>
+      </c>
+      <c r="B110" t="s">
+        <v>133</v>
+      </c>
+      <c r="C110" t="s">
         <v>136</v>
       </c>
-      <c r="B110" t="s">
-        <v>134</v>
-      </c>
-      <c r="C110" t="s">
-        <v>137</v>
-      </c>
       <c r="D110" t="s">
         <v>11</v>
       </c>
       <c r="E110" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F110" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G110" t="s">
         <v>19</v>
@@ -4323,7 +4302,7 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D111" t="s">
         <v>11</v>
@@ -4334,22 +4313,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>137</v>
+      </c>
+      <c r="B112" t="s">
+        <v>133</v>
+      </c>
+      <c r="C112" t="s">
         <v>138</v>
       </c>
-      <c r="B112" t="s">
-        <v>134</v>
-      </c>
-      <c r="C112" t="s">
-        <v>139</v>
-      </c>
       <c r="D112" t="s">
         <v>11</v>
       </c>
       <c r="E112" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F112" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G112" t="s">
         <v>19</v>
@@ -4360,7 +4339,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D113" t="s">
         <v>11</v>
@@ -4371,22 +4350,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>139</v>
+      </c>
+      <c r="B114" t="s">
+        <v>133</v>
+      </c>
+      <c r="C114" t="s">
         <v>140</v>
       </c>
-      <c r="B114" t="s">
-        <v>134</v>
-      </c>
-      <c r="C114" t="s">
-        <v>141</v>
-      </c>
       <c r="D114" t="s">
         <v>11</v>
       </c>
       <c r="E114" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F114" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G114" t="s">
         <v>19</v>
@@ -4397,7 +4376,7 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D115" t="s">
         <v>11</v>
@@ -4408,22 +4387,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>141</v>
+      </c>
+      <c r="B116" t="s">
+        <v>133</v>
+      </c>
+      <c r="C116" t="s">
         <v>142</v>
       </c>
-      <c r="B116" t="s">
-        <v>134</v>
-      </c>
-      <c r="C116" t="s">
-        <v>143</v>
-      </c>
       <c r="D116" t="s">
         <v>11</v>
       </c>
       <c r="E116" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F116" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G116" t="s">
         <v>19</v>
@@ -4434,7 +4413,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D117" t="s">
         <v>11</v>
@@ -4445,22 +4424,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>143</v>
+      </c>
+      <c r="B118" t="s">
+        <v>133</v>
+      </c>
+      <c r="C118" t="s">
         <v>144</v>
       </c>
-      <c r="B118" t="s">
-        <v>134</v>
-      </c>
-      <c r="C118" t="s">
-        <v>145</v>
-      </c>
       <c r="D118" t="s">
         <v>11</v>
       </c>
       <c r="E118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G118" t="s">
         <v>19</v>
@@ -4471,7 +4450,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D119" t="s">
         <v>11</v>
@@ -4482,22 +4461,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>145</v>
+      </c>
+      <c r="B120" t="s">
+        <v>133</v>
+      </c>
+      <c r="C120" t="s">
         <v>146</v>
       </c>
-      <c r="B120" t="s">
-        <v>134</v>
-      </c>
-      <c r="C120" t="s">
-        <v>147</v>
-      </c>
       <c r="D120" t="s">
         <v>11</v>
       </c>
       <c r="E120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G120" t="s">
         <v>19</v>
@@ -4508,7 +4487,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D121" t="s">
         <v>11</v>
@@ -4519,22 +4498,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>147</v>
+      </c>
+      <c r="B122" t="s">
+        <v>133</v>
+      </c>
+      <c r="C122" t="s">
         <v>148</v>
       </c>
-      <c r="B122" t="s">
-        <v>134</v>
-      </c>
-      <c r="C122" t="s">
-        <v>149</v>
-      </c>
       <c r="D122" t="s">
         <v>11</v>
       </c>
       <c r="E122" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F122" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G122" t="s">
         <v>19</v>
@@ -4545,7 +4524,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D123" t="s">
         <v>11</v>
@@ -4556,22 +4535,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>149</v>
+      </c>
+      <c r="B124" t="s">
+        <v>133</v>
+      </c>
+      <c r="C124" t="s">
         <v>150</v>
       </c>
-      <c r="B124" t="s">
-        <v>134</v>
-      </c>
-      <c r="C124" t="s">
-        <v>151</v>
-      </c>
       <c r="D124" t="s">
         <v>11</v>
       </c>
       <c r="E124" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F124" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G124" t="s">
         <v>19</v>
@@ -4582,7 +4561,7 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D125" t="s">
         <v>11</v>
@@ -4593,22 +4572,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>151</v>
+      </c>
+      <c r="B126" t="s">
+        <v>133</v>
+      </c>
+      <c r="C126" t="s">
         <v>152</v>
       </c>
-      <c r="B126" t="s">
-        <v>134</v>
-      </c>
-      <c r="C126" t="s">
-        <v>153</v>
-      </c>
       <c r="D126" t="s">
         <v>11</v>
       </c>
       <c r="E126" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F126" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G126" t="s">
         <v>19</v>
@@ -4619,7 +4598,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D127" t="s">
         <v>11</v>
@@ -4630,22 +4609,22 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>153</v>
+      </c>
+      <c r="B128" t="s">
+        <v>133</v>
+      </c>
+      <c r="C128" t="s">
         <v>154</v>
       </c>
-      <c r="B128" t="s">
-        <v>134</v>
-      </c>
-      <c r="C128" t="s">
-        <v>155</v>
-      </c>
       <c r="D128" t="s">
         <v>11</v>
       </c>
       <c r="E128" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F128" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G128" t="s">
         <v>19</v>
@@ -4656,7 +4635,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D129" t="s">
         <v>11</v>
@@ -4667,22 +4646,22 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C130" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D130" t="s">
         <v>11</v>
       </c>
       <c r="E130" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F130" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G130" t="s">
         <v>19</v>
@@ -4693,7 +4672,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D131" t="s">
         <v>11</v>
@@ -4704,22 +4683,22 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>156</v>
+      </c>
+      <c r="B132" t="s">
+        <v>133</v>
+      </c>
+      <c r="C132" t="s">
         <v>157</v>
       </c>
-      <c r="B132" t="s">
-        <v>134</v>
-      </c>
-      <c r="C132" t="s">
-        <v>158</v>
-      </c>
       <c r="D132" t="s">
         <v>11</v>
       </c>
       <c r="E132" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F132" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G132" t="s">
         <v>19</v>
@@ -4730,7 +4709,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D133" t="s">
         <v>11</v>
@@ -4741,22 +4720,22 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>158</v>
+      </c>
+      <c r="B134" t="s">
+        <v>133</v>
+      </c>
+      <c r="C134" t="s">
         <v>159</v>
       </c>
-      <c r="B134" t="s">
-        <v>134</v>
-      </c>
-      <c r="C134" t="s">
-        <v>160</v>
-      </c>
       <c r="D134" t="s">
         <v>11</v>
       </c>
       <c r="E134" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F134" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G134" t="s">
         <v>19</v>
@@ -4767,7 +4746,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D135" t="s">
         <v>11</v>
@@ -4778,22 +4757,22 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>160</v>
+      </c>
+      <c r="B136" t="s">
+        <v>133</v>
+      </c>
+      <c r="C136" t="s">
         <v>161</v>
       </c>
-      <c r="B136" t="s">
-        <v>134</v>
-      </c>
-      <c r="C136" t="s">
-        <v>162</v>
-      </c>
       <c r="D136" t="s">
         <v>11</v>
       </c>
       <c r="E136" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F136" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G136" t="s">
         <v>19</v>
@@ -4804,7 +4783,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D137" t="s">
         <v>11</v>
@@ -4815,22 +4794,22 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>162</v>
+      </c>
+      <c r="B138" t="s">
+        <v>133</v>
+      </c>
+      <c r="C138" t="s">
         <v>163</v>
       </c>
-      <c r="B138" t="s">
-        <v>134</v>
-      </c>
-      <c r="C138" t="s">
-        <v>164</v>
-      </c>
       <c r="D138" t="s">
         <v>11</v>
       </c>
       <c r="E138" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F138" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G138" t="s">
         <v>19</v>
@@ -4841,7 +4820,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D139" t="s">
         <v>11</v>
@@ -4852,22 +4831,22 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>164</v>
+      </c>
+      <c r="B140" t="s">
+        <v>133</v>
+      </c>
+      <c r="C140" t="s">
         <v>165</v>
       </c>
-      <c r="B140" t="s">
-        <v>134</v>
-      </c>
-      <c r="C140" t="s">
-        <v>166</v>
-      </c>
       <c r="D140" t="s">
         <v>11</v>
       </c>
       <c r="E140" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F140" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G140" t="s">
         <v>19</v>
@@ -4878,7 +4857,7 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D141" t="s">
         <v>11</v>
@@ -4889,22 +4868,22 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B142" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C142" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D142" t="s">
         <v>11</v>
       </c>
       <c r="E142" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F142" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G142" t="s">
         <v>19</v>
@@ -4915,7 +4894,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D143" t="s">
         <v>11</v>
@@ -4926,22 +4905,22 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B144" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C144" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D144" t="s">
         <v>11</v>
       </c>
       <c r="E144" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F144" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G144" t="s">
         <v>19</v>
@@ -4952,7 +4931,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D145" t="s">
         <v>11</v>
@@ -4963,22 +4942,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>168</v>
+      </c>
+      <c r="B146" t="s">
+        <v>133</v>
+      </c>
+      <c r="C146" t="s">
         <v>169</v>
       </c>
-      <c r="B146" t="s">
-        <v>134</v>
-      </c>
-      <c r="C146" t="s">
-        <v>170</v>
-      </c>
       <c r="D146" t="s">
         <v>11</v>
       </c>
       <c r="E146" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F146" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G146" t="s">
         <v>19</v>
@@ -4989,7 +4968,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D147" t="s">
         <v>11</v>
@@ -5000,22 +4979,22 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B148" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C148" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D148" t="s">
         <v>11</v>
       </c>
       <c r="E148" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F148" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G148" t="s">
         <v>19</v>
@@ -5026,7 +5005,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D149" t="s">
         <v>11</v>
@@ -5037,22 +5016,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>171</v>
+      </c>
+      <c r="B150" t="s">
+        <v>133</v>
+      </c>
+      <c r="C150" t="s">
         <v>172</v>
       </c>
-      <c r="B150" t="s">
-        <v>134</v>
-      </c>
-      <c r="C150" t="s">
-        <v>173</v>
-      </c>
       <c r="D150" t="s">
         <v>11</v>
       </c>
       <c r="E150" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F150" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G150" t="s">
         <v>19</v>
@@ -5063,7 +5042,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D151" t="s">
         <v>11</v>
@@ -5074,22 +5053,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>173</v>
+      </c>
+      <c r="B152" t="s">
+        <v>133</v>
+      </c>
+      <c r="C152" t="s">
         <v>174</v>
       </c>
-      <c r="B152" t="s">
-        <v>134</v>
-      </c>
-      <c r="C152" t="s">
-        <v>175</v>
-      </c>
       <c r="D152" t="s">
         <v>11</v>
       </c>
       <c r="E152" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F152" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G152" t="s">
         <v>19</v>
@@ -5100,7 +5079,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D153" t="s">
         <v>11</v>
@@ -5111,22 +5090,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>175</v>
+      </c>
+      <c r="B154" t="s">
+        <v>133</v>
+      </c>
+      <c r="C154" t="s">
         <v>176</v>
       </c>
-      <c r="B154" t="s">
-        <v>134</v>
-      </c>
-      <c r="C154" t="s">
-        <v>177</v>
-      </c>
       <c r="D154" t="s">
         <v>11</v>
       </c>
       <c r="E154" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F154" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G154" t="s">
         <v>19</v>
@@ -5137,7 +5116,7 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D155" t="s">
         <v>11</v>
@@ -5148,22 +5127,22 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>177</v>
+      </c>
+      <c r="B156" t="s">
+        <v>133</v>
+      </c>
+      <c r="C156" t="s">
         <v>178</v>
       </c>
-      <c r="B156" t="s">
-        <v>134</v>
-      </c>
-      <c r="C156" t="s">
-        <v>179</v>
-      </c>
       <c r="D156" t="s">
         <v>11</v>
       </c>
       <c r="E156" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F156" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G156" t="s">
         <v>19</v>
@@ -5174,7 +5153,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D157" t="s">
         <v>11</v>
@@ -5185,48 +5164,48 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>179</v>
+      </c>
+      <c r="B158" t="s">
+        <v>133</v>
+      </c>
+      <c r="C158" t="s">
         <v>180</v>
       </c>
-      <c r="B158" t="s">
-        <v>134</v>
-      </c>
-      <c r="C158" t="s">
-        <v>181</v>
-      </c>
       <c r="D158" t="s">
         <v>11</v>
       </c>
       <c r="E158" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F158" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G158" t="s">
         <v>19</v>
       </c>
       <c r="H158" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B159" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C159" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="D159" t="s">
         <v>11</v>
       </c>
       <c r="E159" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F159" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G159" t="s">
         <v>19</v>
@@ -5237,22 +5216,22 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>181</v>
+      </c>
+      <c r="B160" t="s">
+        <v>133</v>
+      </c>
+      <c r="C160" t="s">
         <v>182</v>
       </c>
-      <c r="B160" t="s">
-        <v>134</v>
-      </c>
-      <c r="C160" t="s">
-        <v>183</v>
-      </c>
       <c r="D160" t="s">
         <v>11</v>
       </c>
       <c r="E160" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F160" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G160" t="s">
         <v>19</v>
@@ -5263,7 +5242,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D161" t="s">
         <v>11</v>
@@ -5274,22 +5253,22 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>183</v>
+      </c>
+      <c r="B162" t="s">
+        <v>133</v>
+      </c>
+      <c r="C162" t="s">
         <v>184</v>
       </c>
-      <c r="B162" t="s">
-        <v>134</v>
-      </c>
-      <c r="C162" t="s">
-        <v>185</v>
-      </c>
       <c r="D162" t="s">
         <v>11</v>
       </c>
       <c r="E162" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F162" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G162" t="s">
         <v>19</v>
@@ -5300,7 +5279,7 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D163" t="s">
         <v>11</v>
@@ -5311,22 +5290,22 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>185</v>
+      </c>
+      <c r="B164" t="s">
+        <v>133</v>
+      </c>
+      <c r="C164" t="s">
         <v>186</v>
       </c>
-      <c r="B164" t="s">
-        <v>134</v>
-      </c>
-      <c r="C164" t="s">
-        <v>187</v>
-      </c>
       <c r="D164" t="s">
         <v>11</v>
       </c>
       <c r="E164" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F164" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G164" t="s">
         <v>19</v>
@@ -5337,7 +5316,7 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D165" t="s">
         <v>11</v>
@@ -5348,22 +5327,22 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B166" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C166" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D166" t="s">
         <v>11</v>
       </c>
       <c r="E166" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F166" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G166" t="s">
         <v>19</v>
@@ -5374,7 +5353,7 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D167" t="s">
         <v>11</v>
@@ -5385,48 +5364,48 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>188</v>
+      </c>
+      <c r="B168" t="s">
+        <v>133</v>
+      </c>
+      <c r="C168" t="s">
         <v>189</v>
       </c>
-      <c r="B168" t="s">
-        <v>134</v>
-      </c>
-      <c r="C168" t="s">
-        <v>190</v>
-      </c>
       <c r="D168" t="s">
         <v>11</v>
       </c>
       <c r="E168" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F168" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G168" t="s">
         <v>19</v>
       </c>
       <c r="H168" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B169" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C169" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D169" t="s">
         <v>11</v>
       </c>
       <c r="E169" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F169" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G169" t="s">
         <v>19</v>
@@ -5437,22 +5416,22 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>190</v>
+      </c>
+      <c r="B170" t="s">
+        <v>133</v>
+      </c>
+      <c r="C170" t="s">
         <v>191</v>
       </c>
-      <c r="B170" t="s">
-        <v>134</v>
-      </c>
-      <c r="C170" t="s">
-        <v>192</v>
-      </c>
       <c r="D170" t="s">
         <v>11</v>
       </c>
       <c r="E170" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F170" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G170" t="s">
         <v>19</v>
@@ -5463,7 +5442,7 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D171" t="s">
         <v>11</v>
@@ -5474,22 +5453,22 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>192</v>
+      </c>
+      <c r="B172" t="s">
+        <v>133</v>
+      </c>
+      <c r="C172" t="s">
         <v>193</v>
       </c>
-      <c r="B172" t="s">
-        <v>134</v>
-      </c>
-      <c r="C172" t="s">
-        <v>194</v>
-      </c>
       <c r="D172" t="s">
         <v>11</v>
       </c>
       <c r="E172" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F172" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G172" t="s">
         <v>19</v>
@@ -5500,7 +5479,7 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D173" t="s">
         <v>11</v>
@@ -5511,48 +5490,48 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>194</v>
+      </c>
+      <c r="B174" t="s">
+        <v>133</v>
+      </c>
+      <c r="C174" t="s">
         <v>195</v>
       </c>
-      <c r="B174" t="s">
-        <v>134</v>
-      </c>
-      <c r="C174" t="s">
-        <v>196</v>
-      </c>
       <c r="D174" t="s">
         <v>11</v>
       </c>
       <c r="E174" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F174" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G174" t="s">
         <v>19</v>
       </c>
       <c r="H174" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B175" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C175" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D175" t="s">
         <v>11</v>
       </c>
       <c r="E175" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F175" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G175" t="s">
         <v>19</v>
@@ -5563,22 +5542,22 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>196</v>
+      </c>
+      <c r="B176" t="s">
+        <v>133</v>
+      </c>
+      <c r="C176" t="s">
         <v>197</v>
       </c>
-      <c r="B176" t="s">
-        <v>134</v>
-      </c>
-      <c r="C176" t="s">
-        <v>198</v>
-      </c>
       <c r="D176" t="s">
         <v>11</v>
       </c>
       <c r="E176" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F176" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G176" t="s">
         <v>19</v>
@@ -5589,7 +5568,7 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D177" t="s">
         <v>11</v>
@@ -5600,22 +5579,22 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>198</v>
+      </c>
+      <c r="B178" t="s">
+        <v>133</v>
+      </c>
+      <c r="C178" t="s">
         <v>199</v>
       </c>
-      <c r="B178" t="s">
-        <v>134</v>
-      </c>
-      <c r="C178" t="s">
-        <v>200</v>
-      </c>
       <c r="D178" t="s">
         <v>11</v>
       </c>
       <c r="E178" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F178" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G178" t="s">
         <v>19</v>
@@ -5626,22 +5605,22 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B179" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C179" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D179" t="s">
         <v>11</v>
       </c>
       <c r="E179" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F179" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G179" t="s">
         <v>19</v>
@@ -5652,48 +5631,48 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>200</v>
+      </c>
+      <c r="B180" t="s">
+        <v>133</v>
+      </c>
+      <c r="C180" t="s">
         <v>201</v>
       </c>
-      <c r="B180" t="s">
-        <v>134</v>
-      </c>
-      <c r="C180" t="s">
-        <v>202</v>
-      </c>
       <c r="D180" t="s">
         <v>11</v>
       </c>
       <c r="E180" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F180" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G180" t="s">
         <v>19</v>
       </c>
       <c r="H180" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B181" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C181" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="D181" t="s">
         <v>11</v>
       </c>
       <c r="E181" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F181" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G181" t="s">
         <v>19</v>
@@ -5704,22 +5683,22 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>202</v>
+      </c>
+      <c r="B182" t="s">
+        <v>133</v>
+      </c>
+      <c r="C182" t="s">
         <v>203</v>
       </c>
-      <c r="B182" t="s">
-        <v>134</v>
-      </c>
-      <c r="C182" t="s">
-        <v>204</v>
-      </c>
       <c r="D182" t="s">
         <v>11</v>
       </c>
       <c r="E182" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F182" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G182" t="s">
         <v>19</v>
@@ -5730,7 +5709,7 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D183" t="s">
         <v>11</v>
@@ -5741,22 +5720,22 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>204</v>
+      </c>
+      <c r="B184" t="s">
+        <v>133</v>
+      </c>
+      <c r="C184" t="s">
         <v>205</v>
       </c>
-      <c r="B184" t="s">
-        <v>134</v>
-      </c>
-      <c r="C184" t="s">
-        <v>206</v>
-      </c>
       <c r="D184" t="s">
         <v>11</v>
       </c>
       <c r="E184" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F184" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G184" t="s">
         <v>19</v>
@@ -5767,7 +5746,7 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D185" t="s">
         <v>11</v>
@@ -5778,22 +5757,22 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>206</v>
+      </c>
+      <c r="B186" t="s">
+        <v>133</v>
+      </c>
+      <c r="C186" t="s">
         <v>207</v>
       </c>
-      <c r="B186" t="s">
-        <v>134</v>
-      </c>
-      <c r="C186" t="s">
-        <v>208</v>
-      </c>
       <c r="D186" t="s">
         <v>11</v>
       </c>
       <c r="E186" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F186" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G186" t="s">
         <v>19</v>
@@ -5804,7 +5783,7 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D187" t="s">
         <v>11</v>
@@ -5815,22 +5794,22 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>208</v>
+      </c>
+      <c r="B188" t="s">
+        <v>133</v>
+      </c>
+      <c r="C188" t="s">
         <v>209</v>
       </c>
-      <c r="B188" t="s">
-        <v>134</v>
-      </c>
-      <c r="C188" t="s">
-        <v>210</v>
-      </c>
       <c r="D188" t="s">
         <v>11</v>
       </c>
       <c r="E188" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F188" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G188" t="s">
         <v>19</v>
@@ -5841,7 +5820,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D189" t="s">
         <v>11</v>
@@ -5852,22 +5831,22 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>210</v>
+      </c>
+      <c r="B190" t="s">
+        <v>133</v>
+      </c>
+      <c r="C190" t="s">
         <v>211</v>
       </c>
-      <c r="B190" t="s">
-        <v>134</v>
-      </c>
-      <c r="C190" t="s">
-        <v>212</v>
-      </c>
       <c r="D190" t="s">
         <v>11</v>
       </c>
       <c r="E190" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F190" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G190" t="s">
         <v>19</v>
@@ -5878,7 +5857,7 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D191" t="s">
         <v>11</v>
@@ -5889,22 +5868,22 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>212</v>
+      </c>
+      <c r="B192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C192" t="s">
         <v>213</v>
       </c>
-      <c r="B192" t="s">
-        <v>134</v>
-      </c>
-      <c r="C192" t="s">
-        <v>214</v>
-      </c>
       <c r="D192" t="s">
         <v>11</v>
       </c>
       <c r="E192" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F192" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G192" t="s">
         <v>19</v>
@@ -5915,7 +5894,7 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D193" t="s">
         <v>11</v>
@@ -5926,22 +5905,22 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>214</v>
+      </c>
+      <c r="B194" t="s">
+        <v>133</v>
+      </c>
+      <c r="C194" t="s">
         <v>215</v>
       </c>
-      <c r="B194" t="s">
-        <v>134</v>
-      </c>
-      <c r="C194" t="s">
-        <v>216</v>
-      </c>
       <c r="D194" t="s">
         <v>11</v>
       </c>
       <c r="E194" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F194" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G194" t="s">
         <v>19</v>
@@ -5952,7 +5931,7 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D195" t="s">
         <v>11</v>
@@ -5963,22 +5942,22 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>216</v>
+      </c>
+      <c r="B196" t="s">
+        <v>133</v>
+      </c>
+      <c r="C196" t="s">
         <v>217</v>
       </c>
-      <c r="B196" t="s">
-        <v>134</v>
-      </c>
-      <c r="C196" t="s">
-        <v>218</v>
-      </c>
       <c r="D196" t="s">
         <v>11</v>
       </c>
       <c r="E196" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F196" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G196" t="s">
         <v>19</v>
@@ -5989,7 +5968,7 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D197" t="s">
         <v>11</v>
@@ -6000,22 +5979,22 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>218</v>
+      </c>
+      <c r="B198" t="s">
+        <v>133</v>
+      </c>
+      <c r="C198" t="s">
         <v>219</v>
       </c>
-      <c r="B198" t="s">
-        <v>134</v>
-      </c>
-      <c r="C198" t="s">
-        <v>220</v>
-      </c>
       <c r="D198" t="s">
         <v>11</v>
       </c>
       <c r="E198" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F198" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G198" t="s">
         <v>19</v>
@@ -6026,7 +6005,7 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D199" t="s">
         <v>11</v>
@@ -6037,22 +6016,22 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>220</v>
+      </c>
+      <c r="B200" t="s">
+        <v>133</v>
+      </c>
+      <c r="C200" t="s">
         <v>221</v>
       </c>
-      <c r="B200" t="s">
-        <v>134</v>
-      </c>
-      <c r="C200" t="s">
-        <v>222</v>
-      </c>
       <c r="D200" t="s">
         <v>11</v>
       </c>
       <c r="E200" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F200" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G200" t="s">
         <v>19</v>
@@ -6063,7 +6042,7 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D201" t="s">
         <v>11</v>
@@ -6074,22 +6053,22 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>222</v>
+      </c>
+      <c r="B202" t="s">
+        <v>133</v>
+      </c>
+      <c r="C202" t="s">
         <v>223</v>
       </c>
-      <c r="B202" t="s">
-        <v>134</v>
-      </c>
-      <c r="C202" t="s">
-        <v>224</v>
-      </c>
       <c r="D202" t="s">
         <v>11</v>
       </c>
       <c r="E202" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F202" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G202" t="s">
         <v>19</v>
@@ -6100,7 +6079,7 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D203" t="s">
         <v>11</v>
@@ -6111,22 +6090,22 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>224</v>
+      </c>
+      <c r="B204" t="s">
+        <v>133</v>
+      </c>
+      <c r="C204" t="s">
         <v>225</v>
       </c>
-      <c r="B204" t="s">
-        <v>134</v>
-      </c>
-      <c r="C204" t="s">
-        <v>226</v>
-      </c>
       <c r="D204" t="s">
         <v>11</v>
       </c>
       <c r="E204" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F204" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G204" t="s">
         <v>19</v>
@@ -6137,7 +6116,7 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D205" t="s">
         <v>11</v>
@@ -6148,22 +6127,22 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>226</v>
+      </c>
+      <c r="B206" t="s">
+        <v>133</v>
+      </c>
+      <c r="C206" t="s">
         <v>227</v>
       </c>
-      <c r="B206" t="s">
-        <v>134</v>
-      </c>
-      <c r="C206" t="s">
-        <v>228</v>
-      </c>
       <c r="D206" t="s">
         <v>11</v>
       </c>
       <c r="E206" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F206" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G206" t="s">
         <v>19</v>
@@ -6174,7 +6153,7 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D207" t="s">
         <v>11</v>
@@ -6185,22 +6164,22 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>228</v>
+      </c>
+      <c r="B208" t="s">
+        <v>133</v>
+      </c>
+      <c r="C208" t="s">
         <v>229</v>
       </c>
-      <c r="B208" t="s">
-        <v>134</v>
-      </c>
-      <c r="C208" t="s">
-        <v>230</v>
-      </c>
       <c r="D208" t="s">
         <v>11</v>
       </c>
       <c r="E208" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F208" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G208" t="s">
         <v>19</v>
@@ -6211,7 +6190,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D209" t="s">
         <v>11</v>
@@ -6222,22 +6201,22 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>230</v>
+      </c>
+      <c r="B210" t="s">
+        <v>133</v>
+      </c>
+      <c r="C210" t="s">
         <v>231</v>
       </c>
-      <c r="B210" t="s">
-        <v>134</v>
-      </c>
-      <c r="C210" t="s">
-        <v>232</v>
-      </c>
       <c r="D210" t="s">
         <v>11</v>
       </c>
       <c r="E210" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F210" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G210" t="s">
         <v>19</v>
@@ -6248,7 +6227,7 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D211" t="s">
         <v>11</v>
@@ -6259,22 +6238,22 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>232</v>
+      </c>
+      <c r="B212" t="s">
+        <v>133</v>
+      </c>
+      <c r="C212" t="s">
         <v>233</v>
       </c>
-      <c r="B212" t="s">
-        <v>134</v>
-      </c>
-      <c r="C212" t="s">
-        <v>234</v>
-      </c>
       <c r="D212" t="s">
         <v>11</v>
       </c>
       <c r="E212" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F212" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G212" t="s">
         <v>19</v>
@@ -6285,7 +6264,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D213" t="s">
         <v>11</v>
@@ -6296,22 +6275,22 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>234</v>
+      </c>
+      <c r="B214" t="s">
+        <v>133</v>
+      </c>
+      <c r="C214" t="s">
         <v>235</v>
       </c>
-      <c r="B214" t="s">
-        <v>134</v>
-      </c>
-      <c r="C214" t="s">
-        <v>236</v>
-      </c>
       <c r="D214" t="s">
         <v>11</v>
       </c>
       <c r="E214" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F214" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G214" t="s">
         <v>19</v>
@@ -6322,7 +6301,7 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D215" t="s">
         <v>11</v>
@@ -6333,22 +6312,22 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>236</v>
+      </c>
+      <c r="B216" t="s">
+        <v>133</v>
+      </c>
+      <c r="C216" t="s">
         <v>237</v>
       </c>
-      <c r="B216" t="s">
-        <v>134</v>
-      </c>
-      <c r="C216" t="s">
-        <v>238</v>
-      </c>
       <c r="D216" t="s">
         <v>11</v>
       </c>
       <c r="E216" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F216" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G216" t="s">
         <v>19</v>
@@ -6359,7 +6338,7 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D217" t="s">
         <v>11</v>
@@ -6370,22 +6349,22 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>238</v>
+      </c>
+      <c r="B218" t="s">
+        <v>133</v>
+      </c>
+      <c r="C218" t="s">
         <v>239</v>
       </c>
-      <c r="B218" t="s">
-        <v>134</v>
-      </c>
-      <c r="C218" t="s">
-        <v>240</v>
-      </c>
       <c r="D218" t="s">
         <v>11</v>
       </c>
       <c r="E218" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F218" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G218" t="s">
         <v>19</v>
@@ -6396,7 +6375,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D219" t="s">
         <v>11</v>
@@ -6407,22 +6386,22 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>240</v>
+      </c>
+      <c r="B220" t="s">
+        <v>133</v>
+      </c>
+      <c r="C220" t="s">
         <v>241</v>
       </c>
-      <c r="B220" t="s">
-        <v>134</v>
-      </c>
-      <c r="C220" t="s">
-        <v>242</v>
-      </c>
       <c r="D220" t="s">
         <v>11</v>
       </c>
       <c r="E220" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F220" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G220" t="s">
         <v>19</v>
@@ -6433,7 +6412,7 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D221" t="s">
         <v>11</v>
@@ -6444,22 +6423,22 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B222" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C222" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D222" t="s">
         <v>11</v>
       </c>
       <c r="E222" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F222" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G222" t="s">
         <v>19</v>
@@ -6470,7 +6449,7 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D223" t="s">
         <v>11</v>
@@ -6481,22 +6460,22 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>243</v>
+      </c>
+      <c r="B224" t="s">
+        <v>133</v>
+      </c>
+      <c r="C224" t="s">
         <v>244</v>
       </c>
-      <c r="B224" t="s">
-        <v>134</v>
-      </c>
-      <c r="C224" t="s">
-        <v>245</v>
-      </c>
       <c r="D224" t="s">
         <v>11</v>
       </c>
       <c r="E224" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F224" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G224" t="s">
         <v>19</v>
@@ -6507,7 +6486,7 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D225" t="s">
         <v>11</v>
@@ -6518,22 +6497,22 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B226" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C226" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D226" t="s">
         <v>11</v>
       </c>
       <c r="E226" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F226" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G226" t="s">
         <v>19</v>
@@ -6544,7 +6523,7 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D227" t="s">
         <v>11</v>
@@ -6555,22 +6534,22 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>246</v>
+      </c>
+      <c r="B228" t="s">
+        <v>133</v>
+      </c>
+      <c r="C228" t="s">
         <v>247</v>
       </c>
-      <c r="B228" t="s">
-        <v>134</v>
-      </c>
-      <c r="C228" t="s">
-        <v>248</v>
-      </c>
       <c r="D228" t="s">
         <v>11</v>
       </c>
       <c r="E228" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F228" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G228" t="s">
         <v>19</v>
@@ -6581,7 +6560,7 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D229" t="s">
         <v>11</v>
@@ -6592,22 +6571,22 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>248</v>
+      </c>
+      <c r="B230" t="s">
+        <v>133</v>
+      </c>
+      <c r="C230" t="s">
         <v>249</v>
       </c>
-      <c r="B230" t="s">
-        <v>134</v>
-      </c>
-      <c r="C230" t="s">
-        <v>250</v>
-      </c>
       <c r="D230" t="s">
         <v>11</v>
       </c>
       <c r="E230" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F230" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G230" t="s">
         <v>19</v>
@@ -6618,7 +6597,7 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D231" t="s">
         <v>11</v>
@@ -6629,22 +6608,22 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>250</v>
+      </c>
+      <c r="B232" t="s">
+        <v>133</v>
+      </c>
+      <c r="C232" t="s">
         <v>251</v>
       </c>
-      <c r="B232" t="s">
-        <v>134</v>
-      </c>
-      <c r="C232" t="s">
-        <v>252</v>
-      </c>
       <c r="D232" t="s">
         <v>11</v>
       </c>
       <c r="E232" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F232" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G232" t="s">
         <v>19</v>
@@ -6655,7 +6634,7 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D233" t="s">
         <v>11</v>
@@ -6666,22 +6645,22 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
+        <v>252</v>
+      </c>
+      <c r="B234" t="s">
+        <v>133</v>
+      </c>
+      <c r="C234" t="s">
         <v>253</v>
       </c>
-      <c r="B234" t="s">
-        <v>134</v>
-      </c>
-      <c r="C234" t="s">
-        <v>254</v>
-      </c>
       <c r="D234" t="s">
         <v>11</v>
       </c>
       <c r="E234" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F234" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G234" t="s">
         <v>19</v>
@@ -6692,7 +6671,7 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D235" t="s">
         <v>11</v>
@@ -6703,22 +6682,22 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
+        <v>254</v>
+      </c>
+      <c r="B236" t="s">
+        <v>133</v>
+      </c>
+      <c r="C236" t="s">
         <v>255</v>
       </c>
-      <c r="B236" t="s">
-        <v>134</v>
-      </c>
-      <c r="C236" t="s">
-        <v>256</v>
-      </c>
       <c r="D236" t="s">
         <v>11</v>
       </c>
       <c r="E236" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F236" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G236" t="s">
         <v>19</v>
@@ -6729,7 +6708,7 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D237" t="s">
         <v>11</v>
@@ -6740,22 +6719,22 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
+        <v>256</v>
+      </c>
+      <c r="B238" t="s">
+        <v>133</v>
+      </c>
+      <c r="C238" t="s">
         <v>257</v>
       </c>
-      <c r="B238" t="s">
-        <v>134</v>
-      </c>
-      <c r="C238" t="s">
-        <v>258</v>
-      </c>
       <c r="D238" t="s">
         <v>11</v>
       </c>
       <c r="E238" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F238" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G238" t="s">
         <v>19</v>
@@ -6766,7 +6745,7 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D239" t="s">
         <v>11</v>
@@ -6777,22 +6756,22 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>258</v>
+      </c>
+      <c r="B240" t="s">
+        <v>133</v>
+      </c>
+      <c r="C240" t="s">
         <v>259</v>
       </c>
-      <c r="B240" t="s">
-        <v>134</v>
-      </c>
-      <c r="C240" t="s">
-        <v>260</v>
-      </c>
       <c r="D240" t="s">
         <v>11</v>
       </c>
       <c r="E240" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F240" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G240" t="s">
         <v>19</v>
@@ -6803,7 +6782,7 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D241" t="s">
         <v>11</v>
@@ -6814,22 +6793,22 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>260</v>
+      </c>
+      <c r="B242" t="s">
+        <v>133</v>
+      </c>
+      <c r="C242" t="s">
         <v>261</v>
       </c>
-      <c r="B242" t="s">
-        <v>134</v>
-      </c>
-      <c r="C242" t="s">
-        <v>262</v>
-      </c>
       <c r="D242" t="s">
         <v>11</v>
       </c>
       <c r="E242" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F242" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G242" t="s">
         <v>19</v>
@@ -6840,7 +6819,7 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D243" t="s">
         <v>11</v>
@@ -6851,22 +6830,22 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>262</v>
+      </c>
+      <c r="B244" t="s">
+        <v>133</v>
+      </c>
+      <c r="C244" t="s">
         <v>263</v>
       </c>
-      <c r="B244" t="s">
-        <v>134</v>
-      </c>
-      <c r="C244" t="s">
-        <v>264</v>
-      </c>
       <c r="D244" t="s">
         <v>11</v>
       </c>
       <c r="E244" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F244" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G244" t="s">
         <v>19</v>
@@ -6877,7 +6856,7 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D245" t="s">
         <v>11</v>
@@ -6888,48 +6867,48 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>264</v>
+      </c>
+      <c r="B246" t="s">
+        <v>133</v>
+      </c>
+      <c r="C246" t="s">
         <v>265</v>
       </c>
-      <c r="B246" t="s">
-        <v>134</v>
-      </c>
-      <c r="C246" t="s">
-        <v>266</v>
-      </c>
       <c r="D246" t="s">
         <v>11</v>
       </c>
       <c r="E246" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F246" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G246" t="s">
         <v>19</v>
       </c>
       <c r="H246" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B247" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C247" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D247" t="s">
         <v>11</v>
       </c>
       <c r="E247" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F247" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G247" t="s">
         <v>19</v>
@@ -6940,22 +6919,22 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>266</v>
+      </c>
+      <c r="B248" t="s">
+        <v>133</v>
+      </c>
+      <c r="C248" t="s">
         <v>267</v>
       </c>
-      <c r="B248" t="s">
-        <v>134</v>
-      </c>
-      <c r="C248" t="s">
-        <v>268</v>
-      </c>
       <c r="D248" t="s">
         <v>11</v>
       </c>
       <c r="E248" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F248" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G248" t="s">
         <v>19</v>
@@ -6966,7 +6945,7 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D249" t="s">
         <v>11</v>
@@ -6977,22 +6956,22 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
+        <v>268</v>
+      </c>
+      <c r="B250" t="s">
+        <v>133</v>
+      </c>
+      <c r="C250" t="s">
         <v>269</v>
-      </c>
-      <c r="B250" t="s">
-        <v>134</v>
-      </c>
-      <c r="C250" t="s">
-        <v>270</v>
       </c>
       <c r="D250" t="s">
         <v>105</v>
       </c>
       <c r="E250" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F250" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G250" t="s">
         <v>19</v>
@@ -7003,7 +6982,7 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D251" t="s">
         <v>11</v>
@@ -7014,22 +6993,22 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B252" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C252" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D252" t="s">
         <v>11</v>
       </c>
       <c r="E252" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F252" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G252" t="s">
         <v>19</v>
@@ -7040,7 +7019,7 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D253" t="s">
         <v>11</v>
@@ -7051,22 +7030,22 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
+        <v>271</v>
+      </c>
+      <c r="B254" t="s">
+        <v>133</v>
+      </c>
+      <c r="C254" t="s">
         <v>272</v>
       </c>
-      <c r="B254" t="s">
-        <v>134</v>
-      </c>
-      <c r="C254" t="s">
-        <v>273</v>
-      </c>
       <c r="D254" t="s">
         <v>11</v>
       </c>
       <c r="E254" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F254" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G254" t="s">
         <v>19</v>
@@ -7077,7 +7056,7 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D255" t="s">
         <v>11</v>
@@ -7088,22 +7067,22 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
+        <v>273</v>
+      </c>
+      <c r="B256" t="s">
+        <v>133</v>
+      </c>
+      <c r="C256" t="s">
         <v>274</v>
       </c>
-      <c r="B256" t="s">
-        <v>134</v>
-      </c>
-      <c r="C256" t="s">
-        <v>275</v>
-      </c>
       <c r="D256" t="s">
         <v>11</v>
       </c>
       <c r="E256" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F256" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G256" t="s">
         <v>19</v>
@@ -7114,7 +7093,7 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D257" t="s">
         <v>11</v>
@@ -7125,22 +7104,22 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
+        <v>275</v>
+      </c>
+      <c r="B258" t="s">
+        <v>133</v>
+      </c>
+      <c r="C258" t="s">
         <v>276</v>
       </c>
-      <c r="B258" t="s">
-        <v>134</v>
-      </c>
-      <c r="C258" t="s">
-        <v>277</v>
-      </c>
       <c r="D258" t="s">
         <v>11</v>
       </c>
       <c r="E258" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F258" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G258" t="s">
         <v>19</v>
@@ -7151,7 +7130,7 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D259" t="s">
         <v>11</v>
@@ -7162,22 +7141,22 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>277</v>
+      </c>
+      <c r="B260" t="s">
+        <v>133</v>
+      </c>
+      <c r="C260" t="s">
         <v>278</v>
       </c>
-      <c r="B260" t="s">
-        <v>134</v>
-      </c>
-      <c r="C260" t="s">
-        <v>279</v>
-      </c>
       <c r="D260" t="s">
         <v>11</v>
       </c>
       <c r="E260" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F260" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G260" t="s">
         <v>19</v>
@@ -7188,7 +7167,7 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D261" t="s">
         <v>11</v>
@@ -7199,22 +7178,22 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>279</v>
+      </c>
+      <c r="B262" t="s">
+        <v>133</v>
+      </c>
+      <c r="C262" t="s">
         <v>280</v>
       </c>
-      <c r="B262" t="s">
-        <v>134</v>
-      </c>
-      <c r="C262" t="s">
-        <v>281</v>
-      </c>
       <c r="D262" t="s">
         <v>11</v>
       </c>
       <c r="E262" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F262" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G262" t="s">
         <v>19</v>
@@ -7225,7 +7204,7 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D263" t="s">
         <v>11</v>
@@ -7236,22 +7215,22 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>281</v>
+      </c>
+      <c r="B264" t="s">
+        <v>133</v>
+      </c>
+      <c r="C264" t="s">
         <v>282</v>
       </c>
-      <c r="B264" t="s">
-        <v>134</v>
-      </c>
-      <c r="C264" t="s">
-        <v>283</v>
-      </c>
       <c r="D264" t="s">
         <v>11</v>
       </c>
       <c r="E264" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F264" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G264" t="s">
         <v>19</v>
@@ -7262,7 +7241,7 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D265" t="s">
         <v>11</v>
@@ -7273,22 +7252,22 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>283</v>
+      </c>
+      <c r="B266" t="s">
+        <v>133</v>
+      </c>
+      <c r="C266" t="s">
         <v>284</v>
       </c>
-      <c r="B266" t="s">
-        <v>134</v>
-      </c>
-      <c r="C266" t="s">
-        <v>285</v>
-      </c>
       <c r="D266" t="s">
         <v>11</v>
       </c>
       <c r="E266" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F266" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G266" t="s">
         <v>19</v>
@@ -7299,7 +7278,7 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D267" t="s">
         <v>11</v>
@@ -7310,22 +7289,22 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>285</v>
+      </c>
+      <c r="B268" t="s">
+        <v>133</v>
+      </c>
+      <c r="C268" t="s">
         <v>286</v>
       </c>
-      <c r="B268" t="s">
-        <v>134</v>
-      </c>
-      <c r="C268" t="s">
-        <v>287</v>
-      </c>
       <c r="D268" t="s">
         <v>11</v>
       </c>
       <c r="E268" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F268" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G268" t="s">
         <v>19</v>
@@ -7336,7 +7315,7 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D269" t="s">
         <v>11</v>
@@ -7347,22 +7326,22 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
+        <v>287</v>
+      </c>
+      <c r="B270" t="s">
+        <v>133</v>
+      </c>
+      <c r="C270" t="s">
         <v>288</v>
       </c>
-      <c r="B270" t="s">
-        <v>134</v>
-      </c>
-      <c r="C270" t="s">
-        <v>289</v>
-      </c>
       <c r="D270" t="s">
         <v>11</v>
       </c>
       <c r="E270" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F270" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G270" t="s">
         <v>19</v>
@@ -7373,7 +7352,7 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D271" t="s">
         <v>11</v>
@@ -7384,22 +7363,22 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>289</v>
+      </c>
+      <c r="B272" t="s">
+        <v>133</v>
+      </c>
+      <c r="C272" t="s">
         <v>290</v>
       </c>
-      <c r="B272" t="s">
-        <v>134</v>
-      </c>
-      <c r="C272" t="s">
-        <v>291</v>
-      </c>
       <c r="D272" t="s">
         <v>11</v>
       </c>
       <c r="E272" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F272" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G272" t="s">
         <v>19</v>
@@ -7410,7 +7389,7 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D273" t="s">
         <v>11</v>
@@ -7421,22 +7400,22 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
+        <v>291</v>
+      </c>
+      <c r="B274" t="s">
+        <v>133</v>
+      </c>
+      <c r="C274" t="s">
         <v>292</v>
       </c>
-      <c r="B274" t="s">
-        <v>134</v>
-      </c>
-      <c r="C274" t="s">
-        <v>293</v>
-      </c>
       <c r="D274" t="s">
         <v>11</v>
       </c>
       <c r="E274" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F274" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G274" t="s">
         <v>19</v>
@@ -7447,7 +7426,7 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D275" t="s">
         <v>11</v>
@@ -7458,22 +7437,22 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
+        <v>293</v>
+      </c>
+      <c r="B276" t="s">
+        <v>133</v>
+      </c>
+      <c r="C276" t="s">
         <v>294</v>
       </c>
-      <c r="B276" t="s">
-        <v>134</v>
-      </c>
-      <c r="C276" t="s">
-        <v>295</v>
-      </c>
       <c r="D276" t="s">
         <v>11</v>
       </c>
       <c r="E276" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F276" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G276" t="s">
         <v>19</v>
@@ -7484,7 +7463,7 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D277" t="s">
         <v>11</v>
@@ -7495,22 +7474,22 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
+        <v>295</v>
+      </c>
+      <c r="B278" t="s">
+        <v>133</v>
+      </c>
+      <c r="C278" t="s">
         <v>296</v>
       </c>
-      <c r="B278" t="s">
-        <v>134</v>
-      </c>
-      <c r="C278" t="s">
-        <v>297</v>
-      </c>
       <c r="D278" t="s">
         <v>11</v>
       </c>
       <c r="E278" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F278" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G278" t="s">
         <v>19</v>
@@ -7521,7 +7500,7 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D279" t="s">
         <v>11</v>
@@ -7532,22 +7511,22 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>297</v>
+      </c>
+      <c r="B280" t="s">
+        <v>133</v>
+      </c>
+      <c r="C280" t="s">
         <v>298</v>
       </c>
-      <c r="B280" t="s">
-        <v>134</v>
-      </c>
-      <c r="C280" t="s">
-        <v>299</v>
-      </c>
       <c r="D280" t="s">
         <v>11</v>
       </c>
       <c r="E280" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F280" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G280" t="s">
         <v>19</v>
@@ -7558,7 +7537,7 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D281" t="s">
         <v>11</v>
@@ -7569,48 +7548,48 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>299</v>
+      </c>
+      <c r="B282" t="s">
+        <v>133</v>
+      </c>
+      <c r="C282" t="s">
         <v>300</v>
       </c>
-      <c r="B282" t="s">
-        <v>134</v>
-      </c>
-      <c r="C282" t="s">
-        <v>301</v>
-      </c>
       <c r="D282" t="s">
         <v>11</v>
       </c>
       <c r="E282" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F282" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G282" t="s">
         <v>19</v>
       </c>
       <c r="H282" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B283" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C283" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D283" t="s">
         <v>11</v>
       </c>
       <c r="E283" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F283" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G283" t="s">
         <v>19</v>
@@ -7621,48 +7600,48 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
+        <v>301</v>
+      </c>
+      <c r="B284" t="s">
+        <v>133</v>
+      </c>
+      <c r="C284" t="s">
         <v>302</v>
       </c>
-      <c r="B284" t="s">
-        <v>134</v>
-      </c>
-      <c r="C284" t="s">
-        <v>303</v>
-      </c>
       <c r="D284" t="s">
         <v>11</v>
       </c>
       <c r="E284" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F284" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G284" t="s">
         <v>19</v>
       </c>
       <c r="H284" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B285" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C285" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D285" t="s">
         <v>11</v>
       </c>
       <c r="E285" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F285" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G285" t="s">
         <v>19</v>
@@ -7673,22 +7652,22 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>303</v>
+      </c>
+      <c r="B286" t="s">
+        <v>133</v>
+      </c>
+      <c r="C286" t="s">
         <v>304</v>
       </c>
-      <c r="B286" t="s">
-        <v>134</v>
-      </c>
-      <c r="C286" t="s">
-        <v>305</v>
-      </c>
       <c r="D286" t="s">
         <v>11</v>
       </c>
       <c r="E286" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F286" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G286" t="s">
         <v>19</v>
@@ -7699,7 +7678,7 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D287" t="s">
         <v>11</v>
@@ -7710,22 +7689,22 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
+        <v>305</v>
+      </c>
+      <c r="B288" t="s">
+        <v>133</v>
+      </c>
+      <c r="C288" t="s">
         <v>306</v>
       </c>
-      <c r="B288" t="s">
-        <v>134</v>
-      </c>
-      <c r="C288" t="s">
-        <v>307</v>
-      </c>
       <c r="D288" t="s">
         <v>11</v>
       </c>
       <c r="E288" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F288" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G288" t="s">
         <v>19</v>
@@ -7736,7 +7715,7 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D289" t="s">
         <v>11</v>
@@ -7747,39 +7726,36 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
+        <v>307</v>
+      </c>
+      <c r="B290" t="s">
         <v>308</v>
       </c>
-      <c r="B290" t="s">
+      <c r="C290" t="s">
         <v>309</v>
       </c>
-      <c r="C290" t="s">
-        <v>11</v>
-      </c>
       <c r="D290" t="s">
         <v>11</v>
       </c>
       <c r="E290" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F290" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G290" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="H290" t="s">
-        <v>312</v>
+        <v>13</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>327</v>
-      </c>
-      <c r="C291" t="s">
-        <v>11</v>
-      </c>
-      <c r="D291" t="s">
-        <v>11</v>
+        <v>320</v>
+      </c>
+      <c r="E291" t="s">
+        <v>308</v>
       </c>
       <c r="H291" t="s">
         <v>11</v>
@@ -7787,39 +7763,33 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B292" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C292" t="s">
-        <v>11</v>
+        <v>310</v>
       </c>
       <c r="D292" t="s">
         <v>11</v>
       </c>
       <c r="E292" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F292" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G292" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="H292" t="s">
-        <v>312</v>
+        <v>13</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>327</v>
-      </c>
-      <c r="C293" t="s">
-        <v>11</v>
-      </c>
-      <c r="D293" t="s">
-        <v>11</v>
+        <v>320</v>
       </c>
       <c r="H293" t="s">
         <v>11</v>
@@ -7827,36 +7797,51 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
+        <v>313</v>
+      </c>
+      <c r="B294" t="s">
+        <v>311</v>
+      </c>
+      <c r="C294" t="s">
         <v>314</v>
       </c>
-      <c r="B294" t="s">
-        <v>315</v>
-      </c>
-      <c r="C294" t="s">
-        <v>316</v>
-      </c>
       <c r="D294" t="s">
         <v>11</v>
       </c>
       <c r="E294" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F294" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G294" t="s">
-        <v>24</v>
+        <v>312</v>
       </c>
       <c r="H294" t="s">
-        <v>13</v>
+        <v>338</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>327</v>
+        <v>313</v>
+      </c>
+      <c r="B295" t="s">
+        <v>311</v>
+      </c>
+      <c r="C295" t="s">
+        <v>349</v>
+      </c>
+      <c r="D295" t="s">
+        <v>11</v>
       </c>
       <c r="E295" t="s">
-        <v>315</v>
+        <v>311</v>
+      </c>
+      <c r="F295" t="s">
+        <v>311</v>
+      </c>
+      <c r="G295" t="s">
+        <v>312</v>
       </c>
       <c r="H295" t="s">
         <v>11</v>
@@ -7864,33 +7849,51 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B296" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C296" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D296" t="s">
         <v>11</v>
       </c>
       <c r="E296" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F296" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G296" t="s">
-        <v>24</v>
+        <v>312</v>
       </c>
       <c r="H296" t="s">
-        <v>13</v>
+        <v>338</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>327</v>
+        <v>315</v>
+      </c>
+      <c r="B297" t="s">
+        <v>311</v>
+      </c>
+      <c r="C297" t="s">
+        <v>350</v>
+      </c>
+      <c r="D297" t="s">
+        <v>11</v>
+      </c>
+      <c r="E297" t="s">
+        <v>311</v>
+      </c>
+      <c r="F297" t="s">
+        <v>311</v>
+      </c>
+      <c r="G297" t="s">
+        <v>312</v>
       </c>
       <c r="H297" t="s">
         <v>11</v>
@@ -7898,157 +7901,53 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B298" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C298" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D298" t="s">
         <v>11</v>
       </c>
       <c r="E298" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="F298" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="G298" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="H298" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B299" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C299" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D299" t="s">
         <v>11</v>
       </c>
       <c r="E299" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="F299" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="G299" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="H299" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
-        <v>322</v>
-      </c>
-      <c r="B300" t="s">
-        <v>318</v>
-      </c>
-      <c r="C300" t="s">
-        <v>323</v>
-      </c>
-      <c r="D300" t="s">
-        <v>11</v>
-      </c>
-      <c r="E300" t="s">
-        <v>318</v>
-      </c>
-      <c r="F300" t="s">
-        <v>318</v>
-      </c>
-      <c r="G300" t="s">
-        <v>319</v>
-      </c>
-      <c r="H300" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>322</v>
-      </c>
-      <c r="B301" t="s">
-        <v>318</v>
-      </c>
-      <c r="C301" t="s">
-        <v>357</v>
-      </c>
-      <c r="D301" t="s">
-        <v>11</v>
-      </c>
-      <c r="E301" t="s">
-        <v>318</v>
-      </c>
-      <c r="F301" t="s">
-        <v>318</v>
-      </c>
-      <c r="G301" t="s">
-        <v>319</v>
-      </c>
-      <c r="H301" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>322</v>
-      </c>
-      <c r="B302" t="s">
-        <v>318</v>
-      </c>
-      <c r="C302" t="s">
-        <v>324</v>
-      </c>
-      <c r="D302" t="s">
-        <v>11</v>
-      </c>
-      <c r="E302" t="s">
-        <v>318</v>
-      </c>
-      <c r="F302" t="s">
-        <v>318</v>
-      </c>
-      <c r="G302" t="s">
-        <v>319</v>
-      </c>
-      <c r="H302" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>322</v>
-      </c>
-      <c r="B303" t="s">
-        <v>318</v>
-      </c>
-      <c r="C303" t="s">
-        <v>358</v>
-      </c>
-      <c r="D303" t="s">
-        <v>11</v>
-      </c>
-      <c r="E303" t="s">
-        <v>318</v>
-      </c>
-      <c r="F303" t="s">
-        <v>318</v>
-      </c>
-      <c r="G303" t="s">
-        <v>319</v>
-      </c>
-      <c r="H303" t="s">
         <v>11</v>
       </c>
     </row>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB132F56-C59C-46DF-A0EA-DBB39C453F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43077977-735F-4DB7-AE0F-5A9017EB215F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="348">
   <si>
     <t>Kod</t>
   </si>
@@ -83,12 +83,6 @@
     <t>Krótka</t>
   </si>
   <si>
-    <t>Chojnice</t>
-  </si>
-  <si>
-    <t>chojnicki</t>
-  </si>
-  <si>
     <t>pomorskie</t>
   </si>
   <si>
@@ -156,18 +150,6 @@
   </si>
   <si>
     <t>Róż Al.</t>
-  </si>
-  <si>
-    <t>89-608</t>
-  </si>
-  <si>
-    <t>Kamionka</t>
-  </si>
-  <si>
-    <t>Brak miasta: Kamionka w gminie Chojnice</t>
-  </si>
-  <si>
-    <t>89-620</t>
   </si>
   <si>
     <t>62-500</t>
@@ -1973,7 +1955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H299"/>
+  <dimension ref="A1:H295"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -2035,7 +2017,7 @@
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2046,7 +2028,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -2087,12 +2069,12 @@
         <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -2103,51 +2085,51 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
       <c r="H6" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
-        <v>322</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>23</v>
-      </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -2155,51 +2137,51 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
         <v>26</v>
       </c>
-      <c r="C8" t="s">
+      <c r="G8" t="s">
         <v>27</v>
       </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" t="s">
-        <v>29</v>
-      </c>
       <c r="H8" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
         <v>26</v>
       </c>
-      <c r="C9" t="s">
-        <v>324</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" t="s">
-        <v>28</v>
-      </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -2207,51 +2189,51 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" t="s">
-        <v>325</v>
-      </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" t="s">
-        <v>28</v>
-      </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
@@ -2259,51 +2241,51 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
@@ -2311,25 +2293,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
         <v>34</v>
       </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H14" t="s">
         <v>13</v>
@@ -2337,7 +2319,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -2348,51 +2330,51 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -2400,39 +2382,51 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
         <v>41</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" t="s">
         <v>42</v>
       </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" t="s">
-        <v>18</v>
-      </c>
       <c r="H18" t="s">
-        <v>43</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>320</v>
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>323</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" t="s">
+        <v>42</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
@@ -2440,39 +2434,51 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
         <v>44</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" t="s">
         <v>42</v>
       </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" t="s">
-        <v>18</v>
-      </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>320</v>
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>325</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" t="s">
+        <v>42</v>
       </c>
       <c r="H21" t="s">
         <v>11</v>
@@ -2480,51 +2486,51 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
         <v>45</v>
       </c>
-      <c r="B22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" t="s">
-        <v>47</v>
-      </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F22" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H22" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G23" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
@@ -2532,51 +2538,51 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
         <v>46</v>
       </c>
-      <c r="C24" t="s">
-        <v>50</v>
-      </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H24" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
@@ -2584,51 +2590,51 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G26" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H26" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G27" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
@@ -2636,51 +2642,36 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G28" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H28" t="s">
-        <v>323</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>46</v>
-      </c>
-      <c r="F29" t="s">
-        <v>46</v>
-      </c>
-      <c r="G29" t="s">
-        <v>48</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
@@ -2688,51 +2679,36 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G30" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H30" t="s">
-        <v>323</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
-      </c>
-      <c r="E31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
-      </c>
-      <c r="G31" t="s">
-        <v>48</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
@@ -2740,25 +2716,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F32" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H32" t="s">
         <v>13</v>
@@ -2766,7 +2742,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -2777,13 +2753,13 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
@@ -2792,21 +2768,36 @@
         <v>54</v>
       </c>
       <c r="F34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G34" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="H34" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>320</v>
+        <v>53</v>
+      </c>
+      <c r="B35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" t="s">
+        <v>329</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" t="s">
+        <v>56</v>
+      </c>
+      <c r="G35" t="s">
+        <v>57</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -2814,7 +2805,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
         <v>54</v>
@@ -2829,21 +2820,36 @@
         <v>54</v>
       </c>
       <c r="F36" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G36" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="H36" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>320</v>
+        <v>53</v>
+      </c>
+      <c r="B37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" t="s">
+        <v>330</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" t="s">
+        <v>56</v>
+      </c>
+      <c r="G37" t="s">
+        <v>57</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -2866,36 +2872,24 @@
         <v>60</v>
       </c>
       <c r="F38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G38" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H38" t="s">
-        <v>323</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" t="s">
+        <v>314</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" t="s">
         <v>60</v>
-      </c>
-      <c r="C39" t="s">
-        <v>335</v>
-      </c>
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" t="s">
-        <v>60</v>
-      </c>
-      <c r="F39" t="s">
-        <v>62</v>
-      </c>
-      <c r="G39" t="s">
-        <v>63</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
@@ -2903,13 +2897,13 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -2918,24 +2912,24 @@
         <v>60</v>
       </c>
       <c r="F40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G40" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H40" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B41" t="s">
         <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -2944,10 +2938,10 @@
         <v>60</v>
       </c>
       <c r="F41" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G41" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
@@ -2955,25 +2949,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" t="s">
         <v>65</v>
       </c>
-      <c r="B42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" t="s">
-        <v>67</v>
-      </c>
       <c r="D42" t="s">
         <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F42" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G42" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
@@ -2981,13 +2975,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
-      </c>
-      <c r="F43" t="s">
-        <v>66</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
@@ -2995,51 +2986,33 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" t="s">
         <v>66</v>
       </c>
-      <c r="C44" t="s">
-        <v>69</v>
-      </c>
       <c r="D44" t="s">
         <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F44" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G44" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H44" t="s">
-        <v>338</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>68</v>
-      </c>
-      <c r="B45" t="s">
-        <v>66</v>
-      </c>
-      <c r="C45" t="s">
-        <v>337</v>
-      </c>
-      <c r="D45" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" t="s">
-        <v>66</v>
-      </c>
-      <c r="F45" t="s">
-        <v>66</v>
-      </c>
-      <c r="G45" t="s">
-        <v>63</v>
+        <v>314</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
@@ -3047,36 +3020,51 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>68</v>
+      </c>
+      <c r="F46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G46" t="s">
         <v>70</v>
       </c>
-      <c r="B46" t="s">
-        <v>66</v>
-      </c>
-      <c r="C46" t="s">
-        <v>71</v>
-      </c>
-      <c r="D46" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" t="s">
-        <v>66</v>
-      </c>
-      <c r="F46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G46" t="s">
-        <v>63</v>
-      </c>
       <c r="H46" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>320</v>
+        <v>67</v>
+      </c>
+      <c r="B47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" t="s">
+        <v>333</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>68</v>
+      </c>
+      <c r="F47" t="s">
+        <v>68</v>
+      </c>
+      <c r="G47" t="s">
+        <v>70</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
@@ -3084,10 +3072,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
         <v>72</v>
@@ -3096,13 +3084,13 @@
         <v>11</v>
       </c>
       <c r="E48" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F48" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G48" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H48" t="s">
         <v>13</v>
@@ -3110,7 +3098,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>320</v>
+        <v>314</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -3121,48 +3112,33 @@
         <v>73</v>
       </c>
       <c r="B50" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" t="s">
         <v>74</v>
       </c>
-      <c r="C50" t="s">
-        <v>75</v>
-      </c>
       <c r="D50" t="s">
         <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F50" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G50" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H50" t="s">
-        <v>323</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>73</v>
-      </c>
-      <c r="B51" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
-      </c>
-      <c r="E51" t="s">
-        <v>74</v>
-      </c>
-      <c r="F51" t="s">
-        <v>74</v>
-      </c>
-      <c r="G51" t="s">
-        <v>76</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -3170,25 +3146,25 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F52" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G52" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H52" t="s">
         <v>13</v>
@@ -3196,7 +3172,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -3207,25 +3183,25 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F54" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G54" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H54" t="s">
         <v>13</v>
@@ -3233,7 +3209,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -3244,25 +3220,25 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F56" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G56" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H56" t="s">
         <v>13</v>
@@ -3270,7 +3246,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -3281,25 +3257,25 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
       </c>
       <c r="E58" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F58" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G58" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H58" t="s">
         <v>13</v>
@@ -3307,7 +3283,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -3318,25 +3294,25 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B60" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C60" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F60" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G60" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H60" t="s">
         <v>13</v>
@@ -3344,7 +3320,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -3355,25 +3331,25 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B62" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F62" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G62" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H62" t="s">
         <v>13</v>
@@ -3381,7 +3357,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -3392,25 +3368,25 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F64" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G64" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H64" t="s">
         <v>13</v>
@@ -3418,7 +3394,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
@@ -3429,25 +3405,25 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
       </c>
       <c r="E66" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F66" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G66" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H66" t="s">
         <v>13</v>
@@ -3455,7 +3431,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
@@ -3466,25 +3442,25 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C68" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
       </c>
       <c r="E68" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F68" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G68" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H68" t="s">
         <v>13</v>
@@ -3492,7 +3468,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
@@ -3503,25 +3479,25 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
       </c>
       <c r="E70" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F70" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G70" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H70" t="s">
         <v>13</v>
@@ -3529,7 +3505,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -3540,25 +3516,25 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B72" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C72" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
       </c>
       <c r="E72" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F72" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G72" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H72" t="s">
         <v>13</v>
@@ -3566,7 +3542,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -3577,25 +3553,25 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>97</v>
+      </c>
+      <c r="B74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C74" t="s">
+        <v>98</v>
+      </c>
+      <c r="D74" t="s">
         <v>99</v>
       </c>
-      <c r="B74" t="s">
-        <v>74</v>
-      </c>
-      <c r="C74" t="s">
-        <v>100</v>
-      </c>
-      <c r="D74" t="s">
-        <v>11</v>
-      </c>
       <c r="E74" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F74" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G74" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H74" t="s">
         <v>13</v>
@@ -3603,10 +3579,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>320</v>
-      </c>
-      <c r="D75" t="s">
-        <v>11</v>
+        <v>314</v>
       </c>
       <c r="H75" t="s">
         <v>11</v>
@@ -3614,25 +3587,25 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>100</v>
+      </c>
+      <c r="B76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C76" t="s">
         <v>101</v>
       </c>
-      <c r="B76" t="s">
-        <v>74</v>
-      </c>
-      <c r="C76" t="s">
-        <v>102</v>
-      </c>
       <c r="D76" t="s">
         <v>11</v>
       </c>
       <c r="E76" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F76" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G76" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H76" t="s">
         <v>13</v>
@@ -3640,10 +3613,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>320</v>
-      </c>
-      <c r="D77" t="s">
-        <v>11</v>
+        <v>314</v>
       </c>
       <c r="H77" t="s">
         <v>11</v>
@@ -3651,33 +3621,51 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C78" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D78" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F78" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G78" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H78" t="s">
-        <v>13</v>
+        <v>332</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>320</v>
+        <v>95</v>
+      </c>
+      <c r="B79" t="s">
+        <v>68</v>
+      </c>
+      <c r="C79" t="s">
+        <v>334</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" t="s">
+        <v>68</v>
+      </c>
+      <c r="F79" t="s">
+        <v>68</v>
+      </c>
+      <c r="G79" t="s">
+        <v>70</v>
       </c>
       <c r="H79" t="s">
         <v>11</v>
@@ -3685,25 +3673,25 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B80" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D80" t="s">
         <v>11</v>
       </c>
       <c r="E80" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F80" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G80" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H80" t="s">
         <v>13</v>
@@ -3711,7 +3699,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>320</v>
+        <v>314</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
       </c>
       <c r="H81" t="s">
         <v>11</v>
@@ -3719,51 +3710,33 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B82" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C82" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D82" t="s">
         <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F82" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G82" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H82" t="s">
-        <v>338</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>101</v>
-      </c>
-      <c r="B83" t="s">
-        <v>74</v>
-      </c>
-      <c r="C83" t="s">
-        <v>340</v>
-      </c>
-      <c r="D83" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" t="s">
-        <v>74</v>
-      </c>
-      <c r="F83" t="s">
-        <v>74</v>
-      </c>
-      <c r="G83" t="s">
-        <v>76</v>
+        <v>314</v>
       </c>
       <c r="H83" t="s">
         <v>11</v>
@@ -3771,25 +3744,25 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B84" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C84" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D84" t="s">
         <v>11</v>
       </c>
       <c r="E84" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F84" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G84" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H84" t="s">
         <v>13</v>
@@ -3797,7 +3770,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
@@ -3808,25 +3781,25 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B86" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F86" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G86" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H86" t="s">
         <v>13</v>
@@ -3834,7 +3807,10 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>320</v>
+        <v>314</v>
+      </c>
+      <c r="D87" t="s">
+        <v>11</v>
       </c>
       <c r="H87" t="s">
         <v>11</v>
@@ -3842,25 +3818,25 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>110</v>
+      </c>
+      <c r="B88" t="s">
+        <v>68</v>
+      </c>
+      <c r="C88" t="s">
         <v>111</v>
       </c>
-      <c r="B88" t="s">
-        <v>74</v>
-      </c>
-      <c r="C88" t="s">
-        <v>113</v>
-      </c>
       <c r="D88" t="s">
         <v>11</v>
       </c>
       <c r="E88" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F88" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G88" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H88" t="s">
         <v>13</v>
@@ -3868,7 +3844,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D89" t="s">
         <v>11</v>
@@ -3879,25 +3855,25 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B90" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C90" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D90" t="s">
         <v>11</v>
       </c>
       <c r="E90" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F90" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G90" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H90" t="s">
         <v>13</v>
@@ -3905,7 +3881,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D91" t="s">
         <v>11</v>
@@ -3916,25 +3892,25 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B92" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C92" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D92" t="s">
         <v>11</v>
       </c>
       <c r="E92" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F92" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G92" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H92" t="s">
         <v>13</v>
@@ -3942,7 +3918,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
@@ -3953,25 +3929,25 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B94" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C94" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="D94" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="E94" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F94" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G94" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H94" t="s">
         <v>13</v>
@@ -3979,10 +3955,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>320</v>
-      </c>
-      <c r="D95" t="s">
-        <v>11</v>
+        <v>314</v>
       </c>
       <c r="H95" t="s">
         <v>11</v>
@@ -3990,25 +3963,25 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B96" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C96" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
       </c>
       <c r="E96" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F96" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G96" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H96" t="s">
         <v>13</v>
@@ -4016,7 +3989,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D97" t="s">
         <v>11</v>
@@ -4027,33 +4000,51 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B98" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C98" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D98" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="E98" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F98" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G98" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H98" t="s">
-        <v>13</v>
+        <v>313</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>320</v>
+        <v>119</v>
+      </c>
+      <c r="B99" t="s">
+        <v>68</v>
+      </c>
+      <c r="C99" t="s">
+        <v>335</v>
+      </c>
+      <c r="D99" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" t="s">
+        <v>68</v>
+      </c>
+      <c r="F99" t="s">
+        <v>68</v>
+      </c>
+      <c r="G99" t="s">
+        <v>70</v>
       </c>
       <c r="H99" t="s">
         <v>11</v>
@@ -4061,25 +4052,25 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B100" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D100" t="s">
         <v>11</v>
       </c>
       <c r="E100" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F100" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G100" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H100" t="s">
         <v>13</v>
@@ -4087,7 +4078,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D101" t="s">
         <v>11</v>
@@ -4098,51 +4089,51 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>124</v>
+      </c>
+      <c r="B102" t="s">
+        <v>123</v>
+      </c>
+      <c r="C102" t="s">
         <v>125</v>
       </c>
-      <c r="B102" t="s">
-        <v>74</v>
-      </c>
-      <c r="C102" t="s">
-        <v>126</v>
-      </c>
       <c r="D102" t="s">
         <v>11</v>
       </c>
       <c r="E102" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="F102" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="G102" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="H102" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B103" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="C103" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="D103" t="s">
         <v>11</v>
       </c>
       <c r="E103" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="F103" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="G103" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="H103" t="s">
         <v>11</v>
@@ -4150,10 +4141,10 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B104" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="C104" t="s">
         <v>128</v>
@@ -4162,13 +4153,13 @@
         <v>11</v>
       </c>
       <c r="E104" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="F104" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="G104" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H104" t="s">
         <v>13</v>
@@ -4176,7 +4167,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
@@ -4187,51 +4178,36 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>129</v>
+      </c>
+      <c r="B106" t="s">
+        <v>127</v>
+      </c>
+      <c r="C106" t="s">
         <v>130</v>
       </c>
-      <c r="B106" t="s">
-        <v>129</v>
-      </c>
-      <c r="C106" t="s">
-        <v>131</v>
-      </c>
       <c r="D106" t="s">
         <v>11</v>
       </c>
       <c r="E106" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F106" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G106" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H106" t="s">
-        <v>323</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>130</v>
-      </c>
-      <c r="B107" t="s">
-        <v>129</v>
-      </c>
-      <c r="C107" t="s">
-        <v>342</v>
+        <v>314</v>
       </c>
       <c r="D107" t="s">
         <v>11</v>
-      </c>
-      <c r="E107" t="s">
-        <v>129</v>
-      </c>
-      <c r="F107" t="s">
-        <v>129</v>
-      </c>
-      <c r="G107" t="s">
-        <v>29</v>
       </c>
       <c r="H107" t="s">
         <v>11</v>
@@ -4239,25 +4215,25 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>131</v>
+      </c>
+      <c r="B108" t="s">
+        <v>127</v>
+      </c>
+      <c r="C108" t="s">
         <v>132</v>
       </c>
-      <c r="B108" t="s">
-        <v>133</v>
-      </c>
-      <c r="C108" t="s">
-        <v>134</v>
-      </c>
       <c r="D108" t="s">
         <v>11</v>
       </c>
       <c r="E108" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F108" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G108" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H108" t="s">
         <v>13</v>
@@ -4265,7 +4241,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D109" t="s">
         <v>11</v>
@@ -4276,25 +4252,25 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B110" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C110" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D110" t="s">
         <v>11</v>
       </c>
       <c r="E110" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F110" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G110" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H110" t="s">
         <v>13</v>
@@ -4302,7 +4278,7 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D111" t="s">
         <v>11</v>
@@ -4313,25 +4289,25 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B112" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C112" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D112" t="s">
         <v>11</v>
       </c>
       <c r="E112" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F112" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G112" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H112" t="s">
         <v>13</v>
@@ -4339,7 +4315,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D113" t="s">
         <v>11</v>
@@ -4350,25 +4326,25 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B114" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C114" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D114" t="s">
         <v>11</v>
       </c>
       <c r="E114" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F114" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G114" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H114" t="s">
         <v>13</v>
@@ -4376,7 +4352,7 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D115" t="s">
         <v>11</v>
@@ -4387,25 +4363,25 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B116" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C116" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D116" t="s">
         <v>11</v>
       </c>
       <c r="E116" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F116" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G116" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H116" t="s">
         <v>13</v>
@@ -4413,7 +4389,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D117" t="s">
         <v>11</v>
@@ -4424,25 +4400,25 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B118" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C118" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D118" t="s">
         <v>11</v>
       </c>
       <c r="E118" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F118" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G118" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H118" t="s">
         <v>13</v>
@@ -4450,7 +4426,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D119" t="s">
         <v>11</v>
@@ -4461,25 +4437,25 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B120" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C120" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D120" t="s">
         <v>11</v>
       </c>
       <c r="E120" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F120" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G120" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H120" t="s">
         <v>13</v>
@@ -4487,7 +4463,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D121" t="s">
         <v>11</v>
@@ -4498,25 +4474,25 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B122" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D122" t="s">
         <v>11</v>
       </c>
       <c r="E122" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F122" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G122" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H122" t="s">
         <v>13</v>
@@ -4524,7 +4500,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D123" t="s">
         <v>11</v>
@@ -4535,25 +4511,25 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B124" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C124" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D124" t="s">
         <v>11</v>
       </c>
       <c r="E124" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F124" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G124" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H124" t="s">
         <v>13</v>
@@ -4561,7 +4537,7 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D125" t="s">
         <v>11</v>
@@ -4572,25 +4548,25 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B126" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C126" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D126" t="s">
         <v>11</v>
       </c>
       <c r="E126" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F126" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G126" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H126" t="s">
         <v>13</v>
@@ -4598,7 +4574,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D127" t="s">
         <v>11</v>
@@ -4609,25 +4585,25 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B128" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C128" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D128" t="s">
         <v>11</v>
       </c>
       <c r="E128" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F128" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G128" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H128" t="s">
         <v>13</v>
@@ -4635,7 +4611,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D129" t="s">
         <v>11</v>
@@ -4646,25 +4622,25 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B130" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C130" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D130" t="s">
         <v>11</v>
       </c>
       <c r="E130" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F130" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G130" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H130" t="s">
         <v>13</v>
@@ -4672,7 +4648,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D131" t="s">
         <v>11</v>
@@ -4683,25 +4659,25 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B132" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C132" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D132" t="s">
         <v>11</v>
       </c>
       <c r="E132" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F132" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G132" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H132" t="s">
         <v>13</v>
@@ -4709,7 +4685,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D133" t="s">
         <v>11</v>
@@ -4720,25 +4696,25 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C134" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D134" t="s">
         <v>11</v>
       </c>
       <c r="E134" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F134" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G134" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H134" t="s">
         <v>13</v>
@@ -4746,7 +4722,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D135" t="s">
         <v>11</v>
@@ -4757,25 +4733,25 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B136" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C136" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D136" t="s">
         <v>11</v>
       </c>
       <c r="E136" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F136" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G136" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H136" t="s">
         <v>13</v>
@@ -4783,7 +4759,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D137" t="s">
         <v>11</v>
@@ -4794,25 +4770,25 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B138" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C138" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D138" t="s">
         <v>11</v>
       </c>
       <c r="E138" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F138" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G138" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H138" t="s">
         <v>13</v>
@@ -4820,7 +4796,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D139" t="s">
         <v>11</v>
@@ -4831,25 +4807,25 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B140" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C140" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D140" t="s">
         <v>11</v>
       </c>
       <c r="E140" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F140" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G140" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H140" t="s">
         <v>13</v>
@@ -4857,7 +4833,7 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D141" t="s">
         <v>11</v>
@@ -4868,25 +4844,25 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B142" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C142" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D142" t="s">
         <v>11</v>
       </c>
       <c r="E142" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F142" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G142" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H142" t="s">
         <v>13</v>
@@ -4894,7 +4870,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D143" t="s">
         <v>11</v>
@@ -4905,25 +4881,25 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C144" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D144" t="s">
         <v>11</v>
       </c>
       <c r="E144" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F144" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G144" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H144" t="s">
         <v>13</v>
@@ -4931,7 +4907,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D145" t="s">
         <v>11</v>
@@ -4942,25 +4918,25 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B146" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C146" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D146" t="s">
         <v>11</v>
       </c>
       <c r="E146" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F146" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G146" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H146" t="s">
         <v>13</v>
@@ -4968,7 +4944,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D147" t="s">
         <v>11</v>
@@ -4979,25 +4955,25 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B148" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C148" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D148" t="s">
         <v>11</v>
       </c>
       <c r="E148" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F148" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G148" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H148" t="s">
         <v>13</v>
@@ -5005,7 +4981,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D149" t="s">
         <v>11</v>
@@ -5016,25 +4992,25 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B150" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C150" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D150" t="s">
         <v>11</v>
       </c>
       <c r="E150" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F150" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G150" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H150" t="s">
         <v>13</v>
@@ -5042,7 +5018,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D151" t="s">
         <v>11</v>
@@ -5053,25 +5029,25 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B152" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C152" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D152" t="s">
         <v>11</v>
       </c>
       <c r="E152" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F152" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G152" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H152" t="s">
         <v>13</v>
@@ -5079,7 +5055,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D153" t="s">
         <v>11</v>
@@ -5090,36 +5066,51 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B154" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C154" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D154" t="s">
         <v>11</v>
       </c>
       <c r="E154" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F154" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G154" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H154" t="s">
-        <v>13</v>
+        <v>313</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>320</v>
+        <v>173</v>
+      </c>
+      <c r="B155" t="s">
+        <v>127</v>
+      </c>
+      <c r="C155" t="s">
+        <v>337</v>
       </c>
       <c r="D155" t="s">
         <v>11</v>
+      </c>
+      <c r="E155" t="s">
+        <v>127</v>
+      </c>
+      <c r="F155" t="s">
+        <v>127</v>
+      </c>
+      <c r="G155" t="s">
+        <v>17</v>
       </c>
       <c r="H155" t="s">
         <v>11</v>
@@ -5127,25 +5118,25 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B156" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C156" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D156" t="s">
         <v>11</v>
       </c>
       <c r="E156" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F156" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G156" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H156" t="s">
         <v>13</v>
@@ -5153,7 +5144,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D157" t="s">
         <v>11</v>
@@ -5164,51 +5155,36 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B158" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C158" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D158" t="s">
         <v>11</v>
       </c>
       <c r="E158" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F158" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G158" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H158" t="s">
-        <v>319</v>
+        <v>13</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>179</v>
-      </c>
-      <c r="B159" t="s">
-        <v>133</v>
-      </c>
-      <c r="C159" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="D159" t="s">
         <v>11</v>
-      </c>
-      <c r="E159" t="s">
-        <v>133</v>
-      </c>
-      <c r="F159" t="s">
-        <v>133</v>
-      </c>
-      <c r="G159" t="s">
-        <v>19</v>
       </c>
       <c r="H159" t="s">
         <v>11</v>
@@ -5216,25 +5192,25 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B160" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C160" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D160" t="s">
         <v>11</v>
       </c>
       <c r="E160" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F160" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G160" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H160" t="s">
         <v>13</v>
@@ -5242,7 +5218,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D161" t="s">
         <v>11</v>
@@ -5253,25 +5229,25 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B162" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C162" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D162" t="s">
         <v>11</v>
       </c>
       <c r="E162" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F162" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G162" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H162" t="s">
         <v>13</v>
@@ -5279,7 +5255,7 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D163" t="s">
         <v>11</v>
@@ -5290,36 +5266,51 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B164" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C164" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D164" t="s">
         <v>11</v>
       </c>
       <c r="E164" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F164" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G164" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H164" t="s">
-        <v>13</v>
+        <v>332</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>320</v>
+        <v>182</v>
+      </c>
+      <c r="B165" t="s">
+        <v>127</v>
+      </c>
+      <c r="C165" t="s">
+        <v>346</v>
       </c>
       <c r="D165" t="s">
         <v>11</v>
+      </c>
+      <c r="E165" t="s">
+        <v>127</v>
+      </c>
+      <c r="F165" t="s">
+        <v>127</v>
+      </c>
+      <c r="G165" t="s">
+        <v>17</v>
       </c>
       <c r="H165" t="s">
         <v>11</v>
@@ -5327,25 +5318,25 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B166" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C166" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D166" t="s">
         <v>11</v>
       </c>
       <c r="E166" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F166" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G166" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H166" t="s">
         <v>13</v>
@@ -5353,7 +5344,7 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D167" t="s">
         <v>11</v>
@@ -5364,51 +5355,36 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B168" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C168" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D168" t="s">
         <v>11</v>
       </c>
       <c r="E168" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F168" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G168" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H168" t="s">
-        <v>338</v>
+        <v>13</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>188</v>
-      </c>
-      <c r="B169" t="s">
-        <v>133</v>
-      </c>
-      <c r="C169" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="D169" t="s">
         <v>11</v>
-      </c>
-      <c r="E169" t="s">
-        <v>133</v>
-      </c>
-      <c r="F169" t="s">
-        <v>133</v>
-      </c>
-      <c r="G169" t="s">
-        <v>19</v>
       </c>
       <c r="H169" t="s">
         <v>11</v>
@@ -5416,36 +5392,51 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B170" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C170" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D170" t="s">
         <v>11</v>
       </c>
       <c r="E170" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F170" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G170" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H170" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>320</v>
+        <v>188</v>
+      </c>
+      <c r="B171" t="s">
+        <v>127</v>
+      </c>
+      <c r="C171" t="s">
+        <v>342</v>
       </c>
       <c r="D171" t="s">
         <v>11</v>
+      </c>
+      <c r="E171" t="s">
+        <v>127</v>
+      </c>
+      <c r="F171" t="s">
+        <v>127</v>
+      </c>
+      <c r="G171" t="s">
+        <v>17</v>
       </c>
       <c r="H171" t="s">
         <v>11</v>
@@ -5453,25 +5444,25 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B172" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C172" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D172" t="s">
         <v>11</v>
       </c>
       <c r="E172" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F172" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G172" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H172" t="s">
         <v>13</v>
@@ -5479,7 +5470,7 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D173" t="s">
         <v>11</v>
@@ -5490,51 +5481,51 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B174" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C174" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D174" t="s">
         <v>11</v>
       </c>
       <c r="E174" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F174" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G174" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H174" t="s">
-        <v>323</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B175" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C175" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D175" t="s">
         <v>11</v>
       </c>
       <c r="E175" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F175" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G175" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H175" t="s">
         <v>11</v>
@@ -5542,36 +5533,51 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B176" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C176" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D176" t="s">
         <v>11</v>
       </c>
       <c r="E176" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F176" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G176" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H176" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>320</v>
+        <v>194</v>
+      </c>
+      <c r="B177" t="s">
+        <v>127</v>
+      </c>
+      <c r="C177" t="s">
+        <v>338</v>
       </c>
       <c r="D177" t="s">
         <v>11</v>
+      </c>
+      <c r="E177" t="s">
+        <v>127</v>
+      </c>
+      <c r="F177" t="s">
+        <v>127</v>
+      </c>
+      <c r="G177" t="s">
+        <v>17</v>
       </c>
       <c r="H177" t="s">
         <v>11</v>
@@ -5579,25 +5585,25 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B178" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C178" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D178" t="s">
         <v>11</v>
       </c>
       <c r="E178" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F178" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G178" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H178" t="s">
         <v>13</v>
@@ -5605,25 +5611,10 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>198</v>
-      </c>
-      <c r="B179" t="s">
-        <v>133</v>
-      </c>
-      <c r="C179" t="s">
-        <v>353</v>
+        <v>314</v>
       </c>
       <c r="D179" t="s">
         <v>11</v>
-      </c>
-      <c r="E179" t="s">
-        <v>133</v>
-      </c>
-      <c r="F179" t="s">
-        <v>133</v>
-      </c>
-      <c r="G179" t="s">
-        <v>19</v>
       </c>
       <c r="H179" t="s">
         <v>11</v>
@@ -5631,51 +5622,36 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B180" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C180" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D180" t="s">
         <v>11</v>
       </c>
       <c r="E180" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F180" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G180" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H180" t="s">
-        <v>323</v>
+        <v>13</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>200</v>
-      </c>
-      <c r="B181" t="s">
-        <v>133</v>
-      </c>
-      <c r="C181" t="s">
-        <v>344</v>
+        <v>314</v>
       </c>
       <c r="D181" t="s">
         <v>11</v>
-      </c>
-      <c r="E181" t="s">
-        <v>133</v>
-      </c>
-      <c r="F181" t="s">
-        <v>133</v>
-      </c>
-      <c r="G181" t="s">
-        <v>19</v>
       </c>
       <c r="H181" t="s">
         <v>11</v>
@@ -5683,25 +5659,25 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B182" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C182" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D182" t="s">
         <v>11</v>
       </c>
       <c r="E182" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F182" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G182" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H182" t="s">
         <v>13</v>
@@ -5709,7 +5685,7 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D183" t="s">
         <v>11</v>
@@ -5720,25 +5696,25 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B184" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C184" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D184" t="s">
         <v>11</v>
       </c>
       <c r="E184" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F184" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G184" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H184" t="s">
         <v>13</v>
@@ -5746,7 +5722,7 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D185" t="s">
         <v>11</v>
@@ -5757,25 +5733,25 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B186" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C186" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D186" t="s">
         <v>11</v>
       </c>
       <c r="E186" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F186" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G186" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H186" t="s">
         <v>13</v>
@@ -5783,7 +5759,7 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D187" t="s">
         <v>11</v>
@@ -5794,25 +5770,25 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B188" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C188" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D188" t="s">
         <v>11</v>
       </c>
       <c r="E188" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F188" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G188" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H188" t="s">
         <v>13</v>
@@ -5820,7 +5796,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D189" t="s">
         <v>11</v>
@@ -5831,25 +5807,25 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B190" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C190" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D190" t="s">
         <v>11</v>
       </c>
       <c r="E190" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F190" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G190" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H190" t="s">
         <v>13</v>
@@ -5857,7 +5833,7 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D191" t="s">
         <v>11</v>
@@ -5868,25 +5844,25 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B192" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C192" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D192" t="s">
         <v>11</v>
       </c>
       <c r="E192" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F192" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G192" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H192" t="s">
         <v>13</v>
@@ -5894,7 +5870,7 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D193" t="s">
         <v>11</v>
@@ -5905,25 +5881,25 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B194" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C194" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D194" t="s">
         <v>11</v>
       </c>
       <c r="E194" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F194" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G194" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H194" t="s">
         <v>13</v>
@@ -5931,7 +5907,7 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D195" t="s">
         <v>11</v>
@@ -5942,25 +5918,25 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B196" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C196" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D196" t="s">
         <v>11</v>
       </c>
       <c r="E196" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F196" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G196" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H196" t="s">
         <v>13</v>
@@ -5968,7 +5944,7 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D197" t="s">
         <v>11</v>
@@ -5979,25 +5955,25 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B198" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C198" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D198" t="s">
         <v>11</v>
       </c>
       <c r="E198" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F198" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G198" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H198" t="s">
         <v>13</v>
@@ -6005,7 +5981,7 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D199" t="s">
         <v>11</v>
@@ -6016,25 +5992,25 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B200" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C200" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D200" t="s">
         <v>11</v>
       </c>
       <c r="E200" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F200" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G200" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H200" t="s">
         <v>13</v>
@@ -6042,7 +6018,7 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D201" t="s">
         <v>11</v>
@@ -6053,25 +6029,25 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B202" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C202" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D202" t="s">
         <v>11</v>
       </c>
       <c r="E202" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F202" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G202" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H202" t="s">
         <v>13</v>
@@ -6079,7 +6055,7 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D203" t="s">
         <v>11</v>
@@ -6090,25 +6066,25 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B204" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C204" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D204" t="s">
         <v>11</v>
       </c>
       <c r="E204" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F204" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G204" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H204" t="s">
         <v>13</v>
@@ -6116,7 +6092,7 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D205" t="s">
         <v>11</v>
@@ -6127,25 +6103,25 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B206" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C206" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D206" t="s">
         <v>11</v>
       </c>
       <c r="E206" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F206" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G206" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H206" t="s">
         <v>13</v>
@@ -6153,7 +6129,7 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D207" t="s">
         <v>11</v>
@@ -6164,25 +6140,25 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B208" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C208" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D208" t="s">
         <v>11</v>
       </c>
       <c r="E208" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F208" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G208" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H208" t="s">
         <v>13</v>
@@ -6190,7 +6166,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D209" t="s">
         <v>11</v>
@@ -6201,25 +6177,25 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B210" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C210" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D210" t="s">
         <v>11</v>
       </c>
       <c r="E210" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F210" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G210" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H210" t="s">
         <v>13</v>
@@ -6227,7 +6203,7 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D211" t="s">
         <v>11</v>
@@ -6238,25 +6214,25 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B212" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C212" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D212" t="s">
         <v>11</v>
       </c>
       <c r="E212" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F212" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G212" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H212" t="s">
         <v>13</v>
@@ -6264,7 +6240,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D213" t="s">
         <v>11</v>
@@ -6275,25 +6251,25 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B214" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C214" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D214" t="s">
         <v>11</v>
       </c>
       <c r="E214" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F214" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G214" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H214" t="s">
         <v>13</v>
@@ -6301,7 +6277,7 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D215" t="s">
         <v>11</v>
@@ -6312,25 +6288,25 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B216" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C216" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D216" t="s">
         <v>11</v>
       </c>
       <c r="E216" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F216" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G216" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H216" t="s">
         <v>13</v>
@@ -6338,7 +6314,7 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D217" t="s">
         <v>11</v>
@@ -6349,25 +6325,25 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="B218" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C218" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D218" t="s">
         <v>11</v>
       </c>
       <c r="E218" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F218" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G218" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H218" t="s">
         <v>13</v>
@@ -6375,7 +6351,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D219" t="s">
         <v>11</v>
@@ -6386,25 +6362,25 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B220" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C220" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D220" t="s">
         <v>11</v>
       </c>
       <c r="E220" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F220" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G220" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H220" t="s">
         <v>13</v>
@@ -6412,7 +6388,7 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D221" t="s">
         <v>11</v>
@@ -6423,25 +6399,25 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B222" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C222" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D222" t="s">
         <v>11</v>
       </c>
       <c r="E222" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F222" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G222" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H222" t="s">
         <v>13</v>
@@ -6449,7 +6425,7 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D223" t="s">
         <v>11</v>
@@ -6460,25 +6436,25 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B224" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C224" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D224" t="s">
         <v>11</v>
       </c>
       <c r="E224" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F224" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G224" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H224" t="s">
         <v>13</v>
@@ -6486,7 +6462,7 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D225" t="s">
         <v>11</v>
@@ -6497,25 +6473,25 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B226" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C226" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D226" t="s">
         <v>11</v>
       </c>
       <c r="E226" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F226" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G226" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H226" t="s">
         <v>13</v>
@@ -6523,7 +6499,7 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D227" t="s">
         <v>11</v>
@@ -6534,25 +6510,25 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B228" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C228" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D228" t="s">
         <v>11</v>
       </c>
       <c r="E228" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F228" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G228" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H228" t="s">
         <v>13</v>
@@ -6560,7 +6536,7 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D229" t="s">
         <v>11</v>
@@ -6571,25 +6547,25 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B230" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C230" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D230" t="s">
         <v>11</v>
       </c>
       <c r="E230" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F230" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G230" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H230" t="s">
         <v>13</v>
@@ -6597,7 +6573,7 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D231" t="s">
         <v>11</v>
@@ -6608,25 +6584,25 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B232" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C232" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D232" t="s">
         <v>11</v>
       </c>
       <c r="E232" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F232" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G232" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H232" t="s">
         <v>13</v>
@@ -6634,7 +6610,7 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D233" t="s">
         <v>11</v>
@@ -6645,25 +6621,25 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B234" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C234" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D234" t="s">
         <v>11</v>
       </c>
       <c r="E234" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F234" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G234" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H234" t="s">
         <v>13</v>
@@ -6671,7 +6647,7 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D235" t="s">
         <v>11</v>
@@ -6682,25 +6658,25 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B236" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C236" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D236" t="s">
         <v>11</v>
       </c>
       <c r="E236" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F236" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G236" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H236" t="s">
         <v>13</v>
@@ -6708,7 +6684,7 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D237" t="s">
         <v>11</v>
@@ -6719,25 +6695,25 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B238" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C238" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D238" t="s">
         <v>11</v>
       </c>
       <c r="E238" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F238" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G238" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H238" t="s">
         <v>13</v>
@@ -6745,7 +6721,7 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D239" t="s">
         <v>11</v>
@@ -6756,25 +6732,25 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B240" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C240" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D240" t="s">
         <v>11</v>
       </c>
       <c r="E240" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F240" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G240" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H240" t="s">
         <v>13</v>
@@ -6782,7 +6758,7 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D241" t="s">
         <v>11</v>
@@ -6793,36 +6769,51 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B242" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C242" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D242" t="s">
         <v>11</v>
       </c>
       <c r="E242" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F242" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G242" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H242" t="s">
-        <v>13</v>
+        <v>313</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>320</v>
+        <v>258</v>
+      </c>
+      <c r="B243" t="s">
+        <v>127</v>
+      </c>
+      <c r="C243" t="s">
+        <v>339</v>
       </c>
       <c r="D243" t="s">
         <v>11</v>
+      </c>
+      <c r="E243" t="s">
+        <v>127</v>
+      </c>
+      <c r="F243" t="s">
+        <v>127</v>
+      </c>
+      <c r="G243" t="s">
+        <v>17</v>
       </c>
       <c r="H243" t="s">
         <v>11</v>
@@ -6830,25 +6821,25 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B244" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C244" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>11</v>
       </c>
       <c r="E244" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F244" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G244" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H244" t="s">
         <v>13</v>
@@ -6856,7 +6847,7 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D245" t="s">
         <v>11</v>
@@ -6867,51 +6858,36 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B246" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C246" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D246" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="E246" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F246" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G246" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H246" t="s">
-        <v>319</v>
+        <v>13</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>264</v>
-      </c>
-      <c r="B247" t="s">
-        <v>133</v>
-      </c>
-      <c r="C247" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="D247" t="s">
         <v>11</v>
-      </c>
-      <c r="E247" t="s">
-        <v>133</v>
-      </c>
-      <c r="F247" t="s">
-        <v>133</v>
-      </c>
-      <c r="G247" t="s">
-        <v>19</v>
       </c>
       <c r="H247" t="s">
         <v>11</v>
@@ -6919,25 +6895,25 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B248" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C248" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
         <v>11</v>
       </c>
       <c r="E248" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F248" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G248" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H248" t="s">
         <v>13</v>
@@ -6945,7 +6921,7 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D249" t="s">
         <v>11</v>
@@ -6956,25 +6932,25 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B250" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C250" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="E250" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F250" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G250" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H250" t="s">
         <v>13</v>
@@ -6982,7 +6958,7 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D251" t="s">
         <v>11</v>
@@ -6993,25 +6969,25 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
+        <v>267</v>
+      </c>
+      <c r="B252" t="s">
+        <v>127</v>
+      </c>
+      <c r="C252" t="s">
         <v>268</v>
       </c>
-      <c r="B252" t="s">
-        <v>133</v>
-      </c>
-      <c r="C252" t="s">
-        <v>270</v>
-      </c>
       <c r="D252" t="s">
         <v>11</v>
       </c>
       <c r="E252" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F252" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G252" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H252" t="s">
         <v>13</v>
@@ -7019,7 +6995,7 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D253" t="s">
         <v>11</v>
@@ -7030,25 +7006,25 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B254" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C254" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D254" t="s">
         <v>11</v>
       </c>
       <c r="E254" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F254" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G254" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H254" t="s">
         <v>13</v>
@@ -7056,7 +7032,7 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D255" t="s">
         <v>11</v>
@@ -7067,25 +7043,25 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B256" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C256" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D256" t="s">
         <v>11</v>
       </c>
       <c r="E256" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F256" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G256" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H256" t="s">
         <v>13</v>
@@ -7093,7 +7069,7 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D257" t="s">
         <v>11</v>
@@ -7104,25 +7080,25 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B258" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C258" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D258" t="s">
         <v>11</v>
       </c>
       <c r="E258" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F258" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G258" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H258" t="s">
         <v>13</v>
@@ -7130,7 +7106,7 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D259" t="s">
         <v>11</v>
@@ -7141,25 +7117,25 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B260" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C260" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D260" t="s">
         <v>11</v>
       </c>
       <c r="E260" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F260" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G260" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H260" t="s">
         <v>13</v>
@@ -7167,7 +7143,7 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D261" t="s">
         <v>11</v>
@@ -7178,25 +7154,25 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B262" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C262" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D262" t="s">
         <v>11</v>
       </c>
       <c r="E262" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F262" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G262" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H262" t="s">
         <v>13</v>
@@ -7204,7 +7180,7 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D263" t="s">
         <v>11</v>
@@ -7215,25 +7191,25 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B264" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C264" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D264" t="s">
         <v>11</v>
       </c>
       <c r="E264" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F264" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G264" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H264" t="s">
         <v>13</v>
@@ -7241,7 +7217,7 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D265" t="s">
         <v>11</v>
@@ -7252,25 +7228,25 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B266" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C266" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D266" t="s">
         <v>11</v>
       </c>
       <c r="E266" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F266" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G266" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H266" t="s">
         <v>13</v>
@@ -7278,7 +7254,7 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D267" t="s">
         <v>11</v>
@@ -7289,25 +7265,25 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B268" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C268" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D268" t="s">
         <v>11</v>
       </c>
       <c r="E268" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F268" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G268" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H268" t="s">
         <v>13</v>
@@ -7315,7 +7291,7 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D269" t="s">
         <v>11</v>
@@ -7326,25 +7302,25 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B270" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C270" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D270" t="s">
         <v>11</v>
       </c>
       <c r="E270" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F270" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G270" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H270" t="s">
         <v>13</v>
@@ -7352,7 +7328,7 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D271" t="s">
         <v>11</v>
@@ -7363,25 +7339,25 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B272" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C272" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D272" t="s">
         <v>11</v>
       </c>
       <c r="E272" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F272" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G272" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H272" t="s">
         <v>13</v>
@@ -7389,7 +7365,7 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D273" t="s">
         <v>11</v>
@@ -7400,25 +7376,25 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B274" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C274" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D274" t="s">
         <v>11</v>
       </c>
       <c r="E274" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F274" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G274" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H274" t="s">
         <v>13</v>
@@ -7426,7 +7402,7 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D275" t="s">
         <v>11</v>
@@ -7437,25 +7413,25 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B276" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C276" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D276" t="s">
         <v>11</v>
       </c>
       <c r="E276" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F276" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G276" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H276" t="s">
         <v>13</v>
@@ -7463,7 +7439,7 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D277" t="s">
         <v>11</v>
@@ -7474,36 +7450,51 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B278" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C278" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D278" t="s">
         <v>11</v>
       </c>
       <c r="E278" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F278" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G278" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H278" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>320</v>
+        <v>293</v>
+      </c>
+      <c r="B279" t="s">
+        <v>127</v>
+      </c>
+      <c r="C279" t="s">
+        <v>340</v>
       </c>
       <c r="D279" t="s">
         <v>11</v>
+      </c>
+      <c r="E279" t="s">
+        <v>127</v>
+      </c>
+      <c r="F279" t="s">
+        <v>127</v>
+      </c>
+      <c r="G279" t="s">
+        <v>17</v>
       </c>
       <c r="H279" t="s">
         <v>11</v>
@@ -7511,36 +7502,51 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B280" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C280" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D280" t="s">
         <v>11</v>
       </c>
       <c r="E280" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F280" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G280" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H280" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>320</v>
+        <v>295</v>
+      </c>
+      <c r="B281" t="s">
+        <v>127</v>
+      </c>
+      <c r="C281" t="s">
+        <v>341</v>
       </c>
       <c r="D281" t="s">
         <v>11</v>
+      </c>
+      <c r="E281" t="s">
+        <v>127</v>
+      </c>
+      <c r="F281" t="s">
+        <v>127</v>
+      </c>
+      <c r="G281" t="s">
+        <v>17</v>
       </c>
       <c r="H281" t="s">
         <v>11</v>
@@ -7548,51 +7554,36 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B282" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C282" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D282" t="s">
         <v>11</v>
       </c>
       <c r="E282" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F282" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G282" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H282" t="s">
-        <v>323</v>
+        <v>13</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>299</v>
-      </c>
-      <c r="B283" t="s">
-        <v>133</v>
-      </c>
-      <c r="C283" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="D283" t="s">
         <v>11</v>
-      </c>
-      <c r="E283" t="s">
-        <v>133</v>
-      </c>
-      <c r="F283" t="s">
-        <v>133</v>
-      </c>
-      <c r="G283" t="s">
-        <v>19</v>
       </c>
       <c r="H283" t="s">
         <v>11</v>
@@ -7600,51 +7591,36 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B284" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C284" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D284" t="s">
         <v>11</v>
       </c>
       <c r="E284" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F284" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G284" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H284" t="s">
-        <v>323</v>
+        <v>13</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>301</v>
-      </c>
-      <c r="B285" t="s">
-        <v>133</v>
-      </c>
-      <c r="C285" t="s">
-        <v>347</v>
+        <v>314</v>
       </c>
       <c r="D285" t="s">
         <v>11</v>
-      </c>
-      <c r="E285" t="s">
-        <v>133</v>
-      </c>
-      <c r="F285" t="s">
-        <v>133</v>
-      </c>
-      <c r="G285" t="s">
-        <v>19</v>
       </c>
       <c r="H285" t="s">
         <v>11</v>
@@ -7652,25 +7628,25 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>301</v>
+      </c>
+      <c r="B286" t="s">
+        <v>302</v>
+      </c>
+      <c r="C286" t="s">
         <v>303</v>
       </c>
-      <c r="B286" t="s">
-        <v>133</v>
-      </c>
-      <c r="C286" t="s">
-        <v>304</v>
-      </c>
       <c r="D286" t="s">
         <v>11</v>
       </c>
       <c r="E286" t="s">
-        <v>133</v>
+        <v>302</v>
       </c>
       <c r="F286" t="s">
-        <v>133</v>
+        <v>302</v>
       </c>
       <c r="G286" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H286" t="s">
         <v>13</v>
@@ -7678,10 +7654,10 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>320</v>
-      </c>
-      <c r="D287" t="s">
-        <v>11</v>
+        <v>314</v>
+      </c>
+      <c r="E287" t="s">
+        <v>302</v>
       </c>
       <c r="H287" t="s">
         <v>11</v>
@@ -7689,25 +7665,25 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B288" t="s">
-        <v>133</v>
+        <v>302</v>
       </c>
       <c r="C288" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D288" t="s">
         <v>11</v>
       </c>
       <c r="E288" t="s">
-        <v>133</v>
+        <v>302</v>
       </c>
       <c r="F288" t="s">
-        <v>133</v>
+        <v>302</v>
       </c>
       <c r="G288" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H288" t="s">
         <v>13</v>
@@ -7715,10 +7691,7 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>320</v>
-      </c>
-      <c r="D289" t="s">
-        <v>11</v>
+        <v>314</v>
       </c>
       <c r="H289" t="s">
         <v>11</v>
@@ -7729,33 +7702,48 @@
         <v>307</v>
       </c>
       <c r="B290" t="s">
+        <v>305</v>
+      </c>
+      <c r="C290" t="s">
         <v>308</v>
       </c>
-      <c r="C290" t="s">
-        <v>309</v>
-      </c>
       <c r="D290" t="s">
         <v>11</v>
       </c>
       <c r="E290" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F290" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G290" t="s">
-        <v>24</v>
+        <v>306</v>
       </c>
       <c r="H290" t="s">
-        <v>13</v>
+        <v>332</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>320</v>
+        <v>307</v>
+      </c>
+      <c r="B291" t="s">
+        <v>305</v>
+      </c>
+      <c r="C291" t="s">
+        <v>343</v>
+      </c>
+      <c r="D291" t="s">
+        <v>11</v>
       </c>
       <c r="E291" t="s">
-        <v>308</v>
+        <v>305</v>
+      </c>
+      <c r="F291" t="s">
+        <v>305</v>
+      </c>
+      <c r="G291" t="s">
+        <v>306</v>
       </c>
       <c r="H291" t="s">
         <v>11</v>
@@ -7763,10 +7751,10 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B292" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C292" t="s">
         <v>310</v>
@@ -7775,21 +7763,39 @@
         <v>11</v>
       </c>
       <c r="E292" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F292" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G292" t="s">
-        <v>24</v>
+        <v>306</v>
       </c>
       <c r="H292" t="s">
-        <v>13</v>
+        <v>332</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>320</v>
+        <v>309</v>
+      </c>
+      <c r="B293" t="s">
+        <v>305</v>
+      </c>
+      <c r="C293" t="s">
+        <v>344</v>
+      </c>
+      <c r="D293" t="s">
+        <v>11</v>
+      </c>
+      <c r="E293" t="s">
+        <v>305</v>
+      </c>
+      <c r="F293" t="s">
+        <v>305</v>
+      </c>
+      <c r="G293" t="s">
+        <v>306</v>
       </c>
       <c r="H293" t="s">
         <v>11</v>
@@ -7797,157 +7803,53 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B294" t="s">
+        <v>305</v>
+      </c>
+      <c r="C294" t="s">
         <v>311</v>
       </c>
-      <c r="C294" t="s">
-        <v>314</v>
-      </c>
       <c r="D294" t="s">
         <v>11</v>
       </c>
       <c r="E294" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F294" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="G294" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="H294" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B295" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C295" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D295" t="s">
         <v>11</v>
       </c>
       <c r="E295" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F295" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="G295" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="H295" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>315</v>
-      </c>
-      <c r="B296" t="s">
-        <v>311</v>
-      </c>
-      <c r="C296" t="s">
-        <v>316</v>
-      </c>
-      <c r="D296" t="s">
-        <v>11</v>
-      </c>
-      <c r="E296" t="s">
-        <v>311</v>
-      </c>
-      <c r="F296" t="s">
-        <v>311</v>
-      </c>
-      <c r="G296" t="s">
-        <v>312</v>
-      </c>
-      <c r="H296" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>315</v>
-      </c>
-      <c r="B297" t="s">
-        <v>311</v>
-      </c>
-      <c r="C297" t="s">
-        <v>350</v>
-      </c>
-      <c r="D297" t="s">
-        <v>11</v>
-      </c>
-      <c r="E297" t="s">
-        <v>311</v>
-      </c>
-      <c r="F297" t="s">
-        <v>311</v>
-      </c>
-      <c r="G297" t="s">
-        <v>312</v>
-      </c>
-      <c r="H297" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>315</v>
-      </c>
-      <c r="B298" t="s">
-        <v>311</v>
-      </c>
-      <c r="C298" t="s">
-        <v>317</v>
-      </c>
-      <c r="D298" t="s">
-        <v>11</v>
-      </c>
-      <c r="E298" t="s">
-        <v>311</v>
-      </c>
-      <c r="F298" t="s">
-        <v>311</v>
-      </c>
-      <c r="G298" t="s">
-        <v>312</v>
-      </c>
-      <c r="H298" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>315</v>
-      </c>
-      <c r="B299" t="s">
-        <v>311</v>
-      </c>
-      <c r="C299" t="s">
-        <v>351</v>
-      </c>
-      <c r="D299" t="s">
-        <v>11</v>
-      </c>
-      <c r="E299" t="s">
-        <v>311</v>
-      </c>
-      <c r="F299" t="s">
-        <v>311</v>
-      </c>
-      <c r="G299" t="s">
-        <v>312</v>
-      </c>
-      <c r="H299" t="s">
         <v>11</v>
       </c>
     </row>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43077977-735F-4DB7-AE0F-5A9017EB215F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C88D8B2-C6D0-43C3-89C9-7BDA4FE0082F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="423">
   <si>
     <t>Kod</t>
   </si>
@@ -563,9 +563,6 @@
     <t>00-713</t>
   </si>
   <si>
-    <t>Pułku Armii Krajowej Kampinos</t>
-  </si>
-  <si>
     <t>02-983</t>
   </si>
   <si>
@@ -620,9 +617,6 @@
     <t>00-124</t>
   </si>
   <si>
-    <t>Organizacji Narodów Zjednoczonych Rondo</t>
-  </si>
-  <si>
     <t>00-408</t>
   </si>
   <si>
@@ -1049,9 +1043,6 @@
     <t>Al. Na Skarpie</t>
   </si>
   <si>
-    <t>Rondo Organizacji Narodów Zjednoczonych</t>
-  </si>
-  <si>
     <t>IV Poprzeczna</t>
   </si>
   <si>
@@ -1077,6 +1068,240 @@
   </si>
   <si>
     <t>Bohaterów Getta Warszawskiego</t>
+  </si>
+  <si>
+    <t>ONZ Rondo</t>
+  </si>
+  <si>
+    <t>Rondo ONZ</t>
+  </si>
+  <si>
+    <t>15-568</t>
+  </si>
+  <si>
+    <t>św. Proroka Eliasza</t>
+  </si>
+  <si>
+    <t>85-791</t>
+  </si>
+  <si>
+    <t>Bydgoszcz</t>
+  </si>
+  <si>
+    <t>pl. plac św. Mateusza Apostoła i Ewangelisty</t>
+  </si>
+  <si>
+    <t>kujawsko-pomorskie</t>
+  </si>
+  <si>
+    <t>89-600</t>
+  </si>
+  <si>
+    <t>Chojnice</t>
+  </si>
+  <si>
+    <t>ks. płk. Józefa Wrycza</t>
+  </si>
+  <si>
+    <t>chojnicki</t>
+  </si>
+  <si>
+    <t>06-413</t>
+  </si>
+  <si>
+    <t>Ciechanów</t>
+  </si>
+  <si>
+    <t>św. Rodziny</t>
+  </si>
+  <si>
+    <t>ciechanowski</t>
+  </si>
+  <si>
+    <t>42-226</t>
+  </si>
+  <si>
+    <t>Częstochowa</t>
+  </si>
+  <si>
+    <t>św. Łukasza</t>
+  </si>
+  <si>
+    <t>80-893</t>
+  </si>
+  <si>
+    <t>Bastion św. Elżbiety</t>
+  </si>
+  <si>
+    <t>80-299</t>
+  </si>
+  <si>
+    <t>Plac św. Jana Apostoła</t>
+  </si>
+  <si>
+    <t>81-402</t>
+  </si>
+  <si>
+    <t>Gdynia</t>
+  </si>
+  <si>
+    <t>bp. Dominika</t>
+  </si>
+  <si>
+    <t>dolnośląskie</t>
+  </si>
+  <si>
+    <t>30-198</t>
+  </si>
+  <si>
+    <t>Kraków</t>
+  </si>
+  <si>
+    <t>mjr. Łupaszki</t>
+  </si>
+  <si>
+    <t>małopolskie</t>
+  </si>
+  <si>
+    <t>30-432</t>
+  </si>
+  <si>
+    <t>os. Osiedle Zaułek Jugowicki</t>
+  </si>
+  <si>
+    <t>30-611</t>
+  </si>
+  <si>
+    <t>por. Halszki</t>
+  </si>
+  <si>
+    <t>31-046</t>
+  </si>
+  <si>
+    <t>św. Gertrudy</t>
+  </si>
+  <si>
+    <t>1-11</t>
+  </si>
+  <si>
+    <t>31-048</t>
+  </si>
+  <si>
+    <t>12-DK</t>
+  </si>
+  <si>
+    <t>48-300</t>
+  </si>
+  <si>
+    <t>Nysa</t>
+  </si>
+  <si>
+    <t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</t>
+  </si>
+  <si>
+    <t>nyski</t>
+  </si>
+  <si>
+    <t>opolskie</t>
+  </si>
+  <si>
+    <t>60-654</t>
+  </si>
+  <si>
+    <t>Poznań</t>
+  </si>
+  <si>
+    <t>św. Leonarda</t>
+  </si>
+  <si>
+    <t>61-465</t>
+  </si>
+  <si>
+    <t>św. Szczepana</t>
+  </si>
+  <si>
+    <t>41-711</t>
+  </si>
+  <si>
+    <t>Ruda Śląska</t>
+  </si>
+  <si>
+    <t>Dr. Jordana</t>
+  </si>
+  <si>
+    <t>gen. Bema</t>
+  </si>
+  <si>
+    <t>71-522</t>
+  </si>
+  <si>
+    <t>43-100</t>
+  </si>
+  <si>
+    <t>Tychy</t>
+  </si>
+  <si>
+    <t>Beethovena</t>
+  </si>
+  <si>
+    <t>03-029</t>
+  </si>
+  <si>
+    <t>Romana Palestera</t>
+  </si>
+  <si>
+    <t>02-647</t>
+  </si>
+  <si>
+    <t>Rabindranatha Tagore</t>
+  </si>
+  <si>
+    <t>50-070</t>
+  </si>
+  <si>
+    <t>Wrocław</t>
+  </si>
+  <si>
+    <t>św. Doroty</t>
+  </si>
+  <si>
+    <t>50-156</t>
+  </si>
+  <si>
+    <t>Św. Jana Kapistrana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">św. Jana </t>
+  </si>
+  <si>
+    <t>Góry św. Anny</t>
+  </si>
+  <si>
+    <t>Do roboty</t>
+  </si>
+  <si>
+    <t>rondo ONZ</t>
+  </si>
+  <si>
+    <t>Pułku AK Kampinos</t>
+  </si>
+  <si>
+    <t>ks. płk Józefa Wryczy</t>
+  </si>
+  <si>
+    <t>mjr Łupaszki</t>
+  </si>
+  <si>
+    <t>Zaułek Jugowicki</t>
+  </si>
+  <si>
+    <t>gen. Augusta Emila Fieldorfa Nila</t>
+  </si>
+  <si>
+    <t>van Beethovena</t>
+  </si>
+  <si>
+    <t>Romana Palestra</t>
   </si>
 </sst>
 </file>
@@ -1955,7 +2180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:H349"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -2017,7 +2242,7 @@
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2028,7 +2253,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -2069,12 +2294,12 @@
         <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -2106,7 +2331,7 @@
         <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2117,7 +2342,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -2158,7 +2383,7 @@
         <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2169,7 +2394,7 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -2210,7 +2435,7 @@
         <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2221,7 +2446,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -2262,7 +2487,7 @@
         <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -2273,7 +2498,7 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -2319,7 +2544,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -2351,7 +2576,7 @@
         <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -2362,7 +2587,7 @@
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -2403,7 +2628,7 @@
         <v>42</v>
       </c>
       <c r="H18" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -2414,7 +2639,7 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -2455,7 +2680,7 @@
         <v>42</v>
       </c>
       <c r="H20" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -2466,7 +2691,7 @@
         <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -2507,7 +2732,7 @@
         <v>42</v>
       </c>
       <c r="H22" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -2518,7 +2743,7 @@
         <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -2559,7 +2784,7 @@
         <v>42</v>
       </c>
       <c r="H24" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -2570,7 +2795,7 @@
         <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -2611,7 +2836,7 @@
         <v>42</v>
       </c>
       <c r="H26" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -2622,7 +2847,7 @@
         <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -2668,7 +2893,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -2705,7 +2930,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -2742,7 +2967,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -2774,7 +2999,7 @@
         <v>57</v>
       </c>
       <c r="H34" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -2785,7 +3010,7 @@
         <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -2826,7 +3051,7 @@
         <v>57</v>
       </c>
       <c r="H36" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -2837,7 +3062,7 @@
         <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -2883,7 +3108,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
@@ -2918,7 +3143,7 @@
         <v>57</v>
       </c>
       <c r="H40" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -2929,7 +3154,7 @@
         <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -2975,7 +3200,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -3012,7 +3237,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
@@ -3041,7 +3266,7 @@
         <v>70</v>
       </c>
       <c r="H46" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -3052,7 +3277,7 @@
         <v>68</v>
       </c>
       <c r="C47" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
@@ -3098,7 +3323,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -3135,7 +3360,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -3172,7 +3397,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -3209,7 +3434,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -3246,7 +3471,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -3283,7 +3508,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -3320,7 +3545,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -3357,7 +3582,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -3394,7 +3619,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
@@ -3431,7 +3656,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
@@ -3468,7 +3693,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
@@ -3505,7 +3730,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -3542,7 +3767,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -3579,7 +3804,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H75" t="s">
         <v>11</v>
@@ -3613,7 +3838,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H77" t="s">
         <v>11</v>
@@ -3642,7 +3867,7 @@
         <v>70</v>
       </c>
       <c r="H78" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -3653,7 +3878,7 @@
         <v>68</v>
       </c>
       <c r="C79" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D79" t="s">
         <v>11</v>
@@ -3699,7 +3924,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
@@ -3736,7 +3961,7 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H83" t="s">
         <v>11</v>
@@ -3770,7 +3995,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
@@ -3807,7 +4032,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D87" t="s">
         <v>11</v>
@@ -3844,7 +4069,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D89" t="s">
         <v>11</v>
@@ -3881,7 +4106,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D91" t="s">
         <v>11</v>
@@ -3918,7 +4143,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
@@ -3955,7 +4180,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H95" t="s">
         <v>11</v>
@@ -3989,7 +4214,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D97" t="s">
         <v>11</v>
@@ -4021,7 +4246,7 @@
         <v>70</v>
       </c>
       <c r="H98" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -4032,7 +4257,7 @@
         <v>68</v>
       </c>
       <c r="C99" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D99" t="s">
         <v>11</v>
@@ -4078,7 +4303,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D101" t="s">
         <v>11</v>
@@ -4110,7 +4335,7 @@
         <v>27</v>
       </c>
       <c r="H102" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -4121,7 +4346,7 @@
         <v>123</v>
       </c>
       <c r="C103" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D103" t="s">
         <v>11</v>
@@ -4167,7 +4392,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
@@ -4204,7 +4429,7 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D107" t="s">
         <v>11</v>
@@ -4241,7 +4466,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D109" t="s">
         <v>11</v>
@@ -4278,7 +4503,7 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D111" t="s">
         <v>11</v>
@@ -4315,7 +4540,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D113" t="s">
         <v>11</v>
@@ -4352,7 +4577,7 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D115" t="s">
         <v>11</v>
@@ -4389,7 +4614,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D117" t="s">
         <v>11</v>
@@ -4426,7 +4651,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D119" t="s">
         <v>11</v>
@@ -4463,7 +4688,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D121" t="s">
         <v>11</v>
@@ -4500,7 +4725,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D123" t="s">
         <v>11</v>
@@ -4537,7 +4762,7 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D125" t="s">
         <v>11</v>
@@ -4574,7 +4799,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D127" t="s">
         <v>11</v>
@@ -4611,7 +4836,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D129" t="s">
         <v>11</v>
@@ -4648,7 +4873,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D131" t="s">
         <v>11</v>
@@ -4685,7 +4910,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D133" t="s">
         <v>11</v>
@@ -4722,7 +4947,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D135" t="s">
         <v>11</v>
@@ -4759,7 +4984,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D137" t="s">
         <v>11</v>
@@ -4796,7 +5021,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D139" t="s">
         <v>11</v>
@@ -4833,7 +5058,7 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D141" t="s">
         <v>11</v>
@@ -4870,7 +5095,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D143" t="s">
         <v>11</v>
@@ -4907,7 +5132,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D145" t="s">
         <v>11</v>
@@ -4944,7 +5169,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D147" t="s">
         <v>11</v>
@@ -4981,7 +5206,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D149" t="s">
         <v>11</v>
@@ -5018,7 +5243,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D151" t="s">
         <v>11</v>
@@ -5055,7 +5280,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D153" t="s">
         <v>11</v>
@@ -5087,7 +5312,7 @@
         <v>17</v>
       </c>
       <c r="H154" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -5098,7 +5323,7 @@
         <v>127</v>
       </c>
       <c r="C155" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D155" t="s">
         <v>11</v>
@@ -5124,7 +5349,7 @@
         <v>127</v>
       </c>
       <c r="C156" t="s">
-        <v>176</v>
+        <v>416</v>
       </c>
       <c r="D156" t="s">
         <v>11</v>
@@ -5144,7 +5369,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D157" t="s">
         <v>11</v>
@@ -5155,13 +5380,13 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>176</v>
+      </c>
+      <c r="B158" t="s">
+        <v>127</v>
+      </c>
+      <c r="C158" t="s">
         <v>177</v>
-      </c>
-      <c r="B158" t="s">
-        <v>127</v>
-      </c>
-      <c r="C158" t="s">
-        <v>178</v>
       </c>
       <c r="D158" t="s">
         <v>11</v>
@@ -5181,7 +5406,7 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D159" t="s">
         <v>11</v>
@@ -5192,13 +5417,13 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>178</v>
+      </c>
+      <c r="B160" t="s">
+        <v>127</v>
+      </c>
+      <c r="C160" t="s">
         <v>179</v>
-      </c>
-      <c r="B160" t="s">
-        <v>127</v>
-      </c>
-      <c r="C160" t="s">
-        <v>180</v>
       </c>
       <c r="D160" t="s">
         <v>11</v>
@@ -5218,7 +5443,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D161" t="s">
         <v>11</v>
@@ -5229,13 +5454,13 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B162" t="s">
         <v>127</v>
       </c>
       <c r="C162" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D162" t="s">
         <v>11</v>
@@ -5255,7 +5480,7 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D163" t="s">
         <v>11</v>
@@ -5266,14 +5491,14 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>181</v>
+      </c>
+      <c r="B164" t="s">
+        <v>127</v>
+      </c>
+      <c r="C164" t="s">
         <v>182</v>
       </c>
-      <c r="B164" t="s">
-        <v>127</v>
-      </c>
-      <c r="C164" t="s">
-        <v>183</v>
-      </c>
       <c r="D164" t="s">
         <v>11</v>
       </c>
@@ -5287,18 +5512,18 @@
         <v>17</v>
       </c>
       <c r="H164" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B165" t="s">
         <v>127</v>
       </c>
       <c r="C165" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D165" t="s">
         <v>11</v>
@@ -5318,13 +5543,13 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>183</v>
+      </c>
+      <c r="B166" t="s">
+        <v>127</v>
+      </c>
+      <c r="C166" t="s">
         <v>184</v>
-      </c>
-      <c r="B166" t="s">
-        <v>127</v>
-      </c>
-      <c r="C166" t="s">
-        <v>185</v>
       </c>
       <c r="D166" t="s">
         <v>11</v>
@@ -5344,7 +5569,7 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D167" t="s">
         <v>11</v>
@@ -5355,13 +5580,13 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>185</v>
+      </c>
+      <c r="B168" t="s">
+        <v>127</v>
+      </c>
+      <c r="C168" t="s">
         <v>186</v>
-      </c>
-      <c r="B168" t="s">
-        <v>127</v>
-      </c>
-      <c r="C168" t="s">
-        <v>187</v>
       </c>
       <c r="D168" t="s">
         <v>11</v>
@@ -5381,7 +5606,7 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D169" t="s">
         <v>11</v>
@@ -5392,14 +5617,14 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>187</v>
+      </c>
+      <c r="B170" t="s">
+        <v>127</v>
+      </c>
+      <c r="C170" t="s">
         <v>188</v>
       </c>
-      <c r="B170" t="s">
-        <v>127</v>
-      </c>
-      <c r="C170" t="s">
-        <v>189</v>
-      </c>
       <c r="D170" t="s">
         <v>11</v>
       </c>
@@ -5413,18 +5638,18 @@
         <v>17</v>
       </c>
       <c r="H170" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B171" t="s">
         <v>127</v>
       </c>
       <c r="C171" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D171" t="s">
         <v>11</v>
@@ -5444,13 +5669,13 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>189</v>
+      </c>
+      <c r="B172" t="s">
+        <v>127</v>
+      </c>
+      <c r="C172" t="s">
         <v>190</v>
-      </c>
-      <c r="B172" t="s">
-        <v>127</v>
-      </c>
-      <c r="C172" t="s">
-        <v>191</v>
       </c>
       <c r="D172" t="s">
         <v>11</v>
@@ -5470,7 +5695,7 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D173" t="s">
         <v>11</v>
@@ -5481,13 +5706,13 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>191</v>
+      </c>
+      <c r="B174" t="s">
+        <v>127</v>
+      </c>
+      <c r="C174" t="s">
         <v>192</v>
-      </c>
-      <c r="B174" t="s">
-        <v>127</v>
-      </c>
-      <c r="C174" t="s">
-        <v>193</v>
       </c>
       <c r="D174" t="s">
         <v>11</v>
@@ -5507,13 +5732,13 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B175" t="s">
         <v>127</v>
       </c>
       <c r="C175" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D175" t="s">
         <v>11</v>
@@ -5533,13 +5758,13 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B176" t="s">
         <v>127</v>
       </c>
       <c r="C176" t="s">
-        <v>195</v>
+        <v>345</v>
       </c>
       <c r="D176" t="s">
         <v>11</v>
@@ -5554,18 +5779,18 @@
         <v>17</v>
       </c>
       <c r="H176" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B177" t="s">
         <v>127</v>
       </c>
       <c r="C177" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D177" t="s">
         <v>11</v>
@@ -5585,13 +5810,13 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B178" t="s">
         <v>127</v>
       </c>
       <c r="C178" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D178" t="s">
         <v>11</v>
@@ -5611,7 +5836,7 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D179" t="s">
         <v>11</v>
@@ -5622,13 +5847,13 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B180" t="s">
         <v>127</v>
       </c>
       <c r="C180" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D180" t="s">
         <v>11</v>
@@ -5648,7 +5873,7 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D181" t="s">
         <v>11</v>
@@ -5659,13 +5884,13 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B182" t="s">
         <v>127</v>
       </c>
       <c r="C182" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D182" t="s">
         <v>11</v>
@@ -5685,7 +5910,7 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D183" t="s">
         <v>11</v>
@@ -5696,13 +5921,13 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B184" t="s">
         <v>127</v>
       </c>
       <c r="C184" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D184" t="s">
         <v>11</v>
@@ -5722,7 +5947,7 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D185" t="s">
         <v>11</v>
@@ -5733,13 +5958,13 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B186" t="s">
         <v>127</v>
       </c>
       <c r="C186" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D186" t="s">
         <v>11</v>
@@ -5759,7 +5984,7 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D187" t="s">
         <v>11</v>
@@ -5770,13 +5995,13 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B188" t="s">
         <v>127</v>
       </c>
       <c r="C188" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D188" t="s">
         <v>11</v>
@@ -5796,7 +6021,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D189" t="s">
         <v>11</v>
@@ -5807,13 +6032,13 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B190" t="s">
         <v>127</v>
       </c>
       <c r="C190" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D190" t="s">
         <v>11</v>
@@ -5833,7 +6058,7 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D191" t="s">
         <v>11</v>
@@ -5844,13 +6069,13 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B192" t="s">
         <v>127</v>
       </c>
       <c r="C192" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D192" t="s">
         <v>11</v>
@@ -5870,7 +6095,7 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D193" t="s">
         <v>11</v>
@@ -5881,13 +6106,13 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B194" t="s">
         <v>127</v>
       </c>
       <c r="C194" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D194" t="s">
         <v>11</v>
@@ -5907,7 +6132,7 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D195" t="s">
         <v>11</v>
@@ -5918,13 +6143,13 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B196" t="s">
         <v>127</v>
       </c>
       <c r="C196" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D196" t="s">
         <v>11</v>
@@ -5944,7 +6169,7 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D197" t="s">
         <v>11</v>
@@ -5955,13 +6180,13 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B198" t="s">
         <v>127</v>
       </c>
       <c r="C198" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D198" t="s">
         <v>11</v>
@@ -5981,7 +6206,7 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D199" t="s">
         <v>11</v>
@@ -5992,13 +6217,13 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B200" t="s">
         <v>127</v>
       </c>
       <c r="C200" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D200" t="s">
         <v>11</v>
@@ -6018,7 +6243,7 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D201" t="s">
         <v>11</v>
@@ -6029,13 +6254,13 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B202" t="s">
         <v>127</v>
       </c>
       <c r="C202" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D202" t="s">
         <v>11</v>
@@ -6055,7 +6280,7 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D203" t="s">
         <v>11</v>
@@ -6066,13 +6291,13 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B204" t="s">
         <v>127</v>
       </c>
       <c r="C204" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D204" t="s">
         <v>11</v>
@@ -6092,7 +6317,7 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D205" t="s">
         <v>11</v>
@@ -6103,13 +6328,13 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B206" t="s">
         <v>127</v>
       </c>
       <c r="C206" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D206" t="s">
         <v>11</v>
@@ -6129,7 +6354,7 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D207" t="s">
         <v>11</v>
@@ -6140,13 +6365,13 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B208" t="s">
         <v>127</v>
       </c>
       <c r="C208" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D208" t="s">
         <v>11</v>
@@ -6166,7 +6391,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D209" t="s">
         <v>11</v>
@@ -6177,13 +6402,13 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B210" t="s">
         <v>127</v>
       </c>
       <c r="C210" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D210" t="s">
         <v>11</v>
@@ -6203,7 +6428,7 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D211" t="s">
         <v>11</v>
@@ -6214,13 +6439,13 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B212" t="s">
         <v>127</v>
       </c>
       <c r="C212" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D212" t="s">
         <v>11</v>
@@ -6240,7 +6465,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D213" t="s">
         <v>11</v>
@@ -6251,13 +6476,13 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B214" t="s">
         <v>127</v>
       </c>
       <c r="C214" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D214" t="s">
         <v>11</v>
@@ -6277,7 +6502,7 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D215" t="s">
         <v>11</v>
@@ -6288,13 +6513,13 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B216" t="s">
         <v>127</v>
       </c>
       <c r="C216" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D216" t="s">
         <v>11</v>
@@ -6314,7 +6539,7 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D217" t="s">
         <v>11</v>
@@ -6325,13 +6550,13 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B218" t="s">
         <v>127</v>
       </c>
       <c r="C218" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D218" t="s">
         <v>11</v>
@@ -6351,7 +6576,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D219" t="s">
         <v>11</v>
@@ -6362,13 +6587,13 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B220" t="s">
         <v>127</v>
       </c>
       <c r="C220" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D220" t="s">
         <v>11</v>
@@ -6388,7 +6613,7 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D221" t="s">
         <v>11</v>
@@ -6399,13 +6624,13 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B222" t="s">
         <v>127</v>
       </c>
       <c r="C222" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D222" t="s">
         <v>11</v>
@@ -6425,7 +6650,7 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D223" t="s">
         <v>11</v>
@@ -6436,13 +6661,13 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B224" t="s">
         <v>127</v>
       </c>
       <c r="C224" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D224" t="s">
         <v>11</v>
@@ -6462,7 +6687,7 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D225" t="s">
         <v>11</v>
@@ -6473,13 +6698,13 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B226" t="s">
         <v>127</v>
       </c>
       <c r="C226" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D226" t="s">
         <v>11</v>
@@ -6499,7 +6724,7 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D227" t="s">
         <v>11</v>
@@ -6510,13 +6735,13 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B228" t="s">
         <v>127</v>
       </c>
       <c r="C228" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D228" t="s">
         <v>11</v>
@@ -6536,7 +6761,7 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D229" t="s">
         <v>11</v>
@@ -6547,13 +6772,13 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B230" t="s">
         <v>127</v>
       </c>
       <c r="C230" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D230" t="s">
         <v>11</v>
@@ -6573,7 +6798,7 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D231" t="s">
         <v>11</v>
@@ -6584,13 +6809,13 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B232" t="s">
         <v>127</v>
       </c>
       <c r="C232" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D232" t="s">
         <v>11</v>
@@ -6610,7 +6835,7 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D233" t="s">
         <v>11</v>
@@ -6621,13 +6846,13 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B234" t="s">
         <v>127</v>
       </c>
       <c r="C234" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D234" t="s">
         <v>11</v>
@@ -6647,7 +6872,7 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D235" t="s">
         <v>11</v>
@@ -6658,13 +6883,13 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B236" t="s">
         <v>127</v>
       </c>
       <c r="C236" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D236" t="s">
         <v>11</v>
@@ -6684,7 +6909,7 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D237" t="s">
         <v>11</v>
@@ -6695,13 +6920,13 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B238" t="s">
         <v>127</v>
       </c>
       <c r="C238" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D238" t="s">
         <v>11</v>
@@ -6721,7 +6946,7 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D239" t="s">
         <v>11</v>
@@ -6732,13 +6957,13 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B240" t="s">
         <v>127</v>
       </c>
       <c r="C240" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D240" t="s">
         <v>11</v>
@@ -6758,7 +6983,7 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D241" t="s">
         <v>11</v>
@@ -6769,13 +6994,13 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B242" t="s">
         <v>127</v>
       </c>
       <c r="C242" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D242" t="s">
         <v>11</v>
@@ -6790,18 +7015,18 @@
         <v>17</v>
       </c>
       <c r="H242" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B243" t="s">
         <v>127</v>
       </c>
       <c r="C243" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D243" t="s">
         <v>11</v>
@@ -6821,13 +7046,13 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B244" t="s">
         <v>127</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D244" t="s">
         <v>11</v>
@@ -6847,7 +7072,7 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D245" t="s">
         <v>11</v>
@@ -6858,13 +7083,13 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B246" t="s">
         <v>127</v>
       </c>
       <c r="C246" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>99</v>
@@ -6884,7 +7109,7 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D247" t="s">
         <v>11</v>
@@ -6895,13 +7120,13 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>260</v>
+      </c>
+      <c r="B248" t="s">
+        <v>127</v>
+      </c>
+      <c r="C248" t="s">
         <v>262</v>
-      </c>
-      <c r="B248" t="s">
-        <v>127</v>
-      </c>
-      <c r="C248" t="s">
-        <v>264</v>
       </c>
       <c r="D248" t="s">
         <v>11</v>
@@ -6921,7 +7146,7 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D249" t="s">
         <v>11</v>
@@ -6932,13 +7157,13 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B250" t="s">
         <v>127</v>
       </c>
       <c r="C250" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D250" t="s">
         <v>11</v>
@@ -6958,7 +7183,7 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D251" t="s">
         <v>11</v>
@@ -6969,13 +7194,13 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B252" t="s">
         <v>127</v>
       </c>
       <c r="C252" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D252" t="s">
         <v>11</v>
@@ -6995,7 +7220,7 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D253" t="s">
         <v>11</v>
@@ -7006,13 +7231,13 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B254" t="s">
         <v>127</v>
       </c>
       <c r="C254" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D254" t="s">
         <v>11</v>
@@ -7032,7 +7257,7 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D255" t="s">
         <v>11</v>
@@ -7043,13 +7268,13 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B256" t="s">
         <v>127</v>
       </c>
       <c r="C256" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D256" t="s">
         <v>11</v>
@@ -7069,7 +7294,7 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D257" t="s">
         <v>11</v>
@@ -7080,13 +7305,13 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B258" t="s">
         <v>127</v>
       </c>
       <c r="C258" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D258" t="s">
         <v>11</v>
@@ -7106,7 +7331,7 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D259" t="s">
         <v>11</v>
@@ -7117,13 +7342,13 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B260" t="s">
         <v>127</v>
       </c>
       <c r="C260" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D260" t="s">
         <v>11</v>
@@ -7143,7 +7368,7 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D261" t="s">
         <v>11</v>
@@ -7154,13 +7379,13 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B262" t="s">
         <v>127</v>
       </c>
       <c r="C262" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D262" t="s">
         <v>11</v>
@@ -7180,7 +7405,7 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D263" t="s">
         <v>11</v>
@@ -7191,13 +7416,13 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B264" t="s">
         <v>127</v>
       </c>
       <c r="C264" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D264" t="s">
         <v>11</v>
@@ -7217,7 +7442,7 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D265" t="s">
         <v>11</v>
@@ -7228,13 +7453,13 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B266" t="s">
         <v>127</v>
       </c>
       <c r="C266" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D266" t="s">
         <v>11</v>
@@ -7254,7 +7479,7 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D267" t="s">
         <v>11</v>
@@ -7265,13 +7490,13 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B268" t="s">
         <v>127</v>
       </c>
       <c r="C268" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D268" t="s">
         <v>11</v>
@@ -7291,7 +7516,7 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D269" t="s">
         <v>11</v>
@@ -7302,13 +7527,13 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B270" t="s">
         <v>127</v>
       </c>
       <c r="C270" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D270" t="s">
         <v>11</v>
@@ -7328,7 +7553,7 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D271" t="s">
         <v>11</v>
@@ -7339,13 +7564,13 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B272" t="s">
         <v>127</v>
       </c>
       <c r="C272" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D272" t="s">
         <v>11</v>
@@ -7365,7 +7590,7 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D273" t="s">
         <v>11</v>
@@ -7376,13 +7601,13 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B274" t="s">
         <v>127</v>
       </c>
       <c r="C274" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D274" t="s">
         <v>11</v>
@@ -7402,7 +7627,7 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D275" t="s">
         <v>11</v>
@@ -7413,13 +7638,13 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B276" t="s">
         <v>127</v>
       </c>
       <c r="C276" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D276" t="s">
         <v>11</v>
@@ -7439,7 +7664,7 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D277" t="s">
         <v>11</v>
@@ -7450,13 +7675,13 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B278" t="s">
         <v>127</v>
       </c>
       <c r="C278" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D278" t="s">
         <v>11</v>
@@ -7471,18 +7696,18 @@
         <v>17</v>
       </c>
       <c r="H278" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B279" t="s">
         <v>127</v>
       </c>
       <c r="C279" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D279" t="s">
         <v>11</v>
@@ -7502,13 +7727,13 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B280" t="s">
         <v>127</v>
       </c>
       <c r="C280" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D280" t="s">
         <v>11</v>
@@ -7523,18 +7748,18 @@
         <v>17</v>
       </c>
       <c r="H280" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B281" t="s">
         <v>127</v>
       </c>
       <c r="C281" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D281" t="s">
         <v>11</v>
@@ -7554,13 +7779,13 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B282" t="s">
         <v>127</v>
       </c>
       <c r="C282" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D282" t="s">
         <v>11</v>
@@ -7580,7 +7805,7 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D283" t="s">
         <v>11</v>
@@ -7591,13 +7816,13 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B284" t="s">
         <v>127</v>
       </c>
       <c r="C284" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D284" t="s">
         <v>11</v>
@@ -7617,7 +7842,7 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D285" t="s">
         <v>11</v>
@@ -7628,22 +7853,22 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>299</v>
+      </c>
+      <c r="B286" t="s">
+        <v>300</v>
+      </c>
+      <c r="C286" t="s">
         <v>301</v>
       </c>
-      <c r="B286" t="s">
-        <v>302</v>
-      </c>
-      <c r="C286" t="s">
-        <v>303</v>
-      </c>
       <c r="D286" t="s">
         <v>11</v>
       </c>
       <c r="E286" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F286" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G286" t="s">
         <v>22</v>
@@ -7654,10 +7879,10 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E287" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H287" t="s">
         <v>11</v>
@@ -7665,22 +7890,22 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B288" t="s">
+        <v>300</v>
+      </c>
+      <c r="C288" t="s">
         <v>302</v>
       </c>
-      <c r="C288" t="s">
-        <v>304</v>
-      </c>
       <c r="D288" t="s">
         <v>11</v>
       </c>
       <c r="E288" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F288" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G288" t="s">
         <v>22</v>
@@ -7691,7 +7916,7 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H289" t="s">
         <v>11</v>
@@ -7699,51 +7924,51 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B290" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C290" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D290" t="s">
         <v>11</v>
       </c>
       <c r="E290" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F290" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G290" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H290" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B291" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C291" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D291" t="s">
         <v>11</v>
       </c>
       <c r="E291" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F291" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G291" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H291" t="s">
         <v>11</v>
@@ -7751,51 +7976,51 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B292" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C292" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D292" t="s">
         <v>11</v>
       </c>
       <c r="E292" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F292" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G292" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H292" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B293" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C293" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D293" t="s">
         <v>11</v>
       </c>
       <c r="E293" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F293" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G293" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H293" t="s">
         <v>11</v>
@@ -7803,53 +8028,1130 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
+        <v>307</v>
+      </c>
+      <c r="B294" t="s">
+        <v>303</v>
+      </c>
+      <c r="C294" t="s">
         <v>309</v>
       </c>
-      <c r="B294" t="s">
-        <v>305</v>
-      </c>
-      <c r="C294" t="s">
-        <v>311</v>
-      </c>
       <c r="D294" t="s">
         <v>11</v>
       </c>
       <c r="E294" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F294" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G294" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H294" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B295" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C295" t="s">
+        <v>342</v>
+      </c>
+      <c r="D295" t="s">
+        <v>11</v>
+      </c>
+      <c r="E295" t="s">
+        <v>303</v>
+      </c>
+      <c r="F295" t="s">
+        <v>303</v>
+      </c>
+      <c r="G295" t="s">
+        <v>304</v>
+      </c>
+      <c r="H295" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>347</v>
+      </c>
+      <c r="B296" t="s">
+        <v>9</v>
+      </c>
+      <c r="C296" t="s">
+        <v>348</v>
+      </c>
+      <c r="D296" t="s">
+        <v>11</v>
+      </c>
+      <c r="E296" t="s">
+        <v>9</v>
+      </c>
+      <c r="F296" t="s">
+        <v>9</v>
+      </c>
+      <c r="G296" t="s">
+        <v>12</v>
+      </c>
+      <c r="H296" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>312</v>
+      </c>
+      <c r="H297" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>349</v>
+      </c>
+      <c r="B298" t="s">
+        <v>350</v>
+      </c>
+      <c r="C298" t="s">
+        <v>351</v>
+      </c>
+      <c r="D298" t="s">
+        <v>11</v>
+      </c>
+      <c r="E298" t="s">
+        <v>350</v>
+      </c>
+      <c r="F298" t="s">
+        <v>350</v>
+      </c>
+      <c r="G298" t="s">
+        <v>352</v>
+      </c>
+      <c r="H298" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>312</v>
+      </c>
+      <c r="H299" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>353</v>
+      </c>
+      <c r="B300" t="s">
+        <v>354</v>
+      </c>
+      <c r="C300" t="s">
+        <v>355</v>
+      </c>
+      <c r="D300" t="s">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>354</v>
+      </c>
+      <c r="F300" t="s">
+        <v>356</v>
+      </c>
+      <c r="G300" t="s">
+        <v>16</v>
+      </c>
+      <c r="H300" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>353</v>
+      </c>
+      <c r="B301" t="s">
+        <v>354</v>
+      </c>
+      <c r="C301" t="s">
+        <v>417</v>
+      </c>
+      <c r="D301" t="s">
+        <v>11</v>
+      </c>
+      <c r="E301" t="s">
+        <v>354</v>
+      </c>
+      <c r="F301" t="s">
+        <v>356</v>
+      </c>
+      <c r="G301" t="s">
+        <v>16</v>
+      </c>
+      <c r="H301" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>357</v>
+      </c>
+      <c r="B302" t="s">
+        <v>358</v>
+      </c>
+      <c r="C302" t="s">
+        <v>359</v>
+      </c>
+      <c r="D302" t="s">
+        <v>11</v>
+      </c>
+      <c r="E302" t="s">
+        <v>358</v>
+      </c>
+      <c r="F302" t="s">
+        <v>360</v>
+      </c>
+      <c r="G302" t="s">
+        <v>17</v>
+      </c>
+      <c r="H302" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>312</v>
+      </c>
+      <c r="H303" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>361</v>
+      </c>
+      <c r="B304" t="s">
+        <v>362</v>
+      </c>
+      <c r="C304" t="s">
+        <v>363</v>
+      </c>
+      <c r="D304" t="s">
+        <v>11</v>
+      </c>
+      <c r="E304" t="s">
+        <v>362</v>
+      </c>
+      <c r="F304" t="s">
+        <v>362</v>
+      </c>
+      <c r="G304" t="s">
+        <v>22</v>
+      </c>
+      <c r="H304" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>312</v>
+      </c>
+      <c r="H305" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>364</v>
+      </c>
+      <c r="B306" t="s">
+        <v>29</v>
+      </c>
+      <c r="C306" t="s">
+        <v>365</v>
+      </c>
+      <c r="D306" t="s">
+        <v>11</v>
+      </c>
+      <c r="E306" t="s">
+        <v>29</v>
+      </c>
+      <c r="F306" t="s">
+        <v>29</v>
+      </c>
+      <c r="G306" t="s">
+        <v>16</v>
+      </c>
+      <c r="H306" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>312</v>
+      </c>
+      <c r="H307" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>366</v>
+      </c>
+      <c r="B308" t="s">
+        <v>29</v>
+      </c>
+      <c r="C308" t="s">
+        <v>367</v>
+      </c>
+      <c r="D308" t="s">
+        <v>11</v>
+      </c>
+      <c r="E308" t="s">
+        <v>29</v>
+      </c>
+      <c r="F308" t="s">
+        <v>29</v>
+      </c>
+      <c r="G308" t="s">
+        <v>16</v>
+      </c>
+      <c r="H308" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>312</v>
+      </c>
+      <c r="H309" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>368</v>
+      </c>
+      <c r="B310" t="s">
+        <v>369</v>
+      </c>
+      <c r="C310" t="s">
+        <v>370</v>
+      </c>
+      <c r="D310" t="s">
+        <v>11</v>
+      </c>
+      <c r="E310" t="s">
+        <v>369</v>
+      </c>
+      <c r="F310" t="s">
+        <v>369</v>
+      </c>
+      <c r="G310" t="s">
+        <v>16</v>
+      </c>
+      <c r="H310" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>312</v>
+      </c>
+      <c r="H311" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>372</v>
+      </c>
+      <c r="B312" t="s">
+        <v>373</v>
+      </c>
+      <c r="C312" t="s">
+        <v>374</v>
+      </c>
+      <c r="D312" t="s">
+        <v>11</v>
+      </c>
+      <c r="E312" t="s">
+        <v>373</v>
+      </c>
+      <c r="F312" t="s">
+        <v>373</v>
+      </c>
+      <c r="G312" t="s">
+        <v>375</v>
+      </c>
+      <c r="H312" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>372</v>
+      </c>
+      <c r="B313" t="s">
+        <v>373</v>
+      </c>
+      <c r="C313" t="s">
+        <v>418</v>
+      </c>
+      <c r="D313" t="s">
+        <v>11</v>
+      </c>
+      <c r="E313" t="s">
+        <v>373</v>
+      </c>
+      <c r="F313" t="s">
+        <v>373</v>
+      </c>
+      <c r="G313" t="s">
+        <v>375</v>
+      </c>
+      <c r="H313" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>376</v>
+      </c>
+      <c r="B314" t="s">
+        <v>373</v>
+      </c>
+      <c r="C314" t="s">
+        <v>377</v>
+      </c>
+      <c r="D314" t="s">
+        <v>11</v>
+      </c>
+      <c r="E314" t="s">
+        <v>373</v>
+      </c>
+      <c r="F314" t="s">
+        <v>373</v>
+      </c>
+      <c r="G314" t="s">
+        <v>375</v>
+      </c>
+      <c r="H314" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>376</v>
+      </c>
+      <c r="B315" t="s">
+        <v>373</v>
+      </c>
+      <c r="C315" t="s">
+        <v>419</v>
+      </c>
+      <c r="D315" t="s">
+        <v>11</v>
+      </c>
+      <c r="E315" t="s">
+        <v>373</v>
+      </c>
+      <c r="F315" t="s">
+        <v>373</v>
+      </c>
+      <c r="G315" t="s">
+        <v>375</v>
+      </c>
+      <c r="H315" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>378</v>
+      </c>
+      <c r="B316" t="s">
+        <v>373</v>
+      </c>
+      <c r="C316" t="s">
+        <v>379</v>
+      </c>
+      <c r="D316" t="s">
+        <v>11</v>
+      </c>
+      <c r="E316" t="s">
+        <v>373</v>
+      </c>
+      <c r="F316" t="s">
+        <v>373</v>
+      </c>
+      <c r="G316" t="s">
+        <v>375</v>
+      </c>
+      <c r="H316" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>312</v>
+      </c>
+      <c r="H317" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>380</v>
+      </c>
+      <c r="B318" t="s">
+        <v>373</v>
+      </c>
+      <c r="C318" t="s">
+        <v>381</v>
+      </c>
+      <c r="D318" t="s">
+        <v>382</v>
+      </c>
+      <c r="E318" t="s">
+        <v>373</v>
+      </c>
+      <c r="F318" t="s">
+        <v>373</v>
+      </c>
+      <c r="G318" t="s">
+        <v>375</v>
+      </c>
+      <c r="H318" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>312</v>
+      </c>
+      <c r="H319" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>383</v>
+      </c>
+      <c r="B320" t="s">
+        <v>373</v>
+      </c>
+      <c r="C320" t="s">
+        <v>381</v>
+      </c>
+      <c r="D320" t="s">
+        <v>384</v>
+      </c>
+      <c r="E320" t="s">
+        <v>373</v>
+      </c>
+      <c r="F320" t="s">
+        <v>373</v>
+      </c>
+      <c r="G320" t="s">
+        <v>375</v>
+      </c>
+      <c r="H320" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>312</v>
+      </c>
+      <c r="H321" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>385</v>
+      </c>
+      <c r="B322" t="s">
+        <v>386</v>
+      </c>
+      <c r="C322" t="s">
+        <v>387</v>
+      </c>
+      <c r="D322" t="s">
+        <v>11</v>
+      </c>
+      <c r="E322" t="s">
+        <v>386</v>
+      </c>
+      <c r="F322" t="s">
+        <v>388</v>
+      </c>
+      <c r="G322" t="s">
+        <v>389</v>
+      </c>
+      <c r="H322" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>385</v>
+      </c>
+      <c r="B323" t="s">
+        <v>386</v>
+      </c>
+      <c r="C323" t="s">
+        <v>420</v>
+      </c>
+      <c r="D323" t="s">
+        <v>11</v>
+      </c>
+      <c r="E323" t="s">
+        <v>386</v>
+      </c>
+      <c r="F323" t="s">
+        <v>388</v>
+      </c>
+      <c r="G323" t="s">
+        <v>389</v>
+      </c>
+      <c r="H323" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>390</v>
+      </c>
+      <c r="B324" t="s">
+        <v>391</v>
+      </c>
+      <c r="C324" t="s">
+        <v>392</v>
+      </c>
+      <c r="D324" t="s">
+        <v>11</v>
+      </c>
+      <c r="E324" t="s">
+        <v>391</v>
+      </c>
+      <c r="F324" t="s">
+        <v>391</v>
+      </c>
+      <c r="G324" t="s">
+        <v>42</v>
+      </c>
+      <c r="H324" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>312</v>
+      </c>
+      <c r="H325" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>393</v>
+      </c>
+      <c r="B326" t="s">
+        <v>391</v>
+      </c>
+      <c r="C326" t="s">
+        <v>394</v>
+      </c>
+      <c r="D326" t="s">
+        <v>11</v>
+      </c>
+      <c r="E326" t="s">
+        <v>391</v>
+      </c>
+      <c r="F326" t="s">
+        <v>391</v>
+      </c>
+      <c r="G326" t="s">
+        <v>42</v>
+      </c>
+      <c r="H326" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>312</v>
+      </c>
+      <c r="H327" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>395</v>
+      </c>
+      <c r="B328" t="s">
+        <v>396</v>
+      </c>
+      <c r="C328" t="s">
+        <v>397</v>
+      </c>
+      <c r="D328" t="s">
+        <v>11</v>
+      </c>
+      <c r="E328" t="s">
+        <v>396</v>
+      </c>
+      <c r="F328" t="s">
+        <v>396</v>
+      </c>
+      <c r="G328" t="s">
+        <v>22</v>
+      </c>
+      <c r="H328" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>312</v>
+      </c>
+      <c r="H329" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>395</v>
+      </c>
+      <c r="B330" t="s">
+        <v>396</v>
+      </c>
+      <c r="C330" t="s">
+        <v>398</v>
+      </c>
+      <c r="D330" t="s">
+        <v>11</v>
+      </c>
+      <c r="E330" t="s">
+        <v>396</v>
+      </c>
+      <c r="F330" t="s">
+        <v>396</v>
+      </c>
+      <c r="G330" t="s">
+        <v>22</v>
+      </c>
+      <c r="H330" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>312</v>
+      </c>
+      <c r="H331" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>124</v>
+      </c>
+      <c r="B332" t="s">
+        <v>123</v>
+      </c>
+      <c r="C332" t="s">
+        <v>125</v>
+      </c>
+      <c r="D332" t="s">
+        <v>11</v>
+      </c>
+      <c r="E332" t="s">
+        <v>123</v>
+      </c>
+      <c r="F332" t="s">
+        <v>123</v>
+      </c>
+      <c r="G332" t="s">
+        <v>27</v>
+      </c>
+      <c r="H332" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>124</v>
+      </c>
+      <c r="B333" t="s">
+        <v>123</v>
+      </c>
+      <c r="C333" t="s">
+        <v>334</v>
+      </c>
+      <c r="D333" t="s">
+        <v>11</v>
+      </c>
+      <c r="E333" t="s">
+        <v>123</v>
+      </c>
+      <c r="F333" t="s">
+        <v>123</v>
+      </c>
+      <c r="G333" t="s">
+        <v>27</v>
+      </c>
+      <c r="H333" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>399</v>
+      </c>
+      <c r="B334" t="s">
+        <v>123</v>
+      </c>
+      <c r="C334" t="s">
+        <v>363</v>
+      </c>
+      <c r="D334" t="s">
+        <v>11</v>
+      </c>
+      <c r="E334" t="s">
+        <v>123</v>
+      </c>
+      <c r="F334" t="s">
+        <v>123</v>
+      </c>
+      <c r="G334" t="s">
+        <v>27</v>
+      </c>
+      <c r="H334" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>312</v>
+      </c>
+      <c r="H335" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>400</v>
+      </c>
+      <c r="B336" t="s">
+        <v>401</v>
+      </c>
+      <c r="C336" t="s">
+        <v>402</v>
+      </c>
+      <c r="D336" t="s">
+        <v>11</v>
+      </c>
+      <c r="E336" t="s">
+        <v>401</v>
+      </c>
+      <c r="F336" t="s">
+        <v>401</v>
+      </c>
+      <c r="G336" t="s">
+        <v>22</v>
+      </c>
+      <c r="H336" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>400</v>
+      </c>
+      <c r="B337" t="s">
+        <v>401</v>
+      </c>
+      <c r="C337" t="s">
+        <v>421</v>
+      </c>
+      <c r="D337" t="s">
+        <v>11</v>
+      </c>
+      <c r="E337" t="s">
+        <v>401</v>
+      </c>
+      <c r="F337" t="s">
+        <v>401</v>
+      </c>
+      <c r="G337" t="s">
+        <v>22</v>
+      </c>
+      <c r="H337" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>403</v>
+      </c>
+      <c r="B338" t="s">
+        <v>127</v>
+      </c>
+      <c r="C338" t="s">
+        <v>404</v>
+      </c>
+      <c r="D338" t="s">
+        <v>11</v>
+      </c>
+      <c r="E338" t="s">
+        <v>127</v>
+      </c>
+      <c r="F338" t="s">
+        <v>127</v>
+      </c>
+      <c r="G338" t="s">
+        <v>17</v>
+      </c>
+      <c r="H338" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>403</v>
+      </c>
+      <c r="B339" t="s">
+        <v>127</v>
+      </c>
+      <c r="C339" t="s">
+        <v>422</v>
+      </c>
+      <c r="D339" t="s">
+        <v>11</v>
+      </c>
+      <c r="E339" t="s">
+        <v>127</v>
+      </c>
+      <c r="F339" t="s">
+        <v>127</v>
+      </c>
+      <c r="G339" t="s">
+        <v>17</v>
+      </c>
+      <c r="H339" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>405</v>
+      </c>
+      <c r="B340" t="s">
+        <v>127</v>
+      </c>
+      <c r="C340" t="s">
+        <v>406</v>
+      </c>
+      <c r="D340" t="s">
+        <v>11</v>
+      </c>
+      <c r="E340" t="s">
+        <v>127</v>
+      </c>
+      <c r="F340" t="s">
+        <v>127</v>
+      </c>
+      <c r="G340" t="s">
+        <v>17</v>
+      </c>
+      <c r="H340" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>312</v>
+      </c>
+      <c r="H341" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>193</v>
+      </c>
+      <c r="B342" t="s">
+        <v>127</v>
+      </c>
+      <c r="C342" t="s">
         <v>345</v>
       </c>
-      <c r="D295" t="s">
-        <v>11</v>
-      </c>
-      <c r="E295" t="s">
-        <v>305</v>
-      </c>
-      <c r="F295" t="s">
-        <v>305</v>
-      </c>
-      <c r="G295" t="s">
-        <v>306</v>
-      </c>
-      <c r="H295" t="s">
+      <c r="D342" t="s">
+        <v>11</v>
+      </c>
+      <c r="E342" t="s">
+        <v>127</v>
+      </c>
+      <c r="F342" t="s">
+        <v>127</v>
+      </c>
+      <c r="G342" t="s">
+        <v>17</v>
+      </c>
+      <c r="H342" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>193</v>
+      </c>
+      <c r="B343" t="s">
+        <v>127</v>
+      </c>
+      <c r="C343" t="s">
+        <v>415</v>
+      </c>
+      <c r="D343" t="s">
+        <v>11</v>
+      </c>
+      <c r="E343" t="s">
+        <v>127</v>
+      </c>
+      <c r="F343" t="s">
+        <v>127</v>
+      </c>
+      <c r="G343" t="s">
+        <v>17</v>
+      </c>
+      <c r="H343" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>407</v>
+      </c>
+      <c r="B344" t="s">
+        <v>408</v>
+      </c>
+      <c r="C344" t="s">
+        <v>409</v>
+      </c>
+      <c r="D344" t="s">
+        <v>11</v>
+      </c>
+      <c r="E344" t="s">
+        <v>408</v>
+      </c>
+      <c r="F344" t="s">
+        <v>408</v>
+      </c>
+      <c r="G344" t="s">
+        <v>371</v>
+      </c>
+      <c r="H344" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>312</v>
+      </c>
+      <c r="H345" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>410</v>
+      </c>
+      <c r="B346" t="s">
+        <v>408</v>
+      </c>
+      <c r="C346" t="s">
+        <v>411</v>
+      </c>
+      <c r="D346" t="s">
+        <v>11</v>
+      </c>
+      <c r="E346" t="s">
+        <v>408</v>
+      </c>
+      <c r="F346" t="s">
+        <v>408</v>
+      </c>
+      <c r="G346" t="s">
+        <v>371</v>
+      </c>
+      <c r="H346" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>410</v>
+      </c>
+      <c r="B347" t="s">
+        <v>408</v>
+      </c>
+      <c r="C347" t="s">
+        <v>412</v>
+      </c>
+      <c r="D347" t="s">
+        <v>11</v>
+      </c>
+      <c r="E347" t="s">
+        <v>408</v>
+      </c>
+      <c r="F347" t="s">
+        <v>408</v>
+      </c>
+      <c r="G347" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>299</v>
+      </c>
+      <c r="B348" t="s">
+        <v>300</v>
+      </c>
+      <c r="C348" t="s">
+        <v>413</v>
+      </c>
+      <c r="D348" t="s">
+        <v>11</v>
+      </c>
+      <c r="E348" t="s">
+        <v>300</v>
+      </c>
+      <c r="F348" t="s">
+        <v>300</v>
+      </c>
+      <c r="G348" t="s">
+        <v>22</v>
+      </c>
+      <c r="H348" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>312</v>
+      </c>
+      <c r="H349" t="s">
         <v>11</v>
       </c>
     </row>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C88D8B2-C6D0-43C3-89C9-7BDA4FE0082F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3A6F8B-1510-4DBC-BE4F-60DAD425B4A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Błędy PNA" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="388">
   <si>
     <t>Kod</t>
   </si>
@@ -1076,24 +1076,6 @@
     <t>Rondo ONZ</t>
   </si>
   <si>
-    <t>15-568</t>
-  </si>
-  <si>
-    <t>św. Proroka Eliasza</t>
-  </si>
-  <si>
-    <t>85-791</t>
-  </si>
-  <si>
-    <t>Bydgoszcz</t>
-  </si>
-  <si>
-    <t>pl. plac św. Mateusza Apostoła i Ewangelisty</t>
-  </si>
-  <si>
-    <t>kujawsko-pomorskie</t>
-  </si>
-  <si>
     <t>89-600</t>
   </si>
   <si>
@@ -1106,48 +1088,6 @@
     <t>chojnicki</t>
   </si>
   <si>
-    <t>06-413</t>
-  </si>
-  <si>
-    <t>Ciechanów</t>
-  </si>
-  <si>
-    <t>św. Rodziny</t>
-  </si>
-  <si>
-    <t>ciechanowski</t>
-  </si>
-  <si>
-    <t>42-226</t>
-  </si>
-  <si>
-    <t>Częstochowa</t>
-  </si>
-  <si>
-    <t>św. Łukasza</t>
-  </si>
-  <si>
-    <t>80-893</t>
-  </si>
-  <si>
-    <t>Bastion św. Elżbiety</t>
-  </si>
-  <si>
-    <t>80-299</t>
-  </si>
-  <si>
-    <t>Plac św. Jana Apostoła</t>
-  </si>
-  <si>
-    <t>81-402</t>
-  </si>
-  <si>
-    <t>Gdynia</t>
-  </si>
-  <si>
-    <t>bp. Dominika</t>
-  </si>
-  <si>
     <t>dolnośląskie</t>
   </si>
   <si>
@@ -1169,27 +1109,6 @@
     <t>os. Osiedle Zaułek Jugowicki</t>
   </si>
   <si>
-    <t>30-611</t>
-  </si>
-  <si>
-    <t>por. Halszki</t>
-  </si>
-  <si>
-    <t>31-046</t>
-  </si>
-  <si>
-    <t>św. Gertrudy</t>
-  </si>
-  <si>
-    <t>1-11</t>
-  </si>
-  <si>
-    <t>31-048</t>
-  </si>
-  <si>
-    <t>12-DK</t>
-  </si>
-  <si>
     <t>48-300</t>
   </si>
   <si>
@@ -1205,36 +1124,6 @@
     <t>opolskie</t>
   </si>
   <si>
-    <t>60-654</t>
-  </si>
-  <si>
-    <t>Poznań</t>
-  </si>
-  <si>
-    <t>św. Leonarda</t>
-  </si>
-  <si>
-    <t>61-465</t>
-  </si>
-  <si>
-    <t>św. Szczepana</t>
-  </si>
-  <si>
-    <t>41-711</t>
-  </si>
-  <si>
-    <t>Ruda Śląska</t>
-  </si>
-  <si>
-    <t>Dr. Jordana</t>
-  </si>
-  <si>
-    <t>gen. Bema</t>
-  </si>
-  <si>
-    <t>71-522</t>
-  </si>
-  <si>
     <t>43-100</t>
   </si>
   <si>
@@ -1250,21 +1139,9 @@
     <t>Romana Palestera</t>
   </si>
   <si>
-    <t>02-647</t>
-  </si>
-  <si>
-    <t>Rabindranatha Tagore</t>
-  </si>
-  <si>
-    <t>50-070</t>
-  </si>
-  <si>
     <t>Wrocław</t>
   </si>
   <si>
-    <t>św. Doroty</t>
-  </si>
-  <si>
     <t>50-156</t>
   </si>
   <si>
@@ -1274,12 +1151,6 @@
     <t xml:space="preserve">św. Jana </t>
   </si>
   <si>
-    <t>Góry św. Anny</t>
-  </si>
-  <si>
-    <t>Do roboty</t>
-  </si>
-  <si>
     <t>rondo ONZ</t>
   </si>
   <si>
@@ -1302,6 +1173,30 @@
   </si>
   <si>
     <t>Romana Palestra</t>
+  </si>
+  <si>
+    <t>Ostrów Mazowiecka (Komorowo)</t>
+  </si>
+  <si>
+    <t>Ostrów Mazowiecka</t>
+  </si>
+  <si>
+    <t>ostrowski</t>
+  </si>
+  <si>
+    <t>07-310</t>
+  </si>
+  <si>
+    <t>Kolejowa</t>
+  </si>
+  <si>
+    <t>Spokojna</t>
+  </si>
+  <si>
+    <t>Komorowo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ostrów Mazowiecka </t>
   </si>
 </sst>
 </file>
@@ -2180,11 +2075,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H349"/>
+  <dimension ref="A1:H317"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="38.5703125" customWidth="1"/>
     <col min="3" max="3" width="45.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5349,7 +5244,7 @@
         <v>127</v>
       </c>
       <c r="C156" t="s">
-        <v>416</v>
+        <v>373</v>
       </c>
       <c r="D156" t="s">
         <v>11</v>
@@ -8083,30 +7978,48 @@
         <v>347</v>
       </c>
       <c r="B296" t="s">
-        <v>9</v>
+        <v>348</v>
       </c>
       <c r="C296" t="s">
+        <v>349</v>
+      </c>
+      <c r="D296" t="s">
+        <v>11</v>
+      </c>
+      <c r="E296" t="s">
         <v>348</v>
       </c>
-      <c r="D296" t="s">
-        <v>11</v>
-      </c>
-      <c r="E296" t="s">
-        <v>9</v>
-      </c>
       <c r="F296" t="s">
-        <v>9</v>
+        <v>350</v>
       </c>
       <c r="G296" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H296" t="s">
-        <v>414</v>
+        <v>330</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>312</v>
+        <v>347</v>
+      </c>
+      <c r="B297" t="s">
+        <v>348</v>
+      </c>
+      <c r="C297" t="s">
+        <v>374</v>
+      </c>
+      <c r="D297" t="s">
+        <v>11</v>
+      </c>
+      <c r="E297" t="s">
+        <v>348</v>
+      </c>
+      <c r="F297" t="s">
+        <v>350</v>
+      </c>
+      <c r="G297" t="s">
+        <v>16</v>
       </c>
       <c r="H297" t="s">
         <v>11</v>
@@ -8114,33 +8027,51 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B298" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C298" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D298" t="s">
         <v>11</v>
       </c>
       <c r="E298" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F298" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G298" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H298" t="s">
-        <v>414</v>
+        <v>330</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>312</v>
+        <v>352</v>
+      </c>
+      <c r="B299" t="s">
+        <v>353</v>
+      </c>
+      <c r="C299" t="s">
+        <v>375</v>
+      </c>
+      <c r="D299" t="s">
+        <v>11</v>
+      </c>
+      <c r="E299" t="s">
+        <v>353</v>
+      </c>
+      <c r="F299" t="s">
+        <v>353</v>
+      </c>
+      <c r="G299" t="s">
+        <v>355</v>
       </c>
       <c r="H299" t="s">
         <v>11</v>
@@ -8148,25 +8079,25 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
+        <v>356</v>
+      </c>
+      <c r="B300" t="s">
         <v>353</v>
       </c>
-      <c r="B300" t="s">
-        <v>354</v>
-      </c>
       <c r="C300" t="s">
+        <v>357</v>
+      </c>
+      <c r="D300" t="s">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>353</v>
+      </c>
+      <c r="F300" t="s">
+        <v>353</v>
+      </c>
+      <c r="G300" t="s">
         <v>355</v>
-      </c>
-      <c r="D300" t="s">
-        <v>11</v>
-      </c>
-      <c r="E300" t="s">
-        <v>354</v>
-      </c>
-      <c r="F300" t="s">
-        <v>356</v>
-      </c>
-      <c r="G300" t="s">
-        <v>16</v>
       </c>
       <c r="H300" t="s">
         <v>330</v>
@@ -8174,25 +8105,25 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
+        <v>356</v>
+      </c>
+      <c r="B301" t="s">
         <v>353</v>
       </c>
-      <c r="B301" t="s">
-        <v>354</v>
-      </c>
       <c r="C301" t="s">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="D301" t="s">
         <v>11</v>
       </c>
       <c r="E301" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F301" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G301" t="s">
-        <v>16</v>
+        <v>355</v>
       </c>
       <c r="H301" t="s">
         <v>11</v>
@@ -8200,33 +8131,51 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B302" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C302" t="s">
+        <v>360</v>
+      </c>
+      <c r="D302" t="s">
+        <v>11</v>
+      </c>
+      <c r="E302" t="s">
         <v>359</v>
       </c>
-      <c r="D302" t="s">
-        <v>11</v>
-      </c>
-      <c r="E302" t="s">
-        <v>358</v>
-      </c>
       <c r="F302" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G302" t="s">
-        <v>17</v>
+        <v>362</v>
       </c>
       <c r="H302" t="s">
-        <v>414</v>
+        <v>330</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>312</v>
+        <v>358</v>
+      </c>
+      <c r="B303" t="s">
+        <v>359</v>
+      </c>
+      <c r="C303" t="s">
+        <v>377</v>
+      </c>
+      <c r="D303" t="s">
+        <v>11</v>
+      </c>
+      <c r="E303" t="s">
+        <v>359</v>
+      </c>
+      <c r="F303" t="s">
+        <v>361</v>
+      </c>
+      <c r="G303" t="s">
+        <v>362</v>
       </c>
       <c r="H303" t="s">
         <v>11</v>
@@ -8234,33 +8183,51 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>361</v>
+        <v>124</v>
       </c>
       <c r="B304" t="s">
-        <v>362</v>
+        <v>123</v>
       </c>
       <c r="C304" t="s">
-        <v>363</v>
+        <v>125</v>
       </c>
       <c r="D304" t="s">
         <v>11</v>
       </c>
       <c r="E304" t="s">
-        <v>362</v>
+        <v>123</v>
       </c>
       <c r="F304" t="s">
-        <v>362</v>
+        <v>123</v>
       </c>
       <c r="G304" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H304" t="s">
-        <v>414</v>
+        <v>330</v>
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>312</v>
+        <v>124</v>
+      </c>
+      <c r="B305" t="s">
+        <v>123</v>
+      </c>
+      <c r="C305" t="s">
+        <v>334</v>
+      </c>
+      <c r="D305" t="s">
+        <v>11</v>
+      </c>
+      <c r="E305" t="s">
+        <v>123</v>
+      </c>
+      <c r="F305" t="s">
+        <v>123</v>
+      </c>
+      <c r="G305" t="s">
+        <v>27</v>
       </c>
       <c r="H305" t="s">
         <v>11</v>
@@ -8268,10 +8235,10 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
+        <v>363</v>
+      </c>
+      <c r="B306" t="s">
         <v>364</v>
-      </c>
-      <c r="B306" t="s">
-        <v>29</v>
       </c>
       <c r="C306" t="s">
         <v>365</v>
@@ -8280,21 +8247,39 @@
         <v>11</v>
       </c>
       <c r="E306" t="s">
-        <v>29</v>
+        <v>364</v>
       </c>
       <c r="F306" t="s">
-        <v>29</v>
+        <v>364</v>
       </c>
       <c r="G306" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H306" t="s">
-        <v>414</v>
+        <v>330</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>312</v>
+        <v>363</v>
+      </c>
+      <c r="B307" t="s">
+        <v>364</v>
+      </c>
+      <c r="C307" t="s">
+        <v>378</v>
+      </c>
+      <c r="D307" t="s">
+        <v>11</v>
+      </c>
+      <c r="E307" t="s">
+        <v>364</v>
+      </c>
+      <c r="F307" t="s">
+        <v>364</v>
+      </c>
+      <c r="G307" t="s">
+        <v>22</v>
       </c>
       <c r="H307" t="s">
         <v>11</v>
@@ -8305,7 +8290,7 @@
         <v>366</v>
       </c>
       <c r="B308" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="C308" t="s">
         <v>367</v>
@@ -8314,21 +8299,39 @@
         <v>11</v>
       </c>
       <c r="E308" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="F308" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="G308" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H308" t="s">
-        <v>414</v>
+        <v>330</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>312</v>
+        <v>366</v>
+      </c>
+      <c r="B309" t="s">
+        <v>127</v>
+      </c>
+      <c r="C309" t="s">
+        <v>379</v>
+      </c>
+      <c r="D309" t="s">
+        <v>11</v>
+      </c>
+      <c r="E309" t="s">
+        <v>127</v>
+      </c>
+      <c r="F309" t="s">
+        <v>127</v>
+      </c>
+      <c r="G309" t="s">
+        <v>17</v>
       </c>
       <c r="H309" t="s">
         <v>11</v>
@@ -8336,33 +8339,51 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>368</v>
+        <v>193</v>
       </c>
       <c r="B310" t="s">
-        <v>369</v>
+        <v>127</v>
       </c>
       <c r="C310" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="D310" t="s">
         <v>11</v>
       </c>
       <c r="E310" t="s">
-        <v>369</v>
+        <v>127</v>
       </c>
       <c r="F310" t="s">
-        <v>369</v>
+        <v>127</v>
       </c>
       <c r="G310" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H310" t="s">
-        <v>414</v>
+        <v>311</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>312</v>
+        <v>193</v>
+      </c>
+      <c r="B311" t="s">
+        <v>127</v>
+      </c>
+      <c r="C311" t="s">
+        <v>372</v>
+      </c>
+      <c r="D311" t="s">
+        <v>11</v>
+      </c>
+      <c r="E311" t="s">
+        <v>127</v>
+      </c>
+      <c r="F311" t="s">
+        <v>127</v>
+      </c>
+      <c r="G311" t="s">
+        <v>17</v>
       </c>
       <c r="H311" t="s">
         <v>11</v>
@@ -8370,25 +8391,25 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B312" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C312" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D312" t="s">
         <v>11</v>
       </c>
       <c r="E312" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F312" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="G312" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="H312" t="s">
         <v>330</v>
@@ -8396,763 +8417,105 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B313" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C313" t="s">
-        <v>418</v>
+        <v>371</v>
       </c>
       <c r="D313" t="s">
         <v>11</v>
       </c>
       <c r="E313" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F313" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="G313" t="s">
-        <v>375</v>
-      </c>
-      <c r="H313" t="s">
-        <v>11</v>
+        <v>351</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B314" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C314" t="s">
-        <v>377</v>
-      </c>
-      <c r="D314" t="s">
-        <v>11</v>
+        <v>384</v>
       </c>
       <c r="E314" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F314" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="G314" t="s">
-        <v>375</v>
-      </c>
-      <c r="H314" t="s">
-        <v>330</v>
+        <v>17</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B315" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="C315" t="s">
-        <v>419</v>
-      </c>
-      <c r="D315" t="s">
-        <v>11</v>
+        <v>384</v>
       </c>
       <c r="E315" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F315" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="G315" t="s">
-        <v>375</v>
-      </c>
-      <c r="H315" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B316" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C316" t="s">
-        <v>379</v>
-      </c>
-      <c r="D316" t="s">
-        <v>11</v>
+        <v>385</v>
       </c>
       <c r="E316" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F316" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="G316" t="s">
-        <v>375</v>
-      </c>
-      <c r="H316" t="s">
-        <v>414</v>
+        <v>17</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>312</v>
-      </c>
-      <c r="H317" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
-        <v>380</v>
-      </c>
-      <c r="B318" t="s">
-        <v>373</v>
-      </c>
-      <c r="C318" t="s">
+        <v>383</v>
+      </c>
+      <c r="B317" t="s">
+        <v>387</v>
+      </c>
+      <c r="C317" t="s">
+        <v>385</v>
+      </c>
+      <c r="E317" t="s">
         <v>381</v>
       </c>
-      <c r="D318" t="s">
+      <c r="F317" t="s">
         <v>382</v>
       </c>
-      <c r="E318" t="s">
-        <v>373</v>
-      </c>
-      <c r="F318" t="s">
-        <v>373</v>
-      </c>
-      <c r="G318" t="s">
-        <v>375</v>
-      </c>
-      <c r="H318" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
-        <v>312</v>
-      </c>
-      <c r="H319" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
-        <v>383</v>
-      </c>
-      <c r="B320" t="s">
-        <v>373</v>
-      </c>
-      <c r="C320" t="s">
-        <v>381</v>
-      </c>
-      <c r="D320" t="s">
-        <v>384</v>
-      </c>
-      <c r="E320" t="s">
-        <v>373</v>
-      </c>
-      <c r="F320" t="s">
-        <v>373</v>
-      </c>
-      <c r="G320" t="s">
-        <v>375</v>
-      </c>
-      <c r="H320" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
-        <v>312</v>
-      </c>
-      <c r="H321" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
-        <v>385</v>
-      </c>
-      <c r="B322" t="s">
-        <v>386</v>
-      </c>
-      <c r="C322" t="s">
-        <v>387</v>
-      </c>
-      <c r="D322" t="s">
-        <v>11</v>
-      </c>
-      <c r="E322" t="s">
-        <v>386</v>
-      </c>
-      <c r="F322" t="s">
-        <v>388</v>
-      </c>
-      <c r="G322" t="s">
-        <v>389</v>
-      </c>
-      <c r="H322" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
-        <v>385</v>
-      </c>
-      <c r="B323" t="s">
-        <v>386</v>
-      </c>
-      <c r="C323" t="s">
-        <v>420</v>
-      </c>
-      <c r="D323" t="s">
-        <v>11</v>
-      </c>
-      <c r="E323" t="s">
-        <v>386</v>
-      </c>
-      <c r="F323" t="s">
-        <v>388</v>
-      </c>
-      <c r="G323" t="s">
-        <v>389</v>
-      </c>
-      <c r="H323" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A324" t="s">
-        <v>390</v>
-      </c>
-      <c r="B324" t="s">
-        <v>391</v>
-      </c>
-      <c r="C324" t="s">
-        <v>392</v>
-      </c>
-      <c r="D324" t="s">
-        <v>11</v>
-      </c>
-      <c r="E324" t="s">
-        <v>391</v>
-      </c>
-      <c r="F324" t="s">
-        <v>391</v>
-      </c>
-      <c r="G324" t="s">
-        <v>42</v>
-      </c>
-      <c r="H324" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
-        <v>312</v>
-      </c>
-      <c r="H325" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
-        <v>393</v>
-      </c>
-      <c r="B326" t="s">
-        <v>391</v>
-      </c>
-      <c r="C326" t="s">
-        <v>394</v>
-      </c>
-      <c r="D326" t="s">
-        <v>11</v>
-      </c>
-      <c r="E326" t="s">
-        <v>391</v>
-      </c>
-      <c r="F326" t="s">
-        <v>391</v>
-      </c>
-      <c r="G326" t="s">
-        <v>42</v>
-      </c>
-      <c r="H326" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A327" t="s">
-        <v>312</v>
-      </c>
-      <c r="H327" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
-        <v>395</v>
-      </c>
-      <c r="B328" t="s">
-        <v>396</v>
-      </c>
-      <c r="C328" t="s">
-        <v>397</v>
-      </c>
-      <c r="D328" t="s">
-        <v>11</v>
-      </c>
-      <c r="E328" t="s">
-        <v>396</v>
-      </c>
-      <c r="F328" t="s">
-        <v>396</v>
-      </c>
-      <c r="G328" t="s">
-        <v>22</v>
-      </c>
-      <c r="H328" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
-        <v>312</v>
-      </c>
-      <c r="H329" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
-        <v>395</v>
-      </c>
-      <c r="B330" t="s">
-        <v>396</v>
-      </c>
-      <c r="C330" t="s">
-        <v>398</v>
-      </c>
-      <c r="D330" t="s">
-        <v>11</v>
-      </c>
-      <c r="E330" t="s">
-        <v>396</v>
-      </c>
-      <c r="F330" t="s">
-        <v>396</v>
-      </c>
-      <c r="G330" t="s">
-        <v>22</v>
-      </c>
-      <c r="H330" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
-        <v>312</v>
-      </c>
-      <c r="H331" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
-        <v>124</v>
-      </c>
-      <c r="B332" t="s">
-        <v>123</v>
-      </c>
-      <c r="C332" t="s">
-        <v>125</v>
-      </c>
-      <c r="D332" t="s">
-        <v>11</v>
-      </c>
-      <c r="E332" t="s">
-        <v>123</v>
-      </c>
-      <c r="F332" t="s">
-        <v>123</v>
-      </c>
-      <c r="G332" t="s">
-        <v>27</v>
-      </c>
-      <c r="H332" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A333" t="s">
-        <v>124</v>
-      </c>
-      <c r="B333" t="s">
-        <v>123</v>
-      </c>
-      <c r="C333" t="s">
-        <v>334</v>
-      </c>
-      <c r="D333" t="s">
-        <v>11</v>
-      </c>
-      <c r="E333" t="s">
-        <v>123</v>
-      </c>
-      <c r="F333" t="s">
-        <v>123</v>
-      </c>
-      <c r="G333" t="s">
-        <v>27</v>
-      </c>
-      <c r="H333" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>399</v>
-      </c>
-      <c r="B334" t="s">
-        <v>123</v>
-      </c>
-      <c r="C334" t="s">
-        <v>363</v>
-      </c>
-      <c r="D334" t="s">
-        <v>11</v>
-      </c>
-      <c r="E334" t="s">
-        <v>123</v>
-      </c>
-      <c r="F334" t="s">
-        <v>123</v>
-      </c>
-      <c r="G334" t="s">
-        <v>27</v>
-      </c>
-      <c r="H334" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
-        <v>312</v>
-      </c>
-      <c r="H335" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
-        <v>400</v>
-      </c>
-      <c r="B336" t="s">
-        <v>401</v>
-      </c>
-      <c r="C336" t="s">
-        <v>402</v>
-      </c>
-      <c r="D336" t="s">
-        <v>11</v>
-      </c>
-      <c r="E336" t="s">
-        <v>401</v>
-      </c>
-      <c r="F336" t="s">
-        <v>401</v>
-      </c>
-      <c r="G336" t="s">
-        <v>22</v>
-      </c>
-      <c r="H336" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
-        <v>400</v>
-      </c>
-      <c r="B337" t="s">
-        <v>401</v>
-      </c>
-      <c r="C337" t="s">
-        <v>421</v>
-      </c>
-      <c r="D337" t="s">
-        <v>11</v>
-      </c>
-      <c r="E337" t="s">
-        <v>401</v>
-      </c>
-      <c r="F337" t="s">
-        <v>401</v>
-      </c>
-      <c r="G337" t="s">
-        <v>22</v>
-      </c>
-      <c r="H337" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
-        <v>403</v>
-      </c>
-      <c r="B338" t="s">
-        <v>127</v>
-      </c>
-      <c r="C338" t="s">
-        <v>404</v>
-      </c>
-      <c r="D338" t="s">
-        <v>11</v>
-      </c>
-      <c r="E338" t="s">
-        <v>127</v>
-      </c>
-      <c r="F338" t="s">
-        <v>127</v>
-      </c>
-      <c r="G338" t="s">
-        <v>17</v>
-      </c>
-      <c r="H338" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
-        <v>403</v>
-      </c>
-      <c r="B339" t="s">
-        <v>127</v>
-      </c>
-      <c r="C339" t="s">
-        <v>422</v>
-      </c>
-      <c r="D339" t="s">
-        <v>11</v>
-      </c>
-      <c r="E339" t="s">
-        <v>127</v>
-      </c>
-      <c r="F339" t="s">
-        <v>127</v>
-      </c>
-      <c r="G339" t="s">
-        <v>17</v>
-      </c>
-      <c r="H339" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
-        <v>405</v>
-      </c>
-      <c r="B340" t="s">
-        <v>127</v>
-      </c>
-      <c r="C340" t="s">
-        <v>406</v>
-      </c>
-      <c r="D340" t="s">
-        <v>11</v>
-      </c>
-      <c r="E340" t="s">
-        <v>127</v>
-      </c>
-      <c r="F340" t="s">
-        <v>127</v>
-      </c>
-      <c r="G340" t="s">
-        <v>17</v>
-      </c>
-      <c r="H340" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A341" t="s">
-        <v>312</v>
-      </c>
-      <c r="H341" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
-        <v>193</v>
-      </c>
-      <c r="B342" t="s">
-        <v>127</v>
-      </c>
-      <c r="C342" t="s">
-        <v>345</v>
-      </c>
-      <c r="D342" t="s">
-        <v>11</v>
-      </c>
-      <c r="E342" t="s">
-        <v>127</v>
-      </c>
-      <c r="F342" t="s">
-        <v>127</v>
-      </c>
-      <c r="G342" t="s">
-        <v>17</v>
-      </c>
-      <c r="H342" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
-        <v>193</v>
-      </c>
-      <c r="B343" t="s">
-        <v>127</v>
-      </c>
-      <c r="C343" t="s">
-        <v>415</v>
-      </c>
-      <c r="D343" t="s">
-        <v>11</v>
-      </c>
-      <c r="E343" t="s">
-        <v>127</v>
-      </c>
-      <c r="F343" t="s">
-        <v>127</v>
-      </c>
-      <c r="G343" t="s">
-        <v>17</v>
-      </c>
-      <c r="H343" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
-        <v>407</v>
-      </c>
-      <c r="B344" t="s">
-        <v>408</v>
-      </c>
-      <c r="C344" t="s">
-        <v>409</v>
-      </c>
-      <c r="D344" t="s">
-        <v>11</v>
-      </c>
-      <c r="E344" t="s">
-        <v>408</v>
-      </c>
-      <c r="F344" t="s">
-        <v>408</v>
-      </c>
-      <c r="G344" t="s">
-        <v>371</v>
-      </c>
-      <c r="H344" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
-        <v>312</v>
-      </c>
-      <c r="H345" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
-        <v>410</v>
-      </c>
-      <c r="B346" t="s">
-        <v>408</v>
-      </c>
-      <c r="C346" t="s">
-        <v>411</v>
-      </c>
-      <c r="D346" t="s">
-        <v>11</v>
-      </c>
-      <c r="E346" t="s">
-        <v>408</v>
-      </c>
-      <c r="F346" t="s">
-        <v>408</v>
-      </c>
-      <c r="G346" t="s">
-        <v>371</v>
-      </c>
-      <c r="H346" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A347" t="s">
-        <v>410</v>
-      </c>
-      <c r="B347" t="s">
-        <v>408</v>
-      </c>
-      <c r="C347" t="s">
-        <v>412</v>
-      </c>
-      <c r="D347" t="s">
-        <v>11</v>
-      </c>
-      <c r="E347" t="s">
-        <v>408</v>
-      </c>
-      <c r="F347" t="s">
-        <v>408</v>
-      </c>
-      <c r="G347" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
-        <v>299</v>
-      </c>
-      <c r="B348" t="s">
-        <v>300</v>
-      </c>
-      <c r="C348" t="s">
-        <v>413</v>
-      </c>
-      <c r="D348" t="s">
-        <v>11</v>
-      </c>
-      <c r="E348" t="s">
-        <v>300</v>
-      </c>
-      <c r="F348" t="s">
-        <v>300</v>
-      </c>
-      <c r="G348" t="s">
-        <v>22</v>
-      </c>
-      <c r="H348" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A349" t="s">
-        <v>312</v>
-      </c>
-      <c r="H349" t="s">
-        <v>11</v>
+      <c r="G317" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3A6F8B-1510-4DBC-BE4F-60DAD425B4A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365ACE52-9D71-4E85-BAEC-781F0CAF26BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="381">
   <si>
     <t>Kod</t>
   </si>
@@ -1115,9 +1115,6 @@
     <t>Nysa</t>
   </si>
   <si>
-    <t>Generała Augusta Emila Fieldorfa-Pseudonim Nil</t>
-  </si>
-  <si>
     <t>nyski</t>
   </si>
   <si>
@@ -1175,28 +1172,10 @@
     <t>Romana Palestra</t>
   </si>
   <si>
-    <t>Ostrów Mazowiecka (Komorowo)</t>
-  </si>
-  <si>
-    <t>Ostrów Mazowiecka</t>
-  </si>
-  <si>
-    <t>ostrowski</t>
-  </si>
-  <si>
-    <t>07-310</t>
-  </si>
-  <si>
-    <t>Kolejowa</t>
-  </si>
-  <si>
-    <t>Spokojna</t>
-  </si>
-  <si>
-    <t>Komorowo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ostrów Mazowiecka </t>
+    <t>Storrady - Świętosławy</t>
+  </si>
+  <si>
+    <t>Generała Augusta Emila Fieldorfa - Pseudonim Nil</t>
   </si>
 </sst>
 </file>
@@ -2075,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H317"/>
+  <dimension ref="A1:H313"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -5244,7 +5223,7 @@
         <v>127</v>
       </c>
       <c r="C156" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D156" t="s">
         <v>11</v>
@@ -8007,7 +7986,7 @@
         <v>348</v>
       </c>
       <c r="C297" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D297" t="s">
         <v>11</v>
@@ -8059,7 +8038,7 @@
         <v>353</v>
       </c>
       <c r="C299" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D299" t="s">
         <v>11</v>
@@ -8111,7 +8090,7 @@
         <v>353</v>
       </c>
       <c r="C301" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D301" t="s">
         <v>11</v>
@@ -8137,7 +8116,7 @@
         <v>359</v>
       </c>
       <c r="C302" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="D302" t="s">
         <v>11</v>
@@ -8146,10 +8125,10 @@
         <v>359</v>
       </c>
       <c r="F302" t="s">
+        <v>360</v>
+      </c>
+      <c r="G302" t="s">
         <v>361</v>
-      </c>
-      <c r="G302" t="s">
-        <v>362</v>
       </c>
       <c r="H302" t="s">
         <v>330</v>
@@ -8163,7 +8142,7 @@
         <v>359</v>
       </c>
       <c r="C303" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D303" t="s">
         <v>11</v>
@@ -8172,10 +8151,10 @@
         <v>359</v>
       </c>
       <c r="F303" t="s">
+        <v>360</v>
+      </c>
+      <c r="G303" t="s">
         <v>361</v>
-      </c>
-      <c r="G303" t="s">
-        <v>362</v>
       </c>
       <c r="H303" t="s">
         <v>11</v>
@@ -8189,7 +8168,7 @@
         <v>123</v>
       </c>
       <c r="C304" t="s">
-        <v>125</v>
+        <v>379</v>
       </c>
       <c r="D304" t="s">
         <v>11</v>
@@ -8235,22 +8214,22 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
+        <v>362</v>
+      </c>
+      <c r="B306" t="s">
         <v>363</v>
       </c>
-      <c r="B306" t="s">
+      <c r="C306" t="s">
         <v>364</v>
       </c>
-      <c r="C306" t="s">
-        <v>365</v>
-      </c>
       <c r="D306" t="s">
         <v>11</v>
       </c>
       <c r="E306" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F306" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G306" t="s">
         <v>22</v>
@@ -8261,22 +8240,22 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
+        <v>362</v>
+      </c>
+      <c r="B307" t="s">
         <v>363</v>
       </c>
-      <c r="B307" t="s">
-        <v>364</v>
-      </c>
       <c r="C307" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D307" t="s">
         <v>11</v>
       </c>
       <c r="E307" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F307" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G307" t="s">
         <v>22</v>
@@ -8287,13 +8266,13 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
+        <v>365</v>
+      </c>
+      <c r="B308" t="s">
+        <v>127</v>
+      </c>
+      <c r="C308" t="s">
         <v>366</v>
-      </c>
-      <c r="B308" t="s">
-        <v>127</v>
-      </c>
-      <c r="C308" t="s">
-        <v>367</v>
       </c>
       <c r="D308" t="s">
         <v>11</v>
@@ -8313,13 +8292,13 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B309" t="s">
         <v>127</v>
       </c>
       <c r="C309" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D309" t="s">
         <v>11</v>
@@ -8371,7 +8350,7 @@
         <v>127</v>
       </c>
       <c r="C311" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D311" t="s">
         <v>11</v>
@@ -8391,22 +8370,22 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
+        <v>368</v>
+      </c>
+      <c r="B312" t="s">
+        <v>367</v>
+      </c>
+      <c r="C312" t="s">
         <v>369</v>
       </c>
-      <c r="B312" t="s">
-        <v>368</v>
-      </c>
-      <c r="C312" t="s">
-        <v>370</v>
-      </c>
       <c r="D312" t="s">
         <v>11</v>
       </c>
       <c r="E312" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F312" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G312" t="s">
         <v>351</v>
@@ -8417,105 +8396,25 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B313" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C313" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D313" t="s">
         <v>11</v>
       </c>
       <c r="E313" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F313" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G313" t="s">
         <v>351</v>
-      </c>
-    </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>383</v>
-      </c>
-      <c r="B314" t="s">
-        <v>380</v>
-      </c>
-      <c r="C314" t="s">
-        <v>384</v>
-      </c>
-      <c r="E314" t="s">
-        <v>381</v>
-      </c>
-      <c r="F314" t="s">
-        <v>382</v>
-      </c>
-      <c r="G314" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>383</v>
-      </c>
-      <c r="B315" t="s">
-        <v>386</v>
-      </c>
-      <c r="C315" t="s">
-        <v>384</v>
-      </c>
-      <c r="E315" t="s">
-        <v>381</v>
-      </c>
-      <c r="F315" t="s">
-        <v>382</v>
-      </c>
-      <c r="G315" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>383</v>
-      </c>
-      <c r="B316" t="s">
-        <v>380</v>
-      </c>
-      <c r="C316" t="s">
-        <v>385</v>
-      </c>
-      <c r="E316" t="s">
-        <v>381</v>
-      </c>
-      <c r="F316" t="s">
-        <v>382</v>
-      </c>
-      <c r="G316" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
-        <v>383</v>
-      </c>
-      <c r="B317" t="s">
-        <v>387</v>
-      </c>
-      <c r="C317" t="s">
-        <v>385</v>
-      </c>
-      <c r="E317" t="s">
-        <v>381</v>
-      </c>
-      <c r="F317" t="s">
-        <v>382</v>
-      </c>
-      <c r="G317" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365ACE52-9D71-4E85-BAEC-781F0CAF26BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF21D42-CBD8-4B90-B2C4-ACA639C28A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="388">
   <si>
     <t>Kod</t>
   </si>
@@ -1176,6 +1176,27 @@
   </si>
   <si>
     <t>Generała Augusta Emila Fieldorfa - Pseudonim Nil</t>
+  </si>
+  <si>
+    <t>07-310</t>
+  </si>
+  <si>
+    <t>Ostrów Mazowiecka</t>
+  </si>
+  <si>
+    <t>Spokojna</t>
+  </si>
+  <si>
+    <t>ostrowski</t>
+  </si>
+  <si>
+    <t>Dzielnica</t>
+  </si>
+  <si>
+    <t>Komorowo</t>
+  </si>
+  <si>
+    <t>Korekta dzielnicy</t>
   </si>
 </sst>
 </file>
@@ -2054,20 +2075,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H313"/>
+  <dimension ref="A1:I315"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5703125" customWidth="1"/>
-    <col min="3" max="3" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" customWidth="1"/>
-    <col min="8" max="8" width="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="38.5703125" customWidth="1"/>
+    <col min="4" max="4" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" customWidth="1"/>
+    <col min="9" max="9" width="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2075,6346 +2096,6395 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
       <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>310</v>
       </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
         <v>12</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>312</v>
       </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
       <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>21</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>22</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>314</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
       <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>21</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>22</v>
       </c>
-      <c r="H7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>25</v>
       </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
       <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>24</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>26</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>27</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>316</v>
       </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
       <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
         <v>24</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>26</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>27</v>
       </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>28</v>
       </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
       <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>24</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>26</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>27</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>317</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
       <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>24</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>26</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>27</v>
       </c>
-      <c r="H11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>31</v>
       </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>29</v>
       </c>
       <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
         <v>16</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>318</v>
       </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>29</v>
       </c>
       <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
         <v>16</v>
       </c>
-      <c r="H13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>34</v>
       </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
         <v>33</v>
       </c>
       <c r="G14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" t="s">
         <v>22</v>
       </c>
-      <c r="H14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>312</v>
       </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>38</v>
       </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
       <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
         <v>35</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>36</v>
       </c>
-      <c r="G16" t="s">
-        <v>17</v>
-      </c>
       <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>320</v>
       </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
       <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
         <v>35</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>36</v>
       </c>
-      <c r="G17" t="s">
-        <v>17</v>
-      </c>
       <c r="H17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>39</v>
       </c>
       <c r="B18" t="s">
         <v>40</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>41</v>
       </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
         <v>40</v>
       </c>
       <c r="G18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" t="s">
         <v>42</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
       <c r="B19" t="s">
         <v>40</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>321</v>
       </c>
-      <c r="D19" t="s">
-        <v>11</v>
-      </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F19" t="s">
         <v>40</v>
       </c>
       <c r="G19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" t="s">
         <v>42</v>
       </c>
-      <c r="H19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>43</v>
       </c>
       <c r="B20" t="s">
         <v>40</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>44</v>
       </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
         <v>40</v>
       </c>
       <c r="G20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" t="s">
         <v>42</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>43</v>
       </c>
       <c r="B21" t="s">
         <v>40</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>323</v>
       </c>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
       <c r="E21" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F21" t="s">
         <v>40</v>
       </c>
       <c r="G21" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" t="s">
         <v>42</v>
       </c>
-      <c r="H21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>43</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>45</v>
       </c>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
       <c r="E22" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F22" t="s">
         <v>40</v>
       </c>
       <c r="G22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" t="s">
         <v>42</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>43</v>
       </c>
       <c r="B23" t="s">
         <v>40</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>324</v>
       </c>
-      <c r="D23" t="s">
-        <v>11</v>
-      </c>
       <c r="E23" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F23" t="s">
         <v>40</v>
       </c>
       <c r="G23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" t="s">
         <v>42</v>
       </c>
-      <c r="H23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>39</v>
       </c>
       <c r="B24" t="s">
         <v>40</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>46</v>
       </c>
-      <c r="D24" t="s">
-        <v>11</v>
-      </c>
       <c r="E24" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F24" t="s">
         <v>40</v>
       </c>
       <c r="G24" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" t="s">
         <v>42</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>39</v>
       </c>
       <c r="B25" t="s">
         <v>40</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>325</v>
       </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
       <c r="E25" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F25" t="s">
         <v>40</v>
       </c>
       <c r="G25" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" t="s">
         <v>42</v>
       </c>
-      <c r="H25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
       <c r="B26" t="s">
         <v>40</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>47</v>
       </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
       <c r="E26" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F26" t="s">
         <v>40</v>
       </c>
       <c r="G26" t="s">
+        <v>40</v>
+      </c>
+      <c r="H26" t="s">
         <v>42</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
       <c r="B27" t="s">
         <v>40</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>326</v>
       </c>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
       <c r="E27" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F27" t="s">
         <v>40</v>
       </c>
       <c r="G27" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" t="s">
         <v>42</v>
       </c>
-      <c r="H27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>49</v>
       </c>
       <c r="B28" t="s">
         <v>48</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>50</v>
       </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
       <c r="E28" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="F28" t="s">
         <v>48</v>
       </c>
       <c r="G28" t="s">
+        <v>48</v>
+      </c>
+      <c r="H28" t="s">
         <v>27</v>
       </c>
-      <c r="H28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>312</v>
       </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" t="s">
         <v>48</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>51</v>
       </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
       <c r="E30" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="F30" t="s">
         <v>48</v>
       </c>
       <c r="G30" t="s">
+        <v>48</v>
+      </c>
+      <c r="H30" t="s">
         <v>27</v>
       </c>
-      <c r="H30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>312</v>
       </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>49</v>
       </c>
       <c r="B32" t="s">
         <v>48</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>52</v>
       </c>
-      <c r="D32" t="s">
-        <v>11</v>
-      </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="F32" t="s">
         <v>48</v>
       </c>
       <c r="G32" t="s">
+        <v>48</v>
+      </c>
+      <c r="H32" t="s">
         <v>27</v>
       </c>
-      <c r="H32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>312</v>
       </c>
-      <c r="D33" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>53</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>55</v>
       </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
       <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" t="s">
         <v>54</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>56</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>57</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>53</v>
       </c>
       <c r="B35" t="s">
         <v>54</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>327</v>
       </c>
-      <c r="D35" t="s">
-        <v>11</v>
-      </c>
       <c r="E35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" t="s">
         <v>54</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>56</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>57</v>
       </c>
-      <c r="H35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>53</v>
       </c>
       <c r="B36" t="s">
         <v>54</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>58</v>
       </c>
-      <c r="D36" t="s">
-        <v>11</v>
-      </c>
       <c r="E36" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" t="s">
         <v>54</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>56</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>57</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>53</v>
       </c>
       <c r="B37" t="s">
         <v>54</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>328</v>
       </c>
-      <c r="D37" t="s">
-        <v>11</v>
-      </c>
       <c r="E37" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" t="s">
         <v>54</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>56</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>57</v>
       </c>
-      <c r="H37" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>59</v>
       </c>
       <c r="B38" t="s">
         <v>60</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>61</v>
       </c>
-      <c r="D38" t="s">
-        <v>11</v>
-      </c>
       <c r="E38" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="F38" t="s">
         <v>60</v>
       </c>
       <c r="G38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H38" t="s">
         <v>57</v>
       </c>
-      <c r="H38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>312</v>
       </c>
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" t="s">
         <v>60</v>
       </c>
-      <c r="H39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>62</v>
       </c>
       <c r="B40" t="s">
         <v>60</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>63</v>
       </c>
-      <c r="D40" t="s">
-        <v>11</v>
-      </c>
       <c r="E40" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="F40" t="s">
         <v>60</v>
       </c>
       <c r="G40" t="s">
+        <v>60</v>
+      </c>
+      <c r="H40" t="s">
         <v>57</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>62</v>
       </c>
       <c r="B41" t="s">
         <v>60</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>329</v>
       </c>
-      <c r="D41" t="s">
-        <v>11</v>
-      </c>
       <c r="E41" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="F41" t="s">
         <v>60</v>
       </c>
       <c r="G41" t="s">
+        <v>60</v>
+      </c>
+      <c r="H41" t="s">
         <v>57</v>
       </c>
-      <c r="H41" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>64</v>
       </c>
       <c r="B42" t="s">
         <v>60</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>65</v>
       </c>
-      <c r="D42" t="s">
-        <v>11</v>
-      </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="F42" t="s">
         <v>60</v>
       </c>
       <c r="G42" t="s">
+        <v>60</v>
+      </c>
+      <c r="H42" t="s">
         <v>57</v>
       </c>
-      <c r="H42" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>312</v>
       </c>
-      <c r="D43" t="s">
-        <v>11</v>
-      </c>
-      <c r="H43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E43" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>59</v>
       </c>
       <c r="B44" t="s">
         <v>60</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>66</v>
       </c>
-      <c r="D44" t="s">
-        <v>11</v>
-      </c>
       <c r="E44" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="F44" t="s">
         <v>60</v>
       </c>
       <c r="G44" t="s">
+        <v>60</v>
+      </c>
+      <c r="H44" t="s">
         <v>57</v>
       </c>
-      <c r="H44" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>312</v>
       </c>
-      <c r="H45" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>67</v>
       </c>
       <c r="B46" t="s">
         <v>68</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>69</v>
       </c>
-      <c r="D46" t="s">
-        <v>11</v>
-      </c>
       <c r="E46" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F46" t="s">
         <v>68</v>
       </c>
       <c r="G46" t="s">
+        <v>68</v>
+      </c>
+      <c r="H46" t="s">
         <v>70</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>67</v>
       </c>
       <c r="B47" t="s">
         <v>68</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>331</v>
       </c>
-      <c r="D47" t="s">
-        <v>11</v>
-      </c>
       <c r="E47" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F47" t="s">
         <v>68</v>
       </c>
       <c r="G47" t="s">
+        <v>68</v>
+      </c>
+      <c r="H47" t="s">
         <v>70</v>
       </c>
-      <c r="H47" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>71</v>
       </c>
       <c r="B48" t="s">
         <v>68</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>72</v>
       </c>
-      <c r="D48" t="s">
-        <v>11</v>
-      </c>
       <c r="E48" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F48" t="s">
         <v>68</v>
       </c>
       <c r="G48" t="s">
+        <v>68</v>
+      </c>
+      <c r="H48" t="s">
         <v>70</v>
       </c>
-      <c r="H48" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>312</v>
       </c>
-      <c r="D49" t="s">
-        <v>11</v>
-      </c>
-      <c r="H49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E49" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>73</v>
       </c>
       <c r="B50" t="s">
         <v>68</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>74</v>
       </c>
-      <c r="D50" t="s">
-        <v>11</v>
-      </c>
       <c r="E50" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F50" t="s">
         <v>68</v>
       </c>
       <c r="G50" t="s">
+        <v>68</v>
+      </c>
+      <c r="H50" t="s">
         <v>70</v>
       </c>
-      <c r="H50" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I50" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>312</v>
       </c>
-      <c r="D51" t="s">
-        <v>11</v>
-      </c>
-      <c r="H51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>75</v>
       </c>
       <c r="B52" t="s">
         <v>68</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>76</v>
       </c>
-      <c r="D52" t="s">
-        <v>11</v>
-      </c>
       <c r="E52" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F52" t="s">
         <v>68</v>
       </c>
       <c r="G52" t="s">
+        <v>68</v>
+      </c>
+      <c r="H52" t="s">
         <v>70</v>
       </c>
-      <c r="H52" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>312</v>
       </c>
-      <c r="D53" t="s">
-        <v>11</v>
-      </c>
-      <c r="H53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
+        <v>11</v>
+      </c>
+      <c r="I53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>77</v>
       </c>
       <c r="B54" t="s">
         <v>68</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>78</v>
       </c>
-      <c r="D54" t="s">
-        <v>11</v>
-      </c>
       <c r="E54" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F54" t="s">
         <v>68</v>
       </c>
       <c r="G54" t="s">
+        <v>68</v>
+      </c>
+      <c r="H54" t="s">
         <v>70</v>
       </c>
-      <c r="H54" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I54" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>312</v>
       </c>
-      <c r="D55" t="s">
-        <v>11</v>
-      </c>
-      <c r="H55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E55" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>79</v>
       </c>
       <c r="B56" t="s">
         <v>68</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>80</v>
       </c>
-      <c r="D56" t="s">
-        <v>11</v>
-      </c>
       <c r="E56" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F56" t="s">
         <v>68</v>
       </c>
       <c r="G56" t="s">
+        <v>68</v>
+      </c>
+      <c r="H56" t="s">
         <v>70</v>
       </c>
-      <c r="H56" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I56" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>312</v>
       </c>
-      <c r="D57" t="s">
-        <v>11</v>
-      </c>
-      <c r="H57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E57" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>81</v>
       </c>
       <c r="B58" t="s">
         <v>68</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>82</v>
       </c>
-      <c r="D58" t="s">
-        <v>11</v>
-      </c>
       <c r="E58" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F58" t="s">
         <v>68</v>
       </c>
       <c r="G58" t="s">
+        <v>68</v>
+      </c>
+      <c r="H58" t="s">
         <v>70</v>
       </c>
-      <c r="H58" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I58" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>312</v>
       </c>
-      <c r="D59" t="s">
-        <v>11</v>
-      </c>
-      <c r="H59" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E59" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>83</v>
       </c>
       <c r="B60" t="s">
         <v>68</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>84</v>
       </c>
-      <c r="D60" t="s">
-        <v>11</v>
-      </c>
       <c r="E60" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F60" t="s">
         <v>68</v>
       </c>
       <c r="G60" t="s">
+        <v>68</v>
+      </c>
+      <c r="H60" t="s">
         <v>70</v>
       </c>
-      <c r="H60" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I60" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>312</v>
       </c>
-      <c r="D61" t="s">
-        <v>11</v>
-      </c>
-      <c r="H61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E61" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>85</v>
       </c>
       <c r="B62" t="s">
         <v>68</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>86</v>
       </c>
-      <c r="D62" t="s">
-        <v>11</v>
-      </c>
       <c r="E62" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F62" t="s">
         <v>68</v>
       </c>
       <c r="G62" t="s">
+        <v>68</v>
+      </c>
+      <c r="H62" t="s">
         <v>70</v>
       </c>
-      <c r="H62" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I62" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>312</v>
       </c>
-      <c r="D63" t="s">
-        <v>11</v>
-      </c>
-      <c r="H63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E63" t="s">
+        <v>11</v>
+      </c>
+      <c r="I63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>87</v>
       </c>
       <c r="B64" t="s">
         <v>68</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>88</v>
       </c>
-      <c r="D64" t="s">
-        <v>11</v>
-      </c>
       <c r="E64" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F64" t="s">
         <v>68</v>
       </c>
       <c r="G64" t="s">
+        <v>68</v>
+      </c>
+      <c r="H64" t="s">
         <v>70</v>
       </c>
-      <c r="H64" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I64" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>312</v>
       </c>
-      <c r="D65" t="s">
-        <v>11</v>
-      </c>
-      <c r="H65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E65" t="s">
+        <v>11</v>
+      </c>
+      <c r="I65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>89</v>
       </c>
       <c r="B66" t="s">
         <v>68</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>90</v>
       </c>
-      <c r="D66" t="s">
-        <v>11</v>
-      </c>
       <c r="E66" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F66" t="s">
         <v>68</v>
       </c>
       <c r="G66" t="s">
+        <v>68</v>
+      </c>
+      <c r="H66" t="s">
         <v>70</v>
       </c>
-      <c r="H66" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I66" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>312</v>
       </c>
-      <c r="D67" t="s">
-        <v>11</v>
-      </c>
-      <c r="H67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E67" t="s">
+        <v>11</v>
+      </c>
+      <c r="I67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>91</v>
       </c>
       <c r="B68" t="s">
         <v>68</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>92</v>
       </c>
-      <c r="D68" t="s">
-        <v>11</v>
-      </c>
       <c r="E68" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F68" t="s">
         <v>68</v>
       </c>
       <c r="G68" t="s">
+        <v>68</v>
+      </c>
+      <c r="H68" t="s">
         <v>70</v>
       </c>
-      <c r="H68" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I68" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>312</v>
       </c>
-      <c r="D69" t="s">
-        <v>11</v>
-      </c>
-      <c r="H69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E69" t="s">
+        <v>11</v>
+      </c>
+      <c r="I69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>93</v>
       </c>
       <c r="B70" t="s">
         <v>68</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>94</v>
       </c>
-      <c r="D70" t="s">
-        <v>11</v>
-      </c>
       <c r="E70" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F70" t="s">
         <v>68</v>
       </c>
       <c r="G70" t="s">
+        <v>68</v>
+      </c>
+      <c r="H70" t="s">
         <v>70</v>
       </c>
-      <c r="H70" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I70" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>312</v>
       </c>
-      <c r="D71" t="s">
-        <v>11</v>
-      </c>
-      <c r="H71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E71" t="s">
+        <v>11</v>
+      </c>
+      <c r="I71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>95</v>
       </c>
       <c r="B72" t="s">
         <v>68</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>96</v>
       </c>
-      <c r="D72" t="s">
-        <v>11</v>
-      </c>
       <c r="E72" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F72" t="s">
         <v>68</v>
       </c>
       <c r="G72" t="s">
+        <v>68</v>
+      </c>
+      <c r="H72" t="s">
         <v>70</v>
       </c>
-      <c r="H72" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I72" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>312</v>
       </c>
-      <c r="D73" t="s">
-        <v>11</v>
-      </c>
-      <c r="H73" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E73" t="s">
+        <v>11</v>
+      </c>
+      <c r="I73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>97</v>
       </c>
       <c r="B74" t="s">
         <v>68</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>98</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>99</v>
       </c>
-      <c r="E74" t="s">
-        <v>68</v>
-      </c>
       <c r="F74" t="s">
         <v>68</v>
       </c>
       <c r="G74" t="s">
+        <v>68</v>
+      </c>
+      <c r="H74" t="s">
         <v>70</v>
       </c>
-      <c r="H74" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I74" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>312</v>
       </c>
-      <c r="H75" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>100</v>
       </c>
       <c r="B76" t="s">
         <v>68</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>101</v>
       </c>
-      <c r="D76" t="s">
-        <v>11</v>
-      </c>
       <c r="E76" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F76" t="s">
         <v>68</v>
       </c>
       <c r="G76" t="s">
+        <v>68</v>
+      </c>
+      <c r="H76" t="s">
         <v>70</v>
       </c>
-      <c r="H76" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I76" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>312</v>
       </c>
-      <c r="H77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>95</v>
       </c>
       <c r="B78" t="s">
         <v>68</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>102</v>
       </c>
-      <c r="D78" t="s">
-        <v>11</v>
-      </c>
       <c r="E78" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F78" t="s">
         <v>68</v>
       </c>
       <c r="G78" t="s">
+        <v>68</v>
+      </c>
+      <c r="H78" t="s">
         <v>70</v>
       </c>
-      <c r="H78" t="s">
+      <c r="I78" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>95</v>
       </c>
       <c r="B79" t="s">
         <v>68</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>332</v>
       </c>
-      <c r="D79" t="s">
-        <v>11</v>
-      </c>
       <c r="E79" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F79" t="s">
         <v>68</v>
       </c>
       <c r="G79" t="s">
+        <v>68</v>
+      </c>
+      <c r="H79" t="s">
         <v>70</v>
       </c>
-      <c r="H79" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>103</v>
       </c>
       <c r="B80" t="s">
         <v>68</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>104</v>
       </c>
-      <c r="D80" t="s">
-        <v>11</v>
-      </c>
       <c r="E80" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F80" t="s">
         <v>68</v>
       </c>
       <c r="G80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H80" t="s">
         <v>70</v>
       </c>
-      <c r="H80" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I80" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>312</v>
       </c>
-      <c r="D81" t="s">
-        <v>11</v>
-      </c>
-      <c r="H81" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E81" t="s">
+        <v>11</v>
+      </c>
+      <c r="I81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>105</v>
       </c>
       <c r="B82" t="s">
         <v>68</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>106</v>
       </c>
-      <c r="D82" t="s">
-        <v>11</v>
-      </c>
       <c r="E82" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F82" t="s">
         <v>68</v>
       </c>
       <c r="G82" t="s">
+        <v>68</v>
+      </c>
+      <c r="H82" t="s">
         <v>70</v>
       </c>
-      <c r="H82" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I82" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>312</v>
       </c>
-      <c r="H83" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>105</v>
       </c>
       <c r="B84" t="s">
         <v>68</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>107</v>
       </c>
-      <c r="D84" t="s">
-        <v>11</v>
-      </c>
       <c r="E84" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F84" t="s">
         <v>68</v>
       </c>
       <c r="G84" t="s">
+        <v>68</v>
+      </c>
+      <c r="H84" t="s">
         <v>70</v>
       </c>
-      <c r="H84" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I84" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>312</v>
       </c>
-      <c r="D85" t="s">
-        <v>11</v>
-      </c>
-      <c r="H85" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E85" t="s">
+        <v>11</v>
+      </c>
+      <c r="I85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>108</v>
       </c>
       <c r="B86" t="s">
         <v>68</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>109</v>
       </c>
-      <c r="D86" t="s">
-        <v>11</v>
-      </c>
       <c r="E86" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F86" t="s">
         <v>68</v>
       </c>
       <c r="G86" t="s">
+        <v>68</v>
+      </c>
+      <c r="H86" t="s">
         <v>70</v>
       </c>
-      <c r="H86" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I86" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>312</v>
       </c>
-      <c r="D87" t="s">
-        <v>11</v>
-      </c>
-      <c r="H87" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E87" t="s">
+        <v>11</v>
+      </c>
+      <c r="I87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>110</v>
       </c>
       <c r="B88" t="s">
         <v>68</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>111</v>
       </c>
-      <c r="D88" t="s">
-        <v>11</v>
-      </c>
       <c r="E88" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F88" t="s">
         <v>68</v>
       </c>
       <c r="G88" t="s">
+        <v>68</v>
+      </c>
+      <c r="H88" t="s">
         <v>70</v>
       </c>
-      <c r="H88" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I88" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>312</v>
       </c>
-      <c r="D89" t="s">
-        <v>11</v>
-      </c>
-      <c r="H89" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E89" t="s">
+        <v>11</v>
+      </c>
+      <c r="I89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>112</v>
       </c>
       <c r="B90" t="s">
         <v>68</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>113</v>
       </c>
-      <c r="D90" t="s">
-        <v>11</v>
-      </c>
       <c r="E90" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F90" t="s">
         <v>68</v>
       </c>
       <c r="G90" t="s">
+        <v>68</v>
+      </c>
+      <c r="H90" t="s">
         <v>70</v>
       </c>
-      <c r="H90" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>312</v>
       </c>
-      <c r="D91" t="s">
-        <v>11</v>
-      </c>
-      <c r="H91" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E91" t="s">
+        <v>11</v>
+      </c>
+      <c r="I91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>114</v>
       </c>
       <c r="B92" t="s">
         <v>68</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>115</v>
       </c>
-      <c r="D92" t="s">
-        <v>11</v>
-      </c>
       <c r="E92" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F92" t="s">
         <v>68</v>
       </c>
       <c r="G92" t="s">
+        <v>68</v>
+      </c>
+      <c r="H92" t="s">
         <v>70</v>
       </c>
-      <c r="H92" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I92" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>312</v>
       </c>
-      <c r="D93" t="s">
-        <v>11</v>
-      </c>
-      <c r="H93" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E93" t="s">
+        <v>11</v>
+      </c>
+      <c r="I93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>116</v>
       </c>
       <c r="B94" t="s">
         <v>68</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>98</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>99</v>
       </c>
-      <c r="E94" t="s">
-        <v>68</v>
-      </c>
       <c r="F94" t="s">
         <v>68</v>
       </c>
       <c r="G94" t="s">
+        <v>68</v>
+      </c>
+      <c r="H94" t="s">
         <v>70</v>
       </c>
-      <c r="H94" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I94" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>312</v>
       </c>
-      <c r="H95" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>117</v>
       </c>
       <c r="B96" t="s">
         <v>68</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>118</v>
       </c>
-      <c r="D96" t="s">
-        <v>11</v>
-      </c>
       <c r="E96" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F96" t="s">
         <v>68</v>
       </c>
       <c r="G96" t="s">
+        <v>68</v>
+      </c>
+      <c r="H96" t="s">
         <v>70</v>
       </c>
-      <c r="H96" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I96" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>312</v>
       </c>
-      <c r="D97" t="s">
-        <v>11</v>
-      </c>
-      <c r="H97" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E97" t="s">
+        <v>11</v>
+      </c>
+      <c r="I97" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>119</v>
       </c>
       <c r="B98" t="s">
         <v>68</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>120</v>
       </c>
-      <c r="D98" t="s">
-        <v>11</v>
-      </c>
       <c r="E98" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F98" t="s">
         <v>68</v>
       </c>
       <c r="G98" t="s">
+        <v>68</v>
+      </c>
+      <c r="H98" t="s">
         <v>70</v>
       </c>
-      <c r="H98" t="s">
+      <c r="I98" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>119</v>
       </c>
       <c r="B99" t="s">
         <v>68</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>333</v>
       </c>
-      <c r="D99" t="s">
-        <v>11</v>
-      </c>
       <c r="E99" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F99" t="s">
         <v>68</v>
       </c>
       <c r="G99" t="s">
+        <v>68</v>
+      </c>
+      <c r="H99" t="s">
         <v>70</v>
       </c>
-      <c r="H99" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>121</v>
       </c>
       <c r="B100" t="s">
         <v>68</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>122</v>
       </c>
-      <c r="D100" t="s">
-        <v>11</v>
-      </c>
       <c r="E100" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F100" t="s">
         <v>68</v>
       </c>
       <c r="G100" t="s">
+        <v>68</v>
+      </c>
+      <c r="H100" t="s">
         <v>70</v>
       </c>
-      <c r="H100" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I100" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>312</v>
       </c>
-      <c r="D101" t="s">
-        <v>11</v>
-      </c>
-      <c r="H101" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E101" t="s">
+        <v>11</v>
+      </c>
+      <c r="I101" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>124</v>
       </c>
       <c r="B102" t="s">
         <v>123</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>125</v>
       </c>
-      <c r="D102" t="s">
-        <v>11</v>
-      </c>
       <c r="E102" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="F102" t="s">
         <v>123</v>
       </c>
       <c r="G102" t="s">
+        <v>123</v>
+      </c>
+      <c r="H102" t="s">
         <v>27</v>
       </c>
-      <c r="H102" t="s">
+      <c r="I102" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>124</v>
       </c>
       <c r="B103" t="s">
         <v>123</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>334</v>
       </c>
-      <c r="D103" t="s">
-        <v>11</v>
-      </c>
       <c r="E103" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="F103" t="s">
         <v>123</v>
       </c>
       <c r="G103" t="s">
+        <v>123</v>
+      </c>
+      <c r="H103" t="s">
         <v>27</v>
       </c>
-      <c r="H103" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I103" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>126</v>
       </c>
       <c r="B104" t="s">
         <v>127</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>128</v>
       </c>
-      <c r="D104" t="s">
-        <v>11</v>
-      </c>
       <c r="E104" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F104" t="s">
         <v>127</v>
       </c>
       <c r="G104" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H104" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I104" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>312</v>
       </c>
-      <c r="D105" t="s">
-        <v>11</v>
-      </c>
-      <c r="H105" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E105" t="s">
+        <v>11</v>
+      </c>
+      <c r="I105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>129</v>
       </c>
       <c r="B106" t="s">
         <v>127</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>130</v>
       </c>
-      <c r="D106" t="s">
-        <v>11</v>
-      </c>
       <c r="E106" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F106" t="s">
         <v>127</v>
       </c>
       <c r="G106" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H106" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I106" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>312</v>
       </c>
-      <c r="D107" t="s">
-        <v>11</v>
-      </c>
-      <c r="H107" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E107" t="s">
+        <v>11</v>
+      </c>
+      <c r="I107" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>131</v>
       </c>
       <c r="B108" t="s">
         <v>127</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>132</v>
       </c>
-      <c r="D108" t="s">
-        <v>11</v>
-      </c>
       <c r="E108" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F108" t="s">
         <v>127</v>
       </c>
       <c r="G108" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H108" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I108" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>312</v>
       </c>
-      <c r="D109" t="s">
-        <v>11</v>
-      </c>
-      <c r="H109" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E109" t="s">
+        <v>11</v>
+      </c>
+      <c r="I109" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>133</v>
       </c>
       <c r="B110" t="s">
         <v>127</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>134</v>
       </c>
-      <c r="D110" t="s">
-        <v>11</v>
-      </c>
       <c r="E110" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F110" t="s">
         <v>127</v>
       </c>
       <c r="G110" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H110" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I110" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>312</v>
       </c>
-      <c r="D111" t="s">
-        <v>11</v>
-      </c>
-      <c r="H111" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E111" t="s">
+        <v>11</v>
+      </c>
+      <c r="I111" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>135</v>
       </c>
       <c r="B112" t="s">
         <v>127</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>136</v>
       </c>
-      <c r="D112" t="s">
-        <v>11</v>
-      </c>
       <c r="E112" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F112" t="s">
         <v>127</v>
       </c>
       <c r="G112" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H112" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I112" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>312</v>
       </c>
-      <c r="D113" t="s">
-        <v>11</v>
-      </c>
-      <c r="H113" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E113" t="s">
+        <v>11</v>
+      </c>
+      <c r="I113" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>137</v>
       </c>
       <c r="B114" t="s">
         <v>127</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>138</v>
       </c>
-      <c r="D114" t="s">
-        <v>11</v>
-      </c>
       <c r="E114" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F114" t="s">
         <v>127</v>
       </c>
       <c r="G114" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H114" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I114" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>312</v>
       </c>
-      <c r="D115" t="s">
-        <v>11</v>
-      </c>
-      <c r="H115" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E115" t="s">
+        <v>11</v>
+      </c>
+      <c r="I115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>139</v>
       </c>
       <c r="B116" t="s">
         <v>127</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>140</v>
       </c>
-      <c r="D116" t="s">
-        <v>11</v>
-      </c>
       <c r="E116" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F116" t="s">
         <v>127</v>
       </c>
       <c r="G116" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H116" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I116" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>312</v>
       </c>
-      <c r="D117" t="s">
-        <v>11</v>
-      </c>
-      <c r="H117" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E117" t="s">
+        <v>11</v>
+      </c>
+      <c r="I117" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>141</v>
       </c>
       <c r="B118" t="s">
         <v>127</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>142</v>
       </c>
-      <c r="D118" t="s">
-        <v>11</v>
-      </c>
       <c r="E118" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F118" t="s">
         <v>127</v>
       </c>
       <c r="G118" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H118" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I118" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>312</v>
       </c>
-      <c r="D119" t="s">
-        <v>11</v>
-      </c>
-      <c r="H119" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E119" t="s">
+        <v>11</v>
+      </c>
+      <c r="I119" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>143</v>
       </c>
       <c r="B120" t="s">
         <v>127</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>144</v>
       </c>
-      <c r="D120" t="s">
-        <v>11</v>
-      </c>
       <c r="E120" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F120" t="s">
         <v>127</v>
       </c>
       <c r="G120" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H120" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I120" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>312</v>
       </c>
-      <c r="D121" t="s">
-        <v>11</v>
-      </c>
-      <c r="H121" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E121" t="s">
+        <v>11</v>
+      </c>
+      <c r="I121" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>145</v>
       </c>
       <c r="B122" t="s">
         <v>127</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>146</v>
       </c>
-      <c r="D122" t="s">
-        <v>11</v>
-      </c>
       <c r="E122" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F122" t="s">
         <v>127</v>
       </c>
       <c r="G122" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H122" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I122" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>312</v>
       </c>
-      <c r="D123" t="s">
-        <v>11</v>
-      </c>
-      <c r="H123" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E123" t="s">
+        <v>11</v>
+      </c>
+      <c r="I123" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>147</v>
       </c>
       <c r="B124" t="s">
         <v>127</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
         <v>148</v>
       </c>
-      <c r="D124" t="s">
-        <v>11</v>
-      </c>
       <c r="E124" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F124" t="s">
         <v>127</v>
       </c>
       <c r="G124" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H124" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I124" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>312</v>
       </c>
-      <c r="D125" t="s">
-        <v>11</v>
-      </c>
-      <c r="H125" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E125" t="s">
+        <v>11</v>
+      </c>
+      <c r="I125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>145</v>
       </c>
       <c r="B126" t="s">
         <v>127</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
         <v>149</v>
       </c>
-      <c r="D126" t="s">
-        <v>11</v>
-      </c>
       <c r="E126" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F126" t="s">
         <v>127</v>
       </c>
       <c r="G126" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H126" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I126" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>312</v>
       </c>
-      <c r="D127" t="s">
-        <v>11</v>
-      </c>
-      <c r="H127" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E127" t="s">
+        <v>11</v>
+      </c>
+      <c r="I127" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>150</v>
       </c>
       <c r="B128" t="s">
         <v>127</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
         <v>151</v>
       </c>
-      <c r="D128" t="s">
-        <v>11</v>
-      </c>
       <c r="E128" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F128" t="s">
         <v>127</v>
       </c>
       <c r="G128" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H128" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I128" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>312</v>
       </c>
-      <c r="D129" t="s">
-        <v>11</v>
-      </c>
-      <c r="H129" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E129" t="s">
+        <v>11</v>
+      </c>
+      <c r="I129" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>152</v>
       </c>
       <c r="B130" t="s">
         <v>127</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
         <v>153</v>
       </c>
-      <c r="D130" t="s">
-        <v>11</v>
-      </c>
       <c r="E130" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F130" t="s">
         <v>127</v>
       </c>
       <c r="G130" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H130" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I130" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>312</v>
       </c>
-      <c r="D131" t="s">
-        <v>11</v>
-      </c>
-      <c r="H131" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E131" t="s">
+        <v>11</v>
+      </c>
+      <c r="I131" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>154</v>
       </c>
       <c r="B132" t="s">
         <v>127</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>155</v>
       </c>
-      <c r="D132" t="s">
-        <v>11</v>
-      </c>
       <c r="E132" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F132" t="s">
         <v>127</v>
       </c>
       <c r="G132" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H132" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I132" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>312</v>
       </c>
-      <c r="D133" t="s">
-        <v>11</v>
-      </c>
-      <c r="H133" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E133" t="s">
+        <v>11</v>
+      </c>
+      <c r="I133" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>156</v>
       </c>
       <c r="B134" t="s">
         <v>127</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
         <v>157</v>
       </c>
-      <c r="D134" t="s">
-        <v>11</v>
-      </c>
       <c r="E134" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F134" t="s">
         <v>127</v>
       </c>
       <c r="G134" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H134" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I134" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>312</v>
       </c>
-      <c r="D135" t="s">
-        <v>11</v>
-      </c>
-      <c r="H135" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E135" t="s">
+        <v>11</v>
+      </c>
+      <c r="I135" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>158</v>
       </c>
       <c r="B136" t="s">
         <v>127</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
         <v>159</v>
       </c>
-      <c r="D136" t="s">
-        <v>11</v>
-      </c>
       <c r="E136" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F136" t="s">
         <v>127</v>
       </c>
       <c r="G136" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H136" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I136" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>312</v>
       </c>
-      <c r="D137" t="s">
-        <v>11</v>
-      </c>
-      <c r="H137" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E137" t="s">
+        <v>11</v>
+      </c>
+      <c r="I137" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>158</v>
       </c>
       <c r="B138" t="s">
         <v>127</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
         <v>160</v>
       </c>
-      <c r="D138" t="s">
-        <v>11</v>
-      </c>
       <c r="E138" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F138" t="s">
         <v>127</v>
       </c>
       <c r="G138" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H138" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I138" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>312</v>
       </c>
-      <c r="D139" t="s">
-        <v>11</v>
-      </c>
-      <c r="H139" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E139" t="s">
+        <v>11</v>
+      </c>
+      <c r="I139" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>152</v>
       </c>
       <c r="B140" t="s">
         <v>127</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" t="s">
         <v>161</v>
       </c>
-      <c r="D140" t="s">
-        <v>11</v>
-      </c>
       <c r="E140" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F140" t="s">
         <v>127</v>
       </c>
       <c r="G140" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H140" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I140" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>312</v>
       </c>
-      <c r="D141" t="s">
-        <v>11</v>
-      </c>
-      <c r="H141" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E141" t="s">
+        <v>11</v>
+      </c>
+      <c r="I141" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>162</v>
       </c>
       <c r="B142" t="s">
         <v>127</v>
       </c>
-      <c r="C142" t="s">
+      <c r="D142" t="s">
         <v>163</v>
       </c>
-      <c r="D142" t="s">
-        <v>11</v>
-      </c>
       <c r="E142" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F142" t="s">
         <v>127</v>
       </c>
       <c r="G142" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H142" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I142" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>312</v>
       </c>
-      <c r="D143" t="s">
-        <v>11</v>
-      </c>
-      <c r="H143" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E143" t="s">
+        <v>11</v>
+      </c>
+      <c r="I143" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>145</v>
       </c>
       <c r="B144" t="s">
         <v>127</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144" t="s">
         <v>164</v>
       </c>
-      <c r="D144" t="s">
-        <v>11</v>
-      </c>
       <c r="E144" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F144" t="s">
         <v>127</v>
       </c>
       <c r="G144" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H144" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I144" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>312</v>
       </c>
-      <c r="D145" t="s">
-        <v>11</v>
-      </c>
-      <c r="H145" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E145" t="s">
+        <v>11</v>
+      </c>
+      <c r="I145" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>165</v>
       </c>
       <c r="B146" t="s">
         <v>127</v>
       </c>
-      <c r="C146" t="s">
+      <c r="D146" t="s">
         <v>166</v>
       </c>
-      <c r="D146" t="s">
-        <v>11</v>
-      </c>
       <c r="E146" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F146" t="s">
         <v>127</v>
       </c>
       <c r="G146" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H146" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I146" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>312</v>
       </c>
-      <c r="D147" t="s">
-        <v>11</v>
-      </c>
-      <c r="H147" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E147" t="s">
+        <v>11</v>
+      </c>
+      <c r="I147" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>167</v>
       </c>
       <c r="B148" t="s">
         <v>127</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148" t="s">
         <v>168</v>
       </c>
-      <c r="D148" t="s">
-        <v>11</v>
-      </c>
       <c r="E148" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F148" t="s">
         <v>127</v>
       </c>
       <c r="G148" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H148" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I148" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>312</v>
       </c>
-      <c r="D149" t="s">
-        <v>11</v>
-      </c>
-      <c r="H149" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E149" t="s">
+        <v>11</v>
+      </c>
+      <c r="I149" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>169</v>
       </c>
       <c r="B150" t="s">
         <v>127</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D150" t="s">
         <v>170</v>
       </c>
-      <c r="D150" t="s">
-        <v>11</v>
-      </c>
       <c r="E150" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F150" t="s">
         <v>127</v>
       </c>
       <c r="G150" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H150" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I150" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>312</v>
       </c>
-      <c r="D151" t="s">
-        <v>11</v>
-      </c>
-      <c r="H151" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E151" t="s">
+        <v>11</v>
+      </c>
+      <c r="I151" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>171</v>
       </c>
       <c r="B152" t="s">
         <v>127</v>
       </c>
-      <c r="C152" t="s">
+      <c r="D152" t="s">
         <v>172</v>
       </c>
-      <c r="D152" t="s">
-        <v>11</v>
-      </c>
       <c r="E152" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F152" t="s">
         <v>127</v>
       </c>
       <c r="G152" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H152" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I152" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>312</v>
       </c>
-      <c r="D153" t="s">
-        <v>11</v>
-      </c>
-      <c r="H153" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E153" t="s">
+        <v>11</v>
+      </c>
+      <c r="I153" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>173</v>
       </c>
       <c r="B154" t="s">
         <v>127</v>
       </c>
-      <c r="C154" t="s">
+      <c r="D154" t="s">
         <v>174</v>
       </c>
-      <c r="D154" t="s">
-        <v>11</v>
-      </c>
       <c r="E154" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F154" t="s">
         <v>127</v>
       </c>
       <c r="G154" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H154" t="s">
+        <v>17</v>
+      </c>
+      <c r="I154" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>173</v>
       </c>
       <c r="B155" t="s">
         <v>127</v>
       </c>
-      <c r="C155" t="s">
+      <c r="D155" t="s">
         <v>335</v>
       </c>
-      <c r="D155" t="s">
-        <v>11</v>
-      </c>
       <c r="E155" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F155" t="s">
         <v>127</v>
       </c>
       <c r="G155" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H155" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I155" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>175</v>
       </c>
       <c r="B156" t="s">
         <v>127</v>
       </c>
-      <c r="C156" t="s">
+      <c r="D156" t="s">
         <v>372</v>
       </c>
-      <c r="D156" t="s">
-        <v>11</v>
-      </c>
       <c r="E156" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F156" t="s">
         <v>127</v>
       </c>
       <c r="G156" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H156" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I156" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>312</v>
       </c>
-      <c r="D157" t="s">
-        <v>11</v>
-      </c>
-      <c r="H157" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E157" t="s">
+        <v>11</v>
+      </c>
+      <c r="I157" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>176</v>
       </c>
       <c r="B158" t="s">
         <v>127</v>
       </c>
-      <c r="C158" t="s">
+      <c r="D158" t="s">
         <v>177</v>
       </c>
-      <c r="D158" t="s">
-        <v>11</v>
-      </c>
       <c r="E158" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F158" t="s">
         <v>127</v>
       </c>
       <c r="G158" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H158" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I158" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>312</v>
       </c>
-      <c r="D159" t="s">
-        <v>11</v>
-      </c>
-      <c r="H159" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E159" t="s">
+        <v>11</v>
+      </c>
+      <c r="I159" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>178</v>
       </c>
       <c r="B160" t="s">
         <v>127</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160" t="s">
         <v>179</v>
       </c>
-      <c r="D160" t="s">
-        <v>11</v>
-      </c>
       <c r="E160" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F160" t="s">
         <v>127</v>
       </c>
       <c r="G160" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H160" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I160" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>312</v>
       </c>
-      <c r="D161" t="s">
-        <v>11</v>
-      </c>
-      <c r="H161" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E161" t="s">
+        <v>11</v>
+      </c>
+      <c r="I161" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>176</v>
       </c>
       <c r="B162" t="s">
         <v>127</v>
       </c>
-      <c r="C162" t="s">
+      <c r="D162" t="s">
         <v>180</v>
       </c>
-      <c r="D162" t="s">
-        <v>11</v>
-      </c>
       <c r="E162" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F162" t="s">
         <v>127</v>
       </c>
       <c r="G162" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H162" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I162" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>312</v>
       </c>
-      <c r="D163" t="s">
-        <v>11</v>
-      </c>
-      <c r="H163" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E163" t="s">
+        <v>11</v>
+      </c>
+      <c r="I163" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>181</v>
       </c>
       <c r="B164" t="s">
         <v>127</v>
       </c>
-      <c r="C164" t="s">
+      <c r="D164" t="s">
         <v>182</v>
       </c>
-      <c r="D164" t="s">
-        <v>11</v>
-      </c>
       <c r="E164" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F164" t="s">
         <v>127</v>
       </c>
       <c r="G164" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H164" t="s">
+        <v>17</v>
+      </c>
+      <c r="I164" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>181</v>
       </c>
       <c r="B165" t="s">
         <v>127</v>
       </c>
-      <c r="C165" t="s">
+      <c r="D165" t="s">
         <v>343</v>
       </c>
-      <c r="D165" t="s">
-        <v>11</v>
-      </c>
       <c r="E165" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F165" t="s">
         <v>127</v>
       </c>
       <c r="G165" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H165" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I165" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>183</v>
       </c>
       <c r="B166" t="s">
         <v>127</v>
       </c>
-      <c r="C166" t="s">
+      <c r="D166" t="s">
         <v>184</v>
       </c>
-      <c r="D166" t="s">
-        <v>11</v>
-      </c>
       <c r="E166" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F166" t="s">
         <v>127</v>
       </c>
       <c r="G166" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H166" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I166" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>312</v>
       </c>
-      <c r="D167" t="s">
-        <v>11</v>
-      </c>
-      <c r="H167" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E167" t="s">
+        <v>11</v>
+      </c>
+      <c r="I167" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>185</v>
       </c>
       <c r="B168" t="s">
         <v>127</v>
       </c>
-      <c r="C168" t="s">
+      <c r="D168" t="s">
         <v>186</v>
       </c>
-      <c r="D168" t="s">
-        <v>11</v>
-      </c>
       <c r="E168" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F168" t="s">
         <v>127</v>
       </c>
       <c r="G168" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H168" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I168" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>312</v>
       </c>
-      <c r="D169" t="s">
-        <v>11</v>
-      </c>
-      <c r="H169" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E169" t="s">
+        <v>11</v>
+      </c>
+      <c r="I169" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>187</v>
       </c>
       <c r="B170" t="s">
         <v>127</v>
       </c>
-      <c r="C170" t="s">
+      <c r="D170" t="s">
         <v>188</v>
       </c>
-      <c r="D170" t="s">
-        <v>11</v>
-      </c>
       <c r="E170" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F170" t="s">
         <v>127</v>
       </c>
       <c r="G170" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H170" t="s">
+        <v>17</v>
+      </c>
+      <c r="I170" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>187</v>
       </c>
       <c r="B171" t="s">
         <v>127</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
         <v>339</v>
       </c>
-      <c r="D171" t="s">
-        <v>11</v>
-      </c>
       <c r="E171" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F171" t="s">
         <v>127</v>
       </c>
       <c r="G171" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H171" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I171" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>189</v>
       </c>
       <c r="B172" t="s">
         <v>127</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
         <v>190</v>
       </c>
-      <c r="D172" t="s">
-        <v>11</v>
-      </c>
       <c r="E172" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F172" t="s">
         <v>127</v>
       </c>
       <c r="G172" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H172" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I172" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>312</v>
       </c>
-      <c r="D173" t="s">
-        <v>11</v>
-      </c>
-      <c r="H173" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E173" t="s">
+        <v>11</v>
+      </c>
+      <c r="I173" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>191</v>
       </c>
       <c r="B174" t="s">
         <v>127</v>
       </c>
-      <c r="C174" t="s">
+      <c r="D174" t="s">
         <v>192</v>
       </c>
-      <c r="D174" t="s">
-        <v>11</v>
-      </c>
       <c r="E174" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F174" t="s">
         <v>127</v>
       </c>
       <c r="G174" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H174" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I174" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>191</v>
       </c>
       <c r="B175" t="s">
         <v>127</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D175" t="s">
         <v>344</v>
       </c>
-      <c r="D175" t="s">
-        <v>11</v>
-      </c>
       <c r="E175" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F175" t="s">
         <v>127</v>
       </c>
       <c r="G175" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H175" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I175" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>193</v>
       </c>
       <c r="B176" t="s">
         <v>127</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176" t="s">
         <v>345</v>
       </c>
-      <c r="D176" t="s">
-        <v>11</v>
-      </c>
       <c r="E176" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F176" t="s">
         <v>127</v>
       </c>
       <c r="G176" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H176" t="s">
+        <v>17</v>
+      </c>
+      <c r="I176" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>193</v>
       </c>
       <c r="B177" t="s">
         <v>127</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177" t="s">
         <v>346</v>
       </c>
-      <c r="D177" t="s">
-        <v>11</v>
-      </c>
       <c r="E177" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F177" t="s">
         <v>127</v>
       </c>
       <c r="G177" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H177" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I177" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>194</v>
       </c>
       <c r="B178" t="s">
         <v>127</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178" t="s">
         <v>195</v>
       </c>
-      <c r="D178" t="s">
-        <v>11</v>
-      </c>
       <c r="E178" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F178" t="s">
         <v>127</v>
       </c>
       <c r="G178" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H178" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I178" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>312</v>
       </c>
-      <c r="D179" t="s">
-        <v>11</v>
-      </c>
-      <c r="H179" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E179" t="s">
+        <v>11</v>
+      </c>
+      <c r="I179" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>196</v>
       </c>
       <c r="B180" t="s">
         <v>127</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
         <v>197</v>
       </c>
-      <c r="D180" t="s">
-        <v>11</v>
-      </c>
       <c r="E180" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F180" t="s">
         <v>127</v>
       </c>
       <c r="G180" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H180" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I180" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>312</v>
       </c>
-      <c r="D181" t="s">
-        <v>11</v>
-      </c>
-      <c r="H181" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E181" t="s">
+        <v>11</v>
+      </c>
+      <c r="I181" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>198</v>
       </c>
       <c r="B182" t="s">
         <v>127</v>
       </c>
-      <c r="C182" t="s">
+      <c r="D182" t="s">
         <v>199</v>
       </c>
-      <c r="D182" t="s">
-        <v>11</v>
-      </c>
       <c r="E182" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F182" t="s">
         <v>127</v>
       </c>
       <c r="G182" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H182" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I182" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>312</v>
       </c>
-      <c r="D183" t="s">
-        <v>11</v>
-      </c>
-      <c r="H183" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E183" t="s">
+        <v>11</v>
+      </c>
+      <c r="I183" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>200</v>
       </c>
       <c r="B184" t="s">
         <v>127</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D184" t="s">
         <v>201</v>
       </c>
-      <c r="D184" t="s">
-        <v>11</v>
-      </c>
       <c r="E184" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F184" t="s">
         <v>127</v>
       </c>
       <c r="G184" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H184" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I184" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>312</v>
       </c>
-      <c r="D185" t="s">
-        <v>11</v>
-      </c>
-      <c r="H185" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E185" t="s">
+        <v>11</v>
+      </c>
+      <c r="I185" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>202</v>
       </c>
       <c r="B186" t="s">
         <v>127</v>
       </c>
-      <c r="C186" t="s">
+      <c r="D186" t="s">
         <v>203</v>
       </c>
-      <c r="D186" t="s">
-        <v>11</v>
-      </c>
       <c r="E186" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F186" t="s">
         <v>127</v>
       </c>
       <c r="G186" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H186" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I186" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>312</v>
       </c>
-      <c r="D187" t="s">
-        <v>11</v>
-      </c>
-      <c r="H187" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E187" t="s">
+        <v>11</v>
+      </c>
+      <c r="I187" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>204</v>
       </c>
       <c r="B188" t="s">
         <v>127</v>
       </c>
-      <c r="C188" t="s">
+      <c r="D188" t="s">
         <v>205</v>
       </c>
-      <c r="D188" t="s">
-        <v>11</v>
-      </c>
       <c r="E188" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F188" t="s">
         <v>127</v>
       </c>
       <c r="G188" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H188" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I188" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>312</v>
       </c>
-      <c r="D189" t="s">
-        <v>11</v>
-      </c>
-      <c r="H189" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E189" t="s">
+        <v>11</v>
+      </c>
+      <c r="I189" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>206</v>
       </c>
       <c r="B190" t="s">
         <v>127</v>
       </c>
-      <c r="C190" t="s">
+      <c r="D190" t="s">
         <v>207</v>
       </c>
-      <c r="D190" t="s">
-        <v>11</v>
-      </c>
       <c r="E190" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F190" t="s">
         <v>127</v>
       </c>
       <c r="G190" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H190" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I190" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>312</v>
       </c>
-      <c r="D191" t="s">
-        <v>11</v>
-      </c>
-      <c r="H191" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E191" t="s">
+        <v>11</v>
+      </c>
+      <c r="I191" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>208</v>
       </c>
       <c r="B192" t="s">
         <v>127</v>
       </c>
-      <c r="C192" t="s">
+      <c r="D192" t="s">
         <v>209</v>
       </c>
-      <c r="D192" t="s">
-        <v>11</v>
-      </c>
       <c r="E192" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F192" t="s">
         <v>127</v>
       </c>
       <c r="G192" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H192" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I192" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>312</v>
       </c>
-      <c r="D193" t="s">
-        <v>11</v>
-      </c>
-      <c r="H193" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E193" t="s">
+        <v>11</v>
+      </c>
+      <c r="I193" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>210</v>
       </c>
       <c r="B194" t="s">
         <v>127</v>
       </c>
-      <c r="C194" t="s">
+      <c r="D194" t="s">
         <v>211</v>
       </c>
-      <c r="D194" t="s">
-        <v>11</v>
-      </c>
       <c r="E194" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F194" t="s">
         <v>127</v>
       </c>
       <c r="G194" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H194" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I194" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>312</v>
       </c>
-      <c r="D195" t="s">
-        <v>11</v>
-      </c>
-      <c r="H195" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E195" t="s">
+        <v>11</v>
+      </c>
+      <c r="I195" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>212</v>
       </c>
       <c r="B196" t="s">
         <v>127</v>
       </c>
-      <c r="C196" t="s">
+      <c r="D196" t="s">
         <v>213</v>
       </c>
-      <c r="D196" t="s">
-        <v>11</v>
-      </c>
       <c r="E196" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F196" t="s">
         <v>127</v>
       </c>
       <c r="G196" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H196" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I196" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>312</v>
       </c>
-      <c r="D197" t="s">
-        <v>11</v>
-      </c>
-      <c r="H197" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E197" t="s">
+        <v>11</v>
+      </c>
+      <c r="I197" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>214</v>
       </c>
       <c r="B198" t="s">
         <v>127</v>
       </c>
-      <c r="C198" t="s">
+      <c r="D198" t="s">
         <v>215</v>
       </c>
-      <c r="D198" t="s">
-        <v>11</v>
-      </c>
       <c r="E198" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F198" t="s">
         <v>127</v>
       </c>
       <c r="G198" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H198" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I198" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>312</v>
       </c>
-      <c r="D199" t="s">
-        <v>11</v>
-      </c>
-      <c r="H199" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E199" t="s">
+        <v>11</v>
+      </c>
+      <c r="I199" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>216</v>
       </c>
       <c r="B200" t="s">
         <v>127</v>
       </c>
-      <c r="C200" t="s">
+      <c r="D200" t="s">
         <v>217</v>
       </c>
-      <c r="D200" t="s">
-        <v>11</v>
-      </c>
       <c r="E200" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F200" t="s">
         <v>127</v>
       </c>
       <c r="G200" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H200" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I200" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>312</v>
       </c>
-      <c r="D201" t="s">
-        <v>11</v>
-      </c>
-      <c r="H201" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E201" t="s">
+        <v>11</v>
+      </c>
+      <c r="I201" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>218</v>
       </c>
       <c r="B202" t="s">
         <v>127</v>
       </c>
-      <c r="C202" t="s">
+      <c r="D202" t="s">
         <v>219</v>
       </c>
-      <c r="D202" t="s">
-        <v>11</v>
-      </c>
       <c r="E202" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F202" t="s">
         <v>127</v>
       </c>
       <c r="G202" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H202" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I202" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>312</v>
       </c>
-      <c r="D203" t="s">
-        <v>11</v>
-      </c>
-      <c r="H203" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E203" t="s">
+        <v>11</v>
+      </c>
+      <c r="I203" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>220</v>
       </c>
       <c r="B204" t="s">
         <v>127</v>
       </c>
-      <c r="C204" t="s">
+      <c r="D204" t="s">
         <v>221</v>
       </c>
-      <c r="D204" t="s">
-        <v>11</v>
-      </c>
       <c r="E204" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F204" t="s">
         <v>127</v>
       </c>
       <c r="G204" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H204" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I204" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>312</v>
       </c>
-      <c r="D205" t="s">
-        <v>11</v>
-      </c>
-      <c r="H205" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E205" t="s">
+        <v>11</v>
+      </c>
+      <c r="I205" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>222</v>
       </c>
       <c r="B206" t="s">
         <v>127</v>
       </c>
-      <c r="C206" t="s">
+      <c r="D206" t="s">
         <v>223</v>
       </c>
-      <c r="D206" t="s">
-        <v>11</v>
-      </c>
       <c r="E206" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F206" t="s">
         <v>127</v>
       </c>
       <c r="G206" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H206" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I206" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>312</v>
       </c>
-      <c r="D207" t="s">
-        <v>11</v>
-      </c>
-      <c r="H207" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E207" t="s">
+        <v>11</v>
+      </c>
+      <c r="I207" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>224</v>
       </c>
       <c r="B208" t="s">
         <v>127</v>
       </c>
-      <c r="C208" t="s">
+      <c r="D208" t="s">
         <v>225</v>
       </c>
-      <c r="D208" t="s">
-        <v>11</v>
-      </c>
       <c r="E208" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F208" t="s">
         <v>127</v>
       </c>
       <c r="G208" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H208" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I208" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>312</v>
       </c>
-      <c r="D209" t="s">
-        <v>11</v>
-      </c>
-      <c r="H209" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E209" t="s">
+        <v>11</v>
+      </c>
+      <c r="I209" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>226</v>
       </c>
       <c r="B210" t="s">
         <v>127</v>
       </c>
-      <c r="C210" t="s">
+      <c r="D210" t="s">
         <v>227</v>
       </c>
-      <c r="D210" t="s">
-        <v>11</v>
-      </c>
       <c r="E210" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F210" t="s">
         <v>127</v>
       </c>
       <c r="G210" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H210" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I210" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>312</v>
       </c>
-      <c r="D211" t="s">
-        <v>11</v>
-      </c>
-      <c r="H211" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E211" t="s">
+        <v>11</v>
+      </c>
+      <c r="I211" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>228</v>
       </c>
       <c r="B212" t="s">
         <v>127</v>
       </c>
-      <c r="C212" t="s">
+      <c r="D212" t="s">
         <v>229</v>
       </c>
-      <c r="D212" t="s">
-        <v>11</v>
-      </c>
       <c r="E212" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F212" t="s">
         <v>127</v>
       </c>
       <c r="G212" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H212" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I212" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>312</v>
       </c>
-      <c r="D213" t="s">
-        <v>11</v>
-      </c>
-      <c r="H213" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E213" t="s">
+        <v>11</v>
+      </c>
+      <c r="I213" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>230</v>
       </c>
       <c r="B214" t="s">
         <v>127</v>
       </c>
-      <c r="C214" t="s">
+      <c r="D214" t="s">
         <v>231</v>
       </c>
-      <c r="D214" t="s">
-        <v>11</v>
-      </c>
       <c r="E214" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F214" t="s">
         <v>127</v>
       </c>
       <c r="G214" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H214" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I214" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>312</v>
       </c>
-      <c r="D215" t="s">
-        <v>11</v>
-      </c>
-      <c r="H215" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E215" t="s">
+        <v>11</v>
+      </c>
+      <c r="I215" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>232</v>
       </c>
       <c r="B216" t="s">
         <v>127</v>
       </c>
-      <c r="C216" t="s">
+      <c r="D216" t="s">
         <v>233</v>
       </c>
-      <c r="D216" t="s">
-        <v>11</v>
-      </c>
       <c r="E216" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F216" t="s">
         <v>127</v>
       </c>
       <c r="G216" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H216" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I216" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>312</v>
       </c>
-      <c r="D217" t="s">
-        <v>11</v>
-      </c>
-      <c r="H217" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E217" t="s">
+        <v>11</v>
+      </c>
+      <c r="I217" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>224</v>
       </c>
       <c r="B218" t="s">
         <v>127</v>
       </c>
-      <c r="C218" t="s">
+      <c r="D218" t="s">
         <v>234</v>
       </c>
-      <c r="D218" t="s">
-        <v>11</v>
-      </c>
       <c r="E218" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F218" t="s">
         <v>127</v>
       </c>
       <c r="G218" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H218" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I218" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>312</v>
       </c>
-      <c r="D219" t="s">
-        <v>11</v>
-      </c>
-      <c r="H219" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E219" t="s">
+        <v>11</v>
+      </c>
+      <c r="I219" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>235</v>
       </c>
       <c r="B220" t="s">
         <v>127</v>
       </c>
-      <c r="C220" t="s">
+      <c r="D220" t="s">
         <v>236</v>
       </c>
-      <c r="D220" t="s">
-        <v>11</v>
-      </c>
       <c r="E220" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F220" t="s">
         <v>127</v>
       </c>
       <c r="G220" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H220" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I220" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>312</v>
       </c>
-      <c r="D221" t="s">
-        <v>11</v>
-      </c>
-      <c r="H221" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E221" t="s">
+        <v>11</v>
+      </c>
+      <c r="I221" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>232</v>
       </c>
       <c r="B222" t="s">
         <v>127</v>
       </c>
-      <c r="C222" t="s">
+      <c r="D222" t="s">
         <v>237</v>
       </c>
-      <c r="D222" t="s">
-        <v>11</v>
-      </c>
       <c r="E222" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F222" t="s">
         <v>127</v>
       </c>
       <c r="G222" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H222" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I222" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>312</v>
       </c>
-      <c r="D223" t="s">
-        <v>11</v>
-      </c>
-      <c r="H223" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E223" t="s">
+        <v>11</v>
+      </c>
+      <c r="I223" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>238</v>
       </c>
       <c r="B224" t="s">
         <v>127</v>
       </c>
-      <c r="C224" t="s">
+      <c r="D224" t="s">
         <v>239</v>
       </c>
-      <c r="D224" t="s">
-        <v>11</v>
-      </c>
       <c r="E224" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F224" t="s">
         <v>127</v>
       </c>
       <c r="G224" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H224" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I224" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>312</v>
       </c>
-      <c r="D225" t="s">
-        <v>11</v>
-      </c>
-      <c r="H225" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E225" t="s">
+        <v>11</v>
+      </c>
+      <c r="I225" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>240</v>
       </c>
       <c r="B226" t="s">
         <v>127</v>
       </c>
-      <c r="C226" t="s">
+      <c r="D226" t="s">
         <v>241</v>
       </c>
-      <c r="D226" t="s">
-        <v>11</v>
-      </c>
       <c r="E226" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F226" t="s">
         <v>127</v>
       </c>
       <c r="G226" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H226" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I226" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>312</v>
       </c>
-      <c r="D227" t="s">
-        <v>11</v>
-      </c>
-      <c r="H227" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E227" t="s">
+        <v>11</v>
+      </c>
+      <c r="I227" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>242</v>
       </c>
       <c r="B228" t="s">
         <v>127</v>
       </c>
-      <c r="C228" t="s">
+      <c r="D228" t="s">
         <v>243</v>
       </c>
-      <c r="D228" t="s">
-        <v>11</v>
-      </c>
       <c r="E228" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F228" t="s">
         <v>127</v>
       </c>
       <c r="G228" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H228" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I228" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>312</v>
       </c>
-      <c r="D229" t="s">
-        <v>11</v>
-      </c>
-      <c r="H229" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E229" t="s">
+        <v>11</v>
+      </c>
+      <c r="I229" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>244</v>
       </c>
       <c r="B230" t="s">
         <v>127</v>
       </c>
-      <c r="C230" t="s">
+      <c r="D230" t="s">
         <v>245</v>
       </c>
-      <c r="D230" t="s">
-        <v>11</v>
-      </c>
       <c r="E230" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F230" t="s">
         <v>127</v>
       </c>
       <c r="G230" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H230" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I230" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>312</v>
       </c>
-      <c r="D231" t="s">
-        <v>11</v>
-      </c>
-      <c r="H231" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E231" t="s">
+        <v>11</v>
+      </c>
+      <c r="I231" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>246</v>
       </c>
       <c r="B232" t="s">
         <v>127</v>
       </c>
-      <c r="C232" t="s">
+      <c r="D232" t="s">
         <v>247</v>
       </c>
-      <c r="D232" t="s">
-        <v>11</v>
-      </c>
       <c r="E232" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F232" t="s">
         <v>127</v>
       </c>
       <c r="G232" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H232" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I232" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>312</v>
       </c>
-      <c r="D233" t="s">
-        <v>11</v>
-      </c>
-      <c r="H233" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E233" t="s">
+        <v>11</v>
+      </c>
+      <c r="I233" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>248</v>
       </c>
       <c r="B234" t="s">
         <v>127</v>
       </c>
-      <c r="C234" t="s">
+      <c r="D234" t="s">
         <v>249</v>
       </c>
-      <c r="D234" t="s">
-        <v>11</v>
-      </c>
       <c r="E234" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F234" t="s">
         <v>127</v>
       </c>
       <c r="G234" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H234" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I234" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>312</v>
       </c>
-      <c r="D235" t="s">
-        <v>11</v>
-      </c>
-      <c r="H235" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E235" t="s">
+        <v>11</v>
+      </c>
+      <c r="I235" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>250</v>
       </c>
       <c r="B236" t="s">
         <v>127</v>
       </c>
-      <c r="C236" t="s">
+      <c r="D236" t="s">
         <v>251</v>
       </c>
-      <c r="D236" t="s">
-        <v>11</v>
-      </c>
       <c r="E236" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F236" t="s">
         <v>127</v>
       </c>
       <c r="G236" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H236" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I236" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>312</v>
       </c>
-      <c r="D237" t="s">
-        <v>11</v>
-      </c>
-      <c r="H237" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E237" t="s">
+        <v>11</v>
+      </c>
+      <c r="I237" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>252</v>
       </c>
       <c r="B238" t="s">
         <v>127</v>
       </c>
-      <c r="C238" t="s">
+      <c r="D238" t="s">
         <v>253</v>
       </c>
-      <c r="D238" t="s">
-        <v>11</v>
-      </c>
       <c r="E238" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F238" t="s">
         <v>127</v>
       </c>
       <c r="G238" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H238" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I238" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>312</v>
       </c>
-      <c r="D239" t="s">
-        <v>11</v>
-      </c>
-      <c r="H239" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E239" t="s">
+        <v>11</v>
+      </c>
+      <c r="I239" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>254</v>
       </c>
       <c r="B240" t="s">
         <v>127</v>
       </c>
-      <c r="C240" t="s">
+      <c r="D240" t="s">
         <v>255</v>
       </c>
-      <c r="D240" t="s">
-        <v>11</v>
-      </c>
       <c r="E240" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F240" t="s">
         <v>127</v>
       </c>
       <c r="G240" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H240" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I240" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>312</v>
       </c>
-      <c r="D241" t="s">
-        <v>11</v>
-      </c>
-      <c r="H241" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E241" t="s">
+        <v>11</v>
+      </c>
+      <c r="I241" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>256</v>
       </c>
       <c r="B242" t="s">
         <v>127</v>
       </c>
-      <c r="C242" t="s">
+      <c r="D242" t="s">
         <v>257</v>
       </c>
-      <c r="D242" t="s">
-        <v>11</v>
-      </c>
       <c r="E242" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F242" t="s">
         <v>127</v>
       </c>
       <c r="G242" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H242" t="s">
+        <v>17</v>
+      </c>
+      <c r="I242" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>256</v>
       </c>
       <c r="B243" t="s">
         <v>127</v>
       </c>
-      <c r="C243" t="s">
+      <c r="D243" t="s">
         <v>336</v>
       </c>
-      <c r="D243" t="s">
-        <v>11</v>
-      </c>
       <c r="E243" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F243" t="s">
         <v>127</v>
       </c>
       <c r="G243" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H243" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I243" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>258</v>
       </c>
       <c r="B244" t="s">
         <v>127</v>
       </c>
-      <c r="C244" t="s">
+      <c r="D244" t="s">
         <v>259</v>
       </c>
-      <c r="D244" t="s">
-        <v>11</v>
-      </c>
       <c r="E244" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F244" t="s">
         <v>127</v>
       </c>
       <c r="G244" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H244" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I244" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>312</v>
       </c>
-      <c r="D245" t="s">
-        <v>11</v>
-      </c>
-      <c r="H245" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E245" t="s">
+        <v>11</v>
+      </c>
+      <c r="I245" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>260</v>
       </c>
       <c r="B246" t="s">
         <v>127</v>
       </c>
-      <c r="C246" t="s">
+      <c r="D246" t="s">
         <v>261</v>
       </c>
-      <c r="D246" t="s">
+      <c r="E246" t="s">
         <v>99</v>
       </c>
-      <c r="E246" t="s">
-        <v>127</v>
-      </c>
       <c r="F246" t="s">
         <v>127</v>
       </c>
       <c r="G246" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H246" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I246" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>312</v>
       </c>
-      <c r="D247" t="s">
-        <v>11</v>
-      </c>
-      <c r="H247" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E247" t="s">
+        <v>11</v>
+      </c>
+      <c r="I247" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>260</v>
       </c>
       <c r="B248" t="s">
         <v>127</v>
       </c>
-      <c r="C248" t="s">
+      <c r="D248" t="s">
         <v>262</v>
       </c>
-      <c r="D248" t="s">
-        <v>11</v>
-      </c>
       <c r="E248" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F248" t="s">
         <v>127</v>
       </c>
       <c r="G248" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H248" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I248" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>312</v>
       </c>
-      <c r="D249" t="s">
-        <v>11</v>
-      </c>
-      <c r="H249" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E249" t="s">
+        <v>11</v>
+      </c>
+      <c r="I249" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>263</v>
       </c>
       <c r="B250" t="s">
         <v>127</v>
       </c>
-      <c r="C250" t="s">
+      <c r="D250" t="s">
         <v>264</v>
       </c>
-      <c r="D250" t="s">
-        <v>11</v>
-      </c>
       <c r="E250" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F250" t="s">
         <v>127</v>
       </c>
       <c r="G250" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H250" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I250" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>312</v>
       </c>
-      <c r="D251" t="s">
-        <v>11</v>
-      </c>
-      <c r="H251" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E251" t="s">
+        <v>11</v>
+      </c>
+      <c r="I251" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>265</v>
       </c>
       <c r="B252" t="s">
         <v>127</v>
       </c>
-      <c r="C252" t="s">
+      <c r="D252" t="s">
         <v>266</v>
       </c>
-      <c r="D252" t="s">
-        <v>11</v>
-      </c>
       <c r="E252" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F252" t="s">
         <v>127</v>
       </c>
       <c r="G252" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H252" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I252" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>312</v>
       </c>
-      <c r="D253" t="s">
-        <v>11</v>
-      </c>
-      <c r="H253" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E253" t="s">
+        <v>11</v>
+      </c>
+      <c r="I253" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>267</v>
       </c>
       <c r="B254" t="s">
         <v>127</v>
       </c>
-      <c r="C254" t="s">
+      <c r="D254" t="s">
         <v>268</v>
       </c>
-      <c r="D254" t="s">
-        <v>11</v>
-      </c>
       <c r="E254" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F254" t="s">
         <v>127</v>
       </c>
       <c r="G254" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H254" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I254" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>312</v>
       </c>
-      <c r="D255" t="s">
-        <v>11</v>
-      </c>
-      <c r="H255" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E255" t="s">
+        <v>11</v>
+      </c>
+      <c r="I255" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>269</v>
       </c>
       <c r="B256" t="s">
         <v>127</v>
       </c>
-      <c r="C256" t="s">
+      <c r="D256" t="s">
         <v>270</v>
       </c>
-      <c r="D256" t="s">
-        <v>11</v>
-      </c>
       <c r="E256" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F256" t="s">
         <v>127</v>
       </c>
       <c r="G256" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H256" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I256" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>312</v>
       </c>
-      <c r="D257" t="s">
-        <v>11</v>
-      </c>
-      <c r="H257" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E257" t="s">
+        <v>11</v>
+      </c>
+      <c r="I257" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>271</v>
       </c>
       <c r="B258" t="s">
         <v>127</v>
       </c>
-      <c r="C258" t="s">
+      <c r="D258" t="s">
         <v>272</v>
       </c>
-      <c r="D258" t="s">
-        <v>11</v>
-      </c>
       <c r="E258" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F258" t="s">
         <v>127</v>
       </c>
       <c r="G258" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H258" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I258" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>312</v>
       </c>
-      <c r="D259" t="s">
-        <v>11</v>
-      </c>
-      <c r="H259" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E259" t="s">
+        <v>11</v>
+      </c>
+      <c r="I259" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>273</v>
       </c>
       <c r="B260" t="s">
         <v>127</v>
       </c>
-      <c r="C260" t="s">
+      <c r="D260" t="s">
         <v>274</v>
       </c>
-      <c r="D260" t="s">
-        <v>11</v>
-      </c>
       <c r="E260" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F260" t="s">
         <v>127</v>
       </c>
       <c r="G260" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H260" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I260" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>312</v>
       </c>
-      <c r="D261" t="s">
-        <v>11</v>
-      </c>
-      <c r="H261" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E261" t="s">
+        <v>11</v>
+      </c>
+      <c r="I261" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>275</v>
       </c>
       <c r="B262" t="s">
         <v>127</v>
       </c>
-      <c r="C262" t="s">
+      <c r="D262" t="s">
         <v>276</v>
       </c>
-      <c r="D262" t="s">
-        <v>11</v>
-      </c>
       <c r="E262" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F262" t="s">
         <v>127</v>
       </c>
       <c r="G262" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H262" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I262" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>312</v>
       </c>
-      <c r="D263" t="s">
-        <v>11</v>
-      </c>
-      <c r="H263" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E263" t="s">
+        <v>11</v>
+      </c>
+      <c r="I263" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>277</v>
       </c>
       <c r="B264" t="s">
         <v>127</v>
       </c>
-      <c r="C264" t="s">
+      <c r="D264" t="s">
         <v>278</v>
       </c>
-      <c r="D264" t="s">
-        <v>11</v>
-      </c>
       <c r="E264" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F264" t="s">
         <v>127</v>
       </c>
       <c r="G264" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H264" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I264" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>312</v>
       </c>
-      <c r="D265" t="s">
-        <v>11</v>
-      </c>
-      <c r="H265" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E265" t="s">
+        <v>11</v>
+      </c>
+      <c r="I265" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>279</v>
       </c>
       <c r="B266" t="s">
         <v>127</v>
       </c>
-      <c r="C266" t="s">
+      <c r="D266" t="s">
         <v>280</v>
       </c>
-      <c r="D266" t="s">
-        <v>11</v>
-      </c>
       <c r="E266" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F266" t="s">
         <v>127</v>
       </c>
       <c r="G266" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H266" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I266" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>312</v>
       </c>
-      <c r="D267" t="s">
-        <v>11</v>
-      </c>
-      <c r="H267" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E267" t="s">
+        <v>11</v>
+      </c>
+      <c r="I267" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>281</v>
       </c>
       <c r="B268" t="s">
         <v>127</v>
       </c>
-      <c r="C268" t="s">
+      <c r="D268" t="s">
         <v>282</v>
       </c>
-      <c r="D268" t="s">
-        <v>11</v>
-      </c>
       <c r="E268" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F268" t="s">
         <v>127</v>
       </c>
       <c r="G268" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H268" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I268" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>312</v>
       </c>
-      <c r="D269" t="s">
-        <v>11</v>
-      </c>
-      <c r="H269" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E269" t="s">
+        <v>11</v>
+      </c>
+      <c r="I269" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>283</v>
       </c>
       <c r="B270" t="s">
         <v>127</v>
       </c>
-      <c r="C270" t="s">
+      <c r="D270" t="s">
         <v>284</v>
       </c>
-      <c r="D270" t="s">
-        <v>11</v>
-      </c>
       <c r="E270" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F270" t="s">
         <v>127</v>
       </c>
       <c r="G270" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H270" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I270" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>312</v>
       </c>
-      <c r="D271" t="s">
-        <v>11</v>
-      </c>
-      <c r="H271" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E271" t="s">
+        <v>11</v>
+      </c>
+      <c r="I271" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>285</v>
       </c>
       <c r="B272" t="s">
         <v>127</v>
       </c>
-      <c r="C272" t="s">
+      <c r="D272" t="s">
         <v>286</v>
       </c>
-      <c r="D272" t="s">
-        <v>11</v>
-      </c>
       <c r="E272" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F272" t="s">
         <v>127</v>
       </c>
       <c r="G272" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H272" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I272" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>312</v>
       </c>
-      <c r="D273" t="s">
-        <v>11</v>
-      </c>
-      <c r="H273" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E273" t="s">
+        <v>11</v>
+      </c>
+      <c r="I273" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>287</v>
       </c>
       <c r="B274" t="s">
         <v>127</v>
       </c>
-      <c r="C274" t="s">
+      <c r="D274" t="s">
         <v>288</v>
       </c>
-      <c r="D274" t="s">
-        <v>11</v>
-      </c>
       <c r="E274" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F274" t="s">
         <v>127</v>
       </c>
       <c r="G274" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H274" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I274" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>312</v>
       </c>
-      <c r="D275" t="s">
-        <v>11</v>
-      </c>
-      <c r="H275" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E275" t="s">
+        <v>11</v>
+      </c>
+      <c r="I275" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>289</v>
       </c>
       <c r="B276" t="s">
         <v>127</v>
       </c>
-      <c r="C276" t="s">
+      <c r="D276" t="s">
         <v>290</v>
       </c>
-      <c r="D276" t="s">
-        <v>11</v>
-      </c>
       <c r="E276" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F276" t="s">
         <v>127</v>
       </c>
       <c r="G276" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H276" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I276" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>312</v>
       </c>
-      <c r="D277" t="s">
-        <v>11</v>
-      </c>
-      <c r="H277" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E277" t="s">
+        <v>11</v>
+      </c>
+      <c r="I277" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>291</v>
       </c>
       <c r="B278" t="s">
         <v>127</v>
       </c>
-      <c r="C278" t="s">
+      <c r="D278" t="s">
         <v>292</v>
       </c>
-      <c r="D278" t="s">
-        <v>11</v>
-      </c>
       <c r="E278" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F278" t="s">
         <v>127</v>
       </c>
       <c r="G278" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H278" t="s">
+        <v>17</v>
+      </c>
+      <c r="I278" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>291</v>
       </c>
       <c r="B279" t="s">
         <v>127</v>
       </c>
-      <c r="C279" t="s">
+      <c r="D279" t="s">
         <v>337</v>
       </c>
-      <c r="D279" t="s">
-        <v>11</v>
-      </c>
       <c r="E279" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F279" t="s">
         <v>127</v>
       </c>
       <c r="G279" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H279" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I279" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>293</v>
       </c>
       <c r="B280" t="s">
         <v>127</v>
       </c>
-      <c r="C280" t="s">
+      <c r="D280" t="s">
         <v>294</v>
       </c>
-      <c r="D280" t="s">
-        <v>11</v>
-      </c>
       <c r="E280" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F280" t="s">
         <v>127</v>
       </c>
       <c r="G280" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H280" t="s">
+        <v>17</v>
+      </c>
+      <c r="I280" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>293</v>
       </c>
       <c r="B281" t="s">
         <v>127</v>
       </c>
-      <c r="C281" t="s">
+      <c r="D281" t="s">
         <v>338</v>
       </c>
-      <c r="D281" t="s">
-        <v>11</v>
-      </c>
       <c r="E281" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F281" t="s">
         <v>127</v>
       </c>
       <c r="G281" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H281" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I281" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>295</v>
       </c>
       <c r="B282" t="s">
         <v>127</v>
       </c>
-      <c r="C282" t="s">
+      <c r="D282" t="s">
         <v>296</v>
       </c>
-      <c r="D282" t="s">
-        <v>11</v>
-      </c>
       <c r="E282" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F282" t="s">
         <v>127</v>
       </c>
       <c r="G282" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H282" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I282" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>312</v>
       </c>
-      <c r="D283" t="s">
-        <v>11</v>
-      </c>
-      <c r="H283" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E283" t="s">
+        <v>11</v>
+      </c>
+      <c r="I283" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>297</v>
       </c>
       <c r="B284" t="s">
         <v>127</v>
       </c>
-      <c r="C284" t="s">
+      <c r="D284" t="s">
         <v>298</v>
       </c>
-      <c r="D284" t="s">
-        <v>11</v>
-      </c>
       <c r="E284" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F284" t="s">
         <v>127</v>
       </c>
       <c r="G284" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H284" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I284" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>312</v>
       </c>
-      <c r="D285" t="s">
-        <v>11</v>
-      </c>
-      <c r="H285" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E285" t="s">
+        <v>11</v>
+      </c>
+      <c r="I285" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>299</v>
       </c>
       <c r="B286" t="s">
         <v>300</v>
       </c>
-      <c r="C286" t="s">
+      <c r="D286" t="s">
         <v>301</v>
       </c>
-      <c r="D286" t="s">
-        <v>11</v>
-      </c>
       <c r="E286" t="s">
-        <v>300</v>
+        <v>11</v>
       </c>
       <c r="F286" t="s">
         <v>300</v>
       </c>
       <c r="G286" t="s">
+        <v>300</v>
+      </c>
+      <c r="H286" t="s">
         <v>22</v>
       </c>
-      <c r="H286" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I286" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>312</v>
       </c>
-      <c r="E287" t="s">
+      <c r="F287" t="s">
         <v>300</v>
       </c>
-      <c r="H287" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I287" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>299</v>
       </c>
       <c r="B288" t="s">
         <v>300</v>
       </c>
-      <c r="C288" t="s">
+      <c r="D288" t="s">
         <v>302</v>
       </c>
-      <c r="D288" t="s">
-        <v>11</v>
-      </c>
       <c r="E288" t="s">
-        <v>300</v>
+        <v>11</v>
       </c>
       <c r="F288" t="s">
         <v>300</v>
       </c>
       <c r="G288" t="s">
+        <v>300</v>
+      </c>
+      <c r="H288" t="s">
         <v>22</v>
       </c>
-      <c r="H288" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I288" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>312</v>
       </c>
-      <c r="H289" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I289" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>305</v>
       </c>
       <c r="B290" t="s">
         <v>303</v>
       </c>
-      <c r="C290" t="s">
+      <c r="D290" t="s">
         <v>306</v>
       </c>
-      <c r="D290" t="s">
-        <v>11</v>
-      </c>
       <c r="E290" t="s">
-        <v>303</v>
+        <v>11</v>
       </c>
       <c r="F290" t="s">
         <v>303</v>
       </c>
       <c r="G290" t="s">
+        <v>303</v>
+      </c>
+      <c r="H290" t="s">
         <v>304</v>
       </c>
-      <c r="H290" t="s">
+      <c r="I290" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>305</v>
       </c>
       <c r="B291" t="s">
         <v>303</v>
       </c>
-      <c r="C291" t="s">
+      <c r="D291" t="s">
         <v>340</v>
       </c>
-      <c r="D291" t="s">
-        <v>11</v>
-      </c>
       <c r="E291" t="s">
-        <v>303</v>
+        <v>11</v>
       </c>
       <c r="F291" t="s">
         <v>303</v>
       </c>
       <c r="G291" t="s">
+        <v>303</v>
+      </c>
+      <c r="H291" t="s">
         <v>304</v>
       </c>
-      <c r="H291" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I291" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>307</v>
       </c>
       <c r="B292" t="s">
         <v>303</v>
       </c>
-      <c r="C292" t="s">
+      <c r="D292" t="s">
         <v>308</v>
       </c>
-      <c r="D292" t="s">
-        <v>11</v>
-      </c>
       <c r="E292" t="s">
-        <v>303</v>
+        <v>11</v>
       </c>
       <c r="F292" t="s">
         <v>303</v>
       </c>
       <c r="G292" t="s">
+        <v>303</v>
+      </c>
+      <c r="H292" t="s">
         <v>304</v>
       </c>
-      <c r="H292" t="s">
+      <c r="I292" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>307</v>
       </c>
       <c r="B293" t="s">
         <v>303</v>
       </c>
-      <c r="C293" t="s">
+      <c r="D293" t="s">
         <v>341</v>
       </c>
-      <c r="D293" t="s">
-        <v>11</v>
-      </c>
       <c r="E293" t="s">
-        <v>303</v>
+        <v>11</v>
       </c>
       <c r="F293" t="s">
         <v>303</v>
       </c>
       <c r="G293" t="s">
+        <v>303</v>
+      </c>
+      <c r="H293" t="s">
         <v>304</v>
       </c>
-      <c r="H293" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I293" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>307</v>
       </c>
       <c r="B294" t="s">
         <v>303</v>
       </c>
-      <c r="C294" t="s">
+      <c r="D294" t="s">
         <v>309</v>
       </c>
-      <c r="D294" t="s">
-        <v>11</v>
-      </c>
       <c r="E294" t="s">
-        <v>303</v>
+        <v>11</v>
       </c>
       <c r="F294" t="s">
         <v>303</v>
       </c>
       <c r="G294" t="s">
+        <v>303</v>
+      </c>
+      <c r="H294" t="s">
         <v>304</v>
       </c>
-      <c r="H294" t="s">
+      <c r="I294" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>307</v>
       </c>
       <c r="B295" t="s">
         <v>303</v>
       </c>
-      <c r="C295" t="s">
+      <c r="D295" t="s">
         <v>342</v>
       </c>
-      <c r="D295" t="s">
-        <v>11</v>
-      </c>
       <c r="E295" t="s">
-        <v>303</v>
+        <v>11</v>
       </c>
       <c r="F295" t="s">
         <v>303</v>
       </c>
       <c r="G295" t="s">
+        <v>303</v>
+      </c>
+      <c r="H295" t="s">
         <v>304</v>
       </c>
-      <c r="H295" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I295" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>347</v>
       </c>
       <c r="B296" t="s">
         <v>348</v>
       </c>
-      <c r="C296" t="s">
+      <c r="D296" t="s">
         <v>349</v>
       </c>
-      <c r="D296" t="s">
-        <v>11</v>
-      </c>
       <c r="E296" t="s">
+        <v>11</v>
+      </c>
+      <c r="F296" t="s">
         <v>348</v>
       </c>
-      <c r="F296" t="s">
+      <c r="G296" t="s">
         <v>350</v>
       </c>
-      <c r="G296" t="s">
+      <c r="H296" t="s">
         <v>16</v>
       </c>
-      <c r="H296" t="s">
+      <c r="I296" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>347</v>
       </c>
       <c r="B297" t="s">
         <v>348</v>
       </c>
-      <c r="C297" t="s">
+      <c r="D297" t="s">
         <v>373</v>
       </c>
-      <c r="D297" t="s">
-        <v>11</v>
-      </c>
       <c r="E297" t="s">
+        <v>11</v>
+      </c>
+      <c r="F297" t="s">
         <v>348</v>
       </c>
-      <c r="F297" t="s">
+      <c r="G297" t="s">
         <v>350</v>
       </c>
-      <c r="G297" t="s">
+      <c r="H297" t="s">
         <v>16</v>
       </c>
-      <c r="H297" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I297" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>352</v>
       </c>
       <c r="B298" t="s">
         <v>353</v>
       </c>
-      <c r="C298" t="s">
+      <c r="D298" t="s">
         <v>354</v>
       </c>
-      <c r="D298" t="s">
-        <v>11</v>
-      </c>
       <c r="E298" t="s">
-        <v>353</v>
+        <v>11</v>
       </c>
       <c r="F298" t="s">
         <v>353</v>
       </c>
       <c r="G298" t="s">
+        <v>353</v>
+      </c>
+      <c r="H298" t="s">
         <v>355</v>
       </c>
-      <c r="H298" t="s">
+      <c r="I298" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>352</v>
       </c>
       <c r="B299" t="s">
         <v>353</v>
       </c>
-      <c r="C299" t="s">
+      <c r="D299" t="s">
         <v>374</v>
       </c>
-      <c r="D299" t="s">
-        <v>11</v>
-      </c>
       <c r="E299" t="s">
-        <v>353</v>
+        <v>11</v>
       </c>
       <c r="F299" t="s">
         <v>353</v>
       </c>
       <c r="G299" t="s">
+        <v>353</v>
+      </c>
+      <c r="H299" t="s">
         <v>355</v>
       </c>
-      <c r="H299" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I299" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>356</v>
       </c>
       <c r="B300" t="s">
         <v>353</v>
       </c>
-      <c r="C300" t="s">
+      <c r="D300" t="s">
         <v>357</v>
       </c>
-      <c r="D300" t="s">
-        <v>11</v>
-      </c>
       <c r="E300" t="s">
-        <v>353</v>
+        <v>11</v>
       </c>
       <c r="F300" t="s">
         <v>353</v>
       </c>
       <c r="G300" t="s">
+        <v>353</v>
+      </c>
+      <c r="H300" t="s">
         <v>355</v>
       </c>
-      <c r="H300" t="s">
+      <c r="I300" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>356</v>
       </c>
       <c r="B301" t="s">
         <v>353</v>
       </c>
-      <c r="C301" t="s">
+      <c r="D301" t="s">
         <v>375</v>
       </c>
-      <c r="D301" t="s">
-        <v>11</v>
-      </c>
       <c r="E301" t="s">
-        <v>353</v>
+        <v>11</v>
       </c>
       <c r="F301" t="s">
         <v>353</v>
       </c>
       <c r="G301" t="s">
+        <v>353</v>
+      </c>
+      <c r="H301" t="s">
         <v>355</v>
       </c>
-      <c r="H301" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I301" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>358</v>
       </c>
       <c r="B302" t="s">
         <v>359</v>
       </c>
-      <c r="C302" t="s">
+      <c r="D302" t="s">
         <v>380</v>
       </c>
-      <c r="D302" t="s">
-        <v>11</v>
-      </c>
       <c r="E302" t="s">
+        <v>11</v>
+      </c>
+      <c r="F302" t="s">
         <v>359</v>
       </c>
-      <c r="F302" t="s">
+      <c r="G302" t="s">
         <v>360</v>
       </c>
-      <c r="G302" t="s">
+      <c r="H302" t="s">
         <v>361</v>
       </c>
-      <c r="H302" t="s">
+      <c r="I302" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>358</v>
       </c>
       <c r="B303" t="s">
         <v>359</v>
       </c>
-      <c r="C303" t="s">
+      <c r="D303" t="s">
         <v>376</v>
       </c>
-      <c r="D303" t="s">
-        <v>11</v>
-      </c>
       <c r="E303" t="s">
+        <v>11</v>
+      </c>
+      <c r="F303" t="s">
         <v>359</v>
       </c>
-      <c r="F303" t="s">
+      <c r="G303" t="s">
         <v>360</v>
       </c>
-      <c r="G303" t="s">
+      <c r="H303" t="s">
         <v>361</v>
       </c>
-      <c r="H303" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I303" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>124</v>
       </c>
       <c r="B304" t="s">
         <v>123</v>
       </c>
-      <c r="C304" t="s">
+      <c r="D304" t="s">
         <v>379</v>
       </c>
-      <c r="D304" t="s">
-        <v>11</v>
-      </c>
       <c r="E304" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="F304" t="s">
         <v>123</v>
       </c>
       <c r="G304" t="s">
+        <v>123</v>
+      </c>
+      <c r="H304" t="s">
         <v>27</v>
       </c>
-      <c r="H304" t="s">
+      <c r="I304" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>124</v>
       </c>
       <c r="B305" t="s">
         <v>123</v>
       </c>
-      <c r="C305" t="s">
+      <c r="D305" t="s">
         <v>334</v>
       </c>
-      <c r="D305" t="s">
-        <v>11</v>
-      </c>
       <c r="E305" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="F305" t="s">
         <v>123</v>
       </c>
       <c r="G305" t="s">
+        <v>123</v>
+      </c>
+      <c r="H305" t="s">
         <v>27</v>
       </c>
-      <c r="H305" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I305" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>362</v>
       </c>
       <c r="B306" t="s">
         <v>363</v>
       </c>
-      <c r="C306" t="s">
+      <c r="D306" t="s">
         <v>364</v>
       </c>
-      <c r="D306" t="s">
-        <v>11</v>
-      </c>
       <c r="E306" t="s">
-        <v>363</v>
+        <v>11</v>
       </c>
       <c r="F306" t="s">
         <v>363</v>
       </c>
       <c r="G306" t="s">
+        <v>363</v>
+      </c>
+      <c r="H306" t="s">
         <v>22</v>
       </c>
-      <c r="H306" t="s">
+      <c r="I306" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>362</v>
       </c>
       <c r="B307" t="s">
         <v>363</v>
       </c>
-      <c r="C307" t="s">
+      <c r="D307" t="s">
         <v>377</v>
       </c>
-      <c r="D307" t="s">
-        <v>11</v>
-      </c>
       <c r="E307" t="s">
-        <v>363</v>
+        <v>11</v>
       </c>
       <c r="F307" t="s">
         <v>363</v>
       </c>
       <c r="G307" t="s">
+        <v>363</v>
+      </c>
+      <c r="H307" t="s">
         <v>22</v>
       </c>
-      <c r="H307" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I307" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>365</v>
       </c>
       <c r="B308" t="s">
         <v>127</v>
       </c>
-      <c r="C308" t="s">
+      <c r="D308" t="s">
         <v>366</v>
       </c>
-      <c r="D308" t="s">
-        <v>11</v>
-      </c>
       <c r="E308" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F308" t="s">
         <v>127</v>
       </c>
       <c r="G308" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H308" t="s">
+        <v>17</v>
+      </c>
+      <c r="I308" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>365</v>
       </c>
       <c r="B309" t="s">
         <v>127</v>
       </c>
-      <c r="C309" t="s">
+      <c r="D309" t="s">
         <v>378</v>
       </c>
-      <c r="D309" t="s">
-        <v>11</v>
-      </c>
       <c r="E309" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F309" t="s">
         <v>127</v>
       </c>
       <c r="G309" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H309" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I309" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>193</v>
       </c>
       <c r="B310" t="s">
         <v>127</v>
       </c>
-      <c r="C310" t="s">
+      <c r="D310" t="s">
         <v>345</v>
       </c>
-      <c r="D310" t="s">
-        <v>11</v>
-      </c>
       <c r="E310" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F310" t="s">
         <v>127</v>
       </c>
       <c r="G310" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H310" t="s">
+        <v>17</v>
+      </c>
+      <c r="I310" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>193</v>
       </c>
       <c r="B311" t="s">
         <v>127</v>
       </c>
-      <c r="C311" t="s">
+      <c r="D311" t="s">
         <v>371</v>
       </c>
-      <c r="D311" t="s">
-        <v>11</v>
-      </c>
       <c r="E311" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F311" t="s">
         <v>127</v>
       </c>
       <c r="G311" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H311" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I311" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>368</v>
       </c>
       <c r="B312" t="s">
         <v>367</v>
       </c>
-      <c r="C312" t="s">
+      <c r="D312" t="s">
         <v>369</v>
       </c>
-      <c r="D312" t="s">
-        <v>11</v>
-      </c>
       <c r="E312" t="s">
-        <v>367</v>
+        <v>11</v>
       </c>
       <c r="F312" t="s">
         <v>367</v>
       </c>
       <c r="G312" t="s">
+        <v>367</v>
+      </c>
+      <c r="H312" t="s">
         <v>351</v>
       </c>
-      <c r="H312" t="s">
+      <c r="I312" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>368</v>
       </c>
       <c r="B313" t="s">
         <v>367</v>
       </c>
-      <c r="C313" t="s">
+      <c r="D313" t="s">
         <v>370</v>
       </c>
-      <c r="D313" t="s">
-        <v>11</v>
-      </c>
       <c r="E313" t="s">
-        <v>367</v>
+        <v>11</v>
       </c>
       <c r="F313" t="s">
         <v>367</v>
       </c>
       <c r="G313" t="s">
+        <v>367</v>
+      </c>
+      <c r="H313" t="s">
         <v>351</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>381</v>
+      </c>
+      <c r="B314" t="s">
+        <v>382</v>
+      </c>
+      <c r="C314" t="s">
+        <v>386</v>
+      </c>
+      <c r="D314" t="s">
+        <v>383</v>
+      </c>
+      <c r="F314" t="s">
+        <v>382</v>
+      </c>
+      <c r="G314" t="s">
+        <v>384</v>
+      </c>
+      <c r="H314" t="s">
+        <v>17</v>
+      </c>
+      <c r="I314" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>381</v>
+      </c>
+      <c r="B315" t="s">
+        <v>382</v>
+      </c>
+      <c r="D315" t="s">
+        <v>383</v>
+      </c>
+      <c r="F315" t="s">
+        <v>382</v>
+      </c>
+      <c r="G315" t="s">
+        <v>384</v>
+      </c>
+      <c r="H315" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF21D42-CBD8-4B90-B2C4-ACA639C28A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4EFAE8-A533-498F-A621-CE0338158171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2834" uniqueCount="564">
   <si>
     <t>Kod</t>
   </si>
@@ -1028,9 +1028,6 @@
     <t>Korekta nazwy</t>
   </si>
   <si>
-    <t>Al. Chryzantem</t>
-  </si>
-  <si>
     <t>Jeża</t>
   </si>
   <si>
@@ -1052,9 +1049,6 @@
     <t>Al. Harcerska</t>
   </si>
   <si>
-    <t>Al. Kominiarska</t>
-  </si>
-  <si>
     <t>Racula-Jakuba Bojki</t>
   </si>
   <si>
@@ -1067,9 +1061,6 @@
     <t>Galijska</t>
   </si>
   <si>
-    <t>Bohaterów Getta Warszawskiego</t>
-  </si>
-  <si>
     <t>ONZ Rondo</t>
   </si>
   <si>
@@ -1197,6 +1188,543 @@
   </si>
   <si>
     <t>Korekta dzielnicy</t>
+  </si>
+  <si>
+    <t>85-689</t>
+  </si>
+  <si>
+    <t>Bydgoszcz</t>
+  </si>
+  <si>
+    <t>al. Armii Krajowej</t>
+  </si>
+  <si>
+    <t>kujawsko-pomorskie</t>
+  </si>
+  <si>
+    <t>Błędna cecha</t>
+  </si>
+  <si>
+    <t>ul. Armii Krajowej</t>
+  </si>
+  <si>
+    <t>71-432</t>
+  </si>
+  <si>
+    <t>al. Wyzwolenia</t>
+  </si>
+  <si>
+    <t>107-119(n)</t>
+  </si>
+  <si>
+    <t>70-552</t>
+  </si>
+  <si>
+    <t>1-11(n)</t>
+  </si>
+  <si>
+    <t>70-555</t>
+  </si>
+  <si>
+    <t>12-14(p)</t>
+  </si>
+  <si>
+    <t>70-554</t>
+  </si>
+  <si>
+    <t>13-23(n)</t>
+  </si>
+  <si>
+    <t>70-532</t>
+  </si>
+  <si>
+    <t>18-20(p)</t>
+  </si>
+  <si>
+    <t>70-553</t>
+  </si>
+  <si>
+    <t>2-10(p)</t>
+  </si>
+  <si>
+    <t>70-531</t>
+  </si>
+  <si>
+    <t>25-47(n)</t>
+  </si>
+  <si>
+    <t>71-500</t>
+  </si>
+  <si>
+    <t>30-50(p)</t>
+  </si>
+  <si>
+    <t>71-400</t>
+  </si>
+  <si>
+    <t>49-71(n)</t>
+  </si>
+  <si>
+    <t>71-506</t>
+  </si>
+  <si>
+    <t>52-70(p)</t>
+  </si>
+  <si>
+    <t>71-401</t>
+  </si>
+  <si>
+    <t>73-75(n)</t>
+  </si>
+  <si>
+    <t>71-411</t>
+  </si>
+  <si>
+    <t>77-97(n)</t>
+  </si>
+  <si>
+    <t>71-560</t>
+  </si>
+  <si>
+    <t>80-86(p)</t>
+  </si>
+  <si>
+    <t>71-421</t>
+  </si>
+  <si>
+    <t>99-105b(n)</t>
+  </si>
+  <si>
+    <t>ul. Wyzwolenia</t>
+  </si>
+  <si>
+    <t>41-500</t>
+  </si>
+  <si>
+    <t>Chorzów</t>
+  </si>
+  <si>
+    <t>Al. Wycieczkowa</t>
+  </si>
+  <si>
+    <t>ul. Wycieczkowa</t>
+  </si>
+  <si>
+    <t>15-111</t>
+  </si>
+  <si>
+    <t>Al. 1000-lecia Państwa Polskiego</t>
+  </si>
+  <si>
+    <t>ul. 1000-lecia Państwa Polskiego</t>
+  </si>
+  <si>
+    <t>43-140</t>
+  </si>
+  <si>
+    <t>Lędziny</t>
+  </si>
+  <si>
+    <t>Al. Matki Boskiej Różańcowej</t>
+  </si>
+  <si>
+    <t>bieruńsko-lędziński</t>
+  </si>
+  <si>
+    <t>20-814</t>
+  </si>
+  <si>
+    <t>Al. generała Władysława Sikorskiego</t>
+  </si>
+  <si>
+    <t>20-315</t>
+  </si>
+  <si>
+    <t>Al. Wincentego Witosa</t>
+  </si>
+  <si>
+    <t>20-249</t>
+  </si>
+  <si>
+    <t>al. Władysława Andersa</t>
+  </si>
+  <si>
+    <t>ul. Matki Boskiej Różańcowej</t>
+  </si>
+  <si>
+    <t>ul. generała Władysława Sikorskiego</t>
+  </si>
+  <si>
+    <t>ul. Wincentego Witosa</t>
+  </si>
+  <si>
+    <t>ul. Władysława Andersa</t>
+  </si>
+  <si>
+    <t>ul. Chryzantem</t>
+  </si>
+  <si>
+    <t>Al. Spacerowa</t>
+  </si>
+  <si>
+    <t>71-373</t>
+  </si>
+  <si>
+    <t>Al. Przyjaciół</t>
+  </si>
+  <si>
+    <t>70-833</t>
+  </si>
+  <si>
+    <t>ul. Przyjaciół</t>
+  </si>
+  <si>
+    <t>ul. Spacerowa</t>
+  </si>
+  <si>
+    <t>01-317</t>
+  </si>
+  <si>
+    <t>Władysława Strzyżewskiego Al.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al. Władysława Strzyżewskiego </t>
+  </si>
+  <si>
+    <t>03-127</t>
+  </si>
+  <si>
+    <t>Janiny Porazińskiej</t>
+  </si>
+  <si>
+    <t>park Janiny Porazińskiej</t>
+  </si>
+  <si>
+    <t>Andrzeja Witkowskiego</t>
+  </si>
+  <si>
+    <t>02-722</t>
+  </si>
+  <si>
+    <t>Harcerzy Rzeczypospolitej</t>
+  </si>
+  <si>
+    <t>al. Harcerzy Rzeczypospolitej</t>
+  </si>
+  <si>
+    <t>Chodzi chyba o rondo i o inną osobę</t>
+  </si>
+  <si>
+    <t>rondo Stanisława Witkowskiego</t>
+  </si>
+  <si>
+    <t>Jawaharlala Nehru</t>
+  </si>
+  <si>
+    <t>00-719</t>
+  </si>
+  <si>
+    <t>rondo Jawaharlala Nehru</t>
+  </si>
+  <si>
+    <t>Antoniego Władysława Żurowskiego</t>
+  </si>
+  <si>
+    <t>03-435</t>
+  </si>
+  <si>
+    <t>skwer pułkownika Władysława Żurowskiego</t>
+  </si>
+  <si>
+    <t>Chodzi chyba o skwer i inną osobę</t>
+  </si>
+  <si>
+    <t>8-52(p)</t>
+  </si>
+  <si>
+    <t>Gen. Antoniego Chruściela Montera</t>
+  </si>
+  <si>
+    <t>04-401</t>
+  </si>
+  <si>
+    <t>54-106(p)</t>
+  </si>
+  <si>
+    <t>04-412</t>
+  </si>
+  <si>
+    <t>43-105(n)</t>
+  </si>
+  <si>
+    <t>04-414</t>
+  </si>
+  <si>
+    <t>1-41(n)</t>
+  </si>
+  <si>
+    <t>04-454</t>
+  </si>
+  <si>
+    <t>al. Gen. Antoniego Chruściela Montera</t>
+  </si>
+  <si>
+    <t>ul. Kominiarska</t>
+  </si>
+  <si>
+    <t>inwersja i błędna cecha</t>
+  </si>
+  <si>
+    <t>pl. Bohaterów Getta Warszawskiego</t>
+  </si>
+  <si>
+    <t>To jest plac a nie ulica</t>
+  </si>
+  <si>
+    <t>90-457</t>
+  </si>
+  <si>
+    <t>Katedralny im. Jana Pawła II Pl.</t>
+  </si>
+  <si>
+    <t>Wojciecha Korfantego</t>
+  </si>
+  <si>
+    <t>92-432</t>
+  </si>
+  <si>
+    <t>Romana Dmowskiego</t>
+  </si>
+  <si>
+    <t>92-430</t>
+  </si>
+  <si>
+    <t>Szarych Szeregów</t>
+  </si>
+  <si>
+    <t>94-402</t>
+  </si>
+  <si>
+    <t>park Szarych Szeregów</t>
+  </si>
+  <si>
+    <t>To jest park a nie ulica</t>
+  </si>
+  <si>
+    <t>pl. Romana Dmowskiego</t>
+  </si>
+  <si>
+    <t>rondo Wojciecha Korfantego</t>
+  </si>
+  <si>
+    <t>To jest rondo a nie ulica</t>
+  </si>
+  <si>
+    <t>32-300</t>
+  </si>
+  <si>
+    <t>Olkusz</t>
+  </si>
+  <si>
+    <t>skwer Skwer</t>
+  </si>
+  <si>
+    <t>olkuski</t>
+  </si>
+  <si>
+    <t>Skwer</t>
+  </si>
+  <si>
+    <t>Duplikacja</t>
+  </si>
+  <si>
+    <t>Nie ta nazwa i to jest plac a nie ulica</t>
+  </si>
+  <si>
+    <t>Legionów</t>
+  </si>
+  <si>
+    <t>Osiedle Legionów</t>
+  </si>
+  <si>
+    <t>To jest osiedle</t>
+  </si>
+  <si>
+    <t>25-022</t>
+  </si>
+  <si>
+    <t>Kielce</t>
+  </si>
+  <si>
+    <t>skwer Harcerski im. Szarych Szeregów</t>
+  </si>
+  <si>
+    <t>świętokrzyskie</t>
+  </si>
+  <si>
+    <t>skwer Szarych Szeregów</t>
+  </si>
+  <si>
+    <t>Łódź-Śródmieście</t>
+  </si>
+  <si>
+    <t>pl. Jana Pawła II</t>
+  </si>
+  <si>
+    <t>Inwersja i inna nazwa</t>
+  </si>
+  <si>
+    <t>61-772</t>
+  </si>
+  <si>
+    <t>Poznań</t>
+  </si>
+  <si>
+    <t>Stary Rynek</t>
+  </si>
+  <si>
+    <t>1-84, 6-26(p), 25-29(n)</t>
+  </si>
+  <si>
+    <t>61-773</t>
+  </si>
+  <si>
+    <t>85-100, 89/90-97/98(n)</t>
+  </si>
+  <si>
+    <t>pl. Stary Rynek</t>
+  </si>
+  <si>
+    <t>15-166</t>
+  </si>
+  <si>
+    <t>Bagnówka-Kolonia</t>
+  </si>
+  <si>
+    <t>Zielony Zaułek</t>
+  </si>
+  <si>
+    <t>31-001</t>
+  </si>
+  <si>
+    <t>Kraków-Śródmieście</t>
+  </si>
+  <si>
+    <t>Zamek Wawel</t>
+  </si>
+  <si>
+    <t>57-400</t>
+  </si>
+  <si>
+    <t>Nowa Ruda</t>
+  </si>
+  <si>
+    <t>Góra Anny</t>
+  </si>
+  <si>
+    <t>kłodzki</t>
+  </si>
+  <si>
+    <t>08-101</t>
+  </si>
+  <si>
+    <t>Siedlce</t>
+  </si>
+  <si>
+    <t>Dom Kolejowy</t>
+  </si>
+  <si>
+    <t>41-208</t>
+  </si>
+  <si>
+    <t>Sosnowiec</t>
+  </si>
+  <si>
+    <t>Stacja Jęzor</t>
+  </si>
+  <si>
+    <t>71-376</t>
+  </si>
+  <si>
+    <t>Gajówka Owczary</t>
+  </si>
+  <si>
+    <t>70-535</t>
+  </si>
+  <si>
+    <t>Targ Rybny</t>
+  </si>
+  <si>
+    <t>33-100</t>
+  </si>
+  <si>
+    <t>Tarnów</t>
+  </si>
+  <si>
+    <t>Zakątek Spycimira Leliwity</t>
+  </si>
+  <si>
+    <t>50-159</t>
+  </si>
+  <si>
+    <t>Wrocław-Stare Miasto</t>
+  </si>
+  <si>
+    <t>Przejście Słodowe</t>
+  </si>
+  <si>
+    <t>Góry św. Anny</t>
+  </si>
+  <si>
+    <t>66-006</t>
+  </si>
+  <si>
+    <t>Ochla-Osiedle Dworskie</t>
+  </si>
+  <si>
+    <t>Racula-Im. Rodła</t>
+  </si>
+  <si>
+    <t>inne Bagnówka-Kolonia</t>
+  </si>
+  <si>
+    <t>inne Zielony Zaułek</t>
+  </si>
+  <si>
+    <t>inne Zamek Wawel</t>
+  </si>
+  <si>
+    <t>inne Góra Anny</t>
+  </si>
+  <si>
+    <t>inne Dom Kolejowy</t>
+  </si>
+  <si>
+    <t>inne Stacja Jęzor</t>
+  </si>
+  <si>
+    <t>inne Gajówka Owczary</t>
+  </si>
+  <si>
+    <t>inne Targ Rybny</t>
+  </si>
+  <si>
+    <t>inne Zakątek Spycimira Leliwity</t>
+  </si>
+  <si>
+    <t>inne Przejście Słodowe</t>
+  </si>
+  <si>
+    <t>inne Góry św. Anny</t>
+  </si>
+  <si>
+    <t>inne Ochla-Osiedle Dworskie</t>
+  </si>
+  <si>
+    <t>inne Racula-Im. Rodła</t>
+  </si>
+  <si>
+    <t>Inne - nie ulica</t>
   </si>
 </sst>
 </file>
@@ -2075,11 +2603,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I315"/>
+  <dimension ref="A1:I425"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="38.5703125" customWidth="1"/>
+    <col min="2" max="2" width="38.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
     <col min="4" max="4" width="45.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -2096,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -3164,7 +3693,7 @@
         <v>70</v>
       </c>
       <c r="I46" t="s">
-        <v>315</v>
+        <v>479</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -3175,7 +3704,7 @@
         <v>68</v>
       </c>
       <c r="D47" t="s">
-        <v>331</v>
+        <v>442</v>
       </c>
       <c r="E47" t="s">
         <v>11</v>
@@ -3776,7 +4305,7 @@
         <v>68</v>
       </c>
       <c r="D79" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E79" t="s">
         <v>11</v>
@@ -4155,7 +4684,7 @@
         <v>68</v>
       </c>
       <c r="D99" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E99" t="s">
         <v>11</v>
@@ -4244,7 +4773,7 @@
         <v>123</v>
       </c>
       <c r="D103" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E103" t="s">
         <v>11</v>
@@ -5221,7 +5750,7 @@
         <v>127</v>
       </c>
       <c r="D155" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E155" t="s">
         <v>11</v>
@@ -5247,7 +5776,7 @@
         <v>127</v>
       </c>
       <c r="D156" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E156" t="s">
         <v>11</v>
@@ -5421,7 +5950,7 @@
         <v>127</v>
       </c>
       <c r="D165" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E165" t="s">
         <v>11</v>
@@ -5536,7 +6065,7 @@
         <v>17</v>
       </c>
       <c r="I170" t="s">
-        <v>315</v>
+        <v>479</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
@@ -5547,7 +6076,7 @@
         <v>127</v>
       </c>
       <c r="D171" t="s">
-        <v>339</v>
+        <v>478</v>
       </c>
       <c r="E171" t="s">
         <v>11</v>
@@ -5625,7 +6154,7 @@
         <v>17</v>
       </c>
       <c r="I174" t="s">
-        <v>13</v>
+        <v>501</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
@@ -5636,7 +6165,7 @@
         <v>127</v>
       </c>
       <c r="D175" t="s">
-        <v>344</v>
+        <v>480</v>
       </c>
       <c r="E175" t="s">
         <v>11</v>
@@ -5662,7 +6191,7 @@
         <v>127</v>
       </c>
       <c r="D176" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E176" t="s">
         <v>11</v>
@@ -5688,7 +6217,7 @@
         <v>127</v>
       </c>
       <c r="D177" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E177" t="s">
         <v>11</v>
@@ -6924,7 +7453,7 @@
         <v>127</v>
       </c>
       <c r="D243" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E243" t="s">
         <v>11</v>
@@ -7605,7 +8134,7 @@
         <v>127</v>
       </c>
       <c r="D279" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E279" t="s">
         <v>11</v>
@@ -7657,7 +8186,7 @@
         <v>127</v>
       </c>
       <c r="D281" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E281" t="s">
         <v>11</v>
@@ -7854,7 +8383,7 @@
         <v>303</v>
       </c>
       <c r="D291" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E291" t="s">
         <v>11</v>
@@ -7906,7 +8435,7 @@
         <v>303</v>
       </c>
       <c r="D293" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E293" t="s">
         <v>11</v>
@@ -7958,7 +8487,7 @@
         <v>303</v>
       </c>
       <c r="D295" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E295" t="s">
         <v>11</v>
@@ -7978,22 +8507,22 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
+        <v>344</v>
+      </c>
+      <c r="B296" t="s">
+        <v>345</v>
+      </c>
+      <c r="D296" t="s">
+        <v>346</v>
+      </c>
+      <c r="E296" t="s">
+        <v>11</v>
+      </c>
+      <c r="F296" t="s">
+        <v>345</v>
+      </c>
+      <c r="G296" t="s">
         <v>347</v>
-      </c>
-      <c r="B296" t="s">
-        <v>348</v>
-      </c>
-      <c r="D296" t="s">
-        <v>349</v>
-      </c>
-      <c r="E296" t="s">
-        <v>11</v>
-      </c>
-      <c r="F296" t="s">
-        <v>348</v>
-      </c>
-      <c r="G296" t="s">
-        <v>350</v>
       </c>
       <c r="H296" t="s">
         <v>16</v>
@@ -8004,22 +8533,22 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
+        <v>344</v>
+      </c>
+      <c r="B297" t="s">
+        <v>345</v>
+      </c>
+      <c r="D297" t="s">
+        <v>370</v>
+      </c>
+      <c r="E297" t="s">
+        <v>11</v>
+      </c>
+      <c r="F297" t="s">
+        <v>345</v>
+      </c>
+      <c r="G297" t="s">
         <v>347</v>
-      </c>
-      <c r="B297" t="s">
-        <v>348</v>
-      </c>
-      <c r="D297" t="s">
-        <v>373</v>
-      </c>
-      <c r="E297" t="s">
-        <v>11</v>
-      </c>
-      <c r="F297" t="s">
-        <v>348</v>
-      </c>
-      <c r="G297" t="s">
-        <v>350</v>
       </c>
       <c r="H297" t="s">
         <v>16</v>
@@ -8030,25 +8559,25 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
+        <v>349</v>
+      </c>
+      <c r="B298" t="s">
+        <v>350</v>
+      </c>
+      <c r="D298" t="s">
+        <v>351</v>
+      </c>
+      <c r="E298" t="s">
+        <v>11</v>
+      </c>
+      <c r="F298" t="s">
+        <v>350</v>
+      </c>
+      <c r="G298" t="s">
+        <v>350</v>
+      </c>
+      <c r="H298" t="s">
         <v>352</v>
-      </c>
-      <c r="B298" t="s">
-        <v>353</v>
-      </c>
-      <c r="D298" t="s">
-        <v>354</v>
-      </c>
-      <c r="E298" t="s">
-        <v>11</v>
-      </c>
-      <c r="F298" t="s">
-        <v>353</v>
-      </c>
-      <c r="G298" t="s">
-        <v>353</v>
-      </c>
-      <c r="H298" t="s">
-        <v>355</v>
       </c>
       <c r="I298" t="s">
         <v>330</v>
@@ -8056,25 +8585,25 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
+        <v>349</v>
+      </c>
+      <c r="B299" t="s">
+        <v>350</v>
+      </c>
+      <c r="D299" t="s">
+        <v>371</v>
+      </c>
+      <c r="E299" t="s">
+        <v>11</v>
+      </c>
+      <c r="F299" t="s">
+        <v>350</v>
+      </c>
+      <c r="G299" t="s">
+        <v>350</v>
+      </c>
+      <c r="H299" t="s">
         <v>352</v>
-      </c>
-      <c r="B299" t="s">
-        <v>353</v>
-      </c>
-      <c r="D299" t="s">
-        <v>374</v>
-      </c>
-      <c r="E299" t="s">
-        <v>11</v>
-      </c>
-      <c r="F299" t="s">
-        <v>353</v>
-      </c>
-      <c r="G299" t="s">
-        <v>353</v>
-      </c>
-      <c r="H299" t="s">
-        <v>355</v>
       </c>
       <c r="I299" t="s">
         <v>11</v>
@@ -8082,25 +8611,25 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B300" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D300" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E300" t="s">
         <v>11</v>
       </c>
       <c r="F300" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G300" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H300" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="I300" t="s">
         <v>330</v>
@@ -8108,25 +8637,25 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B301" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D301" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E301" t="s">
         <v>11</v>
       </c>
       <c r="F301" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G301" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H301" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="I301" t="s">
         <v>11</v>
@@ -8134,25 +8663,25 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
+        <v>355</v>
+      </c>
+      <c r="B302" t="s">
+        <v>356</v>
+      </c>
+      <c r="D302" t="s">
+        <v>377</v>
+      </c>
+      <c r="E302" t="s">
+        <v>11</v>
+      </c>
+      <c r="F302" t="s">
+        <v>356</v>
+      </c>
+      <c r="G302" t="s">
+        <v>357</v>
+      </c>
+      <c r="H302" t="s">
         <v>358</v>
-      </c>
-      <c r="B302" t="s">
-        <v>359</v>
-      </c>
-      <c r="D302" t="s">
-        <v>380</v>
-      </c>
-      <c r="E302" t="s">
-        <v>11</v>
-      </c>
-      <c r="F302" t="s">
-        <v>359</v>
-      </c>
-      <c r="G302" t="s">
-        <v>360</v>
-      </c>
-      <c r="H302" t="s">
-        <v>361</v>
       </c>
       <c r="I302" t="s">
         <v>330</v>
@@ -8160,25 +8689,25 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
+        <v>355</v>
+      </c>
+      <c r="B303" t="s">
+        <v>356</v>
+      </c>
+      <c r="D303" t="s">
+        <v>373</v>
+      </c>
+      <c r="E303" t="s">
+        <v>11</v>
+      </c>
+      <c r="F303" t="s">
+        <v>356</v>
+      </c>
+      <c r="G303" t="s">
+        <v>357</v>
+      </c>
+      <c r="H303" t="s">
         <v>358</v>
-      </c>
-      <c r="B303" t="s">
-        <v>359</v>
-      </c>
-      <c r="D303" t="s">
-        <v>376</v>
-      </c>
-      <c r="E303" t="s">
-        <v>11</v>
-      </c>
-      <c r="F303" t="s">
-        <v>359</v>
-      </c>
-      <c r="G303" t="s">
-        <v>360</v>
-      </c>
-      <c r="H303" t="s">
-        <v>361</v>
       </c>
       <c r="I303" t="s">
         <v>11</v>
@@ -8192,7 +8721,7 @@
         <v>123</v>
       </c>
       <c r="D304" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E304" t="s">
         <v>11</v>
@@ -8218,7 +8747,7 @@
         <v>123</v>
       </c>
       <c r="D305" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E305" t="s">
         <v>11</v>
@@ -8238,22 +8767,22 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B306" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D306" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E306" t="s">
         <v>11</v>
       </c>
       <c r="F306" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G306" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H306" t="s">
         <v>22</v>
@@ -8264,22 +8793,22 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B307" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D307" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E307" t="s">
         <v>11</v>
       </c>
       <c r="F307" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G307" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H307" t="s">
         <v>22</v>
@@ -8290,13 +8819,13 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B308" t="s">
         <v>127</v>
       </c>
       <c r="D308" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E308" t="s">
         <v>11</v>
@@ -8316,13 +8845,13 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B309" t="s">
         <v>127</v>
       </c>
       <c r="D309" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E309" t="s">
         <v>11</v>
@@ -8348,7 +8877,7 @@
         <v>127</v>
       </c>
       <c r="D310" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E310" t="s">
         <v>11</v>
@@ -8374,7 +8903,7 @@
         <v>127</v>
       </c>
       <c r="D311" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E311" t="s">
         <v>11</v>
@@ -8394,25 +8923,25 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B312" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D312" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E312" t="s">
         <v>11</v>
       </c>
       <c r="F312" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G312" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H312" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="I312" t="s">
         <v>330</v>
@@ -8420,71 +8949,3024 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B313" t="s">
+        <v>364</v>
+      </c>
+      <c r="D313" t="s">
         <v>367</v>
       </c>
-      <c r="D313" t="s">
-        <v>370</v>
-      </c>
       <c r="E313" t="s">
         <v>11</v>
       </c>
       <c r="F313" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G313" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H313" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
+        <v>378</v>
+      </c>
+      <c r="B314" t="s">
+        <v>379</v>
+      </c>
+      <c r="C314" t="s">
+        <v>383</v>
+      </c>
+      <c r="D314" t="s">
+        <v>380</v>
+      </c>
+      <c r="F314" t="s">
+        <v>379</v>
+      </c>
+      <c r="G314" t="s">
         <v>381</v>
       </c>
-      <c r="B314" t="s">
-        <v>382</v>
-      </c>
-      <c r="C314" t="s">
-        <v>386</v>
-      </c>
-      <c r="D314" t="s">
-        <v>383</v>
-      </c>
-      <c r="F314" t="s">
-        <v>382</v>
-      </c>
-      <c r="G314" t="s">
+      <c r="H314" t="s">
+        <v>17</v>
+      </c>
+      <c r="I314" t="s">
         <v>384</v>
-      </c>
-      <c r="H314" t="s">
-        <v>17</v>
-      </c>
-      <c r="I314" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
+        <v>378</v>
+      </c>
+      <c r="B315" t="s">
+        <v>379</v>
+      </c>
+      <c r="D315" t="s">
+        <v>380</v>
+      </c>
+      <c r="F315" t="s">
+        <v>379</v>
+      </c>
+      <c r="G315" t="s">
         <v>381</v>
       </c>
-      <c r="B315" t="s">
-        <v>382</v>
-      </c>
-      <c r="D315" t="s">
-        <v>383</v>
-      </c>
-      <c r="F315" t="s">
-        <v>382</v>
-      </c>
-      <c r="G315" t="s">
-        <v>384</v>
-      </c>
       <c r="H315" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>385</v>
+      </c>
+      <c r="B316" t="s">
+        <v>386</v>
+      </c>
+      <c r="D316" t="s">
+        <v>387</v>
+      </c>
+      <c r="E316" t="s">
+        <v>11</v>
+      </c>
+      <c r="F316" t="s">
+        <v>386</v>
+      </c>
+      <c r="G316" t="s">
+        <v>386</v>
+      </c>
+      <c r="H316" t="s">
+        <v>388</v>
+      </c>
+      <c r="I316" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>385</v>
+      </c>
+      <c r="B317" t="s">
+        <v>386</v>
+      </c>
+      <c r="D317" t="s">
+        <v>390</v>
+      </c>
+      <c r="E317" t="s">
+        <v>11</v>
+      </c>
+      <c r="F317" t="s">
+        <v>386</v>
+      </c>
+      <c r="G317" t="s">
+        <v>386</v>
+      </c>
+      <c r="H317" t="s">
+        <v>388</v>
+      </c>
+      <c r="I317" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>391</v>
+      </c>
+      <c r="B318" t="s">
+        <v>123</v>
+      </c>
+      <c r="D318" t="s">
+        <v>392</v>
+      </c>
+      <c r="E318" t="s">
+        <v>393</v>
+      </c>
+      <c r="F318" t="s">
+        <v>123</v>
+      </c>
+      <c r="G318" t="s">
+        <v>123</v>
+      </c>
+      <c r="H318" t="s">
+        <v>27</v>
+      </c>
+      <c r="I318" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>391</v>
+      </c>
+      <c r="B319" t="s">
+        <v>123</v>
+      </c>
+      <c r="D319" t="s">
+        <v>420</v>
+      </c>
+      <c r="E319" t="s">
+        <v>393</v>
+      </c>
+      <c r="F319" t="s">
+        <v>123</v>
+      </c>
+      <c r="G319" t="s">
+        <v>123</v>
+      </c>
+      <c r="H319" t="s">
+        <v>27</v>
+      </c>
+      <c r="I319" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>394</v>
+      </c>
+      <c r="B320" t="s">
+        <v>123</v>
+      </c>
+      <c r="D320" t="s">
+        <v>392</v>
+      </c>
+      <c r="E320" t="s">
+        <v>395</v>
+      </c>
+      <c r="F320" t="s">
+        <v>123</v>
+      </c>
+      <c r="G320" t="s">
+        <v>123</v>
+      </c>
+      <c r="H320" t="s">
+        <v>27</v>
+      </c>
+      <c r="I320" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>394</v>
+      </c>
+      <c r="B321" t="s">
+        <v>123</v>
+      </c>
+      <c r="D321" t="s">
+        <v>420</v>
+      </c>
+      <c r="E321" t="s">
+        <v>395</v>
+      </c>
+      <c r="F321" t="s">
+        <v>123</v>
+      </c>
+      <c r="G321" t="s">
+        <v>123</v>
+      </c>
+      <c r="H321" t="s">
+        <v>27</v>
+      </c>
+      <c r="I321" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>396</v>
+      </c>
+      <c r="B322" t="s">
+        <v>123</v>
+      </c>
+      <c r="D322" t="s">
+        <v>392</v>
+      </c>
+      <c r="E322" t="s">
+        <v>397</v>
+      </c>
+      <c r="F322" t="s">
+        <v>123</v>
+      </c>
+      <c r="G322" t="s">
+        <v>123</v>
+      </c>
+      <c r="H322" t="s">
+        <v>27</v>
+      </c>
+      <c r="I322" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>396</v>
+      </c>
+      <c r="B323" t="s">
+        <v>123</v>
+      </c>
+      <c r="D323" t="s">
+        <v>420</v>
+      </c>
+      <c r="E323" t="s">
+        <v>397</v>
+      </c>
+      <c r="F323" t="s">
+        <v>123</v>
+      </c>
+      <c r="G323" t="s">
+        <v>123</v>
+      </c>
+      <c r="H323" t="s">
+        <v>27</v>
+      </c>
+      <c r="I323" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>398</v>
+      </c>
+      <c r="B324" t="s">
+        <v>123</v>
+      </c>
+      <c r="D324" t="s">
+        <v>392</v>
+      </c>
+      <c r="E324" t="s">
+        <v>399</v>
+      </c>
+      <c r="F324" t="s">
+        <v>123</v>
+      </c>
+      <c r="G324" t="s">
+        <v>123</v>
+      </c>
+      <c r="H324" t="s">
+        <v>27</v>
+      </c>
+      <c r="I324" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>398</v>
+      </c>
+      <c r="B325" t="s">
+        <v>123</v>
+      </c>
+      <c r="D325" t="s">
+        <v>420</v>
+      </c>
+      <c r="E325" t="s">
+        <v>399</v>
+      </c>
+      <c r="F325" t="s">
+        <v>123</v>
+      </c>
+      <c r="G325" t="s">
+        <v>123</v>
+      </c>
+      <c r="H325" t="s">
+        <v>27</v>
+      </c>
+      <c r="I325" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>400</v>
+      </c>
+      <c r="B326" t="s">
+        <v>123</v>
+      </c>
+      <c r="D326" t="s">
+        <v>392</v>
+      </c>
+      <c r="E326" t="s">
+        <v>401</v>
+      </c>
+      <c r="F326" t="s">
+        <v>123</v>
+      </c>
+      <c r="G326" t="s">
+        <v>123</v>
+      </c>
+      <c r="H326" t="s">
+        <v>27</v>
+      </c>
+      <c r="I326" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>400</v>
+      </c>
+      <c r="B327" t="s">
+        <v>123</v>
+      </c>
+      <c r="D327" t="s">
+        <v>420</v>
+      </c>
+      <c r="E327" t="s">
+        <v>401</v>
+      </c>
+      <c r="F327" t="s">
+        <v>123</v>
+      </c>
+      <c r="G327" t="s">
+        <v>123</v>
+      </c>
+      <c r="H327" t="s">
+        <v>27</v>
+      </c>
+      <c r="I327" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>402</v>
+      </c>
+      <c r="B328" t="s">
+        <v>123</v>
+      </c>
+      <c r="D328" t="s">
+        <v>392</v>
+      </c>
+      <c r="E328" t="s">
+        <v>403</v>
+      </c>
+      <c r="F328" t="s">
+        <v>123</v>
+      </c>
+      <c r="G328" t="s">
+        <v>123</v>
+      </c>
+      <c r="H328" t="s">
+        <v>27</v>
+      </c>
+      <c r="I328" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>402</v>
+      </c>
+      <c r="B329" t="s">
+        <v>123</v>
+      </c>
+      <c r="D329" t="s">
+        <v>420</v>
+      </c>
+      <c r="E329" t="s">
+        <v>403</v>
+      </c>
+      <c r="F329" t="s">
+        <v>123</v>
+      </c>
+      <c r="G329" t="s">
+        <v>123</v>
+      </c>
+      <c r="H329" t="s">
+        <v>27</v>
+      </c>
+      <c r="I329" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>404</v>
+      </c>
+      <c r="B330" t="s">
+        <v>123</v>
+      </c>
+      <c r="D330" t="s">
+        <v>392</v>
+      </c>
+      <c r="E330" t="s">
+        <v>405</v>
+      </c>
+      <c r="F330" t="s">
+        <v>123</v>
+      </c>
+      <c r="G330" t="s">
+        <v>123</v>
+      </c>
+      <c r="H330" t="s">
+        <v>27</v>
+      </c>
+      <c r="I330" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>404</v>
+      </c>
+      <c r="B331" t="s">
+        <v>123</v>
+      </c>
+      <c r="D331" t="s">
+        <v>420</v>
+      </c>
+      <c r="E331" t="s">
+        <v>405</v>
+      </c>
+      <c r="F331" t="s">
+        <v>123</v>
+      </c>
+      <c r="G331" t="s">
+        <v>123</v>
+      </c>
+      <c r="H331" t="s">
+        <v>27</v>
+      </c>
+      <c r="I331" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>406</v>
+      </c>
+      <c r="B332" t="s">
+        <v>123</v>
+      </c>
+      <c r="D332" t="s">
+        <v>392</v>
+      </c>
+      <c r="E332" t="s">
+        <v>407</v>
+      </c>
+      <c r="F332" t="s">
+        <v>123</v>
+      </c>
+      <c r="G332" t="s">
+        <v>123</v>
+      </c>
+      <c r="H332" t="s">
+        <v>27</v>
+      </c>
+      <c r="I332" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>406</v>
+      </c>
+      <c r="B333" t="s">
+        <v>123</v>
+      </c>
+      <c r="D333" t="s">
+        <v>420</v>
+      </c>
+      <c r="E333" t="s">
+        <v>407</v>
+      </c>
+      <c r="F333" t="s">
+        <v>123</v>
+      </c>
+      <c r="G333" t="s">
+        <v>123</v>
+      </c>
+      <c r="H333" t="s">
+        <v>27</v>
+      </c>
+      <c r="I333" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>408</v>
+      </c>
+      <c r="B334" t="s">
+        <v>123</v>
+      </c>
+      <c r="D334" t="s">
+        <v>392</v>
+      </c>
+      <c r="E334" t="s">
+        <v>409</v>
+      </c>
+      <c r="F334" t="s">
+        <v>123</v>
+      </c>
+      <c r="G334" t="s">
+        <v>123</v>
+      </c>
+      <c r="H334" t="s">
+        <v>27</v>
+      </c>
+      <c r="I334" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>408</v>
+      </c>
+      <c r="B335" t="s">
+        <v>123</v>
+      </c>
+      <c r="D335" t="s">
+        <v>420</v>
+      </c>
+      <c r="E335" t="s">
+        <v>409</v>
+      </c>
+      <c r="F335" t="s">
+        <v>123</v>
+      </c>
+      <c r="G335" t="s">
+        <v>123</v>
+      </c>
+      <c r="H335" t="s">
+        <v>27</v>
+      </c>
+      <c r="I335" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>410</v>
+      </c>
+      <c r="B336" t="s">
+        <v>123</v>
+      </c>
+      <c r="D336" t="s">
+        <v>392</v>
+      </c>
+      <c r="E336" t="s">
+        <v>411</v>
+      </c>
+      <c r="F336" t="s">
+        <v>123</v>
+      </c>
+      <c r="G336" t="s">
+        <v>123</v>
+      </c>
+      <c r="H336" t="s">
+        <v>27</v>
+      </c>
+      <c r="I336" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>410</v>
+      </c>
+      <c r="B337" t="s">
+        <v>123</v>
+      </c>
+      <c r="D337" t="s">
+        <v>420</v>
+      </c>
+      <c r="E337" t="s">
+        <v>411</v>
+      </c>
+      <c r="F337" t="s">
+        <v>123</v>
+      </c>
+      <c r="G337" t="s">
+        <v>123</v>
+      </c>
+      <c r="H337" t="s">
+        <v>27</v>
+      </c>
+      <c r="I337" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>412</v>
+      </c>
+      <c r="B338" t="s">
+        <v>123</v>
+      </c>
+      <c r="D338" t="s">
+        <v>392</v>
+      </c>
+      <c r="E338" t="s">
+        <v>413</v>
+      </c>
+      <c r="F338" t="s">
+        <v>123</v>
+      </c>
+      <c r="G338" t="s">
+        <v>123</v>
+      </c>
+      <c r="H338" t="s">
+        <v>27</v>
+      </c>
+      <c r="I338" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>412</v>
+      </c>
+      <c r="B339" t="s">
+        <v>123</v>
+      </c>
+      <c r="D339" t="s">
+        <v>420</v>
+      </c>
+      <c r="E339" t="s">
+        <v>413</v>
+      </c>
+      <c r="F339" t="s">
+        <v>123</v>
+      </c>
+      <c r="G339" t="s">
+        <v>123</v>
+      </c>
+      <c r="H339" t="s">
+        <v>27</v>
+      </c>
+      <c r="I339" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>414</v>
+      </c>
+      <c r="B340" t="s">
+        <v>123</v>
+      </c>
+      <c r="D340" t="s">
+        <v>392</v>
+      </c>
+      <c r="E340" t="s">
+        <v>415</v>
+      </c>
+      <c r="F340" t="s">
+        <v>123</v>
+      </c>
+      <c r="G340" t="s">
+        <v>123</v>
+      </c>
+      <c r="H340" t="s">
+        <v>27</v>
+      </c>
+      <c r="I340" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>414</v>
+      </c>
+      <c r="B341" t="s">
+        <v>123</v>
+      </c>
+      <c r="D341" t="s">
+        <v>420</v>
+      </c>
+      <c r="E341" t="s">
+        <v>415</v>
+      </c>
+      <c r="F341" t="s">
+        <v>123</v>
+      </c>
+      <c r="G341" t="s">
+        <v>123</v>
+      </c>
+      <c r="H341" t="s">
+        <v>27</v>
+      </c>
+      <c r="I341" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>416</v>
+      </c>
+      <c r="B342" t="s">
+        <v>123</v>
+      </c>
+      <c r="D342" t="s">
+        <v>392</v>
+      </c>
+      <c r="E342" t="s">
+        <v>417</v>
+      </c>
+      <c r="F342" t="s">
+        <v>123</v>
+      </c>
+      <c r="G342" t="s">
+        <v>123</v>
+      </c>
+      <c r="H342" t="s">
+        <v>27</v>
+      </c>
+      <c r="I342" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>416</v>
+      </c>
+      <c r="B343" t="s">
+        <v>123</v>
+      </c>
+      <c r="D343" t="s">
+        <v>420</v>
+      </c>
+      <c r="E343" t="s">
+        <v>417</v>
+      </c>
+      <c r="F343" t="s">
+        <v>123</v>
+      </c>
+      <c r="G343" t="s">
+        <v>123</v>
+      </c>
+      <c r="H343" t="s">
+        <v>27</v>
+      </c>
+      <c r="I343" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>418</v>
+      </c>
+      <c r="B344" t="s">
+        <v>123</v>
+      </c>
+      <c r="D344" t="s">
+        <v>392</v>
+      </c>
+      <c r="E344" t="s">
+        <v>419</v>
+      </c>
+      <c r="F344" t="s">
+        <v>123</v>
+      </c>
+      <c r="G344" t="s">
+        <v>123</v>
+      </c>
+      <c r="H344" t="s">
+        <v>27</v>
+      </c>
+      <c r="I344" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>418</v>
+      </c>
+      <c r="B345" t="s">
+        <v>123</v>
+      </c>
+      <c r="D345" t="s">
+        <v>420</v>
+      </c>
+      <c r="E345" t="s">
+        <v>419</v>
+      </c>
+      <c r="F345" t="s">
+        <v>123</v>
+      </c>
+      <c r="G345" t="s">
+        <v>123</v>
+      </c>
+      <c r="H345" t="s">
+        <v>27</v>
+      </c>
+      <c r="I345" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>421</v>
+      </c>
+      <c r="B346" t="s">
+        <v>422</v>
+      </c>
+      <c r="D346" t="s">
+        <v>423</v>
+      </c>
+      <c r="E346" t="s">
+        <v>11</v>
+      </c>
+      <c r="F346" t="s">
+        <v>422</v>
+      </c>
+      <c r="G346" t="s">
+        <v>422</v>
+      </c>
+      <c r="H346" t="s">
+        <v>22</v>
+      </c>
+      <c r="I346" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>421</v>
+      </c>
+      <c r="B347" t="s">
+        <v>422</v>
+      </c>
+      <c r="D347" t="s">
+        <v>424</v>
+      </c>
+      <c r="E347" t="s">
+        <v>11</v>
+      </c>
+      <c r="F347" t="s">
+        <v>422</v>
+      </c>
+      <c r="G347" t="s">
+        <v>422</v>
+      </c>
+      <c r="H347" t="s">
+        <v>22</v>
+      </c>
+      <c r="I347" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>425</v>
+      </c>
+      <c r="B348" t="s">
+        <v>9</v>
+      </c>
+      <c r="D348" t="s">
+        <v>426</v>
+      </c>
+      <c r="E348" t="s">
+        <v>11</v>
+      </c>
+      <c r="F348" t="s">
+        <v>9</v>
+      </c>
+      <c r="G348" t="s">
+        <v>9</v>
+      </c>
+      <c r="H348" t="s">
+        <v>12</v>
+      </c>
+      <c r="I348" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>425</v>
+      </c>
+      <c r="B349" t="s">
+        <v>9</v>
+      </c>
+      <c r="D349" t="s">
+        <v>427</v>
+      </c>
+      <c r="E349" t="s">
+        <v>11</v>
+      </c>
+      <c r="F349" t="s">
+        <v>9</v>
+      </c>
+      <c r="G349" t="s">
+        <v>9</v>
+      </c>
+      <c r="H349" t="s">
+        <v>12</v>
+      </c>
+      <c r="I349" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>428</v>
+      </c>
+      <c r="B350" t="s">
+        <v>429</v>
+      </c>
+      <c r="D350" t="s">
+        <v>430</v>
+      </c>
+      <c r="E350" t="s">
+        <v>11</v>
+      </c>
+      <c r="F350" t="s">
+        <v>429</v>
+      </c>
+      <c r="G350" t="s">
+        <v>431</v>
+      </c>
+      <c r="H350" t="s">
+        <v>22</v>
+      </c>
+      <c r="I350" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>428</v>
+      </c>
+      <c r="B351" t="s">
+        <v>429</v>
+      </c>
+      <c r="D351" t="s">
+        <v>438</v>
+      </c>
+      <c r="E351" t="s">
+        <v>11</v>
+      </c>
+      <c r="F351" t="s">
+        <v>429</v>
+      </c>
+      <c r="G351" t="s">
+        <v>431</v>
+      </c>
+      <c r="H351" t="s">
+        <v>22</v>
+      </c>
+      <c r="I351" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>432</v>
+      </c>
+      <c r="B352" t="s">
+        <v>60</v>
+      </c>
+      <c r="D352" t="s">
+        <v>433</v>
+      </c>
+      <c r="E352" t="s">
+        <v>11</v>
+      </c>
+      <c r="F352" t="s">
+        <v>60</v>
+      </c>
+      <c r="G352" t="s">
+        <v>60</v>
+      </c>
+      <c r="H352" t="s">
+        <v>57</v>
+      </c>
+      <c r="I352" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>432</v>
+      </c>
+      <c r="B353" t="s">
+        <v>60</v>
+      </c>
+      <c r="D353" t="s">
+        <v>439</v>
+      </c>
+      <c r="E353" t="s">
+        <v>11</v>
+      </c>
+      <c r="F353" t="s">
+        <v>60</v>
+      </c>
+      <c r="G353" t="s">
+        <v>60</v>
+      </c>
+      <c r="H353" t="s">
+        <v>57</v>
+      </c>
+      <c r="I353" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>434</v>
+      </c>
+      <c r="B354" t="s">
+        <v>60</v>
+      </c>
+      <c r="D354" t="s">
+        <v>435</v>
+      </c>
+      <c r="E354" t="s">
+        <v>11</v>
+      </c>
+      <c r="F354" t="s">
+        <v>60</v>
+      </c>
+      <c r="G354" t="s">
+        <v>60</v>
+      </c>
+      <c r="H354" t="s">
+        <v>57</v>
+      </c>
+      <c r="I354" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>434</v>
+      </c>
+      <c r="B355" t="s">
+        <v>60</v>
+      </c>
+      <c r="D355" t="s">
+        <v>440</v>
+      </c>
+      <c r="E355" t="s">
+        <v>11</v>
+      </c>
+      <c r="F355" t="s">
+        <v>60</v>
+      </c>
+      <c r="G355" t="s">
+        <v>60</v>
+      </c>
+      <c r="H355" t="s">
+        <v>57</v>
+      </c>
+      <c r="I355" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>436</v>
+      </c>
+      <c r="B356" t="s">
+        <v>60</v>
+      </c>
+      <c r="D356" t="s">
+        <v>437</v>
+      </c>
+      <c r="E356" t="s">
+        <v>11</v>
+      </c>
+      <c r="F356" t="s">
+        <v>60</v>
+      </c>
+      <c r="G356" t="s">
+        <v>60</v>
+      </c>
+      <c r="H356" t="s">
+        <v>57</v>
+      </c>
+      <c r="I356" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>436</v>
+      </c>
+      <c r="B357" t="s">
+        <v>60</v>
+      </c>
+      <c r="D357" t="s">
+        <v>441</v>
+      </c>
+      <c r="E357" t="s">
+        <v>11</v>
+      </c>
+      <c r="F357" t="s">
+        <v>60</v>
+      </c>
+      <c r="G357" t="s">
+        <v>60</v>
+      </c>
+      <c r="H357" t="s">
+        <v>57</v>
+      </c>
+      <c r="I357" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>446</v>
+      </c>
+      <c r="B358" t="s">
+        <v>123</v>
+      </c>
+      <c r="D358" t="s">
+        <v>445</v>
+      </c>
+      <c r="E358" t="s">
+        <v>11</v>
+      </c>
+      <c r="F358" t="s">
+        <v>123</v>
+      </c>
+      <c r="G358" t="s">
+        <v>123</v>
+      </c>
+      <c r="H358" t="s">
+        <v>27</v>
+      </c>
+      <c r="I358" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>446</v>
+      </c>
+      <c r="B359" t="s">
+        <v>123</v>
+      </c>
+      <c r="D359" t="s">
+        <v>447</v>
+      </c>
+      <c r="E359" t="s">
+        <v>11</v>
+      </c>
+      <c r="F359" t="s">
+        <v>123</v>
+      </c>
+      <c r="G359" t="s">
+        <v>123</v>
+      </c>
+      <c r="H359" t="s">
+        <v>27</v>
+      </c>
+      <c r="I359" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>444</v>
+      </c>
+      <c r="B360" t="s">
+        <v>123</v>
+      </c>
+      <c r="D360" t="s">
+        <v>443</v>
+      </c>
+      <c r="E360" t="s">
+        <v>11</v>
+      </c>
+      <c r="F360" t="s">
+        <v>123</v>
+      </c>
+      <c r="G360" t="s">
+        <v>123</v>
+      </c>
+      <c r="H360" t="s">
+        <v>27</v>
+      </c>
+      <c r="I360" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>444</v>
+      </c>
+      <c r="B361" t="s">
+        <v>123</v>
+      </c>
+      <c r="D361" t="s">
+        <v>448</v>
+      </c>
+      <c r="E361" t="s">
+        <v>11</v>
+      </c>
+      <c r="F361" t="s">
+        <v>123</v>
+      </c>
+      <c r="G361" t="s">
+        <v>123</v>
+      </c>
+      <c r="H361" t="s">
+        <v>27</v>
+      </c>
+      <c r="I361" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>449</v>
+      </c>
+      <c r="B362" t="s">
+        <v>127</v>
+      </c>
+      <c r="D362" t="s">
+        <v>450</v>
+      </c>
+      <c r="E362" t="s">
+        <v>11</v>
+      </c>
+      <c r="F362" t="s">
+        <v>127</v>
+      </c>
+      <c r="G362" t="s">
+        <v>127</v>
+      </c>
+      <c r="H362" t="s">
+        <v>17</v>
+      </c>
+      <c r="I362" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>449</v>
+      </c>
+      <c r="B363" t="s">
+        <v>127</v>
+      </c>
+      <c r="D363" t="s">
+        <v>451</v>
+      </c>
+      <c r="E363" t="s">
+        <v>11</v>
+      </c>
+      <c r="F363" t="s">
+        <v>127</v>
+      </c>
+      <c r="G363" t="s">
+        <v>127</v>
+      </c>
+      <c r="H363" t="s">
+        <v>17</v>
+      </c>
+      <c r="I363" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>452</v>
+      </c>
+      <c r="B364" t="s">
+        <v>127</v>
+      </c>
+      <c r="D364" t="s">
+        <v>453</v>
+      </c>
+      <c r="E364" t="s">
+        <v>11</v>
+      </c>
+      <c r="F364" t="s">
+        <v>127</v>
+      </c>
+      <c r="G364" t="s">
+        <v>127</v>
+      </c>
+      <c r="H364" t="s">
+        <v>17</v>
+      </c>
+      <c r="I364" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>452</v>
+      </c>
+      <c r="B365" t="s">
+        <v>127</v>
+      </c>
+      <c r="D365" t="s">
+        <v>454</v>
+      </c>
+      <c r="E365" t="s">
+        <v>11</v>
+      </c>
+      <c r="F365" t="s">
+        <v>127</v>
+      </c>
+      <c r="G365" t="s">
+        <v>127</v>
+      </c>
+      <c r="H365" t="s">
+        <v>17</v>
+      </c>
+      <c r="I365" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>176</v>
+      </c>
+      <c r="B366" t="s">
+        <v>127</v>
+      </c>
+      <c r="D366" t="s">
+        <v>455</v>
+      </c>
+      <c r="E366" t="s">
+        <v>11</v>
+      </c>
+      <c r="F366" t="s">
+        <v>127</v>
+      </c>
+      <c r="G366" t="s">
+        <v>127</v>
+      </c>
+      <c r="H366" t="s">
+        <v>17</v>
+      </c>
+      <c r="I366" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>176</v>
+      </c>
+      <c r="B367" t="s">
+        <v>127</v>
+      </c>
+      <c r="D367" t="s">
+        <v>460</v>
+      </c>
+      <c r="E367" t="s">
+        <v>11</v>
+      </c>
+      <c r="F367" t="s">
+        <v>127</v>
+      </c>
+      <c r="G367" t="s">
+        <v>127</v>
+      </c>
+      <c r="H367" t="s">
+        <v>17</v>
+      </c>
+      <c r="I367" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>456</v>
+      </c>
+      <c r="B368" t="s">
+        <v>127</v>
+      </c>
+      <c r="D368" t="s">
+        <v>457</v>
+      </c>
+      <c r="E368" t="s">
+        <v>11</v>
+      </c>
+      <c r="F368" t="s">
+        <v>127</v>
+      </c>
+      <c r="G368" t="s">
+        <v>127</v>
+      </c>
+      <c r="H368" t="s">
+        <v>17</v>
+      </c>
+      <c r="I368" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>456</v>
+      </c>
+      <c r="B369" t="s">
+        <v>127</v>
+      </c>
+      <c r="D369" t="s">
+        <v>458</v>
+      </c>
+      <c r="E369" t="s">
+        <v>11</v>
+      </c>
+      <c r="F369" t="s">
+        <v>127</v>
+      </c>
+      <c r="G369" t="s">
+        <v>127</v>
+      </c>
+      <c r="H369" t="s">
+        <v>17</v>
+      </c>
+      <c r="I369" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>462</v>
+      </c>
+      <c r="B370" t="s">
+        <v>127</v>
+      </c>
+      <c r="D370" t="s">
+        <v>461</v>
+      </c>
+      <c r="E370" t="s">
+        <v>11</v>
+      </c>
+      <c r="F370" t="s">
+        <v>127</v>
+      </c>
+      <c r="G370" t="s">
+        <v>127</v>
+      </c>
+      <c r="H370" t="s">
+        <v>17</v>
+      </c>
+      <c r="I370" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>462</v>
+      </c>
+      <c r="B371" t="s">
+        <v>127</v>
+      </c>
+      <c r="D371" t="s">
+        <v>463</v>
+      </c>
+      <c r="E371" t="s">
+        <v>11</v>
+      </c>
+      <c r="F371" t="s">
+        <v>127</v>
+      </c>
+      <c r="G371" t="s">
+        <v>127</v>
+      </c>
+      <c r="H371" t="s">
+        <v>17</v>
+      </c>
+      <c r="I371" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>465</v>
+      </c>
+      <c r="B372" t="s">
+        <v>127</v>
+      </c>
+      <c r="D372" t="s">
+        <v>464</v>
+      </c>
+      <c r="E372" t="s">
+        <v>11</v>
+      </c>
+      <c r="F372" t="s">
+        <v>127</v>
+      </c>
+      <c r="G372" t="s">
+        <v>127</v>
+      </c>
+      <c r="H372" t="s">
+        <v>17</v>
+      </c>
+      <c r="I372" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>465</v>
+      </c>
+      <c r="B373" t="s">
+        <v>127</v>
+      </c>
+      <c r="D373" t="s">
+        <v>466</v>
+      </c>
+      <c r="E373" t="s">
+        <v>11</v>
+      </c>
+      <c r="F373" t="s">
+        <v>127</v>
+      </c>
+      <c r="G373" t="s">
+        <v>127</v>
+      </c>
+      <c r="H373" t="s">
+        <v>17</v>
+      </c>
+      <c r="I373" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>476</v>
+      </c>
+      <c r="B374" t="s">
+        <v>127</v>
+      </c>
+      <c r="D374" t="s">
+        <v>469</v>
+      </c>
+      <c r="E374" t="s">
+        <v>475</v>
+      </c>
+      <c r="F374" t="s">
+        <v>127</v>
+      </c>
+      <c r="G374" t="s">
+        <v>127</v>
+      </c>
+      <c r="H374" t="s">
+        <v>17</v>
+      </c>
+      <c r="I374" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>476</v>
+      </c>
+      <c r="B375" t="s">
+        <v>127</v>
+      </c>
+      <c r="D375" t="s">
+        <v>477</v>
+      </c>
+      <c r="E375" t="s">
+        <v>475</v>
+      </c>
+      <c r="F375" t="s">
+        <v>127</v>
+      </c>
+      <c r="G375" t="s">
+        <v>127</v>
+      </c>
+      <c r="H375" t="s">
+        <v>17</v>
+      </c>
+      <c r="I375" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>474</v>
+      </c>
+      <c r="B376" t="s">
+        <v>127</v>
+      </c>
+      <c r="D376" t="s">
+        <v>469</v>
+      </c>
+      <c r="E376" t="s">
+        <v>473</v>
+      </c>
+      <c r="F376" t="s">
+        <v>127</v>
+      </c>
+      <c r="G376" t="s">
+        <v>127</v>
+      </c>
+      <c r="H376" t="s">
+        <v>17</v>
+      </c>
+      <c r="I376" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>474</v>
+      </c>
+      <c r="B377" t="s">
+        <v>127</v>
+      </c>
+      <c r="D377" t="s">
+        <v>477</v>
+      </c>
+      <c r="E377" t="s">
+        <v>473</v>
+      </c>
+      <c r="F377" t="s">
+        <v>127</v>
+      </c>
+      <c r="G377" t="s">
+        <v>127</v>
+      </c>
+      <c r="H377" t="s">
+        <v>17</v>
+      </c>
+      <c r="I377" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>472</v>
+      </c>
+      <c r="B378" t="s">
+        <v>127</v>
+      </c>
+      <c r="D378" t="s">
+        <v>469</v>
+      </c>
+      <c r="E378" t="s">
+        <v>471</v>
+      </c>
+      <c r="F378" t="s">
+        <v>127</v>
+      </c>
+      <c r="G378" t="s">
+        <v>127</v>
+      </c>
+      <c r="H378" t="s">
+        <v>17</v>
+      </c>
+      <c r="I378" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>472</v>
+      </c>
+      <c r="B379" t="s">
+        <v>127</v>
+      </c>
+      <c r="D379" t="s">
+        <v>477</v>
+      </c>
+      <c r="E379" t="s">
+        <v>471</v>
+      </c>
+      <c r="F379" t="s">
+        <v>127</v>
+      </c>
+      <c r="G379" t="s">
+        <v>127</v>
+      </c>
+      <c r="H379" t="s">
+        <v>17</v>
+      </c>
+      <c r="I379" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>470</v>
+      </c>
+      <c r="B380" t="s">
+        <v>127</v>
+      </c>
+      <c r="D380" t="s">
+        <v>469</v>
+      </c>
+      <c r="E380" t="s">
+        <v>468</v>
+      </c>
+      <c r="F380" t="s">
+        <v>127</v>
+      </c>
+      <c r="G380" t="s">
+        <v>127</v>
+      </c>
+      <c r="H380" t="s">
+        <v>17</v>
+      </c>
+      <c r="I380" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>470</v>
+      </c>
+      <c r="B381" t="s">
+        <v>127</v>
+      </c>
+      <c r="D381" t="s">
+        <v>477</v>
+      </c>
+      <c r="E381" t="s">
+        <v>468</v>
+      </c>
+      <c r="F381" t="s">
+        <v>127</v>
+      </c>
+      <c r="G381" t="s">
+        <v>127</v>
+      </c>
+      <c r="H381" t="s">
+        <v>17</v>
+      </c>
+      <c r="I381" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>489</v>
+      </c>
+      <c r="B382" t="s">
+        <v>68</v>
+      </c>
+      <c r="D382" t="s">
+        <v>488</v>
+      </c>
+      <c r="E382" t="s">
+        <v>11</v>
+      </c>
+      <c r="F382" t="s">
+        <v>68</v>
+      </c>
+      <c r="G382" t="s">
+        <v>68</v>
+      </c>
+      <c r="H382" t="s">
+        <v>70</v>
+      </c>
+      <c r="I382" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>489</v>
+      </c>
+      <c r="B383" t="s">
+        <v>68</v>
+      </c>
+      <c r="D383" t="s">
+        <v>490</v>
+      </c>
+      <c r="E383" t="s">
+        <v>11</v>
+      </c>
+      <c r="F383" t="s">
+        <v>68</v>
+      </c>
+      <c r="G383" t="s">
+        <v>68</v>
+      </c>
+      <c r="H383" t="s">
+        <v>70</v>
+      </c>
+      <c r="I383" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>487</v>
+      </c>
+      <c r="B384" t="s">
+        <v>68</v>
+      </c>
+      <c r="D384" t="s">
+        <v>486</v>
+      </c>
+      <c r="E384" t="s">
+        <v>11</v>
+      </c>
+      <c r="F384" t="s">
+        <v>68</v>
+      </c>
+      <c r="G384" t="s">
+        <v>68</v>
+      </c>
+      <c r="H384" t="s">
+        <v>70</v>
+      </c>
+      <c r="I384" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>487</v>
+      </c>
+      <c r="B385" t="s">
+        <v>68</v>
+      </c>
+      <c r="D385" t="s">
+        <v>492</v>
+      </c>
+      <c r="E385" t="s">
+        <v>11</v>
+      </c>
+      <c r="F385" t="s">
+        <v>68</v>
+      </c>
+      <c r="G385" t="s">
+        <v>68</v>
+      </c>
+      <c r="H385" t="s">
+        <v>70</v>
+      </c>
+      <c r="I385" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>485</v>
+      </c>
+      <c r="B386" t="s">
+        <v>68</v>
+      </c>
+      <c r="D386" t="s">
+        <v>484</v>
+      </c>
+      <c r="E386" t="s">
+        <v>11</v>
+      </c>
+      <c r="F386" t="s">
+        <v>68</v>
+      </c>
+      <c r="G386" t="s">
+        <v>68</v>
+      </c>
+      <c r="H386" t="s">
+        <v>70</v>
+      </c>
+      <c r="I386" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>485</v>
+      </c>
+      <c r="B387" t="s">
+        <v>68</v>
+      </c>
+      <c r="D387" t="s">
+        <v>493</v>
+      </c>
+      <c r="E387" t="s">
+        <v>11</v>
+      </c>
+      <c r="F387" t="s">
+        <v>68</v>
+      </c>
+      <c r="G387" t="s">
+        <v>68</v>
+      </c>
+      <c r="H387" t="s">
+        <v>70</v>
+      </c>
+      <c r="I387" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>495</v>
+      </c>
+      <c r="B388" t="s">
+        <v>496</v>
+      </c>
+      <c r="D388" t="s">
+        <v>497</v>
+      </c>
+      <c r="E388" t="s">
+        <v>11</v>
+      </c>
+      <c r="F388" t="s">
+        <v>496</v>
+      </c>
+      <c r="G388" t="s">
+        <v>498</v>
+      </c>
+      <c r="H388" t="s">
+        <v>352</v>
+      </c>
+      <c r="I388" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>495</v>
+      </c>
+      <c r="B389" t="s">
+        <v>496</v>
+      </c>
+      <c r="D389" t="s">
+        <v>499</v>
+      </c>
+      <c r="E389" t="s">
+        <v>11</v>
+      </c>
+      <c r="F389" t="s">
+        <v>496</v>
+      </c>
+      <c r="G389" t="s">
+        <v>498</v>
+      </c>
+      <c r="H389" t="s">
+        <v>352</v>
+      </c>
+      <c r="I389" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>43</v>
+      </c>
+      <c r="B390" t="s">
+        <v>40</v>
+      </c>
+      <c r="C390" t="s">
+        <v>11</v>
+      </c>
+      <c r="D390" t="s">
+        <v>502</v>
+      </c>
+      <c r="E390" t="s">
+        <v>11</v>
+      </c>
+      <c r="F390" t="s">
+        <v>40</v>
+      </c>
+      <c r="G390" t="s">
+        <v>40</v>
+      </c>
+      <c r="H390" t="s">
+        <v>42</v>
+      </c>
+      <c r="I390" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>43</v>
+      </c>
+      <c r="B391" t="s">
+        <v>40</v>
+      </c>
+      <c r="C391" t="s">
+        <v>11</v>
+      </c>
+      <c r="D391" t="s">
+        <v>503</v>
+      </c>
+      <c r="E391" t="s">
+        <v>11</v>
+      </c>
+      <c r="F391" t="s">
+        <v>40</v>
+      </c>
+      <c r="G391" t="s">
+        <v>40</v>
+      </c>
+      <c r="H391" t="s">
+        <v>42</v>
+      </c>
+      <c r="I391" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>505</v>
+      </c>
+      <c r="B392" t="s">
+        <v>506</v>
+      </c>
+      <c r="C392" t="s">
+        <v>11</v>
+      </c>
+      <c r="D392" t="s">
+        <v>507</v>
+      </c>
+      <c r="E392" t="s">
+        <v>11</v>
+      </c>
+      <c r="F392" t="s">
+        <v>506</v>
+      </c>
+      <c r="G392" t="s">
+        <v>506</v>
+      </c>
+      <c r="H392" t="s">
+        <v>508</v>
+      </c>
+      <c r="I392" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>505</v>
+      </c>
+      <c r="B393" t="s">
+        <v>506</v>
+      </c>
+      <c r="C393" t="s">
+        <v>11</v>
+      </c>
+      <c r="D393" t="s">
+        <v>509</v>
+      </c>
+      <c r="E393" t="s">
+        <v>11</v>
+      </c>
+      <c r="F393" t="s">
+        <v>506</v>
+      </c>
+      <c r="G393" t="s">
+        <v>506</v>
+      </c>
+      <c r="H393" t="s">
+        <v>508</v>
+      </c>
+      <c r="I393" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>482</v>
+      </c>
+      <c r="B394" t="s">
+        <v>68</v>
+      </c>
+      <c r="C394" t="s">
+        <v>510</v>
+      </c>
+      <c r="D394" t="s">
+        <v>483</v>
+      </c>
+      <c r="E394" t="s">
+        <v>11</v>
+      </c>
+      <c r="F394" t="s">
+        <v>68</v>
+      </c>
+      <c r="G394" t="s">
+        <v>68</v>
+      </c>
+      <c r="H394" t="s">
+        <v>70</v>
+      </c>
+      <c r="I394" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>482</v>
+      </c>
+      <c r="B395" t="s">
+        <v>68</v>
+      </c>
+      <c r="D395" t="s">
+        <v>511</v>
+      </c>
+      <c r="E395" t="s">
+        <v>11</v>
+      </c>
+      <c r="F395" t="s">
+        <v>68</v>
+      </c>
+      <c r="G395" t="s">
+        <v>68</v>
+      </c>
+      <c r="H395" t="s">
+        <v>70</v>
+      </c>
+      <c r="I395" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>513</v>
+      </c>
+      <c r="B396" t="s">
+        <v>514</v>
+      </c>
+      <c r="D396" t="s">
+        <v>515</v>
+      </c>
+      <c r="E396" t="s">
+        <v>516</v>
+      </c>
+      <c r="F396" t="s">
+        <v>514</v>
+      </c>
+      <c r="G396" t="s">
+        <v>514</v>
+      </c>
+      <c r="H396" t="s">
+        <v>42</v>
+      </c>
+      <c r="I396" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>513</v>
+      </c>
+      <c r="B397" t="s">
+        <v>514</v>
+      </c>
+      <c r="D397" t="s">
+        <v>519</v>
+      </c>
+      <c r="E397" t="s">
+        <v>516</v>
+      </c>
+      <c r="F397" t="s">
+        <v>514</v>
+      </c>
+      <c r="G397" t="s">
+        <v>514</v>
+      </c>
+      <c r="H397" t="s">
+        <v>42</v>
+      </c>
+      <c r="I397" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>517</v>
+      </c>
+      <c r="B398" t="s">
+        <v>514</v>
+      </c>
+      <c r="D398" t="s">
+        <v>515</v>
+      </c>
+      <c r="E398" t="s">
+        <v>518</v>
+      </c>
+      <c r="F398" t="s">
+        <v>514</v>
+      </c>
+      <c r="G398" t="s">
+        <v>514</v>
+      </c>
+      <c r="H398" t="s">
+        <v>42</v>
+      </c>
+      <c r="I398" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>517</v>
+      </c>
+      <c r="B399" t="s">
+        <v>514</v>
+      </c>
+      <c r="D399" t="s">
+        <v>519</v>
+      </c>
+      <c r="E399" t="s">
+        <v>518</v>
+      </c>
+      <c r="F399" t="s">
+        <v>514</v>
+      </c>
+      <c r="G399" t="s">
+        <v>514</v>
+      </c>
+      <c r="H399" t="s">
+        <v>42</v>
+      </c>
+      <c r="I399" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>520</v>
+      </c>
+      <c r="B400" t="s">
+        <v>9</v>
+      </c>
+      <c r="C400" t="s">
+        <v>11</v>
+      </c>
+      <c r="D400" t="s">
+        <v>521</v>
+      </c>
+      <c r="E400" t="s">
+        <v>11</v>
+      </c>
+      <c r="F400" t="s">
+        <v>9</v>
+      </c>
+      <c r="G400" t="s">
+        <v>9</v>
+      </c>
+      <c r="H400" t="s">
+        <v>12</v>
+      </c>
+      <c r="I400" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>520</v>
+      </c>
+      <c r="B401" t="s">
+        <v>9</v>
+      </c>
+      <c r="C401" t="s">
+        <v>11</v>
+      </c>
+      <c r="D401" t="s">
+        <v>550</v>
+      </c>
+      <c r="E401" t="s">
+        <v>11</v>
+      </c>
+      <c r="F401" t="s">
+        <v>9</v>
+      </c>
+      <c r="G401" t="s">
+        <v>9</v>
+      </c>
+      <c r="H401" t="s">
+        <v>12</v>
+      </c>
+      <c r="I401" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>421</v>
+      </c>
+      <c r="B402" t="s">
+        <v>422</v>
+      </c>
+      <c r="C402" t="s">
+        <v>11</v>
+      </c>
+      <c r="D402" t="s">
+        <v>522</v>
+      </c>
+      <c r="E402" t="s">
+        <v>11</v>
+      </c>
+      <c r="F402" t="s">
+        <v>422</v>
+      </c>
+      <c r="G402" t="s">
+        <v>422</v>
+      </c>
+      <c r="H402" t="s">
+        <v>22</v>
+      </c>
+      <c r="I402" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>421</v>
+      </c>
+      <c r="B403" t="s">
+        <v>422</v>
+      </c>
+      <c r="C403" t="s">
+        <v>11</v>
+      </c>
+      <c r="D403" t="s">
+        <v>551</v>
+      </c>
+      <c r="E403" t="s">
+        <v>11</v>
+      </c>
+      <c r="F403" t="s">
+        <v>422</v>
+      </c>
+      <c r="G403" t="s">
+        <v>422</v>
+      </c>
+      <c r="H403" t="s">
+        <v>22</v>
+      </c>
+      <c r="I403" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>523</v>
+      </c>
+      <c r="B404" t="s">
+        <v>350</v>
+      </c>
+      <c r="C404" t="s">
+        <v>524</v>
+      </c>
+      <c r="D404" t="s">
+        <v>525</v>
+      </c>
+      <c r="E404" t="s">
+        <v>11</v>
+      </c>
+      <c r="F404" t="s">
+        <v>350</v>
+      </c>
+      <c r="G404" t="s">
+        <v>350</v>
+      </c>
+      <c r="H404" t="s">
+        <v>352</v>
+      </c>
+      <c r="I404" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>523</v>
+      </c>
+      <c r="B405" t="s">
+        <v>350</v>
+      </c>
+      <c r="C405" t="s">
+        <v>524</v>
+      </c>
+      <c r="D405" t="s">
+        <v>552</v>
+      </c>
+      <c r="E405" t="s">
+        <v>11</v>
+      </c>
+      <c r="F405" t="s">
+        <v>350</v>
+      </c>
+      <c r="G405" t="s">
+        <v>350</v>
+      </c>
+      <c r="H405" t="s">
+        <v>352</v>
+      </c>
+      <c r="I405" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>526</v>
+      </c>
+      <c r="B406" t="s">
+        <v>527</v>
+      </c>
+      <c r="C406" t="s">
+        <v>11</v>
+      </c>
+      <c r="D406" t="s">
+        <v>528</v>
+      </c>
+      <c r="E406" t="s">
+        <v>11</v>
+      </c>
+      <c r="F406" t="s">
+        <v>527</v>
+      </c>
+      <c r="G406" t="s">
+        <v>529</v>
+      </c>
+      <c r="H406" t="s">
+        <v>348</v>
+      </c>
+      <c r="I406" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>526</v>
+      </c>
+      <c r="B407" t="s">
+        <v>527</v>
+      </c>
+      <c r="C407" t="s">
+        <v>11</v>
+      </c>
+      <c r="D407" t="s">
+        <v>553</v>
+      </c>
+      <c r="E407" t="s">
+        <v>11</v>
+      </c>
+      <c r="F407" t="s">
+        <v>527</v>
+      </c>
+      <c r="G407" t="s">
+        <v>529</v>
+      </c>
+      <c r="H407" t="s">
+        <v>348</v>
+      </c>
+      <c r="I407" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>530</v>
+      </c>
+      <c r="B408" t="s">
+        <v>531</v>
+      </c>
+      <c r="C408" t="s">
+        <v>11</v>
+      </c>
+      <c r="D408" t="s">
+        <v>532</v>
+      </c>
+      <c r="E408" t="s">
+        <v>11</v>
+      </c>
+      <c r="F408" t="s">
+        <v>531</v>
+      </c>
+      <c r="G408" t="s">
+        <v>531</v>
+      </c>
+      <c r="H408" t="s">
+        <v>17</v>
+      </c>
+      <c r="I408" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>530</v>
+      </c>
+      <c r="B409" t="s">
+        <v>531</v>
+      </c>
+      <c r="C409" t="s">
+        <v>11</v>
+      </c>
+      <c r="D409" t="s">
+        <v>554</v>
+      </c>
+      <c r="E409" t="s">
+        <v>11</v>
+      </c>
+      <c r="F409" t="s">
+        <v>531</v>
+      </c>
+      <c r="G409" t="s">
+        <v>531</v>
+      </c>
+      <c r="H409" t="s">
+        <v>17</v>
+      </c>
+      <c r="I409" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>533</v>
+      </c>
+      <c r="B410" t="s">
+        <v>534</v>
+      </c>
+      <c r="C410" t="s">
+        <v>11</v>
+      </c>
+      <c r="D410" t="s">
+        <v>535</v>
+      </c>
+      <c r="E410" t="s">
+        <v>11</v>
+      </c>
+      <c r="F410" t="s">
+        <v>534</v>
+      </c>
+      <c r="G410" t="s">
+        <v>534</v>
+      </c>
+      <c r="H410" t="s">
+        <v>22</v>
+      </c>
+      <c r="I410" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>533</v>
+      </c>
+      <c r="B411" t="s">
+        <v>534</v>
+      </c>
+      <c r="C411" t="s">
+        <v>11</v>
+      </c>
+      <c r="D411" t="s">
+        <v>555</v>
+      </c>
+      <c r="E411" t="s">
+        <v>11</v>
+      </c>
+      <c r="F411" t="s">
+        <v>534</v>
+      </c>
+      <c r="G411" t="s">
+        <v>534</v>
+      </c>
+      <c r="H411" t="s">
+        <v>22</v>
+      </c>
+      <c r="I411" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>536</v>
+      </c>
+      <c r="B412" t="s">
+        <v>123</v>
+      </c>
+      <c r="C412" t="s">
+        <v>11</v>
+      </c>
+      <c r="D412" t="s">
+        <v>537</v>
+      </c>
+      <c r="E412" t="s">
+        <v>11</v>
+      </c>
+      <c r="F412" t="s">
+        <v>123</v>
+      </c>
+      <c r="G412" t="s">
+        <v>123</v>
+      </c>
+      <c r="H412" t="s">
+        <v>27</v>
+      </c>
+      <c r="I412" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>536</v>
+      </c>
+      <c r="B413" t="s">
+        <v>123</v>
+      </c>
+      <c r="C413" t="s">
+        <v>11</v>
+      </c>
+      <c r="D413" t="s">
+        <v>556</v>
+      </c>
+      <c r="E413" t="s">
+        <v>11</v>
+      </c>
+      <c r="F413" t="s">
+        <v>123</v>
+      </c>
+      <c r="G413" t="s">
+        <v>123</v>
+      </c>
+      <c r="H413" t="s">
+        <v>27</v>
+      </c>
+      <c r="I413" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>538</v>
+      </c>
+      <c r="B414" t="s">
+        <v>123</v>
+      </c>
+      <c r="C414" t="s">
+        <v>11</v>
+      </c>
+      <c r="D414" t="s">
+        <v>539</v>
+      </c>
+      <c r="E414" t="s">
+        <v>11</v>
+      </c>
+      <c r="F414" t="s">
+        <v>123</v>
+      </c>
+      <c r="G414" t="s">
+        <v>123</v>
+      </c>
+      <c r="H414" t="s">
+        <v>27</v>
+      </c>
+      <c r="I414" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>538</v>
+      </c>
+      <c r="B415" t="s">
+        <v>123</v>
+      </c>
+      <c r="C415" t="s">
+        <v>11</v>
+      </c>
+      <c r="D415" t="s">
+        <v>557</v>
+      </c>
+      <c r="E415" t="s">
+        <v>11</v>
+      </c>
+      <c r="F415" t="s">
+        <v>123</v>
+      </c>
+      <c r="G415" t="s">
+        <v>123</v>
+      </c>
+      <c r="H415" t="s">
+        <v>27</v>
+      </c>
+      <c r="I415" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>540</v>
+      </c>
+      <c r="B416" t="s">
+        <v>541</v>
+      </c>
+      <c r="C416" t="s">
+        <v>11</v>
+      </c>
+      <c r="D416" t="s">
+        <v>542</v>
+      </c>
+      <c r="E416" t="s">
+        <v>11</v>
+      </c>
+      <c r="F416" t="s">
+        <v>541</v>
+      </c>
+      <c r="G416" t="s">
+        <v>541</v>
+      </c>
+      <c r="H416" t="s">
+        <v>352</v>
+      </c>
+      <c r="I416" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>540</v>
+      </c>
+      <c r="B417" t="s">
+        <v>541</v>
+      </c>
+      <c r="C417" t="s">
+        <v>11</v>
+      </c>
+      <c r="D417" t="s">
+        <v>558</v>
+      </c>
+      <c r="E417" t="s">
+        <v>11</v>
+      </c>
+      <c r="F417" t="s">
+        <v>541</v>
+      </c>
+      <c r="G417" t="s">
+        <v>541</v>
+      </c>
+      <c r="H417" t="s">
+        <v>352</v>
+      </c>
+      <c r="I417" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>543</v>
+      </c>
+      <c r="B418" t="s">
+        <v>364</v>
+      </c>
+      <c r="C418" t="s">
+        <v>544</v>
+      </c>
+      <c r="D418" t="s">
+        <v>545</v>
+      </c>
+      <c r="E418" t="s">
+        <v>11</v>
+      </c>
+      <c r="F418" t="s">
+        <v>364</v>
+      </c>
+      <c r="G418" t="s">
+        <v>364</v>
+      </c>
+      <c r="H418" t="s">
+        <v>348</v>
+      </c>
+      <c r="I418" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>543</v>
+      </c>
+      <c r="B419" t="s">
+        <v>364</v>
+      </c>
+      <c r="C419" t="s">
+        <v>544</v>
+      </c>
+      <c r="D419" t="s">
+        <v>559</v>
+      </c>
+      <c r="E419" t="s">
+        <v>11</v>
+      </c>
+      <c r="F419" t="s">
+        <v>364</v>
+      </c>
+      <c r="G419" t="s">
+        <v>364</v>
+      </c>
+      <c r="H419" t="s">
+        <v>348</v>
+      </c>
+      <c r="I419" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>299</v>
+      </c>
+      <c r="B420" t="s">
+        <v>300</v>
+      </c>
+      <c r="C420" t="s">
+        <v>11</v>
+      </c>
+      <c r="D420" t="s">
+        <v>546</v>
+      </c>
+      <c r="E420" t="s">
+        <v>11</v>
+      </c>
+      <c r="F420" t="s">
+        <v>300</v>
+      </c>
+      <c r="G420" t="s">
+        <v>300</v>
+      </c>
+      <c r="H420" t="s">
+        <v>22</v>
+      </c>
+      <c r="I420" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>299</v>
+      </c>
+      <c r="B421" t="s">
+        <v>300</v>
+      </c>
+      <c r="C421" t="s">
+        <v>11</v>
+      </c>
+      <c r="D421" t="s">
+        <v>560</v>
+      </c>
+      <c r="E421" t="s">
+        <v>11</v>
+      </c>
+      <c r="F421" t="s">
+        <v>300</v>
+      </c>
+      <c r="G421" t="s">
+        <v>300</v>
+      </c>
+      <c r="H421" t="s">
+        <v>22</v>
+      </c>
+      <c r="I421" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>547</v>
+      </c>
+      <c r="B422" t="s">
+        <v>303</v>
+      </c>
+      <c r="C422" t="s">
+        <v>11</v>
+      </c>
+      <c r="D422" t="s">
+        <v>548</v>
+      </c>
+      <c r="E422" t="s">
+        <v>11</v>
+      </c>
+      <c r="F422" t="s">
+        <v>303</v>
+      </c>
+      <c r="G422" t="s">
+        <v>303</v>
+      </c>
+      <c r="H422" t="s">
+        <v>304</v>
+      </c>
+      <c r="I422" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>547</v>
+      </c>
+      <c r="B423" t="s">
+        <v>303</v>
+      </c>
+      <c r="C423" t="s">
+        <v>11</v>
+      </c>
+      <c r="D423" t="s">
+        <v>561</v>
+      </c>
+      <c r="E423" t="s">
+        <v>11</v>
+      </c>
+      <c r="F423" t="s">
+        <v>303</v>
+      </c>
+      <c r="G423" t="s">
+        <v>303</v>
+      </c>
+      <c r="H423" t="s">
+        <v>304</v>
+      </c>
+      <c r="I423" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>305</v>
+      </c>
+      <c r="B424" t="s">
+        <v>303</v>
+      </c>
+      <c r="C424" t="s">
+        <v>11</v>
+      </c>
+      <c r="D424" t="s">
+        <v>549</v>
+      </c>
+      <c r="E424" t="s">
+        <v>11</v>
+      </c>
+      <c r="F424" t="s">
+        <v>303</v>
+      </c>
+      <c r="G424" t="s">
+        <v>303</v>
+      </c>
+      <c r="H424" t="s">
+        <v>304</v>
+      </c>
+      <c r="I424" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>305</v>
+      </c>
+      <c r="B425" t="s">
+        <v>303</v>
+      </c>
+      <c r="C425" t="s">
+        <v>11</v>
+      </c>
+      <c r="D425" t="s">
+        <v>562</v>
+      </c>
+      <c r="E425" t="s">
+        <v>11</v>
+      </c>
+      <c r="F425" t="s">
+        <v>303</v>
+      </c>
+      <c r="G425" t="s">
+        <v>303</v>
+      </c>
+      <c r="H425" t="s">
+        <v>304</v>
+      </c>
+      <c r="I425" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4EFAE8-A533-498F-A621-CE0338158171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4C7654-8187-473C-B4C9-8024AA076269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2834" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2797" uniqueCount="557">
   <si>
     <t>Kod</t>
   </si>
@@ -1484,9 +1484,6 @@
     <t>90-457</t>
   </si>
   <si>
-    <t>Katedralny im. Jana Pawła II Pl.</t>
-  </si>
-  <si>
     <t>Wojciecha Korfantego</t>
   </si>
   <si>
@@ -1565,12 +1562,6 @@
     <t>skwer Szarych Szeregów</t>
   </si>
   <si>
-    <t>Łódź-Śródmieście</t>
-  </si>
-  <si>
-    <t>pl. Jana Pawła II</t>
-  </si>
-  <si>
     <t>Inwersja i inna nazwa</t>
   </si>
   <si>
@@ -1592,9 +1583,6 @@
     <t>85-100, 89/90-97/98(n)</t>
   </si>
   <si>
-    <t>pl. Stary Rynek</t>
-  </si>
-  <si>
     <t>15-166</t>
   </si>
   <si>
@@ -1613,18 +1601,6 @@
     <t>Zamek Wawel</t>
   </si>
   <si>
-    <t>57-400</t>
-  </si>
-  <si>
-    <t>Nowa Ruda</t>
-  </si>
-  <si>
-    <t>Góra Anny</t>
-  </si>
-  <si>
-    <t>kłodzki</t>
-  </si>
-  <si>
     <t>08-101</t>
   </si>
   <si>
@@ -1673,9 +1649,6 @@
     <t>Przejście Słodowe</t>
   </si>
   <si>
-    <t>Góry św. Anny</t>
-  </si>
-  <si>
     <t>66-006</t>
   </si>
   <si>
@@ -1694,9 +1667,6 @@
     <t>inne Zamek Wawel</t>
   </si>
   <si>
-    <t>inne Góra Anny</t>
-  </si>
-  <si>
     <t>inne Dom Kolejowy</t>
   </si>
   <si>
@@ -1715,16 +1685,25 @@
     <t>inne Przejście Słodowe</t>
   </si>
   <si>
-    <t>inne Góry św. Anny</t>
-  </si>
-  <si>
     <t>inne Ochla-Osiedle Dworskie</t>
   </si>
   <si>
-    <t>inne Racula-Im. Rodła</t>
-  </si>
-  <si>
     <t>Inne - nie ulica</t>
+  </si>
+  <si>
+    <t>rynek Stary Rynek</t>
+  </si>
+  <si>
+    <t>To jest rynek a nie ulica</t>
+  </si>
+  <si>
+    <t>Racula-Rodła</t>
+  </si>
+  <si>
+    <t>pl. św. papieża Jana Pawła II</t>
+  </si>
+  <si>
+    <t>Katedralny Imienia Jana Pawła II Pl.</t>
   </si>
 </sst>
 </file>
@@ -2603,12 +2582,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I425"/>
+  <dimension ref="A1:I421"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="52.85546875" customWidth="1"/>
     <col min="4" max="4" width="45.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6154,7 +6133,7 @@
         <v>17</v>
       </c>
       <c r="I174" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
@@ -10734,13 +10713,13 @@
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B382" t="s">
         <v>68</v>
       </c>
       <c r="D382" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E382" t="s">
         <v>11</v>
@@ -10755,18 +10734,18 @@
         <v>70</v>
       </c>
       <c r="I382" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B383" t="s">
         <v>68</v>
       </c>
       <c r="D383" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E383" t="s">
         <v>11</v>
@@ -10786,13 +10765,13 @@
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B384" t="s">
         <v>68</v>
       </c>
       <c r="D384" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E384" t="s">
         <v>11</v>
@@ -10812,13 +10791,13 @@
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B385" t="s">
         <v>68</v>
       </c>
       <c r="D385" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E385" t="s">
         <v>11</v>
@@ -10838,13 +10817,13 @@
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B386" t="s">
         <v>68</v>
       </c>
       <c r="D386" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E386" t="s">
         <v>11</v>
@@ -10859,18 +10838,18 @@
         <v>70</v>
       </c>
       <c r="I386" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B387" t="s">
         <v>68</v>
       </c>
       <c r="D387" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E387" t="s">
         <v>11</v>
@@ -10890,48 +10869,48 @@
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
+        <v>494</v>
+      </c>
+      <c r="B388" t="s">
         <v>495</v>
       </c>
-      <c r="B388" t="s">
+      <c r="D388" t="s">
         <v>496</v>
       </c>
-      <c r="D388" t="s">
+      <c r="E388" t="s">
+        <v>11</v>
+      </c>
+      <c r="F388" t="s">
+        <v>495</v>
+      </c>
+      <c r="G388" t="s">
         <v>497</v>
-      </c>
-      <c r="E388" t="s">
-        <v>11</v>
-      </c>
-      <c r="F388" t="s">
-        <v>496</v>
-      </c>
-      <c r="G388" t="s">
-        <v>498</v>
       </c>
       <c r="H388" t="s">
         <v>352</v>
       </c>
       <c r="I388" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
+        <v>494</v>
+      </c>
+      <c r="B389" t="s">
         <v>495</v>
       </c>
-      <c r="B389" t="s">
-        <v>496</v>
-      </c>
       <c r="D389" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E389" t="s">
         <v>11</v>
       </c>
       <c r="F389" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G389" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H389" t="s">
         <v>352</v>
@@ -10951,7 +10930,7 @@
         <v>11</v>
       </c>
       <c r="D390" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E390" t="s">
         <v>11</v>
@@ -10966,7 +10945,7 @@
         <v>42</v>
       </c>
       <c r="I390" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.25">
@@ -10980,7 +10959,7 @@
         <v>11</v>
       </c>
       <c r="D391" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E391" t="s">
         <v>11</v>
@@ -11000,28 +10979,28 @@
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
+        <v>504</v>
+      </c>
+      <c r="B392" t="s">
         <v>505</v>
       </c>
-      <c r="B392" t="s">
+      <c r="C392" t="s">
+        <v>11</v>
+      </c>
+      <c r="D392" t="s">
         <v>506</v>
       </c>
-      <c r="C392" t="s">
-        <v>11</v>
-      </c>
-      <c r="D392" t="s">
+      <c r="E392" t="s">
+        <v>11</v>
+      </c>
+      <c r="F392" t="s">
+        <v>505</v>
+      </c>
+      <c r="G392" t="s">
+        <v>505</v>
+      </c>
+      <c r="H392" t="s">
         <v>507</v>
-      </c>
-      <c r="E392" t="s">
-        <v>11</v>
-      </c>
-      <c r="F392" t="s">
-        <v>506</v>
-      </c>
-      <c r="G392" t="s">
-        <v>506</v>
-      </c>
-      <c r="H392" t="s">
-        <v>508</v>
       </c>
       <c r="I392" t="s">
         <v>330</v>
@@ -11029,28 +11008,28 @@
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
+        <v>504</v>
+      </c>
+      <c r="B393" t="s">
         <v>505</v>
       </c>
-      <c r="B393" t="s">
-        <v>506</v>
-      </c>
       <c r="C393" t="s">
         <v>11</v>
       </c>
       <c r="D393" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E393" t="s">
         <v>11</v>
       </c>
       <c r="F393" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G393" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H393" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="I393" t="s">
         <v>11</v>
@@ -11063,11 +11042,8 @@
       <c r="B394" t="s">
         <v>68</v>
       </c>
-      <c r="C394" t="s">
-        <v>510</v>
-      </c>
       <c r="D394" t="s">
-        <v>483</v>
+        <v>556</v>
       </c>
       <c r="E394" t="s">
         <v>11</v>
@@ -11082,7 +11058,7 @@
         <v>70</v>
       </c>
       <c r="I394" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.25">
@@ -11093,7 +11069,7 @@
         <v>68</v>
       </c>
       <c r="D395" t="s">
-        <v>511</v>
+        <v>555</v>
       </c>
       <c r="E395" t="s">
         <v>11</v>
@@ -11113,48 +11089,48 @@
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
+        <v>510</v>
+      </c>
+      <c r="B396" t="s">
+        <v>511</v>
+      </c>
+      <c r="D396" t="s">
+        <v>512</v>
+      </c>
+      <c r="E396" t="s">
         <v>513</v>
       </c>
-      <c r="B396" t="s">
-        <v>514</v>
-      </c>
-      <c r="D396" t="s">
-        <v>515</v>
-      </c>
-      <c r="E396" t="s">
-        <v>516</v>
-      </c>
       <c r="F396" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="G396" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H396" t="s">
         <v>42</v>
       </c>
       <c r="I396" t="s">
-        <v>481</v>
+        <v>553</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
+        <v>510</v>
+      </c>
+      <c r="B397" t="s">
+        <v>511</v>
+      </c>
+      <c r="D397" t="s">
+        <v>552</v>
+      </c>
+      <c r="E397" t="s">
         <v>513</v>
       </c>
-      <c r="B397" t="s">
-        <v>514</v>
-      </c>
-      <c r="D397" t="s">
-        <v>519</v>
-      </c>
-      <c r="E397" t="s">
-        <v>516</v>
-      </c>
       <c r="F397" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="G397" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H397" t="s">
         <v>42</v>
@@ -11165,48 +11141,48 @@
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B398" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D398" t="s">
+        <v>512</v>
+      </c>
+      <c r="E398" t="s">
         <v>515</v>
       </c>
-      <c r="E398" t="s">
-        <v>518</v>
-      </c>
       <c r="F398" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="G398" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H398" t="s">
         <v>42</v>
       </c>
       <c r="I398" t="s">
-        <v>481</v>
+        <v>553</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B399" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D399" t="s">
-        <v>519</v>
+        <v>552</v>
       </c>
       <c r="E399" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F399" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="G399" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H399" t="s">
         <v>42</v>
@@ -11217,7 +11193,7 @@
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B400" t="s">
         <v>9</v>
@@ -11226,7 +11202,7 @@
         <v>11</v>
       </c>
       <c r="D400" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E400" t="s">
         <v>11</v>
@@ -11241,12 +11217,12 @@
         <v>12</v>
       </c>
       <c r="I400" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B401" t="s">
         <v>9</v>
@@ -11255,7 +11231,7 @@
         <v>11</v>
       </c>
       <c r="D401" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="E401" t="s">
         <v>11</v>
@@ -11284,7 +11260,7 @@
         <v>11</v>
       </c>
       <c r="D402" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E402" t="s">
         <v>11</v>
@@ -11299,7 +11275,7 @@
         <v>22</v>
       </c>
       <c r="I402" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
@@ -11313,7 +11289,7 @@
         <v>11</v>
       </c>
       <c r="D403" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="E403" t="s">
         <v>11</v>
@@ -11333,16 +11309,16 @@
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B404" t="s">
         <v>350</v>
       </c>
       <c r="C404" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D404" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E404" t="s">
         <v>11</v>
@@ -11357,21 +11333,21 @@
         <v>352</v>
       </c>
       <c r="I404" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B405" t="s">
         <v>350</v>
       </c>
       <c r="C405" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D405" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="E405" t="s">
         <v>11</v>
@@ -11391,57 +11367,57 @@
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B406" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C406" t="s">
         <v>11</v>
       </c>
       <c r="D406" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E406" t="s">
         <v>11</v>
       </c>
       <c r="F406" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="G406" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="H406" t="s">
-        <v>348</v>
+        <v>17</v>
       </c>
       <c r="I406" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B407" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C407" t="s">
         <v>11</v>
       </c>
       <c r="D407" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="E407" t="s">
         <v>11</v>
       </c>
       <c r="F407" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="G407" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="H407" t="s">
-        <v>348</v>
+        <v>17</v>
       </c>
       <c r="I407" t="s">
         <v>11</v>
@@ -11449,57 +11425,57 @@
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B408" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C408" t="s">
         <v>11</v>
       </c>
       <c r="D408" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="E408" t="s">
         <v>11</v>
       </c>
       <c r="F408" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="G408" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="H408" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I408" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B409" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C409" t="s">
         <v>11</v>
       </c>
       <c r="D409" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="E409" t="s">
         <v>11</v>
       </c>
       <c r="F409" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="G409" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="H409" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I409" t="s">
         <v>11</v>
@@ -11507,57 +11483,57 @@
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B410" t="s">
-        <v>534</v>
+        <v>123</v>
       </c>
       <c r="C410" t="s">
         <v>11</v>
       </c>
       <c r="D410" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E410" t="s">
         <v>11</v>
       </c>
       <c r="F410" t="s">
-        <v>534</v>
+        <v>123</v>
       </c>
       <c r="G410" t="s">
-        <v>534</v>
+        <v>123</v>
       </c>
       <c r="H410" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I410" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B411" t="s">
-        <v>534</v>
+        <v>123</v>
       </c>
       <c r="C411" t="s">
         <v>11</v>
       </c>
       <c r="D411" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="E411" t="s">
         <v>11</v>
       </c>
       <c r="F411" t="s">
-        <v>534</v>
+        <v>123</v>
       </c>
       <c r="G411" t="s">
-        <v>534</v>
+        <v>123</v>
       </c>
       <c r="H411" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I411" t="s">
         <v>11</v>
@@ -11565,7 +11541,7 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="B412" t="s">
         <v>123</v>
@@ -11574,7 +11550,7 @@
         <v>11</v>
       </c>
       <c r="D412" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="E412" t="s">
         <v>11</v>
@@ -11589,12 +11565,12 @@
         <v>27</v>
       </c>
       <c r="I412" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="B413" t="s">
         <v>123</v>
@@ -11603,7 +11579,7 @@
         <v>11</v>
       </c>
       <c r="D413" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="E413" t="s">
         <v>11</v>
@@ -11623,57 +11599,57 @@
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B414" t="s">
-        <v>123</v>
+        <v>533</v>
       </c>
       <c r="C414" t="s">
         <v>11</v>
       </c>
       <c r="D414" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="E414" t="s">
         <v>11</v>
       </c>
       <c r="F414" t="s">
-        <v>123</v>
+        <v>533</v>
       </c>
       <c r="G414" t="s">
-        <v>123</v>
+        <v>533</v>
       </c>
       <c r="H414" t="s">
-        <v>27</v>
+        <v>352</v>
       </c>
       <c r="I414" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B415" t="s">
-        <v>123</v>
+        <v>533</v>
       </c>
       <c r="C415" t="s">
         <v>11</v>
       </c>
       <c r="D415" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="E415" t="s">
         <v>11</v>
       </c>
       <c r="F415" t="s">
-        <v>123</v>
+        <v>533</v>
       </c>
       <c r="G415" t="s">
-        <v>123</v>
+        <v>533</v>
       </c>
       <c r="H415" t="s">
-        <v>27</v>
+        <v>352</v>
       </c>
       <c r="I415" t="s">
         <v>11</v>
@@ -11681,57 +11657,57 @@
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="B416" t="s">
-        <v>541</v>
+        <v>364</v>
       </c>
       <c r="C416" t="s">
-        <v>11</v>
+        <v>536</v>
       </c>
       <c r="D416" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="E416" t="s">
         <v>11</v>
       </c>
       <c r="F416" t="s">
-        <v>541</v>
+        <v>364</v>
       </c>
       <c r="G416" t="s">
-        <v>541</v>
+        <v>364</v>
       </c>
       <c r="H416" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="I416" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="B417" t="s">
-        <v>541</v>
+        <v>364</v>
       </c>
       <c r="C417" t="s">
-        <v>11</v>
+        <v>536</v>
       </c>
       <c r="D417" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="E417" t="s">
         <v>11</v>
       </c>
       <c r="F417" t="s">
-        <v>541</v>
+        <v>364</v>
       </c>
       <c r="G417" t="s">
-        <v>541</v>
+        <v>364</v>
       </c>
       <c r="H417" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="I417" t="s">
         <v>11</v>
@@ -11739,57 +11715,57 @@
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B418" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="C418" t="s">
-        <v>544</v>
+        <v>11</v>
       </c>
       <c r="D418" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E418" t="s">
         <v>11</v>
       </c>
       <c r="F418" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="G418" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="H418" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="I418" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B419" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="C419" t="s">
-        <v>544</v>
+        <v>11</v>
       </c>
       <c r="D419" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="E419" t="s">
         <v>11</v>
       </c>
       <c r="F419" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="G419" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="H419" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="I419" t="s">
         <v>11</v>
@@ -11797,175 +11773,59 @@
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B420" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C420" t="s">
         <v>11</v>
       </c>
       <c r="D420" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E420" t="s">
         <v>11</v>
       </c>
       <c r="F420" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G420" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H420" t="s">
-        <v>22</v>
+        <v>304</v>
       </c>
       <c r="I420" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B421" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C421" t="s">
         <v>11</v>
       </c>
       <c r="D421" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E421" t="s">
         <v>11</v>
       </c>
       <c r="F421" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G421" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H421" t="s">
-        <v>22</v>
+        <v>304</v>
       </c>
       <c r="I421" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A422" t="s">
-        <v>547</v>
-      </c>
-      <c r="B422" t="s">
-        <v>303</v>
-      </c>
-      <c r="C422" t="s">
-        <v>11</v>
-      </c>
-      <c r="D422" t="s">
-        <v>548</v>
-      </c>
-      <c r="E422" t="s">
-        <v>11</v>
-      </c>
-      <c r="F422" t="s">
-        <v>303</v>
-      </c>
-      <c r="G422" t="s">
-        <v>303</v>
-      </c>
-      <c r="H422" t="s">
-        <v>304</v>
-      </c>
-      <c r="I422" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A423" t="s">
-        <v>547</v>
-      </c>
-      <c r="B423" t="s">
-        <v>303</v>
-      </c>
-      <c r="C423" t="s">
-        <v>11</v>
-      </c>
-      <c r="D423" t="s">
-        <v>561</v>
-      </c>
-      <c r="E423" t="s">
-        <v>11</v>
-      </c>
-      <c r="F423" t="s">
-        <v>303</v>
-      </c>
-      <c r="G423" t="s">
-        <v>303</v>
-      </c>
-      <c r="H423" t="s">
-        <v>304</v>
-      </c>
-      <c r="I423" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A424" t="s">
-        <v>305</v>
-      </c>
-      <c r="B424" t="s">
-        <v>303</v>
-      </c>
-      <c r="C424" t="s">
-        <v>11</v>
-      </c>
-      <c r="D424" t="s">
-        <v>549</v>
-      </c>
-      <c r="E424" t="s">
-        <v>11</v>
-      </c>
-      <c r="F424" t="s">
-        <v>303</v>
-      </c>
-      <c r="G424" t="s">
-        <v>303</v>
-      </c>
-      <c r="H424" t="s">
-        <v>304</v>
-      </c>
-      <c r="I424" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A425" t="s">
-        <v>305</v>
-      </c>
-      <c r="B425" t="s">
-        <v>303</v>
-      </c>
-      <c r="C425" t="s">
-        <v>11</v>
-      </c>
-      <c r="D425" t="s">
-        <v>562</v>
-      </c>
-      <c r="E425" t="s">
-        <v>11</v>
-      </c>
-      <c r="F425" t="s">
-        <v>303</v>
-      </c>
-      <c r="G425" t="s">
-        <v>303</v>
-      </c>
-      <c r="H425" t="s">
-        <v>304</v>
-      </c>
-      <c r="I425" t="s">
         <v>11</v>
       </c>
     </row>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4C7654-8187-473C-B4C9-8024AA076269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6570AD58-AC18-4AF3-9DA2-BC4996F9BFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2797" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="556">
   <si>
     <t>Kod</t>
   </si>
@@ -1062,9 +1062,6 @@
   </si>
   <si>
     <t>ONZ Rondo</t>
-  </si>
-  <si>
-    <t>Rondo ONZ</t>
   </si>
   <si>
     <t>89-600</t>
@@ -2582,7 +2579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I421"/>
+  <dimension ref="A1:I419"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -2604,7 +2601,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -3672,7 +3669,7 @@
         <v>70</v>
       </c>
       <c r="I46" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -3683,7 +3680,7 @@
         <v>68</v>
       </c>
       <c r="D47" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E47" t="s">
         <v>11</v>
@@ -5755,7 +5752,7 @@
         <v>127</v>
       </c>
       <c r="D156" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E156" t="s">
         <v>11</v>
@@ -6044,7 +6041,7 @@
         <v>17</v>
       </c>
       <c r="I170" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
@@ -6055,7 +6052,7 @@
         <v>127</v>
       </c>
       <c r="D171" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E171" t="s">
         <v>11</v>
@@ -6133,7 +6130,7 @@
         <v>17</v>
       </c>
       <c r="I174" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
@@ -6144,7 +6141,7 @@
         <v>127</v>
       </c>
       <c r="D175" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E175" t="s">
         <v>11</v>
@@ -6196,7 +6193,7 @@
         <v>127</v>
       </c>
       <c r="D177" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="E177" t="s">
         <v>11</v>
@@ -8486,22 +8483,22 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
+        <v>343</v>
+      </c>
+      <c r="B296" t="s">
         <v>344</v>
       </c>
-      <c r="B296" t="s">
+      <c r="D296" t="s">
         <v>345</v>
       </c>
-      <c r="D296" t="s">
+      <c r="E296" t="s">
+        <v>11</v>
+      </c>
+      <c r="F296" t="s">
+        <v>344</v>
+      </c>
+      <c r="G296" t="s">
         <v>346</v>
-      </c>
-      <c r="E296" t="s">
-        <v>11</v>
-      </c>
-      <c r="F296" t="s">
-        <v>345</v>
-      </c>
-      <c r="G296" t="s">
-        <v>347</v>
       </c>
       <c r="H296" t="s">
         <v>16</v>
@@ -8512,22 +8509,22 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
+        <v>343</v>
+      </c>
+      <c r="B297" t="s">
         <v>344</v>
       </c>
-      <c r="B297" t="s">
-        <v>345</v>
-      </c>
       <c r="D297" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E297" t="s">
         <v>11</v>
       </c>
       <c r="F297" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G297" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H297" t="s">
         <v>16</v>
@@ -8538,25 +8535,25 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
+        <v>348</v>
+      </c>
+      <c r="B298" t="s">
         <v>349</v>
       </c>
-      <c r="B298" t="s">
+      <c r="D298" t="s">
         <v>350</v>
       </c>
-      <c r="D298" t="s">
+      <c r="E298" t="s">
+        <v>11</v>
+      </c>
+      <c r="F298" t="s">
+        <v>349</v>
+      </c>
+      <c r="G298" t="s">
+        <v>349</v>
+      </c>
+      <c r="H298" t="s">
         <v>351</v>
-      </c>
-      <c r="E298" t="s">
-        <v>11</v>
-      </c>
-      <c r="F298" t="s">
-        <v>350</v>
-      </c>
-      <c r="G298" t="s">
-        <v>350</v>
-      </c>
-      <c r="H298" t="s">
-        <v>352</v>
       </c>
       <c r="I298" t="s">
         <v>330</v>
@@ -8564,25 +8561,25 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
+        <v>348</v>
+      </c>
+      <c r="B299" t="s">
         <v>349</v>
       </c>
-      <c r="B299" t="s">
-        <v>350</v>
-      </c>
       <c r="D299" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E299" t="s">
         <v>11</v>
       </c>
       <c r="F299" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G299" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H299" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I299" t="s">
         <v>11</v>
@@ -8590,25 +8587,25 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
+        <v>352</v>
+      </c>
+      <c r="B300" t="s">
+        <v>349</v>
+      </c>
+      <c r="D300" t="s">
         <v>353</v>
       </c>
-      <c r="B300" t="s">
-        <v>350</v>
-      </c>
-      <c r="D300" t="s">
-        <v>354</v>
-      </c>
       <c r="E300" t="s">
         <v>11</v>
       </c>
       <c r="F300" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G300" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H300" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I300" t="s">
         <v>330</v>
@@ -8616,25 +8613,25 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B301" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D301" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E301" t="s">
         <v>11</v>
       </c>
       <c r="F301" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G301" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H301" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I301" t="s">
         <v>11</v>
@@ -8642,25 +8639,25 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
+        <v>354</v>
+      </c>
+      <c r="B302" t="s">
         <v>355</v>
       </c>
-      <c r="B302" t="s">
+      <c r="D302" t="s">
+        <v>376</v>
+      </c>
+      <c r="E302" t="s">
+        <v>11</v>
+      </c>
+      <c r="F302" t="s">
+        <v>355</v>
+      </c>
+      <c r="G302" t="s">
         <v>356</v>
       </c>
-      <c r="D302" t="s">
-        <v>377</v>
-      </c>
-      <c r="E302" t="s">
-        <v>11</v>
-      </c>
-      <c r="F302" t="s">
-        <v>356</v>
-      </c>
-      <c r="G302" t="s">
+      <c r="H302" t="s">
         <v>357</v>
-      </c>
-      <c r="H302" t="s">
-        <v>358</v>
       </c>
       <c r="I302" t="s">
         <v>330</v>
@@ -8668,25 +8665,25 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
+        <v>354</v>
+      </c>
+      <c r="B303" t="s">
         <v>355</v>
       </c>
-      <c r="B303" t="s">
+      <c r="D303" t="s">
+        <v>372</v>
+      </c>
+      <c r="E303" t="s">
+        <v>11</v>
+      </c>
+      <c r="F303" t="s">
+        <v>355</v>
+      </c>
+      <c r="G303" t="s">
         <v>356</v>
       </c>
-      <c r="D303" t="s">
-        <v>373</v>
-      </c>
-      <c r="E303" t="s">
-        <v>11</v>
-      </c>
-      <c r="F303" t="s">
-        <v>356</v>
-      </c>
-      <c r="G303" t="s">
+      <c r="H303" t="s">
         <v>357</v>
-      </c>
-      <c r="H303" t="s">
-        <v>358</v>
       </c>
       <c r="I303" t="s">
         <v>11</v>
@@ -8700,7 +8697,7 @@
         <v>123</v>
       </c>
       <c r="D304" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E304" t="s">
         <v>11</v>
@@ -8746,22 +8743,22 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
+        <v>358</v>
+      </c>
+      <c r="B306" t="s">
         <v>359</v>
       </c>
-      <c r="B306" t="s">
+      <c r="D306" t="s">
         <v>360</v>
       </c>
-      <c r="D306" t="s">
-        <v>361</v>
-      </c>
       <c r="E306" t="s">
         <v>11</v>
       </c>
       <c r="F306" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G306" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H306" t="s">
         <v>22</v>
@@ -8772,22 +8769,22 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
+        <v>358</v>
+      </c>
+      <c r="B307" t="s">
         <v>359</v>
       </c>
-      <c r="B307" t="s">
-        <v>360</v>
-      </c>
       <c r="D307" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E307" t="s">
         <v>11</v>
       </c>
       <c r="F307" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G307" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H307" t="s">
         <v>22</v>
@@ -8798,13 +8795,13 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
+        <v>361</v>
+      </c>
+      <c r="B308" t="s">
+        <v>127</v>
+      </c>
+      <c r="D308" t="s">
         <v>362</v>
-      </c>
-      <c r="B308" t="s">
-        <v>127</v>
-      </c>
-      <c r="D308" t="s">
-        <v>363</v>
       </c>
       <c r="E308" t="s">
         <v>11</v>
@@ -8824,13 +8821,13 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B309" t="s">
         <v>127</v>
       </c>
       <c r="D309" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E309" t="s">
         <v>11</v>
@@ -8850,198 +8847,198 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>193</v>
+        <v>364</v>
       </c>
       <c r="B310" t="s">
-        <v>127</v>
+        <v>363</v>
       </c>
       <c r="D310" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="E310" t="s">
         <v>11</v>
       </c>
       <c r="F310" t="s">
-        <v>127</v>
+        <v>363</v>
       </c>
       <c r="G310" t="s">
-        <v>127</v>
+        <v>363</v>
       </c>
       <c r="H310" t="s">
-        <v>17</v>
+        <v>347</v>
       </c>
       <c r="I310" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>193</v>
+        <v>364</v>
       </c>
       <c r="B311" t="s">
-        <v>127</v>
+        <v>363</v>
       </c>
       <c r="D311" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E311" t="s">
         <v>11</v>
       </c>
       <c r="F311" t="s">
-        <v>127</v>
+        <v>363</v>
       </c>
       <c r="G311" t="s">
-        <v>127</v>
+        <v>363</v>
       </c>
       <c r="H311" t="s">
-        <v>17</v>
-      </c>
-      <c r="I311" t="s">
-        <v>11</v>
+        <v>347</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B312" t="s">
-        <v>364</v>
+        <v>378</v>
+      </c>
+      <c r="C312" t="s">
+        <v>382</v>
       </c>
       <c r="D312" t="s">
-        <v>366</v>
-      </c>
-      <c r="E312" t="s">
-        <v>11</v>
+        <v>379</v>
       </c>
       <c r="F312" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="G312" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="H312" t="s">
-        <v>348</v>
+        <v>17</v>
       </c>
       <c r="I312" t="s">
-        <v>330</v>
+        <v>383</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B313" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="D313" t="s">
-        <v>367</v>
-      </c>
-      <c r="E313" t="s">
-        <v>11</v>
+        <v>379</v>
       </c>
       <c r="F313" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="G313" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="H313" t="s">
-        <v>348</v>
+        <v>17</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B314" t="s">
-        <v>379</v>
-      </c>
-      <c r="C314" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D314" t="s">
-        <v>380</v>
+        <v>386</v>
+      </c>
+      <c r="E314" t="s">
+        <v>11</v>
       </c>
       <c r="F314" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G314" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H314" t="s">
-        <v>17</v>
+        <v>387</v>
       </c>
       <c r="I314" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B315" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D315" t="s">
-        <v>380</v>
+        <v>389</v>
+      </c>
+      <c r="E315" t="s">
+        <v>11</v>
       </c>
       <c r="F315" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G315" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H315" t="s">
-        <v>17</v>
+        <v>387</v>
+      </c>
+      <c r="I315" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B316" t="s">
-        <v>386</v>
+        <v>123</v>
       </c>
       <c r="D316" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E316" t="s">
-        <v>11</v>
+        <v>392</v>
       </c>
       <c r="F316" t="s">
-        <v>386</v>
+        <v>123</v>
       </c>
       <c r="G316" t="s">
-        <v>386</v>
+        <v>123</v>
       </c>
       <c r="H316" t="s">
+        <v>27</v>
+      </c>
+      <c r="I316" t="s">
         <v>388</v>
-      </c>
-      <c r="I316" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B317" t="s">
-        <v>386</v>
+        <v>123</v>
       </c>
       <c r="D317" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="E317" t="s">
-        <v>11</v>
+        <v>392</v>
       </c>
       <c r="F317" t="s">
-        <v>386</v>
+        <v>123</v>
       </c>
       <c r="G317" t="s">
-        <v>386</v>
+        <v>123</v>
       </c>
       <c r="H317" t="s">
-        <v>388</v>
+        <v>27</v>
       </c>
       <c r="I317" t="s">
         <v>11</v>
@@ -9049,16 +9046,16 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
+        <v>393</v>
+      </c>
+      <c r="B318" t="s">
+        <v>123</v>
+      </c>
+      <c r="D318" t="s">
         <v>391</v>
       </c>
-      <c r="B318" t="s">
-        <v>123</v>
-      </c>
-      <c r="D318" t="s">
-        <v>392</v>
-      </c>
       <c r="E318" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F318" t="s">
         <v>123</v>
@@ -9070,21 +9067,21 @@
         <v>27</v>
       </c>
       <c r="I318" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B319" t="s">
         <v>123</v>
       </c>
       <c r="D319" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E319" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F319" t="s">
         <v>123</v>
@@ -9101,16 +9098,16 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B320" t="s">
         <v>123</v>
       </c>
       <c r="D320" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E320" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F320" t="s">
         <v>123</v>
@@ -9122,21 +9119,21 @@
         <v>27</v>
       </c>
       <c r="I320" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B321" t="s">
         <v>123</v>
       </c>
       <c r="D321" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E321" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F321" t="s">
         <v>123</v>
@@ -9153,16 +9150,16 @@
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B322" t="s">
         <v>123</v>
       </c>
       <c r="D322" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E322" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F322" t="s">
         <v>123</v>
@@ -9174,21 +9171,21 @@
         <v>27</v>
       </c>
       <c r="I322" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B323" t="s">
         <v>123</v>
       </c>
       <c r="D323" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E323" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F323" t="s">
         <v>123</v>
@@ -9205,16 +9202,16 @@
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B324" t="s">
         <v>123</v>
       </c>
       <c r="D324" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E324" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F324" t="s">
         <v>123</v>
@@ -9226,21 +9223,21 @@
         <v>27</v>
       </c>
       <c r="I324" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B325" t="s">
         <v>123</v>
       </c>
       <c r="D325" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E325" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F325" t="s">
         <v>123</v>
@@ -9257,16 +9254,16 @@
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B326" t="s">
         <v>123</v>
       </c>
       <c r="D326" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E326" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F326" t="s">
         <v>123</v>
@@ -9278,21 +9275,21 @@
         <v>27</v>
       </c>
       <c r="I326" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B327" t="s">
         <v>123</v>
       </c>
       <c r="D327" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E327" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F327" t="s">
         <v>123</v>
@@ -9309,16 +9306,16 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B328" t="s">
         <v>123</v>
       </c>
       <c r="D328" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E328" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F328" t="s">
         <v>123</v>
@@ -9330,21 +9327,21 @@
         <v>27</v>
       </c>
       <c r="I328" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B329" t="s">
         <v>123</v>
       </c>
       <c r="D329" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E329" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F329" t="s">
         <v>123</v>
@@ -9361,16 +9358,16 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B330" t="s">
         <v>123</v>
       </c>
       <c r="D330" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E330" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F330" t="s">
         <v>123</v>
@@ -9382,21 +9379,21 @@
         <v>27</v>
       </c>
       <c r="I330" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B331" t="s">
         <v>123</v>
       </c>
       <c r="D331" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E331" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F331" t="s">
         <v>123</v>
@@ -9413,16 +9410,16 @@
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B332" t="s">
         <v>123</v>
       </c>
       <c r="D332" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E332" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F332" t="s">
         <v>123</v>
@@ -9434,21 +9431,21 @@
         <v>27</v>
       </c>
       <c r="I332" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B333" t="s">
         <v>123</v>
       </c>
       <c r="D333" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E333" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F333" t="s">
         <v>123</v>
@@ -9465,16 +9462,16 @@
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B334" t="s">
         <v>123</v>
       </c>
       <c r="D334" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E334" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F334" t="s">
         <v>123</v>
@@ -9486,21 +9483,21 @@
         <v>27</v>
       </c>
       <c r="I334" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B335" t="s">
         <v>123</v>
       </c>
       <c r="D335" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E335" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F335" t="s">
         <v>123</v>
@@ -9517,16 +9514,16 @@
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B336" t="s">
         <v>123</v>
       </c>
       <c r="D336" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E336" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F336" t="s">
         <v>123</v>
@@ -9538,21 +9535,21 @@
         <v>27</v>
       </c>
       <c r="I336" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B337" t="s">
         <v>123</v>
       </c>
       <c r="D337" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E337" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F337" t="s">
         <v>123</v>
@@ -9569,16 +9566,16 @@
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B338" t="s">
         <v>123</v>
       </c>
       <c r="D338" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E338" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F338" t="s">
         <v>123</v>
@@ -9590,21 +9587,21 @@
         <v>27</v>
       </c>
       <c r="I338" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B339" t="s">
         <v>123</v>
       </c>
       <c r="D339" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E339" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F339" t="s">
         <v>123</v>
@@ -9621,16 +9618,16 @@
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B340" t="s">
         <v>123</v>
       </c>
       <c r="D340" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E340" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F340" t="s">
         <v>123</v>
@@ -9642,21 +9639,21 @@
         <v>27</v>
       </c>
       <c r="I340" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B341" t="s">
         <v>123</v>
       </c>
       <c r="D341" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E341" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F341" t="s">
         <v>123</v>
@@ -9673,16 +9670,16 @@
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B342" t="s">
         <v>123</v>
       </c>
       <c r="D342" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E342" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F342" t="s">
         <v>123</v>
@@ -9694,21 +9691,21 @@
         <v>27</v>
       </c>
       <c r="I342" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B343" t="s">
         <v>123</v>
       </c>
       <c r="D343" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E343" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F343" t="s">
         <v>123</v>
@@ -9725,51 +9722,51 @@
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B344" t="s">
-        <v>123</v>
+        <v>421</v>
       </c>
       <c r="D344" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="E344" t="s">
-        <v>419</v>
+        <v>11</v>
       </c>
       <c r="F344" t="s">
-        <v>123</v>
+        <v>421</v>
       </c>
       <c r="G344" t="s">
-        <v>123</v>
+        <v>421</v>
       </c>
       <c r="H344" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I344" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B345" t="s">
-        <v>123</v>
+        <v>421</v>
       </c>
       <c r="D345" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E345" t="s">
-        <v>419</v>
+        <v>11</v>
       </c>
       <c r="F345" t="s">
-        <v>123</v>
+        <v>421</v>
       </c>
       <c r="G345" t="s">
-        <v>123</v>
+        <v>421</v>
       </c>
       <c r="H345" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I345" t="s">
         <v>11</v>
@@ -9777,51 +9774,51 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B346" t="s">
-        <v>422</v>
+        <v>9</v>
       </c>
       <c r="D346" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E346" t="s">
         <v>11</v>
       </c>
       <c r="F346" t="s">
-        <v>422</v>
+        <v>9</v>
       </c>
       <c r="G346" t="s">
-        <v>422</v>
+        <v>9</v>
       </c>
       <c r="H346" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I346" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B347" t="s">
-        <v>422</v>
+        <v>9</v>
       </c>
       <c r="D347" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E347" t="s">
         <v>11</v>
       </c>
       <c r="F347" t="s">
-        <v>422</v>
+        <v>9</v>
       </c>
       <c r="G347" t="s">
-        <v>422</v>
+        <v>9</v>
       </c>
       <c r="H347" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I347" t="s">
         <v>11</v>
@@ -9829,51 +9826,51 @@
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B348" t="s">
-        <v>9</v>
+        <v>428</v>
       </c>
       <c r="D348" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E348" t="s">
         <v>11</v>
       </c>
       <c r="F348" t="s">
-        <v>9</v>
+        <v>428</v>
       </c>
       <c r="G348" t="s">
-        <v>9</v>
+        <v>430</v>
       </c>
       <c r="H348" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I348" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B349" t="s">
-        <v>9</v>
+        <v>428</v>
       </c>
       <c r="D349" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="E349" t="s">
         <v>11</v>
       </c>
       <c r="F349" t="s">
-        <v>9</v>
+        <v>428</v>
       </c>
       <c r="G349" t="s">
-        <v>9</v>
+        <v>430</v>
       </c>
       <c r="H349" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I349" t="s">
         <v>11</v>
@@ -9881,36 +9878,36 @@
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B350" t="s">
-        <v>429</v>
+        <v>60</v>
       </c>
       <c r="D350" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E350" t="s">
         <v>11</v>
       </c>
       <c r="F350" t="s">
-        <v>429</v>
+        <v>60</v>
       </c>
       <c r="G350" t="s">
-        <v>431</v>
+        <v>60</v>
       </c>
       <c r="H350" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I350" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B351" t="s">
-        <v>429</v>
+        <v>60</v>
       </c>
       <c r="D351" t="s">
         <v>438</v>
@@ -9919,13 +9916,13 @@
         <v>11</v>
       </c>
       <c r="F351" t="s">
-        <v>429</v>
+        <v>60</v>
       </c>
       <c r="G351" t="s">
-        <v>431</v>
+        <v>60</v>
       </c>
       <c r="H351" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I351" t="s">
         <v>11</v>
@@ -9933,13 +9930,13 @@
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B352" t="s">
         <v>60</v>
       </c>
       <c r="D352" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E352" t="s">
         <v>11</v>
@@ -9954,12 +9951,12 @@
         <v>57</v>
       </c>
       <c r="I352" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B353" t="s">
         <v>60</v>
@@ -9985,13 +9982,13 @@
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B354" t="s">
         <v>60</v>
       </c>
       <c r="D354" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E354" t="s">
         <v>11</v>
@@ -10006,12 +10003,12 @@
         <v>57</v>
       </c>
       <c r="I354" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B355" t="s">
         <v>60</v>
@@ -10037,51 +10034,51 @@
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="B356" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="D356" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E356" t="s">
         <v>11</v>
       </c>
       <c r="F356" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="G356" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="H356" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="I356" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="B357" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="D357" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E357" t="s">
         <v>11</v>
       </c>
       <c r="F357" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="G357" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="H357" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="I357" t="s">
         <v>11</v>
@@ -10089,13 +10086,13 @@
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B358" t="s">
         <v>123</v>
       </c>
       <c r="D358" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E358" t="s">
         <v>11</v>
@@ -10110,12 +10107,12 @@
         <v>27</v>
       </c>
       <c r="I358" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B359" t="s">
         <v>123</v>
@@ -10141,51 +10138,51 @@
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B360" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D360" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E360" t="s">
         <v>11</v>
       </c>
       <c r="F360" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G360" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H360" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I360" t="s">
-        <v>389</v>
+        <v>311</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B361" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D361" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E361" t="s">
         <v>11</v>
       </c>
       <c r="F361" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G361" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H361" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I361" t="s">
         <v>11</v>
@@ -10193,13 +10190,13 @@
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B362" t="s">
         <v>127</v>
       </c>
       <c r="D362" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E362" t="s">
         <v>11</v>
@@ -10214,18 +10211,18 @@
         <v>17</v>
       </c>
       <c r="I362" t="s">
-        <v>311</v>
+        <v>388</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B363" t="s">
         <v>127</v>
       </c>
       <c r="D363" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E363" t="s">
         <v>11</v>
@@ -10245,13 +10242,13 @@
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>452</v>
+        <v>176</v>
       </c>
       <c r="B364" t="s">
         <v>127</v>
       </c>
       <c r="D364" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E364" t="s">
         <v>11</v>
@@ -10266,18 +10263,18 @@
         <v>17</v>
       </c>
       <c r="I364" t="s">
-        <v>389</v>
+        <v>458</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>452</v>
+        <v>176</v>
       </c>
       <c r="B365" t="s">
         <v>127</v>
       </c>
       <c r="D365" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E365" t="s">
         <v>11</v>
@@ -10297,13 +10294,13 @@
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>176</v>
+        <v>455</v>
       </c>
       <c r="B366" t="s">
         <v>127</v>
       </c>
       <c r="D366" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E366" t="s">
         <v>11</v>
@@ -10318,18 +10315,18 @@
         <v>17</v>
       </c>
       <c r="I366" t="s">
-        <v>459</v>
+        <v>388</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>176</v>
+        <v>455</v>
       </c>
       <c r="B367" t="s">
         <v>127</v>
       </c>
       <c r="D367" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E367" t="s">
         <v>11</v>
@@ -10349,13 +10346,13 @@
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B368" t="s">
         <v>127</v>
       </c>
       <c r="D368" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E368" t="s">
         <v>11</v>
@@ -10370,18 +10367,18 @@
         <v>17</v>
       </c>
       <c r="I368" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B369" t="s">
         <v>127</v>
       </c>
       <c r="D369" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E369" t="s">
         <v>11</v>
@@ -10401,13 +10398,13 @@
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B370" t="s">
         <v>127</v>
       </c>
       <c r="D370" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E370" t="s">
         <v>11</v>
@@ -10422,18 +10419,18 @@
         <v>17</v>
       </c>
       <c r="I370" t="s">
-        <v>389</v>
+        <v>466</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B371" t="s">
         <v>127</v>
       </c>
       <c r="D371" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E371" t="s">
         <v>11</v>
@@ -10453,16 +10450,16 @@
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="B372" t="s">
         <v>127</v>
       </c>
       <c r="D372" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E372" t="s">
-        <v>11</v>
+        <v>474</v>
       </c>
       <c r="F372" t="s">
         <v>127</v>
@@ -10474,21 +10471,21 @@
         <v>17</v>
       </c>
       <c r="I372" t="s">
-        <v>467</v>
+        <v>388</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="B373" t="s">
         <v>127</v>
       </c>
       <c r="D373" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="E373" t="s">
-        <v>11</v>
+        <v>474</v>
       </c>
       <c r="F373" t="s">
         <v>127</v>
@@ -10505,16 +10502,16 @@
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B374" t="s">
         <v>127</v>
       </c>
       <c r="D374" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E374" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F374" t="s">
         <v>127</v>
@@ -10526,21 +10523,21 @@
         <v>17</v>
       </c>
       <c r="I374" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
+        <v>473</v>
+      </c>
+      <c r="B375" t="s">
+        <v>127</v>
+      </c>
+      <c r="D375" t="s">
         <v>476</v>
       </c>
-      <c r="B375" t="s">
-        <v>127</v>
-      </c>
-      <c r="D375" t="s">
-        <v>477</v>
-      </c>
       <c r="E375" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F375" t="s">
         <v>127</v>
@@ -10557,16 +10554,16 @@
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B376" t="s">
         <v>127</v>
       </c>
       <c r="D376" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E376" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F376" t="s">
         <v>127</v>
@@ -10578,21 +10575,21 @@
         <v>17</v>
       </c>
       <c r="I376" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B377" t="s">
         <v>127</v>
       </c>
       <c r="D377" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E377" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F377" t="s">
         <v>127</v>
@@ -10609,16 +10606,16 @@
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B378" t="s">
         <v>127</v>
       </c>
       <c r="D378" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E378" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F378" t="s">
         <v>127</v>
@@ -10630,21 +10627,21 @@
         <v>17</v>
       </c>
       <c r="I378" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B379" t="s">
         <v>127</v>
       </c>
       <c r="D379" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E379" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F379" t="s">
         <v>127</v>
@@ -10661,51 +10658,51 @@
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="B380" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="D380" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="E380" t="s">
-        <v>468</v>
+        <v>11</v>
       </c>
       <c r="F380" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="G380" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="H380" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="I380" t="s">
-        <v>389</v>
+        <v>489</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="B381" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="D381" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="E381" t="s">
-        <v>468</v>
+        <v>11</v>
       </c>
       <c r="F381" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="G381" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="H381" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="I381" t="s">
         <v>11</v>
@@ -10713,13 +10710,13 @@
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B382" t="s">
         <v>68</v>
       </c>
       <c r="D382" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E382" t="s">
         <v>11</v>
@@ -10734,18 +10731,18 @@
         <v>70</v>
       </c>
       <c r="I382" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B383" t="s">
         <v>68</v>
       </c>
       <c r="D383" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E383" t="s">
         <v>11</v>
@@ -10765,13 +10762,13 @@
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B384" t="s">
         <v>68</v>
       </c>
       <c r="D384" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E384" t="s">
         <v>11</v>
@@ -10786,12 +10783,12 @@
         <v>70</v>
       </c>
       <c r="I384" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B385" t="s">
         <v>68</v>
@@ -10817,51 +10814,51 @@
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B386" t="s">
-        <v>68</v>
+        <v>494</v>
       </c>
       <c r="D386" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="E386" t="s">
         <v>11</v>
       </c>
       <c r="F386" t="s">
-        <v>68</v>
+        <v>494</v>
       </c>
       <c r="G386" t="s">
-        <v>68</v>
+        <v>496</v>
       </c>
       <c r="H386" t="s">
-        <v>70</v>
+        <v>351</v>
       </c>
       <c r="I386" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B387" t="s">
-        <v>68</v>
+        <v>494</v>
       </c>
       <c r="D387" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E387" t="s">
         <v>11</v>
       </c>
       <c r="F387" t="s">
-        <v>68</v>
+        <v>494</v>
       </c>
       <c r="G387" t="s">
-        <v>68</v>
+        <v>496</v>
       </c>
       <c r="H387" t="s">
-        <v>70</v>
+        <v>351</v>
       </c>
       <c r="I387" t="s">
         <v>11</v>
@@ -10869,51 +10866,57 @@
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>494</v>
+        <v>43</v>
       </c>
       <c r="B388" t="s">
-        <v>495</v>
+        <v>40</v>
+      </c>
+      <c r="C388" t="s">
+        <v>11</v>
       </c>
       <c r="D388" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E388" t="s">
         <v>11</v>
       </c>
       <c r="F388" t="s">
-        <v>495</v>
+        <v>40</v>
       </c>
       <c r="G388" t="s">
-        <v>497</v>
+        <v>40</v>
       </c>
       <c r="H388" t="s">
-        <v>352</v>
+        <v>42</v>
       </c>
       <c r="I388" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>494</v>
+        <v>43</v>
       </c>
       <c r="B389" t="s">
-        <v>495</v>
+        <v>40</v>
+      </c>
+      <c r="C389" t="s">
+        <v>11</v>
       </c>
       <c r="D389" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E389" t="s">
         <v>11</v>
       </c>
       <c r="F389" t="s">
-        <v>495</v>
+        <v>40</v>
       </c>
       <c r="G389" t="s">
-        <v>497</v>
+        <v>40</v>
       </c>
       <c r="H389" t="s">
-        <v>352</v>
+        <v>42</v>
       </c>
       <c r="I389" t="s">
         <v>11</v>
@@ -10921,57 +10924,57 @@
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>43</v>
+        <v>503</v>
       </c>
       <c r="B390" t="s">
-        <v>40</v>
+        <v>504</v>
       </c>
       <c r="C390" t="s">
         <v>11</v>
       </c>
       <c r="D390" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E390" t="s">
         <v>11</v>
       </c>
       <c r="F390" t="s">
-        <v>40</v>
+        <v>504</v>
       </c>
       <c r="G390" t="s">
-        <v>40</v>
+        <v>504</v>
       </c>
       <c r="H390" t="s">
-        <v>42</v>
+        <v>506</v>
       </c>
       <c r="I390" t="s">
-        <v>503</v>
+        <v>330</v>
       </c>
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>43</v>
+        <v>503</v>
       </c>
       <c r="B391" t="s">
-        <v>40</v>
+        <v>504</v>
       </c>
       <c r="C391" t="s">
         <v>11</v>
       </c>
       <c r="D391" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E391" t="s">
         <v>11</v>
       </c>
       <c r="F391" t="s">
-        <v>40</v>
+        <v>504</v>
       </c>
       <c r="G391" t="s">
-        <v>40</v>
+        <v>504</v>
       </c>
       <c r="H391" t="s">
-        <v>42</v>
+        <v>506</v>
       </c>
       <c r="I391" t="s">
         <v>11</v>
@@ -10979,57 +10982,51 @@
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="B392" t="s">
-        <v>505</v>
-      </c>
-      <c r="C392" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="D392" t="s">
-        <v>506</v>
+        <v>555</v>
       </c>
       <c r="E392" t="s">
         <v>11</v>
       </c>
       <c r="F392" t="s">
-        <v>505</v>
+        <v>68</v>
       </c>
       <c r="G392" t="s">
-        <v>505</v>
+        <v>68</v>
       </c>
       <c r="H392" t="s">
-        <v>507</v>
+        <v>70</v>
       </c>
       <c r="I392" t="s">
-        <v>330</v>
+        <v>508</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="B393" t="s">
-        <v>505</v>
-      </c>
-      <c r="C393" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="D393" t="s">
-        <v>508</v>
+        <v>554</v>
       </c>
       <c r="E393" t="s">
         <v>11</v>
       </c>
       <c r="F393" t="s">
-        <v>505</v>
+        <v>68</v>
       </c>
       <c r="G393" t="s">
-        <v>505</v>
+        <v>68</v>
       </c>
       <c r="H393" t="s">
-        <v>507</v>
+        <v>70</v>
       </c>
       <c r="I393" t="s">
         <v>11</v>
@@ -11037,51 +11034,51 @@
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>482</v>
+        <v>509</v>
       </c>
       <c r="B394" t="s">
-        <v>68</v>
+        <v>510</v>
       </c>
       <c r="D394" t="s">
-        <v>556</v>
+        <v>511</v>
       </c>
       <c r="E394" t="s">
-        <v>11</v>
+        <v>512</v>
       </c>
       <c r="F394" t="s">
-        <v>68</v>
+        <v>510</v>
       </c>
       <c r="G394" t="s">
-        <v>68</v>
+        <v>510</v>
       </c>
       <c r="H394" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="I394" t="s">
-        <v>509</v>
+        <v>552</v>
       </c>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>482</v>
+        <v>509</v>
       </c>
       <c r="B395" t="s">
-        <v>68</v>
+        <v>510</v>
       </c>
       <c r="D395" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E395" t="s">
-        <v>11</v>
+        <v>512</v>
       </c>
       <c r="F395" t="s">
-        <v>68</v>
+        <v>510</v>
       </c>
       <c r="G395" t="s">
-        <v>68</v>
+        <v>510</v>
       </c>
       <c r="H395" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="I395" t="s">
         <v>11</v>
@@ -11089,48 +11086,48 @@
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
+        <v>513</v>
+      </c>
+      <c r="B396" t="s">
         <v>510</v>
       </c>
-      <c r="B396" t="s">
+      <c r="D396" t="s">
         <v>511</v>
       </c>
-      <c r="D396" t="s">
-        <v>512</v>
-      </c>
       <c r="E396" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F396" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G396" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H396" t="s">
         <v>42</v>
       </c>
       <c r="I396" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
+        <v>513</v>
+      </c>
+      <c r="B397" t="s">
         <v>510</v>
       </c>
-      <c r="B397" t="s">
-        <v>511</v>
-      </c>
       <c r="D397" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E397" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F397" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G397" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H397" t="s">
         <v>42</v>
@@ -11141,51 +11138,57 @@
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B398" t="s">
-        <v>511</v>
+        <v>9</v>
+      </c>
+      <c r="C398" t="s">
+        <v>11</v>
       </c>
       <c r="D398" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E398" t="s">
-        <v>515</v>
+        <v>11</v>
       </c>
       <c r="F398" t="s">
-        <v>511</v>
+        <v>9</v>
       </c>
       <c r="G398" t="s">
-        <v>511</v>
+        <v>9</v>
       </c>
       <c r="H398" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="I398" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B399" t="s">
-        <v>511</v>
+        <v>9</v>
+      </c>
+      <c r="C399" t="s">
+        <v>11</v>
       </c>
       <c r="D399" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="E399" t="s">
-        <v>515</v>
+        <v>11</v>
       </c>
       <c r="F399" t="s">
-        <v>511</v>
+        <v>9</v>
       </c>
       <c r="G399" t="s">
-        <v>511</v>
+        <v>9</v>
       </c>
       <c r="H399" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="I399" t="s">
         <v>11</v>
@@ -11193,10 +11196,10 @@
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>516</v>
+        <v>420</v>
       </c>
       <c r="B400" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
       <c r="C400" t="s">
         <v>11</v>
@@ -11208,24 +11211,24 @@
         <v>11</v>
       </c>
       <c r="F400" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
       <c r="G400" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
       <c r="H400" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I400" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>516</v>
+        <v>420</v>
       </c>
       <c r="B401" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
       <c r="C401" t="s">
         <v>11</v>
@@ -11237,13 +11240,13 @@
         <v>11</v>
       </c>
       <c r="F401" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
       <c r="G401" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
       <c r="H401" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I401" t="s">
         <v>11</v>
@@ -11251,42 +11254,42 @@
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>421</v>
+        <v>518</v>
       </c>
       <c r="B402" t="s">
-        <v>422</v>
+        <v>349</v>
       </c>
       <c r="C402" t="s">
-        <v>11</v>
+        <v>519</v>
       </c>
       <c r="D402" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E402" t="s">
         <v>11</v>
       </c>
       <c r="F402" t="s">
-        <v>422</v>
+        <v>349</v>
       </c>
       <c r="G402" t="s">
-        <v>422</v>
+        <v>349</v>
       </c>
       <c r="H402" t="s">
-        <v>22</v>
+        <v>351</v>
       </c>
       <c r="I402" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>421</v>
+        <v>518</v>
       </c>
       <c r="B403" t="s">
-        <v>422</v>
+        <v>349</v>
       </c>
       <c r="C403" t="s">
-        <v>11</v>
+        <v>519</v>
       </c>
       <c r="D403" t="s">
         <v>542</v>
@@ -11295,13 +11298,13 @@
         <v>11</v>
       </c>
       <c r="F403" t="s">
-        <v>422</v>
+        <v>349</v>
       </c>
       <c r="G403" t="s">
-        <v>422</v>
+        <v>349</v>
       </c>
       <c r="H403" t="s">
-        <v>22</v>
+        <v>351</v>
       </c>
       <c r="I403" t="s">
         <v>11</v>
@@ -11309,42 +11312,42 @@
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B404" t="s">
-        <v>350</v>
+        <v>522</v>
       </c>
       <c r="C404" t="s">
-        <v>520</v>
+        <v>11</v>
       </c>
       <c r="D404" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E404" t="s">
         <v>11</v>
       </c>
       <c r="F404" t="s">
-        <v>350</v>
+        <v>522</v>
       </c>
       <c r="G404" t="s">
-        <v>350</v>
+        <v>522</v>
       </c>
       <c r="H404" t="s">
-        <v>352</v>
+        <v>17</v>
       </c>
       <c r="I404" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B405" t="s">
-        <v>350</v>
+        <v>522</v>
       </c>
       <c r="C405" t="s">
-        <v>520</v>
+        <v>11</v>
       </c>
       <c r="D405" t="s">
         <v>543</v>
@@ -11353,13 +11356,13 @@
         <v>11</v>
       </c>
       <c r="F405" t="s">
-        <v>350</v>
+        <v>522</v>
       </c>
       <c r="G405" t="s">
-        <v>350</v>
+        <v>522</v>
       </c>
       <c r="H405" t="s">
-        <v>352</v>
+        <v>17</v>
       </c>
       <c r="I405" t="s">
         <v>11</v>
@@ -11367,39 +11370,39 @@
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B406" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C406" t="s">
         <v>11</v>
       </c>
       <c r="D406" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E406" t="s">
         <v>11</v>
       </c>
       <c r="F406" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G406" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H406" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I406" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B407" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C407" t="s">
         <v>11</v>
@@ -11411,13 +11414,13 @@
         <v>11</v>
       </c>
       <c r="F407" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G407" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H407" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I407" t="s">
         <v>11</v>
@@ -11425,39 +11428,39 @@
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B408" t="s">
-        <v>526</v>
+        <v>123</v>
       </c>
       <c r="C408" t="s">
         <v>11</v>
       </c>
       <c r="D408" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E408" t="s">
         <v>11</v>
       </c>
       <c r="F408" t="s">
-        <v>526</v>
+        <v>123</v>
       </c>
       <c r="G408" t="s">
-        <v>526</v>
+        <v>123</v>
       </c>
       <c r="H408" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I408" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B409" t="s">
-        <v>526</v>
+        <v>123</v>
       </c>
       <c r="C409" t="s">
         <v>11</v>
@@ -11469,13 +11472,13 @@
         <v>11</v>
       </c>
       <c r="F409" t="s">
-        <v>526</v>
+        <v>123</v>
       </c>
       <c r="G409" t="s">
-        <v>526</v>
+        <v>123</v>
       </c>
       <c r="H409" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I409" t="s">
         <v>11</v>
@@ -11483,7 +11486,7 @@
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B410" t="s">
         <v>123</v>
@@ -11492,7 +11495,7 @@
         <v>11</v>
       </c>
       <c r="D410" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E410" t="s">
         <v>11</v>
@@ -11507,12 +11510,12 @@
         <v>27</v>
       </c>
       <c r="I410" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B411" t="s">
         <v>123</v>
@@ -11541,39 +11544,39 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B412" t="s">
-        <v>123</v>
+        <v>532</v>
       </c>
       <c r="C412" t="s">
         <v>11</v>
       </c>
       <c r="D412" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E412" t="s">
         <v>11</v>
       </c>
       <c r="F412" t="s">
-        <v>123</v>
+        <v>532</v>
       </c>
       <c r="G412" t="s">
-        <v>123</v>
+        <v>532</v>
       </c>
       <c r="H412" t="s">
-        <v>27</v>
+        <v>351</v>
       </c>
       <c r="I412" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B413" t="s">
-        <v>123</v>
+        <v>532</v>
       </c>
       <c r="C413" t="s">
         <v>11</v>
@@ -11585,13 +11588,13 @@
         <v>11</v>
       </c>
       <c r="F413" t="s">
-        <v>123</v>
+        <v>532</v>
       </c>
       <c r="G413" t="s">
-        <v>123</v>
+        <v>532</v>
       </c>
       <c r="H413" t="s">
-        <v>27</v>
+        <v>351</v>
       </c>
       <c r="I413" t="s">
         <v>11</v>
@@ -11599,42 +11602,42 @@
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B414" t="s">
-        <v>533</v>
+        <v>363</v>
       </c>
       <c r="C414" t="s">
-        <v>11</v>
+        <v>535</v>
       </c>
       <c r="D414" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E414" t="s">
         <v>11</v>
       </c>
       <c r="F414" t="s">
-        <v>533</v>
+        <v>363</v>
       </c>
       <c r="G414" t="s">
-        <v>533</v>
+        <v>363</v>
       </c>
       <c r="H414" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="I414" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B415" t="s">
-        <v>533</v>
+        <v>363</v>
       </c>
       <c r="C415" t="s">
-        <v>11</v>
+        <v>535</v>
       </c>
       <c r="D415" t="s">
         <v>548</v>
@@ -11643,13 +11646,13 @@
         <v>11</v>
       </c>
       <c r="F415" t="s">
-        <v>533</v>
+        <v>363</v>
       </c>
       <c r="G415" t="s">
-        <v>533</v>
+        <v>363</v>
       </c>
       <c r="H415" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="I415" t="s">
         <v>11</v>
@@ -11657,42 +11660,42 @@
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B416" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="C416" t="s">
-        <v>536</v>
+        <v>11</v>
       </c>
       <c r="D416" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E416" t="s">
         <v>11</v>
       </c>
       <c r="F416" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="G416" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="H416" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="I416" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B417" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="C417" t="s">
-        <v>536</v>
+        <v>11</v>
       </c>
       <c r="D417" t="s">
         <v>549</v>
@@ -11701,13 +11704,13 @@
         <v>11</v>
       </c>
       <c r="F417" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="G417" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
       <c r="H417" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="I417" t="s">
         <v>11</v>
@@ -11715,7 +11718,7 @@
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>538</v>
+        <v>305</v>
       </c>
       <c r="B418" t="s">
         <v>303</v>
@@ -11739,12 +11742,12 @@
         <v>304</v>
       </c>
       <c r="I418" t="s">
-        <v>551</v>
+        <v>330</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>538</v>
+        <v>305</v>
       </c>
       <c r="B419" t="s">
         <v>303</v>
@@ -11753,7 +11756,7 @@
         <v>11</v>
       </c>
       <c r="D419" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E419" t="s">
         <v>11</v>
@@ -11768,64 +11771,6 @@
         <v>304</v>
       </c>
       <c r="I419" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
-        <v>305</v>
-      </c>
-      <c r="B420" t="s">
-        <v>303</v>
-      </c>
-      <c r="C420" t="s">
-        <v>11</v>
-      </c>
-      <c r="D420" t="s">
-        <v>540</v>
-      </c>
-      <c r="E420" t="s">
-        <v>11</v>
-      </c>
-      <c r="F420" t="s">
-        <v>303</v>
-      </c>
-      <c r="G420" t="s">
-        <v>303</v>
-      </c>
-      <c r="H420" t="s">
-        <v>304</v>
-      </c>
-      <c r="I420" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A421" t="s">
-        <v>305</v>
-      </c>
-      <c r="B421" t="s">
-        <v>303</v>
-      </c>
-      <c r="C421" t="s">
-        <v>11</v>
-      </c>
-      <c r="D421" t="s">
-        <v>554</v>
-      </c>
-      <c r="E421" t="s">
-        <v>11</v>
-      </c>
-      <c r="F421" t="s">
-        <v>303</v>
-      </c>
-      <c r="G421" t="s">
-        <v>303</v>
-      </c>
-      <c r="H421" t="s">
-        <v>304</v>
-      </c>
-      <c r="I421" t="s">
         <v>11</v>
       </c>
     </row>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6570AD58-AC18-4AF3-9DA2-BC4996F9BFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64BB26C-196E-45F3-B7A2-47416B245E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2781" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2871" uniqueCount="572">
   <si>
     <t>Kod</t>
   </si>
@@ -1701,6 +1701,54 @@
   </si>
   <si>
     <t>Katedralny Imienia Jana Pawła II Pl.</t>
+  </si>
+  <si>
+    <t>05-120</t>
+  </si>
+  <si>
+    <t>Legionowo</t>
+  </si>
+  <si>
+    <t>biskupa. Władysława Bandurskiego</t>
+  </si>
+  <si>
+    <t>legionowski</t>
+  </si>
+  <si>
+    <t>biskupa Władysława Bandurskiego</t>
+  </si>
+  <si>
+    <t>15-196</t>
+  </si>
+  <si>
+    <t>Krzysztofa-Kamila Baczyńskiego</t>
+  </si>
+  <si>
+    <t>Krzysztofa Kamila Baczyńskiego</t>
+  </si>
+  <si>
+    <t>Stanisława Ignacego Witkiewicza /Witkacego/</t>
+  </si>
+  <si>
+    <t>Stanisława Ignacego Witkiewicza</t>
+  </si>
+  <si>
+    <t>44-105</t>
+  </si>
+  <si>
+    <t>Ton'ego Halika</t>
+  </si>
+  <si>
+    <t>Tony'ego Halika</t>
+  </si>
+  <si>
+    <t>25-368</t>
+  </si>
+  <si>
+    <t>Wojciecha Bartosa Głowackiego</t>
+  </si>
+  <si>
+    <t>Wojciecha Bartosza Głowackiego</t>
   </si>
 </sst>
 </file>
@@ -2579,7 +2627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I419"/>
+  <dimension ref="A1:I429"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -11774,6 +11822,296 @@
         <v>11</v>
       </c>
     </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>556</v>
+      </c>
+      <c r="B420" t="s">
+        <v>557</v>
+      </c>
+      <c r="C420" t="s">
+        <v>11</v>
+      </c>
+      <c r="D420" t="s">
+        <v>558</v>
+      </c>
+      <c r="E420" t="s">
+        <v>11</v>
+      </c>
+      <c r="F420" t="s">
+        <v>557</v>
+      </c>
+      <c r="G420" t="s">
+        <v>559</v>
+      </c>
+      <c r="H420" t="s">
+        <v>17</v>
+      </c>
+      <c r="I420" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>556</v>
+      </c>
+      <c r="B421" t="s">
+        <v>557</v>
+      </c>
+      <c r="C421" t="s">
+        <v>11</v>
+      </c>
+      <c r="D421" t="s">
+        <v>560</v>
+      </c>
+      <c r="E421" t="s">
+        <v>11</v>
+      </c>
+      <c r="F421" t="s">
+        <v>557</v>
+      </c>
+      <c r="G421" t="s">
+        <v>559</v>
+      </c>
+      <c r="H421" t="s">
+        <v>17</v>
+      </c>
+      <c r="I421" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>561</v>
+      </c>
+      <c r="B422" t="s">
+        <v>9</v>
+      </c>
+      <c r="C422" t="s">
+        <v>11</v>
+      </c>
+      <c r="D422" t="s">
+        <v>562</v>
+      </c>
+      <c r="E422" t="s">
+        <v>11</v>
+      </c>
+      <c r="F422" t="s">
+        <v>9</v>
+      </c>
+      <c r="G422" t="s">
+        <v>9</v>
+      </c>
+      <c r="H422" t="s">
+        <v>12</v>
+      </c>
+      <c r="I422" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>561</v>
+      </c>
+      <c r="B423" t="s">
+        <v>9</v>
+      </c>
+      <c r="C423" t="s">
+        <v>11</v>
+      </c>
+      <c r="D423" t="s">
+        <v>563</v>
+      </c>
+      <c r="E423" t="s">
+        <v>11</v>
+      </c>
+      <c r="F423" t="s">
+        <v>9</v>
+      </c>
+      <c r="G423" t="s">
+        <v>9</v>
+      </c>
+      <c r="H423" t="s">
+        <v>12</v>
+      </c>
+      <c r="I423" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>43</v>
+      </c>
+      <c r="B424" t="s">
+        <v>40</v>
+      </c>
+      <c r="C424" t="s">
+        <v>11</v>
+      </c>
+      <c r="D424" t="s">
+        <v>564</v>
+      </c>
+      <c r="E424" t="s">
+        <v>11</v>
+      </c>
+      <c r="F424" t="s">
+        <v>40</v>
+      </c>
+      <c r="G424" t="s">
+        <v>40</v>
+      </c>
+      <c r="H424" t="s">
+        <v>42</v>
+      </c>
+      <c r="I424" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>43</v>
+      </c>
+      <c r="B425" t="s">
+        <v>40</v>
+      </c>
+      <c r="C425" t="s">
+        <v>11</v>
+      </c>
+      <c r="D425" t="s">
+        <v>565</v>
+      </c>
+      <c r="E425" t="s">
+        <v>11</v>
+      </c>
+      <c r="F425" t="s">
+        <v>40</v>
+      </c>
+      <c r="G425" t="s">
+        <v>40</v>
+      </c>
+      <c r="H425" t="s">
+        <v>42</v>
+      </c>
+      <c r="I425" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>566</v>
+      </c>
+      <c r="B426" t="s">
+        <v>33</v>
+      </c>
+      <c r="C426" t="s">
+        <v>11</v>
+      </c>
+      <c r="D426" t="s">
+        <v>567</v>
+      </c>
+      <c r="E426" t="s">
+        <v>11</v>
+      </c>
+      <c r="F426" t="s">
+        <v>33</v>
+      </c>
+      <c r="G426" t="s">
+        <v>33</v>
+      </c>
+      <c r="H426" t="s">
+        <v>22</v>
+      </c>
+      <c r="I426" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>566</v>
+      </c>
+      <c r="B427" t="s">
+        <v>33</v>
+      </c>
+      <c r="C427" t="s">
+        <v>11</v>
+      </c>
+      <c r="D427" t="s">
+        <v>568</v>
+      </c>
+      <c r="E427" t="s">
+        <v>11</v>
+      </c>
+      <c r="F427" t="s">
+        <v>33</v>
+      </c>
+      <c r="G427" t="s">
+        <v>33</v>
+      </c>
+      <c r="H427" t="s">
+        <v>22</v>
+      </c>
+      <c r="I427" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>569</v>
+      </c>
+      <c r="B428" t="s">
+        <v>504</v>
+      </c>
+      <c r="C428" t="s">
+        <v>11</v>
+      </c>
+      <c r="D428" t="s">
+        <v>570</v>
+      </c>
+      <c r="E428" t="s">
+        <v>11</v>
+      </c>
+      <c r="F428" t="s">
+        <v>504</v>
+      </c>
+      <c r="G428" t="s">
+        <v>504</v>
+      </c>
+      <c r="H428" t="s">
+        <v>506</v>
+      </c>
+      <c r="I428" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>569</v>
+      </c>
+      <c r="B429" t="s">
+        <v>504</v>
+      </c>
+      <c r="C429" t="s">
+        <v>11</v>
+      </c>
+      <c r="D429" t="s">
+        <v>571</v>
+      </c>
+      <c r="E429" t="s">
+        <v>11</v>
+      </c>
+      <c r="F429" t="s">
+        <v>504</v>
+      </c>
+      <c r="G429" t="s">
+        <v>504</v>
+      </c>
+      <c r="H429" t="s">
+        <v>506</v>
+      </c>
+      <c r="I429" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64BB26C-196E-45F3-B7A2-47416B245E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EA9AB2-26AD-4AD8-AF5C-C4B2C81F2541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2871" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2907" uniqueCount="583">
   <si>
     <t>Kod</t>
   </si>
@@ -1652,9 +1652,6 @@
     <t>Ochla-Osiedle Dworskie</t>
   </si>
   <si>
-    <t>Racula-Im. Rodła</t>
-  </si>
-  <si>
     <t>inne Bagnówka-Kolonia</t>
   </si>
   <si>
@@ -1694,9 +1691,6 @@
     <t>To jest rynek a nie ulica</t>
   </si>
   <si>
-    <t>Racula-Rodła</t>
-  </si>
-  <si>
     <t>pl. św. papieża Jana Pawła II</t>
   </si>
   <si>
@@ -1749,6 +1743,45 @@
   </si>
   <si>
     <t>Wojciecha Bartosza Głowackiego</t>
+  </si>
+  <si>
+    <t>41-300</t>
+  </si>
+  <si>
+    <t>Dąbrowa Górnicza</t>
+  </si>
+  <si>
+    <t>Porozumienia Dąbrowskiego 1980</t>
+  </si>
+  <si>
+    <t>1, 2-4(p)</t>
+  </si>
+  <si>
+    <t>02-704</t>
+  </si>
+  <si>
+    <t>Mokotów</t>
+  </si>
+  <si>
+    <t>Piłsudskiego Fort</t>
+  </si>
+  <si>
+    <t>Fort Piłsudskiego</t>
+  </si>
+  <si>
+    <t>31-303</t>
+  </si>
+  <si>
+    <t>Kraków-Krowodrza</t>
+  </si>
+  <si>
+    <t>Józefa Chełmońskiego Deptak</t>
+  </si>
+  <si>
+    <t>Deptak Józefa Chełmońskiego</t>
+  </si>
+  <si>
+    <t>Porozumienia Dąbrowskiego 1980 roku</t>
   </si>
 </sst>
 </file>
@@ -2627,7 +2660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I429"/>
+  <dimension ref="A1:I433"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -11036,7 +11069,7 @@
         <v>68</v>
       </c>
       <c r="D392" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E392" t="s">
         <v>11</v>
@@ -11062,7 +11095,7 @@
         <v>68</v>
       </c>
       <c r="D393" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E393" t="s">
         <v>11</v>
@@ -11103,7 +11136,7 @@
         <v>42</v>
       </c>
       <c r="I394" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.25">
@@ -11114,7 +11147,7 @@
         <v>510</v>
       </c>
       <c r="D395" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E395" t="s">
         <v>512</v>
@@ -11155,7 +11188,7 @@
         <v>42</v>
       </c>
       <c r="I396" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.25">
@@ -11166,7 +11199,7 @@
         <v>510</v>
       </c>
       <c r="D397" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E397" t="s">
         <v>514</v>
@@ -11210,7 +11243,7 @@
         <v>12</v>
       </c>
       <c r="I398" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.25">
@@ -11224,7 +11257,7 @@
         <v>11</v>
       </c>
       <c r="D399" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E399" t="s">
         <v>11</v>
@@ -11268,7 +11301,7 @@
         <v>22</v>
       </c>
       <c r="I400" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.25">
@@ -11282,7 +11315,7 @@
         <v>11</v>
       </c>
       <c r="D401" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E401" t="s">
         <v>11</v>
@@ -11326,7 +11359,7 @@
         <v>351</v>
       </c>
       <c r="I402" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
@@ -11340,7 +11373,7 @@
         <v>519</v>
       </c>
       <c r="D403" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E403" t="s">
         <v>11</v>
@@ -11384,7 +11417,7 @@
         <v>17</v>
       </c>
       <c r="I404" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.25">
@@ -11398,7 +11431,7 @@
         <v>11</v>
       </c>
       <c r="D405" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E405" t="s">
         <v>11</v>
@@ -11442,7 +11475,7 @@
         <v>22</v>
       </c>
       <c r="I406" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.25">
@@ -11456,7 +11489,7 @@
         <v>11</v>
       </c>
       <c r="D407" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E407" t="s">
         <v>11</v>
@@ -11500,7 +11533,7 @@
         <v>27</v>
       </c>
       <c r="I408" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.25">
@@ -11514,7 +11547,7 @@
         <v>11</v>
       </c>
       <c r="D409" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E409" t="s">
         <v>11</v>
@@ -11558,7 +11591,7 @@
         <v>27</v>
       </c>
       <c r="I410" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.25">
@@ -11572,7 +11605,7 @@
         <v>11</v>
       </c>
       <c r="D411" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E411" t="s">
         <v>11</v>
@@ -11616,7 +11649,7 @@
         <v>351</v>
       </c>
       <c r="I412" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.25">
@@ -11630,7 +11663,7 @@
         <v>11</v>
       </c>
       <c r="D413" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E413" t="s">
         <v>11</v>
@@ -11674,7 +11707,7 @@
         <v>347</v>
       </c>
       <c r="I414" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
@@ -11688,7 +11721,7 @@
         <v>535</v>
       </c>
       <c r="D415" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E415" t="s">
         <v>11</v>
@@ -11732,7 +11765,7 @@
         <v>304</v>
       </c>
       <c r="I416" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.25">
@@ -11746,7 +11779,7 @@
         <v>11</v>
       </c>
       <c r="D417" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E417" t="s">
         <v>11</v>
@@ -11766,28 +11799,28 @@
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>305</v>
+        <v>554</v>
       </c>
       <c r="B418" t="s">
-        <v>303</v>
+        <v>555</v>
       </c>
       <c r="C418" t="s">
         <v>11</v>
       </c>
       <c r="D418" t="s">
-        <v>539</v>
+        <v>556</v>
       </c>
       <c r="E418" t="s">
         <v>11</v>
       </c>
       <c r="F418" t="s">
-        <v>303</v>
+        <v>555</v>
       </c>
       <c r="G418" t="s">
-        <v>303</v>
+        <v>557</v>
       </c>
       <c r="H418" t="s">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="I418" t="s">
         <v>330</v>
@@ -11795,28 +11828,28 @@
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>305</v>
+        <v>554</v>
       </c>
       <c r="B419" t="s">
-        <v>303</v>
+        <v>555</v>
       </c>
       <c r="C419" t="s">
         <v>11</v>
       </c>
       <c r="D419" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="E419" t="s">
         <v>11</v>
       </c>
       <c r="F419" t="s">
-        <v>303</v>
+        <v>555</v>
       </c>
       <c r="G419" t="s">
-        <v>303</v>
+        <v>557</v>
       </c>
       <c r="H419" t="s">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="I419" t="s">
         <v>11</v>
@@ -11824,28 +11857,28 @@
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B420" t="s">
-        <v>557</v>
+        <v>9</v>
       </c>
       <c r="C420" t="s">
         <v>11</v>
       </c>
       <c r="D420" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E420" t="s">
         <v>11</v>
       </c>
       <c r="F420" t="s">
-        <v>557</v>
+        <v>9</v>
       </c>
       <c r="G420" t="s">
-        <v>559</v>
+        <v>9</v>
       </c>
       <c r="H420" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I420" t="s">
         <v>330</v>
@@ -11853,28 +11886,28 @@
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B421" t="s">
-        <v>557</v>
+        <v>9</v>
       </c>
       <c r="C421" t="s">
         <v>11</v>
       </c>
       <c r="D421" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E421" t="s">
         <v>11</v>
       </c>
       <c r="F421" t="s">
-        <v>557</v>
+        <v>9</v>
       </c>
       <c r="G421" t="s">
-        <v>559</v>
+        <v>9</v>
       </c>
       <c r="H421" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I421" t="s">
         <v>11</v>
@@ -11882,10 +11915,10 @@
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>561</v>
+        <v>43</v>
       </c>
       <c r="B422" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C422" t="s">
         <v>11</v>
@@ -11897,13 +11930,13 @@
         <v>11</v>
       </c>
       <c r="F422" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="G422" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H422" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="I422" t="s">
         <v>330</v>
@@ -11911,10 +11944,10 @@
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>561</v>
+        <v>43</v>
       </c>
       <c r="B423" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C423" t="s">
         <v>11</v>
@@ -11926,13 +11959,13 @@
         <v>11</v>
       </c>
       <c r="F423" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="G423" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H423" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="I423" t="s">
         <v>11</v>
@@ -11940,28 +11973,28 @@
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>43</v>
+        <v>564</v>
       </c>
       <c r="B424" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C424" t="s">
         <v>11</v>
       </c>
       <c r="D424" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E424" t="s">
         <v>11</v>
       </c>
       <c r="F424" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G424" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H424" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="I424" t="s">
         <v>330</v>
@@ -11969,28 +12002,28 @@
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>43</v>
+        <v>564</v>
       </c>
       <c r="B425" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C425" t="s">
         <v>11</v>
       </c>
       <c r="D425" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E425" t="s">
         <v>11</v>
       </c>
       <c r="F425" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G425" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H425" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="I425" t="s">
         <v>11</v>
@@ -11998,28 +12031,28 @@
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B426" t="s">
-        <v>33</v>
+        <v>504</v>
       </c>
       <c r="C426" t="s">
         <v>11</v>
       </c>
       <c r="D426" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E426" t="s">
         <v>11</v>
       </c>
       <c r="F426" t="s">
-        <v>33</v>
+        <v>504</v>
       </c>
       <c r="G426" t="s">
-        <v>33</v>
+        <v>504</v>
       </c>
       <c r="H426" t="s">
-        <v>22</v>
+        <v>506</v>
       </c>
       <c r="I426" t="s">
         <v>330</v>
@@ -12027,28 +12060,28 @@
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B427" t="s">
-        <v>33</v>
+        <v>504</v>
       </c>
       <c r="C427" t="s">
         <v>11</v>
       </c>
       <c r="D427" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E427" t="s">
         <v>11</v>
       </c>
       <c r="F427" t="s">
-        <v>33</v>
+        <v>504</v>
       </c>
       <c r="G427" t="s">
-        <v>33</v>
+        <v>504</v>
       </c>
       <c r="H427" t="s">
-        <v>22</v>
+        <v>506</v>
       </c>
       <c r="I427" t="s">
         <v>11</v>
@@ -12056,28 +12089,28 @@
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B428" t="s">
-        <v>504</v>
+        <v>571</v>
       </c>
       <c r="C428" t="s">
         <v>11</v>
       </c>
       <c r="D428" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E428" t="s">
-        <v>11</v>
+        <v>573</v>
       </c>
       <c r="F428" t="s">
-        <v>504</v>
+        <v>571</v>
       </c>
       <c r="G428" t="s">
-        <v>504</v>
+        <v>571</v>
       </c>
       <c r="H428" t="s">
-        <v>506</v>
+        <v>22</v>
       </c>
       <c r="I428" t="s">
         <v>330</v>
@@ -12085,30 +12118,146 @@
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B429" t="s">
-        <v>504</v>
+        <v>571</v>
       </c>
       <c r="C429" t="s">
         <v>11</v>
       </c>
       <c r="D429" t="s">
+        <v>582</v>
+      </c>
+      <c r="E429" t="s">
+        <v>573</v>
+      </c>
+      <c r="F429" t="s">
         <v>571</v>
       </c>
-      <c r="E429" t="s">
-        <v>11</v>
-      </c>
-      <c r="F429" t="s">
-        <v>504</v>
-      </c>
       <c r="G429" t="s">
-        <v>504</v>
+        <v>571</v>
       </c>
       <c r="H429" t="s">
-        <v>506</v>
+        <v>22</v>
       </c>
       <c r="I429" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>574</v>
+      </c>
+      <c r="B430" t="s">
+        <v>127</v>
+      </c>
+      <c r="C430" t="s">
+        <v>575</v>
+      </c>
+      <c r="D430" t="s">
+        <v>576</v>
+      </c>
+      <c r="E430" t="s">
+        <v>11</v>
+      </c>
+      <c r="F430" t="s">
+        <v>127</v>
+      </c>
+      <c r="G430" t="s">
+        <v>127</v>
+      </c>
+      <c r="H430" t="s">
+        <v>17</v>
+      </c>
+      <c r="I430" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>574</v>
+      </c>
+      <c r="B431" t="s">
+        <v>127</v>
+      </c>
+      <c r="C431" t="s">
+        <v>575</v>
+      </c>
+      <c r="D431" t="s">
+        <v>577</v>
+      </c>
+      <c r="E431" t="s">
+        <v>11</v>
+      </c>
+      <c r="F431" t="s">
+        <v>127</v>
+      </c>
+      <c r="G431" t="s">
+        <v>127</v>
+      </c>
+      <c r="H431" t="s">
+        <v>17</v>
+      </c>
+      <c r="I431" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>578</v>
+      </c>
+      <c r="B432" t="s">
+        <v>349</v>
+      </c>
+      <c r="C432" t="s">
+        <v>579</v>
+      </c>
+      <c r="D432" t="s">
+        <v>580</v>
+      </c>
+      <c r="E432" t="s">
+        <v>11</v>
+      </c>
+      <c r="F432" t="s">
+        <v>349</v>
+      </c>
+      <c r="G432" t="s">
+        <v>349</v>
+      </c>
+      <c r="H432" t="s">
+        <v>351</v>
+      </c>
+      <c r="I432" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>578</v>
+      </c>
+      <c r="B433" t="s">
+        <v>349</v>
+      </c>
+      <c r="C433" t="s">
+        <v>579</v>
+      </c>
+      <c r="D433" t="s">
+        <v>581</v>
+      </c>
+      <c r="E433" t="s">
+        <v>11</v>
+      </c>
+      <c r="F433" t="s">
+        <v>349</v>
+      </c>
+      <c r="G433" t="s">
+        <v>349</v>
+      </c>
+      <c r="H433" t="s">
+        <v>351</v>
+      </c>
+      <c r="I433" t="s">
         <v>11</v>
       </c>
     </row>

--- a/TerytLoad/AppData/pna/KorektyPna.xlsx
+++ b/TerytLoad/AppData/pna/KorektyPna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\TerytLoad\TerytLoad\AppData\pna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EA9AB2-26AD-4AD8-AF5C-C4B2C81F2541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080D1462-4E00-4048-8B17-F2899E82A998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2907" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3164" uniqueCount="636">
   <si>
     <t>Kod</t>
   </si>
@@ -1703,9 +1703,6 @@
     <t>Legionowo</t>
   </si>
   <si>
-    <t>biskupa. Władysława Bandurskiego</t>
-  </si>
-  <si>
     <t>legionowski</t>
   </si>
   <si>
@@ -1775,13 +1772,175 @@
     <t>Kraków-Krowodrza</t>
   </si>
   <si>
-    <t>Józefa Chełmońskiego Deptak</t>
-  </si>
-  <si>
     <t>Deptak Józefa Chełmońskiego</t>
   </si>
   <si>
     <t>Porozumienia Dąbrowskiego 1980 roku</t>
+  </si>
+  <si>
+    <t>Rusznikarska - Deptak</t>
+  </si>
+  <si>
+    <t>31-261</t>
+  </si>
+  <si>
+    <t>Józefa Chełmońskiego - Deptak</t>
+  </si>
+  <si>
+    <t>Deptak Rusznikarska</t>
+  </si>
+  <si>
+    <t>59-920</t>
+  </si>
+  <si>
+    <t>Bogatynia</t>
+  </si>
+  <si>
+    <t>Prymasa Tysiąclecia Kardynała Stefana Wyszyńskiego</t>
+  </si>
+  <si>
+    <t>zgorzelecki</t>
+  </si>
+  <si>
+    <t>42-530</t>
+  </si>
+  <si>
+    <t>5-13(n)</t>
+  </si>
+  <si>
+    <t>80-338</t>
+  </si>
+  <si>
+    <t>park Oliwski Park imienia Adama Mickiewicza</t>
+  </si>
+  <si>
+    <t>67-200</t>
+  </si>
+  <si>
+    <t>Głogów</t>
+  </si>
+  <si>
+    <t>głogowski</t>
+  </si>
+  <si>
+    <t>Plac Prymasa Polski Stefana Wyszyńskiego</t>
+  </si>
+  <si>
+    <t>bpa. Władysława Bandurskiego</t>
+  </si>
+  <si>
+    <t>45-005</t>
+  </si>
+  <si>
+    <t>Opole</t>
+  </si>
+  <si>
+    <t>płk. poż. Zdzisława Filingiera</t>
+  </si>
+  <si>
+    <t>61-615</t>
+  </si>
+  <si>
+    <t>Poznań-Stare Miasto</t>
+  </si>
+  <si>
+    <t>Stanisława Grzmota-Skotnickiego</t>
+  </si>
+  <si>
+    <t>26-612</t>
+  </si>
+  <si>
+    <t>Radom</t>
+  </si>
+  <si>
+    <t>hm kpt Eugeniusza Stasieckiego</t>
+  </si>
+  <si>
+    <t>park Park Hutniczy</t>
+  </si>
+  <si>
+    <t>44-240</t>
+  </si>
+  <si>
+    <t>Żory</t>
+  </si>
+  <si>
+    <t>św. Augustyna Biskupa</t>
+  </si>
+  <si>
+    <t>Stanisława Skotnickiego</t>
+  </si>
+  <si>
+    <t>park Hutniczy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bp Augustyna </t>
+  </si>
+  <si>
+    <t>Eugeniusza Stasieckiego</t>
+  </si>
+  <si>
+    <t>Zdzisława Filingiera</t>
+  </si>
+  <si>
+    <t>Plac Stefana Wyszyńskiego</t>
+  </si>
+  <si>
+    <t>park Oliwski Adama Mickiewicza</t>
+  </si>
+  <si>
+    <t>Stefana Wyszyńskiego</t>
+  </si>
+  <si>
+    <t>Łódź-Widzew</t>
+  </si>
+  <si>
+    <t>Kazimierza</t>
+  </si>
+  <si>
+    <t>świętego Kazimierza</t>
+  </si>
+  <si>
+    <t>Ludwika</t>
+  </si>
+  <si>
+    <t>92-214</t>
+  </si>
+  <si>
+    <t>03-610</t>
+  </si>
+  <si>
+    <t>Targówek</t>
+  </si>
+  <si>
+    <t>Michała</t>
+  </si>
+  <si>
+    <t>Nie ma takiej ulicy</t>
+  </si>
+  <si>
+    <t>20-627</t>
+  </si>
+  <si>
+    <t>Pana Wołodyjowskiego</t>
+  </si>
+  <si>
+    <t>Pana Michała Wołodyjowskiego</t>
+  </si>
+  <si>
+    <t>11-041</t>
+  </si>
+  <si>
+    <t>Olsztyn</t>
+  </si>
+  <si>
+    <t>Księcia Jaremy</t>
+  </si>
+  <si>
+    <t>warmińsko-mazurskie</t>
+  </si>
+  <si>
+    <t>Księcia Jeremiego Wiśniowieckiego Jaremy</t>
   </si>
 </sst>
 </file>
@@ -2660,7 +2819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I433"/>
+  <dimension ref="A1:I463"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -11799,28 +11958,28 @@
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B418" t="s">
-        <v>555</v>
+        <v>9</v>
       </c>
       <c r="C418" t="s">
         <v>11</v>
       </c>
       <c r="D418" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E418" t="s">
         <v>11</v>
       </c>
       <c r="F418" t="s">
-        <v>555</v>
+        <v>9</v>
       </c>
       <c r="G418" t="s">
-        <v>557</v>
+        <v>9</v>
       </c>
       <c r="H418" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I418" t="s">
         <v>330</v>
@@ -11828,28 +11987,28 @@
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B419" t="s">
-        <v>555</v>
+        <v>9</v>
       </c>
       <c r="C419" t="s">
         <v>11</v>
       </c>
       <c r="D419" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E419" t="s">
         <v>11</v>
       </c>
       <c r="F419" t="s">
-        <v>555</v>
+        <v>9</v>
       </c>
       <c r="G419" t="s">
-        <v>557</v>
+        <v>9</v>
       </c>
       <c r="H419" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I419" t="s">
         <v>11</v>
@@ -11857,28 +12016,28 @@
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>559</v>
+        <v>43</v>
       </c>
       <c r="B420" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C420" t="s">
         <v>11</v>
       </c>
       <c r="D420" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E420" t="s">
         <v>11</v>
       </c>
       <c r="F420" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="G420" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H420" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="I420" t="s">
         <v>330</v>
@@ -11886,28 +12045,28 @@
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>559</v>
+        <v>43</v>
       </c>
       <c r="B421" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C421" t="s">
         <v>11</v>
       </c>
       <c r="D421" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E421" t="s">
         <v>11</v>
       </c>
       <c r="F421" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="G421" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H421" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="I421" t="s">
         <v>11</v>
@@ -11915,28 +12074,28 @@
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>43</v>
+        <v>563</v>
       </c>
       <c r="B422" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C422" t="s">
         <v>11</v>
       </c>
       <c r="D422" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E422" t="s">
         <v>11</v>
       </c>
       <c r="F422" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G422" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H422" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="I422" t="s">
         <v>330</v>
@@ -11944,28 +12103,28 @@
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>43</v>
+        <v>563</v>
       </c>
       <c r="B423" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C423" t="s">
         <v>11</v>
       </c>
       <c r="D423" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E423" t="s">
         <v>11</v>
       </c>
       <c r="F423" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G423" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H423" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="I423" t="s">
         <v>11</v>
@@ -11973,28 +12132,28 @@
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B424" t="s">
-        <v>33</v>
+        <v>504</v>
       </c>
       <c r="C424" t="s">
         <v>11</v>
       </c>
       <c r="D424" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E424" t="s">
         <v>11</v>
       </c>
       <c r="F424" t="s">
-        <v>33</v>
+        <v>504</v>
       </c>
       <c r="G424" t="s">
-        <v>33</v>
+        <v>504</v>
       </c>
       <c r="H424" t="s">
-        <v>22</v>
+        <v>506</v>
       </c>
       <c r="I424" t="s">
         <v>330</v>
@@ -12002,28 +12161,28 @@
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B425" t="s">
-        <v>33</v>
+        <v>504</v>
       </c>
       <c r="C425" t="s">
         <v>11</v>
       </c>
       <c r="D425" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E425" t="s">
         <v>11</v>
       </c>
       <c r="F425" t="s">
-        <v>33</v>
+        <v>504</v>
       </c>
       <c r="G425" t="s">
-        <v>33</v>
+        <v>504</v>
       </c>
       <c r="H425" t="s">
-        <v>22</v>
+        <v>506</v>
       </c>
       <c r="I425" t="s">
         <v>11</v>
@@ -12031,28 +12190,28 @@
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B426" t="s">
-        <v>504</v>
+        <v>570</v>
       </c>
       <c r="C426" t="s">
         <v>11</v>
       </c>
       <c r="D426" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E426" t="s">
-        <v>11</v>
+        <v>572</v>
       </c>
       <c r="F426" t="s">
-        <v>504</v>
+        <v>570</v>
       </c>
       <c r="G426" t="s">
-        <v>504</v>
+        <v>570</v>
       </c>
       <c r="H426" t="s">
-        <v>506</v>
+        <v>22</v>
       </c>
       <c r="I426" t="s">
         <v>330</v>
@@ -12060,28 +12219,28 @@
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B427" t="s">
-        <v>504</v>
+        <v>570</v>
       </c>
       <c r="C427" t="s">
         <v>11</v>
       </c>
       <c r="D427" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="E427" t="s">
-        <v>11</v>
+        <v>572</v>
       </c>
       <c r="F427" t="s">
-        <v>504</v>
+        <v>570</v>
       </c>
       <c r="G427" t="s">
-        <v>504</v>
+        <v>570</v>
       </c>
       <c r="H427" t="s">
-        <v>506</v>
+        <v>22</v>
       </c>
       <c r="I427" t="s">
         <v>11</v>
@@ -12089,57 +12248,57 @@
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B428" t="s">
-        <v>571</v>
+        <v>127</v>
       </c>
       <c r="C428" t="s">
-        <v>11</v>
+        <v>574</v>
       </c>
       <c r="D428" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E428" t="s">
-        <v>573</v>
+        <v>11</v>
       </c>
       <c r="F428" t="s">
-        <v>571</v>
+        <v>127</v>
       </c>
       <c r="G428" t="s">
-        <v>571</v>
+        <v>127</v>
       </c>
       <c r="H428" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I428" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B429" t="s">
-        <v>571</v>
+        <v>127</v>
       </c>
       <c r="C429" t="s">
-        <v>11</v>
+        <v>574</v>
       </c>
       <c r="D429" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="E429" t="s">
-        <v>573</v>
+        <v>11</v>
       </c>
       <c r="F429" t="s">
-        <v>571</v>
+        <v>127</v>
       </c>
       <c r="G429" t="s">
-        <v>571</v>
+        <v>127</v>
       </c>
       <c r="H429" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I429" t="s">
         <v>11</v>
@@ -12147,57 +12306,57 @@
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B430" t="s">
-        <v>127</v>
+        <v>349</v>
       </c>
       <c r="C430" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D430" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="E430" t="s">
         <v>11</v>
       </c>
       <c r="F430" t="s">
-        <v>127</v>
+        <v>349</v>
       </c>
       <c r="G430" t="s">
-        <v>127</v>
+        <v>349</v>
       </c>
       <c r="H430" t="s">
-        <v>17</v>
+        <v>351</v>
       </c>
       <c r="I430" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B431" t="s">
-        <v>127</v>
+        <v>349</v>
       </c>
       <c r="C431" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D431" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E431" t="s">
         <v>11</v>
       </c>
       <c r="F431" t="s">
-        <v>127</v>
+        <v>349</v>
       </c>
       <c r="G431" t="s">
-        <v>127</v>
+        <v>349</v>
       </c>
       <c r="H431" t="s">
-        <v>17</v>
+        <v>351</v>
       </c>
       <c r="I431" t="s">
         <v>11</v>
@@ -12205,16 +12364,16 @@
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B432" t="s">
         <v>349</v>
       </c>
       <c r="C432" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D432" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E432" t="s">
         <v>11</v>
@@ -12229,21 +12388,21 @@
         <v>351</v>
       </c>
       <c r="I432" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B433" t="s">
         <v>349</v>
       </c>
       <c r="C433" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D433" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E433" t="s">
         <v>11</v>
@@ -12258,6 +12417,837 @@
         <v>351</v>
       </c>
       <c r="I433" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>585</v>
+      </c>
+      <c r="B434" t="s">
+        <v>586</v>
+      </c>
+      <c r="C434" t="s">
+        <v>11</v>
+      </c>
+      <c r="D434" t="s">
+        <v>587</v>
+      </c>
+      <c r="E434" t="s">
+        <v>11</v>
+      </c>
+      <c r="F434" t="s">
+        <v>586</v>
+      </c>
+      <c r="G434" t="s">
+        <v>588</v>
+      </c>
+      <c r="H434" t="s">
+        <v>347</v>
+      </c>
+      <c r="I434" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>585</v>
+      </c>
+      <c r="B435" t="s">
+        <v>586</v>
+      </c>
+      <c r="C435" t="s">
+        <v>11</v>
+      </c>
+      <c r="D435" t="s">
+        <v>618</v>
+      </c>
+      <c r="E435" t="s">
+        <v>11</v>
+      </c>
+      <c r="F435" t="s">
+        <v>586</v>
+      </c>
+      <c r="G435" t="s">
+        <v>588</v>
+      </c>
+      <c r="H435" t="s">
+        <v>347</v>
+      </c>
+      <c r="I435" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>589</v>
+      </c>
+      <c r="B436" t="s">
+        <v>570</v>
+      </c>
+      <c r="C436" t="s">
+        <v>11</v>
+      </c>
+      <c r="D436" t="s">
+        <v>571</v>
+      </c>
+      <c r="E436" t="s">
+        <v>590</v>
+      </c>
+      <c r="F436" t="s">
+        <v>570</v>
+      </c>
+      <c r="G436" t="s">
+        <v>570</v>
+      </c>
+      <c r="H436" t="s">
+        <v>22</v>
+      </c>
+      <c r="I436" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>589</v>
+      </c>
+      <c r="B437" t="s">
+        <v>570</v>
+      </c>
+      <c r="C437" t="s">
+        <v>11</v>
+      </c>
+      <c r="D437" t="s">
+        <v>580</v>
+      </c>
+      <c r="E437" t="s">
+        <v>590</v>
+      </c>
+      <c r="F437" t="s">
+        <v>570</v>
+      </c>
+      <c r="G437" t="s">
+        <v>570</v>
+      </c>
+      <c r="H437" t="s">
+        <v>22</v>
+      </c>
+      <c r="I437" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>591</v>
+      </c>
+      <c r="B438" t="s">
+        <v>29</v>
+      </c>
+      <c r="C438" t="s">
+        <v>11</v>
+      </c>
+      <c r="D438" t="s">
+        <v>592</v>
+      </c>
+      <c r="E438" t="s">
+        <v>11</v>
+      </c>
+      <c r="F438" t="s">
+        <v>29</v>
+      </c>
+      <c r="G438" t="s">
+        <v>29</v>
+      </c>
+      <c r="H438" t="s">
+        <v>16</v>
+      </c>
+      <c r="I438" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>591</v>
+      </c>
+      <c r="B439" t="s">
+        <v>29</v>
+      </c>
+      <c r="C439" t="s">
+        <v>11</v>
+      </c>
+      <c r="D439" t="s">
+        <v>617</v>
+      </c>
+      <c r="E439" t="s">
+        <v>11</v>
+      </c>
+      <c r="F439" t="s">
+        <v>29</v>
+      </c>
+      <c r="G439" t="s">
+        <v>29</v>
+      </c>
+      <c r="H439" t="s">
+        <v>16</v>
+      </c>
+      <c r="I439" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>593</v>
+      </c>
+      <c r="B440" t="s">
+        <v>594</v>
+      </c>
+      <c r="C440" t="s">
+        <v>11</v>
+      </c>
+      <c r="D440" t="s">
+        <v>596</v>
+      </c>
+      <c r="E440" t="s">
+        <v>11</v>
+      </c>
+      <c r="F440" t="s">
+        <v>594</v>
+      </c>
+      <c r="G440" t="s">
+        <v>595</v>
+      </c>
+      <c r="H440" t="s">
+        <v>347</v>
+      </c>
+      <c r="I440" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>593</v>
+      </c>
+      <c r="B441" t="s">
+        <v>594</v>
+      </c>
+      <c r="C441" t="s">
+        <v>11</v>
+      </c>
+      <c r="D441" t="s">
+        <v>616</v>
+      </c>
+      <c r="E441" t="s">
+        <v>11</v>
+      </c>
+      <c r="F441" t="s">
+        <v>594</v>
+      </c>
+      <c r="G441" t="s">
+        <v>595</v>
+      </c>
+      <c r="H441" t="s">
+        <v>347</v>
+      </c>
+      <c r="I441" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>554</v>
+      </c>
+      <c r="B442" t="s">
+        <v>555</v>
+      </c>
+      <c r="C442" t="s">
+        <v>11</v>
+      </c>
+      <c r="D442" t="s">
+        <v>597</v>
+      </c>
+      <c r="E442" t="s">
+        <v>11</v>
+      </c>
+      <c r="F442" t="s">
+        <v>555</v>
+      </c>
+      <c r="G442" t="s">
+        <v>556</v>
+      </c>
+      <c r="H442" t="s">
+        <v>17</v>
+      </c>
+      <c r="I442" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>554</v>
+      </c>
+      <c r="B443" t="s">
+        <v>555</v>
+      </c>
+      <c r="C443" t="s">
+        <v>11</v>
+      </c>
+      <c r="D443" t="s">
+        <v>557</v>
+      </c>
+      <c r="E443" t="s">
+        <v>11</v>
+      </c>
+      <c r="F443" t="s">
+        <v>555</v>
+      </c>
+      <c r="G443" t="s">
+        <v>556</v>
+      </c>
+      <c r="H443" t="s">
+        <v>17</v>
+      </c>
+      <c r="I443" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>598</v>
+      </c>
+      <c r="B444" t="s">
+        <v>599</v>
+      </c>
+      <c r="C444" t="s">
+        <v>11</v>
+      </c>
+      <c r="D444" t="s">
+        <v>600</v>
+      </c>
+      <c r="E444" t="s">
+        <v>11</v>
+      </c>
+      <c r="F444" t="s">
+        <v>599</v>
+      </c>
+      <c r="G444" t="s">
+        <v>599</v>
+      </c>
+      <c r="H444" t="s">
+        <v>357</v>
+      </c>
+      <c r="I444" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>598</v>
+      </c>
+      <c r="B445" t="s">
+        <v>599</v>
+      </c>
+      <c r="C445" t="s">
+        <v>11</v>
+      </c>
+      <c r="D445" t="s">
+        <v>615</v>
+      </c>
+      <c r="E445" t="s">
+        <v>11</v>
+      </c>
+      <c r="F445" t="s">
+        <v>599</v>
+      </c>
+      <c r="G445" t="s">
+        <v>599</v>
+      </c>
+      <c r="H445" t="s">
+        <v>357</v>
+      </c>
+      <c r="I445" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>601</v>
+      </c>
+      <c r="B446" t="s">
+        <v>510</v>
+      </c>
+      <c r="C446" t="s">
+        <v>602</v>
+      </c>
+      <c r="D446" t="s">
+        <v>603</v>
+      </c>
+      <c r="E446" t="s">
+        <v>11</v>
+      </c>
+      <c r="F446" t="s">
+        <v>510</v>
+      </c>
+      <c r="G446" t="s">
+        <v>510</v>
+      </c>
+      <c r="H446" t="s">
+        <v>42</v>
+      </c>
+      <c r="I446" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>601</v>
+      </c>
+      <c r="B447" t="s">
+        <v>510</v>
+      </c>
+      <c r="C447" t="s">
+        <v>602</v>
+      </c>
+      <c r="D447" t="s">
+        <v>611</v>
+      </c>
+      <c r="E447" t="s">
+        <v>11</v>
+      </c>
+      <c r="F447" t="s">
+        <v>510</v>
+      </c>
+      <c r="G447" t="s">
+        <v>510</v>
+      </c>
+      <c r="H447" t="s">
+        <v>42</v>
+      </c>
+      <c r="I447" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>604</v>
+      </c>
+      <c r="B448" t="s">
+        <v>605</v>
+      </c>
+      <c r="C448" t="s">
+        <v>11</v>
+      </c>
+      <c r="D448" t="s">
+        <v>606</v>
+      </c>
+      <c r="E448" t="s">
+        <v>11</v>
+      </c>
+      <c r="F448" t="s">
+        <v>605</v>
+      </c>
+      <c r="G448" t="s">
+        <v>605</v>
+      </c>
+      <c r="H448" t="s">
+        <v>17</v>
+      </c>
+      <c r="I448" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>604</v>
+      </c>
+      <c r="B449" t="s">
+        <v>605</v>
+      </c>
+      <c r="C449" t="s">
+        <v>11</v>
+      </c>
+      <c r="D449" t="s">
+        <v>614</v>
+      </c>
+      <c r="E449" t="s">
+        <v>11</v>
+      </c>
+      <c r="F449" t="s">
+        <v>605</v>
+      </c>
+      <c r="G449" t="s">
+        <v>605</v>
+      </c>
+      <c r="H449" t="s">
+        <v>17</v>
+      </c>
+      <c r="I449" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>299</v>
+      </c>
+      <c r="B450" t="s">
+        <v>300</v>
+      </c>
+      <c r="C450" t="s">
+        <v>11</v>
+      </c>
+      <c r="D450" t="s">
+        <v>607</v>
+      </c>
+      <c r="E450" t="s">
+        <v>11</v>
+      </c>
+      <c r="F450" t="s">
+        <v>300</v>
+      </c>
+      <c r="G450" t="s">
+        <v>300</v>
+      </c>
+      <c r="H450" t="s">
+        <v>22</v>
+      </c>
+      <c r="I450" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>299</v>
+      </c>
+      <c r="B451" t="s">
+        <v>300</v>
+      </c>
+      <c r="C451" t="s">
+        <v>11</v>
+      </c>
+      <c r="D451" t="s">
+        <v>612</v>
+      </c>
+      <c r="E451" t="s">
+        <v>11</v>
+      </c>
+      <c r="F451" t="s">
+        <v>300</v>
+      </c>
+      <c r="G451" t="s">
+        <v>300</v>
+      </c>
+      <c r="H451" t="s">
+        <v>22</v>
+      </c>
+      <c r="I451" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>608</v>
+      </c>
+      <c r="B452" t="s">
+        <v>609</v>
+      </c>
+      <c r="C452" t="s">
+        <v>11</v>
+      </c>
+      <c r="D452" t="s">
+        <v>610</v>
+      </c>
+      <c r="E452" t="s">
+        <v>11</v>
+      </c>
+      <c r="F452" t="s">
+        <v>609</v>
+      </c>
+      <c r="G452" t="s">
+        <v>609</v>
+      </c>
+      <c r="H452" t="s">
+        <v>22</v>
+      </c>
+      <c r="I452" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>608</v>
+      </c>
+      <c r="B453" t="s">
+        <v>609</v>
+      </c>
+      <c r="C453" t="s">
+        <v>11</v>
+      </c>
+      <c r="D453" t="s">
+        <v>613</v>
+      </c>
+      <c r="E453" t="s">
+        <v>11</v>
+      </c>
+      <c r="F453" t="s">
+        <v>609</v>
+      </c>
+      <c r="G453" t="s">
+        <v>609</v>
+      </c>
+      <c r="H453" t="s">
+        <v>22</v>
+      </c>
+      <c r="I453" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>117</v>
+      </c>
+      <c r="B454" t="s">
+        <v>68</v>
+      </c>
+      <c r="C454" t="s">
+        <v>619</v>
+      </c>
+      <c r="D454" t="s">
+        <v>620</v>
+      </c>
+      <c r="E454" t="s">
+        <v>11</v>
+      </c>
+      <c r="F454" t="s">
+        <v>68</v>
+      </c>
+      <c r="G454" t="s">
+        <v>68</v>
+      </c>
+      <c r="H454" t="s">
+        <v>70</v>
+      </c>
+      <c r="I454" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>117</v>
+      </c>
+      <c r="B455" t="s">
+        <v>68</v>
+      </c>
+      <c r="C455" t="s">
+        <v>619</v>
+      </c>
+      <c r="D455" t="s">
+        <v>621</v>
+      </c>
+      <c r="E455" t="s">
+        <v>11</v>
+      </c>
+      <c r="F455" t="s">
+        <v>68</v>
+      </c>
+      <c r="G455" t="s">
+        <v>68</v>
+      </c>
+      <c r="H455" t="s">
+        <v>70</v>
+      </c>
+      <c r="I455" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>623</v>
+      </c>
+      <c r="B456" t="s">
+        <v>68</v>
+      </c>
+      <c r="C456" t="s">
+        <v>619</v>
+      </c>
+      <c r="D456" t="s">
+        <v>622</v>
+      </c>
+      <c r="E456" t="s">
+        <v>11</v>
+      </c>
+      <c r="F456" t="s">
+        <v>68</v>
+      </c>
+      <c r="G456" t="s">
+        <v>68</v>
+      </c>
+      <c r="H456" t="s">
+        <v>70</v>
+      </c>
+      <c r="I456" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>312</v>
+      </c>
+      <c r="I457" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>624</v>
+      </c>
+      <c r="B458" t="s">
+        <v>127</v>
+      </c>
+      <c r="C458" t="s">
+        <v>625</v>
+      </c>
+      <c r="D458" t="s">
+        <v>626</v>
+      </c>
+      <c r="E458" t="s">
+        <v>11</v>
+      </c>
+      <c r="F458" t="s">
+        <v>127</v>
+      </c>
+      <c r="G458" t="s">
+        <v>127</v>
+      </c>
+      <c r="H458" t="s">
+        <v>17</v>
+      </c>
+      <c r="I458" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>312</v>
+      </c>
+      <c r="E459" t="s">
+        <v>11</v>
+      </c>
+      <c r="I459" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>628</v>
+      </c>
+      <c r="B460" t="s">
+        <v>60</v>
+      </c>
+      <c r="C460" t="s">
+        <v>11</v>
+      </c>
+      <c r="D460" t="s">
+        <v>629</v>
+      </c>
+      <c r="E460" t="s">
+        <v>11</v>
+      </c>
+      <c r="F460" t="s">
+        <v>60</v>
+      </c>
+      <c r="G460" t="s">
+        <v>60</v>
+      </c>
+      <c r="H460" t="s">
+        <v>57</v>
+      </c>
+      <c r="I460" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>628</v>
+      </c>
+      <c r="B461" t="s">
+        <v>60</v>
+      </c>
+      <c r="C461" t="s">
+        <v>11</v>
+      </c>
+      <c r="D461" t="s">
+        <v>630</v>
+      </c>
+      <c r="E461" t="s">
+        <v>11</v>
+      </c>
+      <c r="F461" t="s">
+        <v>60</v>
+      </c>
+      <c r="G461" t="s">
+        <v>60</v>
+      </c>
+      <c r="H461" t="s">
+        <v>57</v>
+      </c>
+      <c r="I461" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>631</v>
+      </c>
+      <c r="B462" t="s">
+        <v>632</v>
+      </c>
+      <c r="C462" t="s">
+        <v>11</v>
+      </c>
+      <c r="D462" t="s">
+        <v>633</v>
+      </c>
+      <c r="E462" t="s">
+        <v>11</v>
+      </c>
+      <c r="F462" t="s">
+        <v>632</v>
+      </c>
+      <c r="G462" t="s">
+        <v>632</v>
+      </c>
+      <c r="H462" t="s">
+        <v>634</v>
+      </c>
+      <c r="I462" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>631</v>
+      </c>
+      <c r="B463" t="s">
+        <v>632</v>
+      </c>
+      <c r="C463" t="s">
+        <v>11</v>
+      </c>
+      <c r="D463" t="s">
+        <v>635</v>
+      </c>
+      <c r="E463" t="s">
+        <v>11</v>
+      </c>
+      <c r="F463" t="s">
+        <v>632</v>
+      </c>
+      <c r="G463" t="s">
+        <v>632</v>
+      </c>
+      <c r="H463" t="s">
+        <v>634</v>
+      </c>
+      <c r="I463" t="s">
         <v>11</v>
       </c>
     </row>
